--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github_corrigido_dashboard_obrasdinamico\github\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DCFF995-9770-4685-8FB4-A2A5EF8D83C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06CC311A-5D85-4D5F-B548-ADAB37F513D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LEIA-ME" sheetId="1" r:id="rId1"/>
@@ -18165,6 +18165,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:R388"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -18228,7 +18229,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -18278,7 +18279,7 @@
         <v>-46.416253400000002</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -18328,7 +18329,7 @@
         <v>-46.416704099999997</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -18378,7 +18379,7 @@
         <v>-46.417190099999999</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -18428,7 +18429,7 @@
         <v>-46.417341</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -18478,7 +18479,7 @@
         <v>-46.417501700000003</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -18528,7 +18529,7 @@
         <v>-46.4176821</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -18578,7 +18579,7 @@
         <v>-46.417981300000001</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -18628,7 +18629,7 @@
         <v>-46.418407199999997</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -18678,7 +18679,7 @@
         <v>-46.418206699999999</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -18728,7 +18729,7 @@
         <v>-46.4180463</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -18778,7 +18779,7 @@
         <v>-46.418264100000002</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -18828,7 +18829,7 @@
         <v>-46.4183649</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -18878,7 +18879,7 @@
         <v>-46.418435899999999</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -18928,7 +18929,7 @@
         <v>-46.416806899999997</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -18978,7 +18979,7 @@
         <v>-46.416913999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -19028,7 +19029,7 @@
         <v>-46.416511399999997</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -19078,7 +19079,7 @@
         <v>-46.416153399999999</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -19128,7 +19129,7 @@
         <v>-46.416207999999997</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -19178,7 +19179,7 @@
         <v>-46.416177500000003</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -19228,7 +19229,7 @@
         <v>-46.418407199999997</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -19278,7 +19279,7 @@
         <v>-46.418435299999999</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -19328,7 +19329,7 @@
         <v>-46.416253400000002</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -19378,7 +19379,7 @@
         <v>-46.416341899999999</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -19428,7 +19429,7 @@
         <v>-46.416704099999997</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -19478,7 +19479,7 @@
         <v>-46.415709800000002</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -19528,7 +19529,7 @@
         <v>-46.415711799999997</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -19578,7 +19579,7 @@
         <v>-46.416806899999997</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -19628,7 +19629,7 @@
         <v>-46.416340599999998</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -19678,7 +19679,7 @@
         <v>-46.416158799999998</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -19728,7 +19729,7 @@
         <v>-46.416158799999998</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -19778,7 +19779,7 @@
         <v>-46.416511399999997</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>79</v>
       </c>
@@ -19828,7 +19829,7 @@
         <v>-46.38594079802948</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>79</v>
       </c>
@@ -19878,7 +19879,7 @@
         <v>-46.386535748682967</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -19928,7 +19929,7 @@
         <v>-46.385331250405009</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>79</v>
       </c>
@@ -19978,7 +19979,7 @@
         <v>-46.385209892569947</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>79</v>
       </c>
@@ -20446,7 +20447,7 @@
         <v>530</v>
       </c>
       <c r="I45">
-        <v>120.49</v>
+        <v>0</v>
       </c>
       <c r="J45">
         <v>8.2200000000000006</v>
@@ -20502,7 +20503,7 @@
         <v>530</v>
       </c>
       <c r="I46">
-        <v>78.569999999999993</v>
+        <v>0</v>
       </c>
       <c r="J46">
         <v>8.16</v>
@@ -20588,7 +20589,7 @@
         <v>-46.401313100000003</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>117</v>
       </c>
@@ -20644,7 +20645,7 @@
         <v>-46.4176511</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>117</v>
       </c>
@@ -20700,7 +20701,7 @@
         <v>-46.417446300000002</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>117</v>
       </c>
@@ -20756,7 +20757,7 @@
         <v>-46.417286599999997</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>117</v>
       </c>
@@ -20812,7 +20813,7 @@
         <v>-46.418029900000001</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>117</v>
       </c>
@@ -20868,7 +20869,7 @@
         <v>-46.417090700000003</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>117</v>
       </c>
@@ -20924,7 +20925,7 @@
         <v>-46.416909699999998</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>117</v>
       </c>
@@ -20980,7 +20981,7 @@
         <v>-46.416524600000002</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>117</v>
       </c>
@@ -21036,7 +21037,7 @@
         <v>-46.416342700000001</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>117</v>
       </c>
@@ -21092,7 +21093,7 @@
         <v>-46.416342700000001</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>117</v>
       </c>
@@ -21148,7 +21149,7 @@
         <v>-46.4159948</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>117</v>
       </c>
@@ -21204,7 +21205,7 @@
         <v>-46.415814900000001</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>117</v>
       </c>
@@ -21260,7 +21261,7 @@
         <v>-46.415814900000001</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>117</v>
       </c>
@@ -21316,7 +21317,7 @@
         <v>-46.415630399999998</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>117</v>
       </c>
@@ -21372,7 +21373,7 @@
         <v>-46.4153284</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>117</v>
       </c>
@@ -21428,7 +21429,7 @@
         <v>-46.414648700000001</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>117</v>
       </c>
@@ -21484,7 +21485,7 @@
         <v>-46.415173099999997</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>117</v>
       </c>
@@ -21540,7 +21541,7 @@
         <v>-46.4153941</v>
       </c>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>117</v>
       </c>
@@ -21596,7 +21597,7 @@
         <v>-46.4171725</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>117</v>
       </c>
@@ -21652,7 +21653,7 @@
         <v>-46.4164241</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>117</v>
       </c>
@@ -21708,7 +21709,7 @@
         <v>-46.4165888</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>117</v>
       </c>
@@ -21764,7 +21765,7 @@
         <v>-46.415878399999997</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>117</v>
       </c>
@@ -21820,7 +21821,7 @@
         <v>-46.417214999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>165</v>
       </c>
@@ -21876,7 +21877,7 @@
         <v>-46.394514126473538</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>165</v>
       </c>
@@ -21932,7 +21933,7 @@
         <v>-46.39440497485721</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>165</v>
       </c>
@@ -21988,7 +21989,7 @@
         <v>-46.394190685187283</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>165</v>
       </c>
@@ -22044,7 +22045,7 @@
         <v>-46.393867676588513</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>165</v>
       </c>
@@ -22100,7 +22101,7 @@
         <v>-46.393750908484463</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>165</v>
       </c>
@@ -22156,7 +22157,7 @@
         <v>-46.393754824461297</v>
       </c>
     </row>
-    <row r="76" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>165</v>
       </c>
@@ -22212,7 +22213,7 @@
         <v>-46.393677744048787</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>165</v>
       </c>
@@ -22268,7 +22269,7 @@
         <v>-46.393669850604603</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>165</v>
       </c>
@@ -22324,7 +22325,7 @@
         <v>-46.393617999096797</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>165</v>
       </c>
@@ -22380,7 +22381,7 @@
         <v>-46.39342680270682</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>165</v>
       </c>
@@ -22436,7 +22437,7 @@
         <v>-46.393118667987821</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>165</v>
       </c>
@@ -22492,7 +22493,7 @@
         <v>-46.392683603256813</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>165</v>
       </c>
@@ -22548,7 +22549,7 @@
         <v>-46.392567097741733</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>165</v>
       </c>
@@ -22604,7 +22605,7 @@
         <v>-46.392172750576698</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>165</v>
       </c>
@@ -22660,7 +22661,7 @@
         <v>-46.391704600778667</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>165</v>
       </c>
@@ -22716,7 +22717,7 @@
         <v>-46.393984483001361</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>165</v>
       </c>
@@ -22772,7 +22773,7 @@
         <v>-46.39421417616888</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>165</v>
       </c>
@@ -22828,7 +22829,7 @@
         <v>-46.393884994376727</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>165</v>
       </c>
@@ -22884,7 +22885,7 @@
         <v>-46.393931783273203</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>165</v>
       </c>
@@ -22940,7 +22941,7 @@
         <v>-46.393826949732833</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>165</v>
       </c>
@@ -22996,7 +22997,7 @@
         <v>-46.393834080493427</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>165</v>
       </c>
@@ -23052,7 +23053,7 @@
         <v>-46.393874814521602</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>165</v>
       </c>
@@ -23108,7 +23109,7 @@
         <v>-46.393600080891758</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>165</v>
       </c>
@@ -23164,7 +23165,7 @@
         <v>-46.392812880408918</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>165</v>
       </c>
@@ -23220,7 +23221,7 @@
         <v>-46.392828108924483</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>165</v>
       </c>
@@ -23276,7 +23277,7 @@
         <v>-46.392669018473534</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>165</v>
       </c>
@@ -23332,7 +23333,7 @@
         <v>-46.3922548189284</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>165</v>
       </c>
@@ -23388,7 +23389,7 @@
         <v>-46.391867207322441</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>221</v>
       </c>
@@ -23441,7 +23442,7 @@
         <v>-46.385538400000002</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>221</v>
       </c>
@@ -23494,7 +23495,7 @@
         <v>-46.385575299999999</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>221</v>
       </c>
@@ -23547,7 +23548,7 @@
         <v>-46.385641</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>221</v>
       </c>
@@ -23600,7 +23601,7 @@
         <v>-46.386125</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>221</v>
       </c>
@@ -23653,7 +23654,7 @@
         <v>-46.386338700000003</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>221</v>
       </c>
@@ -23706,7 +23707,7 @@
         <v>-46.387470700000002</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>221</v>
       </c>
@@ -23759,7 +23760,7 @@
         <v>-46.3881558</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>221</v>
       </c>
@@ -23812,7 +23813,7 @@
         <v>-46.3889292</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>221</v>
       </c>
@@ -23865,7 +23866,7 @@
         <v>-46.386140400000002</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>221</v>
       </c>
@@ -23918,7 +23919,7 @@
         <v>-46.386125</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>221</v>
       </c>
@@ -23971,7 +23972,7 @@
         <v>-46.386821400000002</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>221</v>
       </c>
@@ -24021,7 +24022,7 @@
         <v>-46.388970100000002</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>240</v>
       </c>
@@ -24077,7 +24078,7 @@
         <v>-46.400490900000001</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>240</v>
       </c>
@@ -24133,7 +24134,7 @@
         <v>-46.400497299999998</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>240</v>
       </c>
@@ -24189,7 +24190,7 @@
         <v>-46.399660099999998</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>240</v>
       </c>
@@ -24245,7 +24246,7 @@
         <v>-46.399546600000001</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>240</v>
       </c>
@@ -24301,7 +24302,7 @@
         <v>-46.399546899999997</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>240</v>
       </c>
@@ -24357,7 +24358,7 @@
         <v>-46.399427899999999</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>240</v>
       </c>
@@ -24413,7 +24414,7 @@
         <v>-46.399406300000003</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>240</v>
       </c>
@@ -24469,7 +24470,7 @@
         <v>-46.3993976</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>240</v>
       </c>
@@ -24525,7 +24526,7 @@
         <v>-46.399673499999999</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>240</v>
       </c>
@@ -24581,7 +24582,7 @@
         <v>-46.3991951</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>240</v>
       </c>
@@ -24637,7 +24638,7 @@
         <v>-46.3992</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>240</v>
       </c>
@@ -24693,7 +24694,7 @@
         <v>-46.399129500000001</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>240</v>
       </c>
@@ -24749,7 +24750,7 @@
         <v>-46.399120400000001</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>240</v>
       </c>
@@ -24805,7 +24806,7 @@
         <v>-46.399127700000001</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>240</v>
       </c>
@@ -24861,7 +24862,7 @@
         <v>-46.399663099999998</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>240</v>
       </c>
@@ -24917,7 +24918,7 @@
         <v>-46.399161700000001</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>240</v>
       </c>
@@ -24973,7 +24974,7 @@
         <v>-46.399083099999999</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>240</v>
       </c>
@@ -25029,7 +25030,7 @@
         <v>-46.399065800000002</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>240</v>
       </c>
@@ -25085,7 +25086,7 @@
         <v>-46.399676200000002</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>240</v>
       </c>
@@ -25141,7 +25142,7 @@
         <v>-46.399061099999997</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>240</v>
       </c>
@@ -25197,7 +25198,7 @@
         <v>-46.398950800000001</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>240</v>
       </c>
@@ -25253,7 +25254,7 @@
         <v>-46.3990565</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>240</v>
       </c>
@@ -25309,7 +25310,7 @@
         <v>-46.3990103</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>240</v>
       </c>
@@ -25365,7 +25366,7 @@
         <v>-46.398947300000003</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>280</v>
       </c>
@@ -25418,7 +25419,7 @@
         <v>-46.388409799999998</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>280</v>
       </c>
@@ -25471,7 +25472,7 @@
         <v>-46.386588699999997</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>280</v>
       </c>
@@ -25524,7 +25525,7 @@
         <v>-46.3864564</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>280</v>
       </c>
@@ -25577,7 +25578,7 @@
         <v>-46.387386399999997</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>280</v>
       </c>
@@ -25630,7 +25631,7 @@
         <v>-46.387402899999998</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>280</v>
       </c>
@@ -25683,7 +25684,7 @@
         <v>-46.3874511</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>280</v>
       </c>
@@ -25736,7 +25737,7 @@
         <v>-46.386536300000003</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>280</v>
       </c>
@@ -25789,7 +25790,7 @@
         <v>-46.3952478</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>280</v>
       </c>
@@ -25842,7 +25843,7 @@
         <v>-46.395421599999999</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>280</v>
       </c>
@@ -25895,7 +25896,7 @@
         <v>-46.395309099999999</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>280</v>
       </c>
@@ -25948,7 +25949,7 @@
         <v>-46.3922934</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>280</v>
       </c>
@@ -26001,7 +26002,7 @@
         <v>-46.3922934</v>
       </c>
     </row>
-    <row r="146" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>280</v>
       </c>
@@ -26054,7 +26055,7 @@
         <v>-46.391816499999997</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>280</v>
       </c>
@@ -26107,7 +26108,7 @@
         <v>-46.391055199999997</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>280</v>
       </c>
@@ -26160,7 +26161,7 @@
         <v>-46.390884300000003</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>280</v>
       </c>
@@ -26213,7 +26214,7 @@
         <v>-46.3907059</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>280</v>
       </c>
@@ -26266,7 +26267,7 @@
         <v>-46.389563600000002</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>280</v>
       </c>
@@ -26319,7 +26320,7 @@
         <v>-46.389226299999997</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>280</v>
       </c>
@@ -26372,7 +26373,7 @@
         <v>-46.388674999999999</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>280</v>
       </c>
@@ -26425,7 +26426,7 @@
         <v>-46.388370600000002</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>280</v>
       </c>
@@ -26478,7 +26479,7 @@
         <v>-46.388409799999998</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>280</v>
       </c>
@@ -26531,7 +26532,7 @@
         <v>-46.387695999999998</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>280</v>
       </c>
@@ -26584,7 +26585,7 @@
         <v>-46.387413700000003</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>280</v>
       </c>
@@ -26637,7 +26638,7 @@
         <v>-46.387386399999997</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>280</v>
       </c>
@@ -26690,7 +26691,7 @@
         <v>-46.387402899999998</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>280</v>
       </c>
@@ -26743,7 +26744,7 @@
         <v>-46.386888200000001</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>280</v>
       </c>
@@ -26796,7 +26797,7 @@
         <v>-46.386210499999997</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>280</v>
       </c>
@@ -26849,7 +26850,7 @@
         <v>-46.386560500000002</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>280</v>
       </c>
@@ -26902,7 +26903,7 @@
         <v>-46.392178299999998</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>280</v>
       </c>
@@ -26955,7 +26956,7 @@
         <v>-46.394682400000001</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>280</v>
       </c>
@@ -27008,7 +27009,7 @@
         <v>-46.393901100000001</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>280</v>
       </c>
@@ -27061,7 +27062,7 @@
         <v>-46.393103199999999</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>280</v>
       </c>
@@ -27114,7 +27115,7 @@
         <v>-46.395246</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>280</v>
       </c>
@@ -27167,7 +27168,7 @@
         <v>-46.390622299999997</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>280</v>
       </c>
@@ -27220,7 +27221,7 @@
         <v>-46.388130599999997</v>
       </c>
     </row>
-    <row r="169" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>305</v>
       </c>
@@ -27273,7 +27274,7 @@
         <v>-46.406078299999997</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>305</v>
       </c>
@@ -27326,7 +27327,7 @@
         <v>-46.406567000000003</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>305</v>
       </c>
@@ -27379,7 +27380,7 @@
         <v>-46.407268500000001</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>305</v>
       </c>
@@ -27432,7 +27433,7 @@
         <v>-46.407628899999999</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>305</v>
       </c>
@@ -27485,7 +27486,7 @@
         <v>-46.4079087</v>
       </c>
     </row>
-    <row r="174" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>305</v>
       </c>
@@ -27538,7 +27539,7 @@
         <v>-46.406060400000001</v>
       </c>
     </row>
-    <row r="175" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>305</v>
       </c>
@@ -27591,7 +27592,7 @@
         <v>-46.408232599999998</v>
       </c>
     </row>
-    <row r="176" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>305</v>
       </c>
@@ -27644,7 +27645,7 @@
         <v>-46.408232599999998</v>
       </c>
     </row>
-    <row r="177" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>305</v>
       </c>
@@ -27697,7 +27698,7 @@
         <v>-46.406567000000003</v>
       </c>
     </row>
-    <row r="178" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>305</v>
       </c>
@@ -27750,7 +27751,7 @@
         <v>-46.407268500000001</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>305</v>
       </c>
@@ -27803,7 +27804,7 @@
         <v>-46.406331600000001</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>305</v>
       </c>
@@ -27856,7 +27857,7 @@
         <v>-46.406856099999999</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>312</v>
       </c>
@@ -27903,7 +27904,7 @@
         <v>-46.399636800000003</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>312</v>
       </c>
@@ -27950,7 +27951,7 @@
         <v>-46.399317199999999</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>312</v>
       </c>
@@ -27997,7 +27998,7 @@
         <v>-46.398956400000003</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>312</v>
       </c>
@@ -28044,7 +28045,7 @@
         <v>-46.398719900000003</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>312</v>
       </c>
@@ -28091,7 +28092,7 @@
         <v>-46.398701299999999</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>312</v>
       </c>
@@ -28138,7 +28139,7 @@
         <v>-46.398651000000001</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>312</v>
       </c>
@@ -28185,7 +28186,7 @@
         <v>-46.398395800000003</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>312</v>
       </c>
@@ -28232,7 +28233,7 @@
         <v>-46.397748900000003</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>312</v>
       </c>
@@ -28279,7 +28280,7 @@
         <v>-46.397582200000002</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>312</v>
       </c>
@@ -28326,7 +28327,7 @@
         <v>-46.397804000000001</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>312</v>
       </c>
@@ -28373,7 +28374,7 @@
         <v>-46.398719900000003</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>312</v>
       </c>
@@ -28420,7 +28421,7 @@
         <v>-46.3982283</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>312</v>
       </c>
@@ -28467,7 +28468,7 @@
         <v>-46.3982283</v>
       </c>
     </row>
-    <row r="194" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>312</v>
       </c>
@@ -28514,7 +28515,7 @@
         <v>-46.398651000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>312</v>
       </c>
@@ -28561,7 +28562,7 @@
         <v>-46.397804000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>317</v>
       </c>
@@ -28614,7 +28615,7 @@
         <v>-46.395039500000003</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>317</v>
       </c>
@@ -28667,7 +28668,7 @@
         <v>-46.399920799999997</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>317</v>
       </c>
@@ -28720,7 +28721,7 @@
         <v>-46.399732299999997</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>317</v>
       </c>
@@ -28773,7 +28774,7 @@
         <v>-46.402293800000002</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>317</v>
       </c>
@@ -28826,7 +28827,7 @@
         <v>-46.401741199999996</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>317</v>
       </c>
@@ -28879,7 +28880,7 @@
         <v>-46.4013214</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>317</v>
       </c>
@@ -28932,7 +28933,7 @@
         <v>-46.400779200000002</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>317</v>
       </c>
@@ -28985,7 +28986,7 @@
         <v>-46.400237500000003</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>317</v>
       </c>
@@ -29038,7 +29039,7 @@
         <v>-46.400053399999997</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>317</v>
       </c>
@@ -29091,7 +29092,7 @@
         <v>-46.397993399999997</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>317</v>
       </c>
@@ -29144,7 +29145,7 @@
         <v>-46.3980842</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>317</v>
       </c>
@@ -29197,7 +29198,7 @@
         <v>-46.398204</v>
       </c>
     </row>
-    <row r="208" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>317</v>
       </c>
@@ -29250,7 +29251,7 @@
         <v>-46.398731099999999</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>317</v>
       </c>
@@ -29303,7 +29304,7 @@
         <v>-46.398578299999997</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>317</v>
       </c>
@@ -29356,7 +29357,7 @@
         <v>-46.399111300000001</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>317</v>
       </c>
@@ -29409,7 +29410,7 @@
         <v>-46.399396500000002</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>317</v>
       </c>
@@ -29462,7 +29463,7 @@
         <v>-46.3996371</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>317</v>
       </c>
@@ -29515,7 +29516,7 @@
         <v>-46.399732299999997</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>317</v>
       </c>
@@ -29568,7 +29569,7 @@
         <v>-46.397703300000003</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>317</v>
       </c>
@@ -29621,7 +29622,7 @@
         <v>-46.397365899999997</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>317</v>
       </c>
@@ -29674,7 +29675,7 @@
         <v>-46.396937700000002</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>317</v>
       </c>
@@ -29727,7 +29728,7 @@
         <v>-46.396631800000002</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>317</v>
       </c>
@@ -29780,7 +29781,7 @@
         <v>-46.396280500000003</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>317</v>
       </c>
@@ -29833,7 +29834,7 @@
         <v>-46.395845000000001</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>317</v>
       </c>
@@ -29886,7 +29887,7 @@
         <v>-46.395425600000003</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>317</v>
       </c>
@@ -29939,7 +29940,7 @@
         <v>-46.395425600000003</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>317</v>
       </c>
@@ -29992,7 +29993,7 @@
         <v>-46.393717500000001</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>317</v>
       </c>
@@ -30045,7 +30046,7 @@
         <v>-46.393569399999997</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>317</v>
       </c>
@@ -30098,7 +30099,7 @@
         <v>-46.393071999999997</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>317</v>
       </c>
@@ -30151,7 +30152,7 @@
         <v>-46.392376200000001</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>317</v>
       </c>
@@ -30204,7 +30205,7 @@
         <v>-46.3960948</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>317</v>
       </c>
@@ -30257,7 +30258,7 @@
         <v>-46.398731099999999</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>317</v>
       </c>
@@ -30310,7 +30311,7 @@
         <v>-46.4022632</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>317</v>
       </c>
@@ -30363,7 +30364,7 @@
         <v>-46.395845000000001</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>317</v>
       </c>
@@ -30416,7 +30417,7 @@
         <v>-46.3960948</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>317</v>
       </c>
@@ -30469,7 +30470,7 @@
         <v>-46.396000600000001</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>317</v>
       </c>
@@ -30522,7 +30523,7 @@
         <v>-46.395630199999999</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>317</v>
       </c>
@@ -30575,7 +30576,7 @@
         <v>-46.397993399999997</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>317</v>
       </c>
@@ -30628,7 +30629,7 @@
         <v>-46.397993399999997</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>317</v>
       </c>
@@ -30681,7 +30682,7 @@
         <v>-46.397979200000002</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>317</v>
       </c>
@@ -30734,7 +30735,7 @@
         <v>-46.3980842</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>317</v>
       </c>
@@ -30784,7 +30785,7 @@
         <v>-46.398089400000003</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>317</v>
       </c>
@@ -30837,7 +30838,7 @@
         <v>-46.392376200000001</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>317</v>
       </c>
@@ -30890,7 +30891,7 @@
         <v>-46.390559500000002</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>317</v>
       </c>
@@ -30943,7 +30944,7 @@
         <v>-46.391169300000001</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>317</v>
       </c>
@@ -30996,7 +30997,7 @@
         <v>-46.391454299999999</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>317</v>
       </c>
@@ -31049,7 +31050,7 @@
         <v>-46.391380099999999</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>317</v>
       </c>
@@ -31102,7 +31103,7 @@
         <v>-46.392123900000001</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>317</v>
       </c>
@@ -31155,7 +31156,7 @@
         <v>-46.391454400000001</v>
       </c>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>317</v>
       </c>
@@ -31208,7 +31209,7 @@
         <v>-46.391457500000001</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>317</v>
       </c>
@@ -31261,7 +31262,7 @@
         <v>-46.390500799999998</v>
       </c>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>317</v>
       </c>
@@ -31314,7 +31315,7 @@
         <v>-46.390509799999997</v>
       </c>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>317</v>
       </c>
@@ -31367,7 +31368,7 @@
         <v>-46.391380099999999</v>
       </c>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>317</v>
       </c>
@@ -31420,7 +31421,7 @@
         <v>-46.390866699999997</v>
       </c>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>317</v>
       </c>
@@ -31473,7 +31474,7 @@
         <v>-46.390534500000001</v>
       </c>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>317</v>
       </c>
@@ -31526,7 +31527,7 @@
         <v>-46.391384500000001</v>
       </c>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>352</v>
       </c>
@@ -31579,7 +31580,7 @@
         <v>-46.392097399999997</v>
       </c>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>352</v>
       </c>
@@ -31632,7 +31633,7 @@
         <v>-46.391953299999997</v>
       </c>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>352</v>
       </c>
@@ -31685,7 +31686,7 @@
         <v>-46.391780500000003</v>
       </c>
     </row>
-    <row r="255" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>352</v>
       </c>
@@ -31738,7 +31739,7 @@
         <v>-46.392170900000004</v>
       </c>
     </row>
-    <row r="256" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>352</v>
       </c>
@@ -31791,7 +31792,7 @@
         <v>-46.392086900000002</v>
       </c>
     </row>
-    <row r="257" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>352</v>
       </c>
@@ -31844,7 +31845,7 @@
         <v>-46.392177699999998</v>
       </c>
     </row>
-    <row r="258" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>352</v>
       </c>
@@ -31897,7 +31898,7 @@
         <v>-46.392434799999997</v>
       </c>
     </row>
-    <row r="259" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>352</v>
       </c>
@@ -31950,7 +31951,7 @@
         <v>-46.3926789</v>
       </c>
     </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>352</v>
       </c>
@@ -32003,7 +32004,7 @@
         <v>-46.392434799999997</v>
       </c>
     </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>352</v>
       </c>
@@ -32056,7 +32057,7 @@
         <v>-46.392170900000004</v>
       </c>
     </row>
-    <row r="262" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>352</v>
       </c>
@@ -32109,7 +32110,7 @@
         <v>-46.391780500000003</v>
       </c>
     </row>
-    <row r="263" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>352</v>
       </c>
@@ -32162,7 +32163,7 @@
         <v>-46.392123900000001</v>
       </c>
     </row>
-    <row r="264" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>352</v>
       </c>
@@ -32215,7 +32216,7 @@
         <v>-46.392097399999997</v>
       </c>
     </row>
-    <row r="265" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>352</v>
       </c>
@@ -32268,7 +32269,7 @@
         <v>-46.391780699999998</v>
       </c>
     </row>
-    <row r="266" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>355</v>
       </c>
@@ -32321,7 +32322,7 @@
         <v>-46.391734700000001</v>
       </c>
     </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>355</v>
       </c>
@@ -32374,7 +32375,7 @@
         <v>-46.391399900000003</v>
       </c>
     </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>355</v>
       </c>
@@ -32427,7 +32428,7 @@
         <v>-46.390832000000003</v>
       </c>
     </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>355</v>
       </c>
@@ -32480,7 +32481,7 @@
         <v>-46.390766499999998</v>
       </c>
     </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>355</v>
       </c>
@@ -32533,7 +32534,7 @@
         <v>-46.390832000000003</v>
       </c>
     </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>355</v>
       </c>
@@ -32586,7 +32587,7 @@
         <v>-46.390613000000002</v>
       </c>
     </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>355</v>
       </c>
@@ -32639,7 +32640,7 @@
         <v>-46.390234300000003</v>
       </c>
     </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>355</v>
       </c>
@@ -32692,7 +32693,7 @@
         <v>-46.389846900000002</v>
       </c>
     </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>355</v>
       </c>
@@ -32745,7 +32746,7 @@
         <v>-46.3894801</v>
       </c>
     </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>355</v>
       </c>
@@ -32798,7 +32799,7 @@
         <v>-46.389092400000003</v>
       </c>
     </row>
-    <row r="276" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>355</v>
       </c>
@@ -32851,7 +32852,7 @@
         <v>-46.388676799999999</v>
       </c>
     </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>355</v>
       </c>
@@ -32904,7 +32905,7 @@
         <v>-46.386397299999999</v>
       </c>
     </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>355</v>
       </c>
@@ -32957,7 +32958,7 @@
         <v>-46.387154600000002</v>
       </c>
     </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>355</v>
       </c>
@@ -33010,7 +33011,7 @@
         <v>-46.3879375</v>
       </c>
     </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>355</v>
       </c>
@@ -33063,7 +33064,7 @@
         <v>-46.3859675</v>
       </c>
     </row>
-    <row r="281" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>355</v>
       </c>
@@ -33116,7 +33117,7 @@
         <v>-46.3862132</v>
       </c>
     </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>355</v>
       </c>
@@ -33169,7 +33170,7 @@
         <v>-46.3863129</v>
       </c>
     </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>355</v>
       </c>
@@ -33222,7 +33223,7 @@
         <v>-46.386583299999998</v>
       </c>
     </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>355</v>
       </c>
@@ -33275,7 +33276,7 @@
         <v>-46.392179599999999</v>
       </c>
     </row>
-    <row r="285" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>355</v>
       </c>
@@ -33328,7 +33329,7 @@
         <v>-46.388432899999998</v>
       </c>
     </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>355</v>
       </c>
@@ -33381,7 +33382,7 @@
         <v>-46.388676799999999</v>
       </c>
     </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>363</v>
       </c>
@@ -33434,7 +33435,7 @@
         <v>-46.397681599999999</v>
       </c>
     </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>363</v>
       </c>
@@ -33487,7 +33488,7 @@
         <v>-46.3974324</v>
       </c>
     </row>
-    <row r="289" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>363</v>
       </c>
@@ -33540,7 +33541,7 @@
         <v>-46.396907200000001</v>
       </c>
     </row>
-    <row r="290" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>363</v>
       </c>
@@ -33593,7 +33594,7 @@
         <v>-46.396283199999999</v>
       </c>
     </row>
-    <row r="291" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>363</v>
       </c>
@@ -33646,7 +33647,7 @@
         <v>-46.396234700000001</v>
       </c>
     </row>
-    <row r="292" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>363</v>
       </c>
@@ -33699,7 +33700,7 @@
         <v>-46.396234700000001</v>
       </c>
     </row>
-    <row r="293" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>363</v>
       </c>
@@ -33752,7 +33753,7 @@
         <v>-46.395672300000001</v>
       </c>
     </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>363</v>
       </c>
@@ -33805,7 +33806,7 @@
         <v>-46.394411300000002</v>
       </c>
     </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>363</v>
       </c>
@@ -33858,7 +33859,7 @@
         <v>-46.393959799999998</v>
       </c>
     </row>
-    <row r="296" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>363</v>
       </c>
@@ -33911,7 +33912,7 @@
         <v>-46.3936408</v>
       </c>
     </row>
-    <row r="297" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>363</v>
       </c>
@@ -33964,7 +33965,7 @@
         <v>-46.393255099999998</v>
       </c>
     </row>
-    <row r="298" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>363</v>
       </c>
@@ -34017,7 +34018,7 @@
         <v>-46.396111300000001</v>
       </c>
     </row>
-    <row r="299" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>363</v>
       </c>
@@ -34070,7 +34071,7 @@
         <v>-46.395125499999999</v>
       </c>
     </row>
-    <row r="300" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>363</v>
       </c>
@@ -34123,7 +34124,7 @@
         <v>-46.397876199999999</v>
       </c>
     </row>
-    <row r="301" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>363</v>
       </c>
@@ -34176,7 +34177,7 @@
         <v>-46.394917599999999</v>
       </c>
     </row>
-    <row r="302" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>363</v>
       </c>
@@ -34229,7 +34230,7 @@
         <v>-46.394633800000001</v>
       </c>
     </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>363</v>
       </c>
@@ -34282,7 +34283,7 @@
         <v>-46.392941700000002</v>
       </c>
     </row>
-    <row r="304" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>363</v>
       </c>
@@ -34335,7 +34336,7 @@
         <v>-46.390125500000003</v>
       </c>
     </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>363</v>
       </c>
@@ -34388,7 +34389,7 @@
         <v>-46.390125500000003</v>
       </c>
     </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>363</v>
       </c>
@@ -34441,7 +34442,7 @@
         <v>-46.389316899999997</v>
       </c>
     </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>363</v>
       </c>
@@ -34494,7 +34495,7 @@
         <v>-46.388850499999997</v>
       </c>
     </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>363</v>
       </c>
@@ -34547,7 +34548,7 @@
         <v>-46.388869300000003</v>
       </c>
     </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>363</v>
       </c>
@@ -34600,7 +34601,7 @@
         <v>-46.388991099999998</v>
       </c>
     </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>363</v>
       </c>
@@ -34653,7 +34654,7 @@
         <v>-46.389474800000002</v>
       </c>
     </row>
-    <row r="311" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>363</v>
       </c>
@@ -34706,7 +34707,7 @@
         <v>-46.389775499999999</v>
       </c>
     </row>
-    <row r="312" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>363</v>
       </c>
@@ -34759,7 +34760,7 @@
         <v>-46.3911503</v>
       </c>
     </row>
-    <row r="313" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>363</v>
       </c>
@@ -34812,7 +34813,7 @@
         <v>-46.390674300000001</v>
       </c>
     </row>
-    <row r="314" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>363</v>
       </c>
@@ -34865,7 +34866,7 @@
         <v>-46.390674300000001</v>
       </c>
     </row>
-    <row r="315" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>363</v>
       </c>
@@ -34918,7 +34919,7 @@
         <v>-46.390674300000001</v>
       </c>
     </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>363</v>
       </c>
@@ -34971,7 +34972,7 @@
         <v>-46.390125500000003</v>
       </c>
     </row>
-    <row r="317" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>363</v>
       </c>
@@ -35024,7 +35025,7 @@
         <v>-46.3936408</v>
       </c>
     </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>363</v>
       </c>
@@ -35077,7 +35078,7 @@
         <v>-46.392461500000003</v>
       </c>
     </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>363</v>
       </c>
@@ -35130,7 +35131,7 @@
         <v>-46.392190599999999</v>
       </c>
     </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>363</v>
       </c>
@@ -35183,7 +35184,7 @@
         <v>-46.391619599999999</v>
       </c>
     </row>
-    <row r="321" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>363</v>
       </c>
@@ -35236,7 +35237,7 @@
         <v>-46.392941700000002</v>
       </c>
     </row>
-    <row r="322" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>363</v>
       </c>
@@ -35289,7 +35290,7 @@
         <v>-46.389474800000002</v>
       </c>
     </row>
-    <row r="323" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>363</v>
       </c>
@@ -35342,7 +35343,7 @@
         <v>-46.393255099999998</v>
       </c>
     </row>
-    <row r="324" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>363</v>
       </c>
@@ -35395,7 +35396,7 @@
         <v>-46.393256299999997</v>
       </c>
     </row>
-    <row r="325" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>363</v>
       </c>
@@ -35448,7 +35449,7 @@
         <v>-46.393255099999998</v>
       </c>
     </row>
-    <row r="326" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>363</v>
       </c>
@@ -35501,7 +35502,7 @@
         <v>-46.392941700000002</v>
       </c>
     </row>
-    <row r="327" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>363</v>
       </c>
@@ -35554,7 +35555,7 @@
         <v>-46.392921100000002</v>
       </c>
     </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>363</v>
       </c>
@@ -35607,7 +35608,7 @@
         <v>-46.392921100000002</v>
       </c>
     </row>
-    <row r="329" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>377</v>
       </c>
@@ -35660,7 +35661,7 @@
         <v>-46.399263099999999</v>
       </c>
     </row>
-    <row r="330" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>377</v>
       </c>
@@ -35713,7 +35714,7 @@
         <v>-46.400001500000002</v>
       </c>
     </row>
-    <row r="331" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>377</v>
       </c>
@@ -35766,7 +35767,7 @@
         <v>-46.400030800000003</v>
       </c>
     </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>377</v>
       </c>
@@ -35819,7 +35820,7 @@
         <v>-46.398584399999997</v>
       </c>
     </row>
-    <row r="333" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>377</v>
       </c>
@@ -35872,7 +35873,7 @@
         <v>-46.399263099999999</v>
       </c>
     </row>
-    <row r="334" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>377</v>
       </c>
@@ -35925,7 +35926,7 @@
         <v>-46.399334099999997</v>
       </c>
     </row>
-    <row r="335" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>377</v>
       </c>
@@ -35978,7 +35979,7 @@
         <v>-46.399334099999997</v>
       </c>
     </row>
-    <row r="336" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>377</v>
       </c>
@@ -36031,7 +36032,7 @@
         <v>-46.398702299999997</v>
       </c>
     </row>
-    <row r="337" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>377</v>
       </c>
@@ -36084,7 +36085,7 @@
         <v>-46.398688399999998</v>
       </c>
     </row>
-    <row r="338" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>377</v>
       </c>
@@ -36137,7 +36138,7 @@
         <v>-46.398706799999999</v>
       </c>
     </row>
-    <row r="339" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>377</v>
       </c>
@@ -36190,7 +36191,7 @@
         <v>-46.398702299999997</v>
       </c>
     </row>
-    <row r="340" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>377</v>
       </c>
@@ -36243,7 +36244,7 @@
         <v>-46.400631799999999</v>
       </c>
     </row>
-    <row r="341" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>377</v>
       </c>
@@ -36296,7 +36297,7 @@
         <v>-46.401348900000002</v>
       </c>
     </row>
-    <row r="342" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
         <v>377</v>
       </c>
@@ -36337,7 +36338,7 @@
         <v>-46.401348900000002</v>
       </c>
     </row>
-    <row r="343" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>377</v>
       </c>
@@ -36378,7 +36379,7 @@
         <v>-46.401776300000002</v>
       </c>
     </row>
-    <row r="344" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>377</v>
       </c>
@@ -36419,7 +36420,7 @@
         <v>-46.401348900000002</v>
       </c>
     </row>
-    <row r="345" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>377</v>
       </c>
@@ -36472,7 +36473,7 @@
         <v>-46.401958399999998</v>
       </c>
     </row>
-    <row r="346" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>377</v>
       </c>
@@ -36525,7 +36526,7 @@
         <v>-46.402794299999996</v>
       </c>
     </row>
-    <row r="347" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>377</v>
       </c>
@@ -36578,7 +36579,7 @@
         <v>-46.402279700000001</v>
       </c>
     </row>
-    <row r="348" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>377</v>
       </c>
@@ -36631,7 +36632,7 @@
         <v>-46.402184699999999</v>
       </c>
     </row>
-    <row r="349" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>377</v>
       </c>
@@ -36684,7 +36685,7 @@
         <v>-46.402279700000001</v>
       </c>
     </row>
-    <row r="350" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>377</v>
       </c>
@@ -36737,7 +36738,7 @@
         <v>-46.401958399999998</v>
       </c>
     </row>
-    <row r="351" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>363</v>
       </c>
@@ -36793,7 +36794,7 @@
         <v>-46.3959507</v>
       </c>
     </row>
-    <row r="352" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>363</v>
       </c>
@@ -36849,7 +36850,7 @@
         <v>-46.396032599999998</v>
       </c>
     </row>
-    <row r="353" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>388</v>
       </c>
@@ -36905,7 +36906,7 @@
         <v>-46.385066799999997</v>
       </c>
     </row>
-    <row r="354" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>388</v>
       </c>
@@ -36961,7 +36962,7 @@
         <v>-46.3856647</v>
       </c>
     </row>
-    <row r="355" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>388</v>
       </c>
@@ -37017,7 +37018,7 @@
         <v>-46.386281199999999</v>
       </c>
     </row>
-    <row r="356" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>388</v>
       </c>
@@ -37073,7 +37074,7 @@
         <v>-46.385869399999997</v>
       </c>
     </row>
-    <row r="357" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>388</v>
       </c>
@@ -37129,7 +37130,7 @@
         <v>-46.385849999999998</v>
       </c>
     </row>
-    <row r="358" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>165</v>
       </c>
@@ -37185,7 +37186,7 @@
         <v>-46.393826947651448</v>
       </c>
     </row>
-    <row r="359" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>165</v>
       </c>
@@ -37241,7 +37242,7 @@
         <v>-46.392254815122861</v>
       </c>
     </row>
-    <row r="360" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>117</v>
       </c>
@@ -37297,7 +37298,7 @@
         <v>-46.4176511</v>
       </c>
     </row>
-    <row r="361" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>117</v>
       </c>
@@ -37353,7 +37354,7 @@
         <v>-46.415050600000001</v>
       </c>
     </row>
-    <row r="362" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>117</v>
       </c>
@@ -37409,7 +37410,7 @@
         <v>-46.416166400000002</v>
       </c>
     </row>
-    <row r="363" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>117</v>
       </c>
@@ -37659,7 +37660,7 @@
         <v>530</v>
       </c>
       <c r="I367">
-        <v>88.66</v>
+        <v>0</v>
       </c>
       <c r="J367">
         <v>7.38</v>
@@ -37745,7 +37746,7 @@
         <v>-46.401156800000003</v>
       </c>
     </row>
-    <row r="369" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>363</v>
       </c>
@@ -37801,7 +37802,7 @@
         <v>-46.396509199999997</v>
       </c>
     </row>
-    <row r="370" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>363</v>
       </c>
@@ -37857,7 +37858,7 @@
         <v>-46.396530900000002</v>
       </c>
     </row>
-    <row r="371" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>421</v>
       </c>
@@ -37913,7 +37914,7 @@
         <v>-46.388130599999997</v>
       </c>
     </row>
-    <row r="372" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>421</v>
       </c>
@@ -37969,7 +37970,7 @@
         <v>-46.388117800000003</v>
       </c>
     </row>
-    <row r="373" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>421</v>
       </c>
@@ -38025,7 +38026,7 @@
         <v>-46.388055299999998</v>
       </c>
     </row>
-    <row r="374" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>421</v>
       </c>
@@ -38081,7 +38082,7 @@
         <v>-46.3875758</v>
       </c>
     </row>
-    <row r="375" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>421</v>
       </c>
@@ -38137,7 +38138,7 @@
         <v>-46.387807600000002</v>
       </c>
     </row>
-    <row r="376" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>421</v>
       </c>
@@ -38193,7 +38194,7 @@
         <v>-46.388296699999998</v>
       </c>
     </row>
-    <row r="377" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>421</v>
       </c>
@@ -38249,7 +38250,7 @@
         <v>-46.388917999999997</v>
       </c>
     </row>
-    <row r="378" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>421</v>
       </c>
@@ -38305,7 +38306,7 @@
         <v>-46.389496999999999</v>
       </c>
     </row>
-    <row r="379" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>421</v>
       </c>
@@ -38361,7 +38362,7 @@
         <v>-46.390075299999999</v>
       </c>
     </row>
-    <row r="380" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>421</v>
       </c>
@@ -38417,7 +38418,7 @@
         <v>-46.390118399999999</v>
       </c>
     </row>
-    <row r="381" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A381" t="s">
         <v>421</v>
       </c>
@@ -38473,7 +38474,7 @@
         <v>-46.388296699999998</v>
       </c>
     </row>
-    <row r="382" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
         <v>439</v>
       </c>
@@ -38529,7 +38530,7 @@
         <v>-46.416035000000001</v>
       </c>
     </row>
-    <row r="383" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>439</v>
       </c>
@@ -38585,7 +38586,7 @@
         <v>-46.416319799999997</v>
       </c>
     </row>
-    <row r="384" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>439</v>
       </c>
@@ -38641,7 +38642,7 @@
         <v>-46.4161942</v>
       </c>
     </row>
-    <row r="385" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>439</v>
       </c>
@@ -38697,7 +38698,7 @@
         <v>-46.416128800000003</v>
       </c>
     </row>
-    <row r="386" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>439</v>
       </c>
@@ -38753,7 +38754,7 @@
         <v>-46.416162700000001</v>
       </c>
     </row>
-    <row r="387" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>439</v>
       </c>
@@ -38809,7 +38810,7 @@
         <v>-46.416152199999999</v>
       </c>
     </row>
-    <row r="388" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>439</v>
       </c>
@@ -38866,7 +38867,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R388" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
+  <autoFilter ref="A1:R388" xr:uid="{00000000-0001-0000-0300-000000000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="conceicao"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -1165,7 +1165,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>joao_canzi</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -18085,7 +18085,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>joao_canzi</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -18133,7 +18133,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>joao_canzi</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -45392,7 +45392,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>joao_canzi</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L377"/>
+  <dimension ref="A1:L378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -18164,17 +18164,65 @@
         <v>-46.3885242</v>
       </c>
       <c r="I377" t="n">
-        <v>765.41</v>
+        <v>765.442</v>
       </c>
       <c r="J377" t="n">
-        <v>762.16</v>
+        <v>762.072</v>
       </c>
       <c r="K377" t="n">
-        <v>3.25</v>
+        <v>3.37</v>
       </c>
       <c r="L377" t="inlineStr">
         <is>
-          <t>Plano de furo FL-01 versão 01, 05.MAI.2026</t>
+          <t>Plano de furo FL-02 versao 01, 07.MAI.2026; trecho PV-06 ao PV-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>JC-PV-08</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>PV-08</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>7396899.021</v>
+      </c>
+      <c r="F378" t="n">
+        <v>358332.965</v>
+      </c>
+      <c r="G378" t="n">
+        <v>-23.532017</v>
+      </c>
+      <c r="H378" t="n">
+        <v>-46.3877722</v>
+      </c>
+      <c r="I378" t="n">
+        <v>767.145</v>
+      </c>
+      <c r="J378" t="n">
+        <v>762.845</v>
+      </c>
+      <c r="K378" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-02 versao 01, 07.MAI.2026; trecho PV-06 ao PV-08</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R389"/>
+  <dimension ref="A1:R390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -45461,6 +45509,80 @@
       </c>
       <c r="R389" t="n">
         <v>-46.3885242</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>JC-002</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>PV-06 - PV-08</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>PV-06</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>PV-08</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G390" t="n">
+        <v>355</v>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I390" t="n">
+        <v>80.53</v>
+      </c>
+      <c r="J390" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="K390" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L390" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>em planejamento</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-02 versao 01, 07.MAI.2026; GALPAO INTERNO RUA GENI GOMES; taxa 0,0096.</t>
+        </is>
+      </c>
+      <c r="O390" t="n">
+        <v>-23.5322365</v>
+      </c>
+      <c r="P390" t="n">
+        <v>-46.3885242</v>
+      </c>
+      <c r="Q390" t="n">
+        <v>-23.532017</v>
+      </c>
+      <c r="R390" t="n">
+        <v>-46.3877722</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -706,22 +706,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>agua_boa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CTS Água Vermelha MD</t>
+          <t>Interligação Agua Boa</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CTS</t>
+          <t>Interl.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Base criada a partir dos PDFs: linhas retas entre PVs/PIs com coordenadas UTM convertidas para latitude/longitude.</t>
+          <t>Base real substituida pelo shape atualizado INT AGUA BOA: SIRGAS 2000 / UTM zona 23S convertida para latitude/longitude.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -733,22 +733,22 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>agua_boa</t>
+          <t>pacheco</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Interligação Agua Boa</t>
+          <t>RCE Pacheco Jordão</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Interl.</t>
+          <t>RCE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Base real substituida pelo shape atualizado INT AGUA BOA: SIRGAS 2000 / UTM zona 23S convertida para latitude/longitude.</t>
+          <t>Base real corrigida pelo shape da RCE Pacheco Jordão: 6 pontos e 5 trechos.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -760,22 +760,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>pacheco</t>
+          <t>luis_botelho</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RCE Pacheco Jordão</t>
+          <t>CTS Luis Botelho Mourao</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>RCE</t>
+          <t>CTS</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Base real corrigida pelo shape da RCE Pacheco Jordão: 6 pontos e 5 trechos.</t>
+          <t>Base real atualizada pelo shape: SIRGAS 2000 / UTM zona 23S convertida para latitude/longitude.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -787,12 +787,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>luis_botelho</t>
+          <t>lageado_montante_bl54_55_56</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CTS Luis Botelho Mourao</t>
+          <t>CT Lageado Montante BL54 - BL55 - BL56</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -802,7 +802,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Base real atualizada pelo shape: SIRGAS 2000 / UTM zona 23S convertida para latitude/longitude.</t>
+          <t>Base criada a partir do PDF CONFERÊNCIA.TRECH.pdf: linhas retas entre PVs/PIs com coordenadas UTM convertidas para latitude/longitude.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -814,22 +814,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>lageado_montante_bl54_55_56</t>
+          <t>rce_souto_maior</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CT Lageado Montante BL54 - BL55 - BL56</t>
+          <t>RCE Souto Maior</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CTS</t>
+          <t>RCE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Base criada a partir do PDF CONFERÊNCIA.TRECH.pdf: linhas retas entre PVs/PIs com coordenadas UTM convertidas para latitude/longitude.</t>
+          <t>Base real do shape: SIRGAS 2000 / UTM zona 23S convertida para latitude/longitude.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -841,22 +841,22 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>rce_souto_maior</t>
+          <t>ct_domingos</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RCE Souto Maior</t>
+          <t>CTS Domingos João de Carvalho</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>RCE</t>
+          <t>CTS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Base real do shape: SIRGAS 2000 / UTM zona 23S convertida para latitude/longitude.</t>
+          <t>Base criada a partir do PDF D.REL. CONFERÊNCIA CT DOMINGOS - BL01 A BL04.R01.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -868,12 +868,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ct_domingos</t>
+          <t>cts_bandeirantes</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CTS Domingos João de Carvalho</t>
+          <t>CTS Bandeirantes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Base criada a partir do PDF D.REL. CONFERÊNCIA CT DOMINGOS - BL01 A BL04.R01.</t>
+          <t>Base real adicionada a partir dos shapefiles enviados em SHAPES.zip.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -895,12 +895,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cts_bandeirantes</t>
+          <t>ct_jaragua</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CTS Bandeirantes</t>
+          <t>CTS Jaraguá</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -922,17 +922,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ct_jaragua</t>
+          <t>rce_barao_luis_de_arariba</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CTS Jaraguá</t>
+          <t>RCE Barão Luis de Arariba</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CTS</t>
+          <t>RCE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -949,12 +949,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>rce_barao_luis_de_arariba</t>
+          <t>rede_se_liga_na_rede_lourdes</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>RCE Barão Luis de Arariba</t>
+          <t>Rede Se Liga na Rede - Lourdes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -976,17 +976,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rede_se_liga_na_rede_lourdes</t>
+          <t>ct_jardim_miriam_blocos_05_a_09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Rede Se Liga na Rede - Lourdes</t>
+          <t>CTS Jardim Miriam Blocos 05 a 09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RCE</t>
+          <t>CTS</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ct_jardim_miriam_blocos_05_a_09</t>
+          <t>ct_miriam_bloco_09</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CTS Jardim Miriam Blocos 05 a 09</t>
+          <t>CTS Miriam Bloco 09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1018,24 +1018,24 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Base real adicionada a partir dos shapefiles enviados em SHAPES.zip.</t>
+          <t>Registro integrado ao CT Jardim Miriam Blocos 05 a 09 para evitar duplicidade no filtro.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SIM</t>
+          <t>NÃO</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ct_miriam_bloco_09</t>
+          <t>cts_doroteia</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CTS Miriam Bloco 09</t>
+          <t>CTS Dorotéia</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1045,24 +1045,24 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Registro integrado ao CT Jardim Miriam Blocos 05 a 09 para evitar duplicidade no filtro.</t>
+          <t>Base real adicionada a partir dos shapefiles enviados em SHAPES.zip.</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NÃO</t>
+          <t>SIM</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>cts_doroteia</t>
+          <t>cts_jardim_lourdes</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CTS Dorotéia</t>
+          <t>CTS Jardim Lourdes</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1084,12 +1084,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>cts_jardim_lourdes</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CTS Jardim Lourdes</t>
+          <t>CTS Mar de Coral</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1111,12 +1111,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>ct_benfica</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CTS Mar de Coral</t>
+          <t>CTS Benfica</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1138,12 +1138,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ct_benfica</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CTS Benfica</t>
+          <t>CTS João Canzi</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Base real adicionada a partir dos shapefiles enviados em SHAPES.zip.</t>
+          <t>Base criada a partir do PDF CTS JOÃO CANZI - FL.01.PLANO DE FURO_PV-17 AO PV-06: coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1165,12 +1165,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CTS João Canzi</t>
+          <t>CTS Água Vermelha MD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Base criada a partir do PDF CTS JOÃO CANZI - FL.01.PLANO DE FURO_PV-17 AO PV-06: coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude.</t>
+          <t>Base criada a partir dos PDFs: linhas retas entre PVs/PIs com coordenadas UTM convertidas para latitude/longitude.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L376"/>
+  <dimension ref="A1:L381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -16495,7 +16495,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>rce</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -16505,45 +16505,45 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>AVMD-PV-001</t>
+          <t>FSM-PV-001</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>PV-D07</t>
+          <t>PVE-4.1</t>
         </is>
       </c>
       <c r="E341" t="n">
-        <v>7398559.386</v>
+        <v>7397834.891</v>
       </c>
       <c r="F341" t="n">
-        <v>355365.005</v>
+        <v>358450.1705</v>
       </c>
       <c r="G341" t="n">
-        <v>-23.5167619</v>
+        <v>-23.5235762</v>
       </c>
       <c r="H341" t="n">
-        <v>-46.416679</v>
+        <v>-46.3865357</v>
       </c>
       <c r="I341" t="n">
-        <v>762.9299999999999</v>
+        <v>814.654</v>
       </c>
       <c r="J341" t="n">
-        <v>757.75</v>
+        <v>811.244</v>
       </c>
       <c r="K341" t="n">
-        <v>5.18</v>
+        <v>3.41</v>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>rce</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -16553,285 +16553,285 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>AVMD-PV-002</t>
+          <t>FSM-PV-002</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>PV-D04</t>
+          <t>PV-4.6</t>
         </is>
       </c>
       <c r="E342" t="n">
-        <v>7398721.942</v>
+        <v>7397867.253</v>
       </c>
       <c r="F342" t="n">
-        <v>355301.361</v>
+        <v>358585.244</v>
       </c>
       <c r="G342" t="n">
-        <v>-23.5152883</v>
+        <v>-23.5232957</v>
       </c>
       <c r="H342" t="n">
-        <v>-46.4172866</v>
+        <v>-46.3852099</v>
       </c>
       <c r="I342" t="n">
-        <v>761.894</v>
+        <v>813.907</v>
       </c>
       <c r="J342" t="n">
-        <v>756.5940000000001</v>
+        <v>812.307</v>
       </c>
       <c r="K342" t="n">
-        <v>5.3</v>
+        <v>1.6</v>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>rce</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>AVMD-PV-003</t>
+          <t>FSM-PI-003</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>PV-D03</t>
+          <t>PI-4.2</t>
         </is>
       </c>
       <c r="E343" t="n">
-        <v>7398779.929</v>
+        <v>7397815.6314</v>
       </c>
       <c r="F343" t="n">
-        <v>355284.478</v>
+        <v>358511.1081</v>
       </c>
       <c r="G343" t="n">
-        <v>-23.5147632</v>
+        <v>-23.5237554</v>
       </c>
       <c r="H343" t="n">
-        <v>-46.4174463</v>
+        <v>-46.3859408</v>
       </c>
       <c r="I343" t="n">
-        <v>761.083</v>
+        <v>813.646</v>
       </c>
       <c r="J343" t="n">
-        <v>756.203</v>
+        <v>812.34</v>
       </c>
       <c r="K343" t="n">
-        <v>4.88</v>
+        <v>1.31</v>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>rce</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>AVMD-PV-004</t>
+          <t>FSM-PI-004</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>PV-D02</t>
+          <t>PI-4.3</t>
         </is>
       </c>
       <c r="E344" t="n">
-        <v>7398829.5</v>
+        <v>7397820.3341</v>
       </c>
       <c r="F344" t="n">
-        <v>355263.076</v>
+        <v>358545.4414</v>
       </c>
       <c r="G344" t="n">
-        <v>-23.5143137</v>
+        <v>-23.523716</v>
       </c>
       <c r="H344" t="n">
-        <v>-46.4176511</v>
+        <v>-46.3856041</v>
       </c>
       <c r="I344" t="n">
-        <v>760.169</v>
+        <v>813.994</v>
       </c>
       <c r="J344" t="n">
-        <v>755.599</v>
+        <v>813.224</v>
       </c>
       <c r="K344" t="n">
-        <v>4.57</v>
+        <v>0.77</v>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>rce</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>AVMD-PV-005</t>
+          <t>FSM-PI-005</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>PV-D05</t>
+          <t>PI-4.4</t>
         </is>
       </c>
       <c r="E345" t="n">
-        <v>7398670.116</v>
+        <v>7397821.2168</v>
       </c>
       <c r="F345" t="n">
-        <v>355321.877</v>
+        <v>358550.9658</v>
       </c>
       <c r="G345" t="n">
-        <v>-23.5157581</v>
+        <v>-23.5237085</v>
       </c>
       <c r="H345" t="n">
-        <v>-46.4170907</v>
+        <v>-46.3855499</v>
       </c>
       <c r="I345" t="n">
-        <v>762.721</v>
+        <v>813.8049999999999</v>
       </c>
       <c r="J345" t="n">
-        <v>757.001</v>
+        <v>812.655</v>
       </c>
       <c r="K345" t="n">
-        <v>5.72</v>
+        <v>1.15</v>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>rce</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>AVMD-PV-006</t>
+          <t>FSM-PI-006</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>PV-D06</t>
+          <t>PI-4.5</t>
         </is>
       </c>
       <c r="E346" t="n">
-        <v>7398622.016</v>
+        <v>7397844.7589</v>
       </c>
       <c r="F346" t="n">
-        <v>355340.833</v>
+        <v>358573.069</v>
       </c>
       <c r="G346" t="n">
-        <v>-23.5161942</v>
+        <v>-23.5234978</v>
       </c>
       <c r="H346" t="n">
-        <v>-46.4169097</v>
+        <v>-46.3853313</v>
       </c>
       <c r="I346" t="n">
-        <v>763.379</v>
+        <v>813.728</v>
       </c>
       <c r="J346" t="n">
-        <v>757.729</v>
+        <v>812.498</v>
       </c>
       <c r="K346" t="n">
-        <v>5.65</v>
+        <v>1.23</v>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>rce</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>AVMD-PV-007</t>
+          <t>FSM-PI-007</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>PV-D10</t>
+          <t>PIE-12</t>
         </is>
       </c>
       <c r="E347" t="n">
-        <v>7398471.802</v>
+        <v>7397868.39</v>
       </c>
       <c r="F347" t="n">
-        <v>355418.221</v>
+        <v>358596.523</v>
       </c>
       <c r="G347" t="n">
-        <v>-23.5175575</v>
+        <v>-23.5232865</v>
       </c>
       <c r="H347" t="n">
-        <v>-46.4161664</v>
+        <v>-46.3850993</v>
       </c>
       <c r="I347" t="n">
-        <v>764.266</v>
+        <v>813.25</v>
       </c>
       <c r="J347" t="n">
-        <v>758.766</v>
+        <v>812.21</v>
       </c>
       <c r="K347" t="n">
-        <v>5.5</v>
+        <v>1.04</v>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -16841,45 +16841,45 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>AVMD-PV-008</t>
+          <t>MDC-PV-001</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>PV-D13</t>
+          <t>PV-05</t>
         </is>
       </c>
       <c r="E348" t="n">
-        <v>7398381.502</v>
+        <v>7397718.525</v>
       </c>
       <c r="F348" t="n">
-        <v>355473.843</v>
+        <v>357460.919</v>
       </c>
       <c r="G348" t="n">
-        <v>-23.5183779</v>
+        <v>-23.5245404</v>
       </c>
       <c r="H348" t="n">
-        <v>-46.4156304</v>
+        <v>-46.3962347</v>
       </c>
       <c r="I348" t="n">
-        <v>765.5549999999999</v>
+        <v>755.5</v>
       </c>
       <c r="J348" t="n">
-        <v>760.0549999999999</v>
+        <v>750.34</v>
       </c>
       <c r="K348" t="n">
-        <v>5.5</v>
+        <v>5.16</v>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -16889,45 +16889,45 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>AVMD-PV-009</t>
+          <t>MDC-PV-002</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>PV-D16</t>
+          <t>PV-5.14</t>
         </is>
       </c>
       <c r="E349" t="n">
-        <v>7398301.344</v>
+        <v>7397529.142</v>
       </c>
       <c r="F349" t="n">
-        <v>355574.885</v>
+        <v>357500.148</v>
       </c>
       <c r="G349" t="n">
-        <v>-23.5191107</v>
+        <v>-23.526254</v>
       </c>
       <c r="H349" t="n">
-        <v>-46.4146487</v>
+        <v>-46.3958686</v>
       </c>
       <c r="I349" t="n">
-        <v>766.971</v>
+        <v>753.473</v>
       </c>
       <c r="J349" t="n">
-        <v>761.511</v>
+        <v>750.813</v>
       </c>
       <c r="K349" t="n">
-        <v>5.46</v>
+        <v>2.66</v>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -16937,45 +16937,45 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>AVMD-PV-010</t>
+          <t>MDC-PV-003</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>PV-D19</t>
+          <t>PV-5.15</t>
         </is>
       </c>
       <c r="E350" t="n">
-        <v>7398196.826</v>
+        <v>7397526.382</v>
       </c>
       <c r="F350" t="n">
-        <v>355500.082</v>
+        <v>357491.786</v>
       </c>
       <c r="G350" t="n">
-        <v>-23.5200479</v>
+        <v>-23.5262782</v>
       </c>
       <c r="H350" t="n">
-        <v>-46.4153913</v>
+        <v>-46.3959507</v>
       </c>
       <c r="I350" t="n">
-        <v>765.548</v>
+        <v>752.963</v>
       </c>
       <c r="J350" t="n">
-        <v>762.3680000000001</v>
+        <v>749.623</v>
       </c>
       <c r="K350" t="n">
-        <v>3.18</v>
+        <v>3.34</v>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -16985,45 +16985,45 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>AVMD-PV-011</t>
+          <t>MDC-PV-004</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>PV-D0</t>
+          <t>PV-5.16</t>
         </is>
       </c>
       <c r="E351" t="n">
-        <v>7398842.289</v>
+        <v>7397522.265</v>
       </c>
       <c r="F351" t="n">
-        <v>355224.263</v>
+        <v>357483.468</v>
       </c>
       <c r="G351" t="n">
-        <v>-23.5141947</v>
+        <v>-23.5263146</v>
       </c>
       <c r="H351" t="n">
-        <v>-46.4180299</v>
+        <v>-46.3960326</v>
       </c>
       <c r="I351" t="n">
-        <v>759.328</v>
+        <v>752.607</v>
       </c>
       <c r="J351" t="n">
-        <v>754.448</v>
+        <v>749.197</v>
       </c>
       <c r="K351" t="n">
-        <v>4.88</v>
+        <v>3.41</v>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -17033,45 +17033,45 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>AVMD-PV-012</t>
+          <t>MDC-PV-005</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>PV-D9</t>
+          <t>PV-5.17</t>
         </is>
       </c>
       <c r="E352" t="n">
-        <v>7398500.509</v>
+        <v>7397554.701</v>
       </c>
       <c r="F352" t="n">
-        <v>355399.93</v>
+        <v>357434.48</v>
       </c>
       <c r="G352" t="n">
-        <v>-23.5172967</v>
+        <v>-23.5260174</v>
       </c>
       <c r="H352" t="n">
-        <v>-46.4163427</v>
+        <v>-46.3965092</v>
       </c>
       <c r="I352" t="n">
-        <v>764.2089999999999</v>
+        <v>752.279</v>
       </c>
       <c r="J352" t="n">
-        <v>758.729</v>
+        <v>748.879</v>
       </c>
       <c r="K352" t="n">
-        <v>5.48</v>
+        <v>3.4</v>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -17081,45 +17081,45 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>AVMD-PV-013</t>
+          <t>MDC-PV-006</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>PV-D12</t>
+          <t>PVE-43</t>
         </is>
       </c>
       <c r="E353" t="n">
-        <v>7398412.234</v>
+        <v>7397554.801</v>
       </c>
       <c r="F353" t="n">
-        <v>355454.703</v>
+        <v>357432.269</v>
       </c>
       <c r="G353" t="n">
-        <v>-23.5180987</v>
+        <v>-23.5260163</v>
       </c>
       <c r="H353" t="n">
-        <v>-46.4158149</v>
+        <v>-46.3965309</v>
       </c>
       <c r="I353" t="n">
-        <v>765.313</v>
+        <v>752.215</v>
       </c>
       <c r="J353" t="n">
-        <v>759.753</v>
+        <v>748.735</v>
       </c>
       <c r="K353" t="n">
-        <v>5.55</v>
+        <v>3.48</v>
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -17129,45 +17129,45 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>AVMD-PV-014</t>
+          <t>MDC-PV-007</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>PV-D14</t>
+          <t>PV-5.10</t>
         </is>
       </c>
       <c r="E354" t="n">
-        <v>7398345.702</v>
+        <v>7397700.382</v>
       </c>
       <c r="F354" t="n">
-        <v>355505.033</v>
+        <v>357396.346</v>
       </c>
       <c r="G354" t="n">
-        <v>-23.5187039</v>
+        <v>-23.5246986</v>
       </c>
       <c r="H354" t="n">
-        <v>-46.4153284</v>
+        <v>-46.3968688</v>
       </c>
       <c r="I354" t="n">
-        <v>766.34</v>
+        <v>753.081</v>
       </c>
       <c r="J354" t="n">
-        <v>760.89</v>
+        <v>750.321</v>
       </c>
       <c r="K354" t="n">
-        <v>5.45</v>
+        <v>2.76</v>
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -17177,134 +17177,134 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>AVMD-PV-015</t>
+          <t>MDC-PV-008</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>PVE-2.1</t>
+          <t>PV-5.11</t>
         </is>
       </c>
       <c r="E355" t="n">
-        <v>7398845.706</v>
+        <v>7397692.992</v>
       </c>
       <c r="F355" t="n">
-        <v>355274.528</v>
+        <v>357383.472</v>
       </c>
       <c r="G355" t="n">
-        <v>-23.5141683</v>
+        <v>-23.5247642</v>
       </c>
       <c r="H355" t="n">
-        <v>-46.4175373</v>
+        <v>-46.3969956</v>
       </c>
       <c r="I355" t="n">
-        <v>760.746</v>
+        <v>752.808</v>
       </c>
       <c r="J355" t="n">
-        <v>758.736</v>
+        <v>750.528</v>
       </c>
       <c r="K355" t="n">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>AVMD-PV-016</t>
+          <t>MDC-PI-009</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>PV-D17</t>
+          <t>PI-5.12</t>
         </is>
       </c>
       <c r="E356" t="n">
-        <v>7398250.603</v>
+        <v>7397654.237</v>
       </c>
       <c r="F356" t="n">
-        <v>355534.342</v>
+        <v>357380.54</v>
       </c>
       <c r="G356" t="n">
-        <v>-23.5195653</v>
+        <v>-23.5251139</v>
       </c>
       <c r="H356" t="n">
-        <v>-46.4150506</v>
+        <v>-46.397028</v>
       </c>
       <c r="I356" t="n">
-        <v>766.593</v>
+        <v>752.158</v>
       </c>
       <c r="J356" t="n">
-        <v>761.843</v>
+        <v>750.698</v>
       </c>
       <c r="K356" t="n">
-        <v>4.17</v>
+        <v>1.46</v>
       </c>
       <c r="L356" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>AVMD-PV-017</t>
+          <t>MDC-PI-010</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>PV-D10.1</t>
+          <t>PI-5.13</t>
         </is>
       </c>
       <c r="E357" t="n">
-        <v>7398448.644</v>
+        <v>7397654.743</v>
       </c>
       <c r="F357" t="n">
-        <v>355376.516</v>
+        <v>357403.848</v>
       </c>
       <c r="G357" t="n">
-        <v>-23.5177629</v>
+        <v>-23.5251114</v>
       </c>
       <c r="H357" t="n">
-        <v>-46.416577</v>
+        <v>-46.3967997</v>
       </c>
       <c r="I357" t="n">
-        <v>762.019</v>
+        <v>752.133</v>
       </c>
       <c r="J357" t="n">
-        <v>760.359</v>
+        <v>751.083</v>
       </c>
       <c r="K357" t="n">
-        <v>1.66</v>
+        <v>1.05</v>
       </c>
       <c r="L357" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
     </row>
@@ -17316,43 +17316,43 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>AVMD-PI-018</t>
+          <t>AVMD-PV-001</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>PI-D7.1</t>
+          <t>PVD-02</t>
         </is>
       </c>
       <c r="E358" t="n">
-        <v>7398544.966</v>
+        <v>7398829.5</v>
       </c>
       <c r="F358" t="n">
-        <v>355333.271</v>
+        <v>355263.076</v>
       </c>
       <c r="G358" t="n">
-        <v>-23.5168893</v>
+        <v>-23.5143137</v>
       </c>
       <c r="H358" t="n">
-        <v>-46.4169912</v>
+        <v>-46.4176511</v>
       </c>
       <c r="I358" t="n">
-        <v>761.353</v>
+        <v>760.169</v>
       </c>
       <c r="J358" t="n">
-        <v>760.1130000000001</v>
+        <v>755.599</v>
       </c>
       <c r="K358" t="n">
-        <v>1.24</v>
+        <v>4.57</v>
       </c>
       <c r="L358" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
     </row>
@@ -17364,50 +17364,50 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>AVMD-PI-019</t>
+          <t>AVMD-PV-002</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>PV-D19.1</t>
+          <t>PVD-03</t>
         </is>
       </c>
       <c r="E359" t="n">
-        <v>7398193.998</v>
+        <v>7398779.929</v>
       </c>
       <c r="F359" t="n">
-        <v>355498.831</v>
+        <v>355284.478</v>
       </c>
       <c r="G359" t="n">
-        <v>-23.5200733</v>
+        <v>-23.5147632</v>
       </c>
       <c r="H359" t="n">
-        <v>-46.4154038</v>
+        <v>-46.4174463</v>
       </c>
       <c r="I359" t="n">
-        <v>765.55</v>
+        <v>761.083</v>
       </c>
       <c r="J359" t="n">
-        <v>764.46</v>
+        <v>756.203</v>
       </c>
       <c r="K359" t="n">
-        <v>1.09</v>
+        <v>4.88</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>rce</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -17417,45 +17417,45 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>FSM-PV-001</t>
+          <t>AVMD-PV-003</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>PVE-4.1</t>
+          <t>PVD-04</t>
         </is>
       </c>
       <c r="E360" t="n">
-        <v>7397834.891</v>
+        <v>7398721.942</v>
       </c>
       <c r="F360" t="n">
-        <v>358450.1705</v>
+        <v>355301.361</v>
       </c>
       <c r="G360" t="n">
-        <v>-23.5235762</v>
+        <v>-23.5152883</v>
       </c>
       <c r="H360" t="n">
-        <v>-46.3865357</v>
+        <v>-46.4172866</v>
       </c>
       <c r="I360" t="n">
-        <v>814.654</v>
+        <v>761.894</v>
       </c>
       <c r="J360" t="n">
-        <v>811.244</v>
+        <v>756.5940000000001</v>
       </c>
       <c r="K360" t="n">
-        <v>3.41</v>
+        <v>5.3</v>
       </c>
       <c r="L360" t="inlineStr">
         <is>
-          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>rce</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -17465,285 +17465,276 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>FSM-PV-002</t>
+          <t>AVMD-PV-004</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>PV-4.6</t>
+          <t>PVD-05</t>
         </is>
       </c>
       <c r="E361" t="n">
-        <v>7397867.253</v>
+        <v>7398670.116</v>
       </c>
       <c r="F361" t="n">
-        <v>358585.244</v>
+        <v>355321.877</v>
       </c>
       <c r="G361" t="n">
-        <v>-23.5232957</v>
+        <v>-23.5157581</v>
       </c>
       <c r="H361" t="n">
-        <v>-46.3852099</v>
+        <v>-46.4170907</v>
       </c>
       <c r="I361" t="n">
-        <v>813.907</v>
+        <v>762.721</v>
       </c>
       <c r="J361" t="n">
-        <v>812.307</v>
+        <v>757.001</v>
       </c>
       <c r="K361" t="n">
-        <v>1.6</v>
+        <v>5.72</v>
       </c>
       <c r="L361" t="inlineStr">
         <is>
-          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>rce</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>FSM-PI-003</t>
+          <t>AVMD-PV-005</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>PI-4.2</t>
+          <t>PVE-D0</t>
         </is>
       </c>
       <c r="E362" t="n">
-        <v>7397815.6314</v>
+        <v>7398842.289</v>
       </c>
       <c r="F362" t="n">
-        <v>358511.1081</v>
+        <v>355224.263</v>
       </c>
       <c r="G362" t="n">
-        <v>-23.5237554</v>
+        <v>-23.5141947</v>
       </c>
       <c r="H362" t="n">
-        <v>-46.3859408</v>
+        <v>-46.4180299</v>
       </c>
       <c r="I362" t="n">
-        <v>813.646</v>
+        <v>759.328</v>
       </c>
       <c r="J362" t="n">
-        <v>812.34</v>
+        <v>754.448</v>
       </c>
       <c r="K362" t="n">
-        <v>1.31</v>
+        <v>4.88</v>
       </c>
       <c r="L362" t="inlineStr">
         <is>
-          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>rce</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>FSM-PI-004</t>
+          <t>AVMD-PV-006</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>PI-4.3</t>
+          <t>PVD-06</t>
         </is>
       </c>
       <c r="E363" t="n">
-        <v>7397820.3341</v>
+        <v>7398622.016</v>
       </c>
       <c r="F363" t="n">
-        <v>358545.4414</v>
+        <v>355340.833</v>
       </c>
       <c r="G363" t="n">
-        <v>-23.523716</v>
+        <v>-23.5161942</v>
       </c>
       <c r="H363" t="n">
-        <v>-46.3856041</v>
+        <v>-46.4169097</v>
       </c>
       <c r="I363" t="n">
-        <v>813.994</v>
+        <v>763.379</v>
       </c>
       <c r="J363" t="n">
-        <v>813.224</v>
+        <v>757.729</v>
       </c>
       <c r="K363" t="n">
-        <v>0.77</v>
+        <v>5.65</v>
       </c>
       <c r="L363" t="inlineStr">
         <is>
-          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>rce</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>FSM-PI-005</t>
+          <t>AVMD-PV-007</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>PI-4.4</t>
+          <t>PVD-07</t>
         </is>
       </c>
       <c r="E364" t="n">
-        <v>7397821.2168</v>
+        <v>7398559.386</v>
       </c>
       <c r="F364" t="n">
-        <v>358550.9658</v>
+        <v>355365.005</v>
       </c>
       <c r="G364" t="n">
-        <v>-23.5237085</v>
+        <v>-23.5167619</v>
       </c>
       <c r="H364" t="n">
-        <v>-46.3855499</v>
+        <v>-46.416679</v>
       </c>
       <c r="I364" t="n">
-        <v>813.8049999999999</v>
+        <v>762.9299999999999</v>
       </c>
       <c r="J364" t="n">
-        <v>812.655</v>
+        <v>757.75</v>
       </c>
       <c r="K364" t="n">
-        <v>1.15</v>
+        <v>5.18</v>
       </c>
       <c r="L364" t="inlineStr">
         <is>
-          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>rce</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>FSM-PI-006</t>
+          <t>AVMD-PV-008</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>PI-4.5</t>
+          <t>PVD-08</t>
         </is>
       </c>
       <c r="E365" t="n">
-        <v>7397844.7589</v>
+        <v>7398530.558</v>
       </c>
       <c r="F365" t="n">
-        <v>358573.069</v>
+        <v>355381.062</v>
       </c>
       <c r="G365" t="n">
-        <v>-23.5234978</v>
+        <v>-23.5170236</v>
       </c>
       <c r="H365" t="n">
-        <v>-46.3853313</v>
-      </c>
-      <c r="I365" t="n">
-        <v>813.728</v>
-      </c>
-      <c r="J365" t="n">
-        <v>812.498</v>
-      </c>
-      <c r="K365" t="n">
-        <v>1.23</v>
+        <v>-46.4165246</v>
       </c>
       <c r="L365" t="inlineStr">
         <is>
-          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
+          <t>PDF Ordem de Serviço</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>rce</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>FSM-PI-007</t>
+          <t>AVMD-PV-009</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>PIE-12</t>
+          <t>PVD-09</t>
         </is>
       </c>
       <c r="E366" t="n">
-        <v>7397868.39</v>
+        <v>7398500.509</v>
       </c>
       <c r="F366" t="n">
-        <v>358596.523</v>
+        <v>355399.93</v>
       </c>
       <c r="G366" t="n">
-        <v>-23.5232865</v>
+        <v>-23.5172967</v>
       </c>
       <c r="H366" t="n">
-        <v>-46.3850993</v>
+        <v>-46.4163427</v>
       </c>
       <c r="I366" t="n">
-        <v>813.25</v>
+        <v>764.2089999999999</v>
       </c>
       <c r="J366" t="n">
-        <v>812.21</v>
+        <v>758.729</v>
       </c>
       <c r="K366" t="n">
-        <v>1.04</v>
+        <v>5.48</v>
       </c>
       <c r="L366" t="inlineStr">
         <is>
-          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -17753,45 +17744,45 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>MDC-PV-001</t>
+          <t>AVMD-PV-010</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>PV-05</t>
+          <t>PVD-10</t>
         </is>
       </c>
       <c r="E367" t="n">
-        <v>7397718.525</v>
+        <v>7398471.802</v>
       </c>
       <c r="F367" t="n">
-        <v>357460.919</v>
+        <v>355418.221</v>
       </c>
       <c r="G367" t="n">
-        <v>-23.5245404</v>
+        <v>-23.5175575</v>
       </c>
       <c r="H367" t="n">
-        <v>-46.3962347</v>
+        <v>-46.4161664</v>
       </c>
       <c r="I367" t="n">
-        <v>755.5</v>
+        <v>764.266</v>
       </c>
       <c r="J367" t="n">
-        <v>750.34</v>
+        <v>758.766</v>
       </c>
       <c r="K367" t="n">
-        <v>5.16</v>
+        <v>5.5</v>
       </c>
       <c r="L367" t="inlineStr">
         <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -17801,45 +17792,36 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>MDC-PV-002</t>
+          <t>AVMD-PV-011</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>PV-5.14</t>
+          <t>PVD-11</t>
         </is>
       </c>
       <c r="E368" t="n">
-        <v>7397529.142</v>
+        <v>7398442.686</v>
       </c>
       <c r="F368" t="n">
-        <v>357500.148</v>
+        <v>355436.028</v>
       </c>
       <c r="G368" t="n">
-        <v>-23.526254</v>
+        <v>-23.517822</v>
       </c>
       <c r="H368" t="n">
-        <v>-46.3958686</v>
-      </c>
-      <c r="I368" t="n">
-        <v>753.473</v>
-      </c>
-      <c r="J368" t="n">
-        <v>750.813</v>
-      </c>
-      <c r="K368" t="n">
-        <v>2.66</v>
+        <v>-46.4159948</v>
       </c>
       <c r="L368" t="inlineStr">
         <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+          <t>PDF Ordem de Serviço</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -17849,45 +17831,45 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>MDC-PV-003</t>
+          <t>AVMD-PV-012</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>PV-5.15</t>
+          <t>PVD-12</t>
         </is>
       </c>
       <c r="E369" t="n">
-        <v>7397526.382</v>
+        <v>7398412.234</v>
       </c>
       <c r="F369" t="n">
-        <v>357491.786</v>
+        <v>355454.703</v>
       </c>
       <c r="G369" t="n">
-        <v>-23.5262782</v>
+        <v>-23.5180987</v>
       </c>
       <c r="H369" t="n">
-        <v>-46.3959507</v>
+        <v>-46.4158149</v>
       </c>
       <c r="I369" t="n">
-        <v>752.963</v>
+        <v>765.313</v>
       </c>
       <c r="J369" t="n">
-        <v>749.623</v>
+        <v>759.753</v>
       </c>
       <c r="K369" t="n">
-        <v>3.34</v>
+        <v>5.55</v>
       </c>
       <c r="L369" t="inlineStr">
         <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -17897,45 +17879,45 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>MDC-PV-004</t>
+          <t>AVMD-PV-013</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>PV-5.16</t>
+          <t>PVD-13</t>
         </is>
       </c>
       <c r="E370" t="n">
-        <v>7397522.265</v>
+        <v>7398381.502</v>
       </c>
       <c r="F370" t="n">
-        <v>357483.468</v>
+        <v>355473.843</v>
       </c>
       <c r="G370" t="n">
-        <v>-23.5263146</v>
+        <v>-23.5183779</v>
       </c>
       <c r="H370" t="n">
-        <v>-46.3960326</v>
+        <v>-46.4156304</v>
       </c>
       <c r="I370" t="n">
-        <v>752.607</v>
+        <v>765.5549999999999</v>
       </c>
       <c r="J370" t="n">
-        <v>749.197</v>
+        <v>760.0549999999999</v>
       </c>
       <c r="K370" t="n">
-        <v>3.41</v>
+        <v>5.5</v>
       </c>
       <c r="L370" t="inlineStr">
         <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -17945,45 +17927,45 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>MDC-PV-005</t>
+          <t>AVMD-PV-014</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>PV-5.17</t>
+          <t>PVD-14</t>
         </is>
       </c>
       <c r="E371" t="n">
-        <v>7397554.701</v>
+        <v>7398345.702</v>
       </c>
       <c r="F371" t="n">
-        <v>357434.48</v>
+        <v>355505.033</v>
       </c>
       <c r="G371" t="n">
-        <v>-23.5260174</v>
+        <v>-23.5187039</v>
       </c>
       <c r="H371" t="n">
-        <v>-46.3965092</v>
+        <v>-46.4153284</v>
       </c>
       <c r="I371" t="n">
-        <v>752.279</v>
+        <v>766.34</v>
       </c>
       <c r="J371" t="n">
-        <v>748.879</v>
+        <v>760.89</v>
       </c>
       <c r="K371" t="n">
-        <v>3.4</v>
+        <v>5.45</v>
       </c>
       <c r="L371" t="inlineStr">
         <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -17993,45 +17975,45 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>MDC-PV-006</t>
+          <t>AVMD-PV-015</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>PVE-43</t>
+          <t>PVD-16</t>
         </is>
       </c>
       <c r="E372" t="n">
-        <v>7397554.801</v>
+        <v>7398301.344</v>
       </c>
       <c r="F372" t="n">
-        <v>357432.269</v>
+        <v>355574.885</v>
       </c>
       <c r="G372" t="n">
-        <v>-23.5260163</v>
+        <v>-23.5191107</v>
       </c>
       <c r="H372" t="n">
-        <v>-46.3965309</v>
+        <v>-46.4146487</v>
       </c>
       <c r="I372" t="n">
-        <v>752.215</v>
+        <v>766.971</v>
       </c>
       <c r="J372" t="n">
-        <v>748.735</v>
+        <v>761.511</v>
       </c>
       <c r="K372" t="n">
-        <v>3.48</v>
+        <v>5.46</v>
       </c>
       <c r="L372" t="inlineStr">
         <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -18041,45 +18023,45 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>MDC-PV-007</t>
+          <t>AVMD-PV-016</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>PV-5.10</t>
+          <t>PVD-17</t>
         </is>
       </c>
       <c r="E373" t="n">
-        <v>7397700.382</v>
+        <v>7398250.603</v>
       </c>
       <c r="F373" t="n">
-        <v>357396.346</v>
+        <v>355534.342</v>
       </c>
       <c r="G373" t="n">
-        <v>-23.5246986</v>
+        <v>-23.5195653</v>
       </c>
       <c r="H373" t="n">
-        <v>-46.3968688</v>
+        <v>-46.4150506</v>
       </c>
       <c r="I373" t="n">
-        <v>753.081</v>
+        <v>766.593</v>
       </c>
       <c r="J373" t="n">
-        <v>750.321</v>
+        <v>761.843</v>
       </c>
       <c r="K373" t="n">
-        <v>2.76</v>
+        <v>4.17</v>
       </c>
       <c r="L373" t="inlineStr">
         <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -18089,134 +18071,320 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>MDC-PV-008</t>
+          <t>AVMD-PV-017</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>PV-5.11</t>
+          <t>PVD-18</t>
         </is>
       </c>
       <c r="E374" t="n">
-        <v>7397692.992</v>
+        <v>7398234.819</v>
       </c>
       <c r="F374" t="n">
-        <v>357383.472</v>
+        <v>355521.988</v>
       </c>
       <c r="G374" t="n">
-        <v>-23.5247642</v>
+        <v>-23.5197067</v>
       </c>
       <c r="H374" t="n">
-        <v>-46.3969956</v>
-      </c>
-      <c r="I374" t="n">
-        <v>752.808</v>
-      </c>
-      <c r="J374" t="n">
-        <v>750.528</v>
-      </c>
-      <c r="K374" t="n">
-        <v>2.28</v>
+        <v>-46.4151731</v>
       </c>
       <c r="L374" t="inlineStr">
         <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+          <t>PDF Ordem de Serviço</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>MDC-PI-009</t>
+          <t>AVMD-PV-018</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>PI-5.12</t>
+          <t>PVD-19</t>
         </is>
       </c>
       <c r="E375" t="n">
-        <v>7397654.237</v>
+        <v>7398196.812</v>
       </c>
       <c r="F375" t="n">
-        <v>357380.54</v>
+        <v>355499.978</v>
       </c>
       <c r="G375" t="n">
-        <v>-23.5251139</v>
+        <v>-23.520048</v>
       </c>
       <c r="H375" t="n">
-        <v>-46.397028</v>
+        <v>-46.4153923</v>
       </c>
       <c r="I375" t="n">
-        <v>752.158</v>
+        <v>765.548</v>
       </c>
       <c r="J375" t="n">
-        <v>750.698</v>
+        <v>762.3680000000001</v>
       </c>
       <c r="K375" t="n">
-        <v>1.46</v>
+        <v>3.18</v>
       </c>
       <c r="L375" t="inlineStr">
         <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>AVMD-PV-019</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>PV-D10.1</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>7398458.598</v>
+      </c>
+      <c r="F376" t="n">
+        <v>355392.034</v>
+      </c>
+      <c r="G376" t="n">
+        <v>-23.5176744</v>
+      </c>
+      <c r="H376" t="n">
+        <v>-46.4164241</v>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>PDF Ordem de Serviço</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>agua_md</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>AVMD-PV-020</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>PVD-13.1</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>7398368.985</v>
+      </c>
+      <c r="F377" t="n">
+        <v>355448.64</v>
+      </c>
+      <c r="G377" t="n">
+        <v>-23.5184887</v>
+      </c>
+      <c r="H377" t="n">
+        <v>-46.4158784</v>
+      </c>
+      <c r="L377" t="inlineStr">
+        <is>
+          <t>PDF Ordem de Serviço</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>agua_md</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>AVMD-PV-021</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>PVD-06.1</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>7398606.921</v>
+      </c>
+      <c r="F378" t="n">
+        <v>355309.805</v>
+      </c>
+      <c r="G378" t="n">
+        <v>-23.5163277</v>
+      </c>
+      <c r="H378" t="n">
+        <v>-46.417215</v>
+      </c>
+      <c r="L378" t="inlineStr">
+        <is>
+          <t>PDF Ordem de Serviço</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>agua_md</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
           <t>PI</t>
         </is>
       </c>
-      <c r="C376" t="inlineStr">
-        <is>
-          <t>MDC-PI-010</t>
-        </is>
-      </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>PI-5.13</t>
-        </is>
-      </c>
-      <c r="E376" t="n">
-        <v>7397654.743</v>
-      </c>
-      <c r="F376" t="n">
-        <v>357403.848</v>
-      </c>
-      <c r="G376" t="n">
-        <v>-23.5251114</v>
-      </c>
-      <c r="H376" t="n">
-        <v>-46.3967997</v>
-      </c>
-      <c r="I376" t="n">
-        <v>752.133</v>
-      </c>
-      <c r="J376" t="n">
-        <v>751.083</v>
-      </c>
-      <c r="K376" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="L376" t="inlineStr">
-        <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>AVMD-PI-001</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>PI-D7.3</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>7398534.667</v>
+      </c>
+      <c r="F379" t="n">
+        <v>355314.853</v>
+      </c>
+      <c r="G379" t="n">
+        <v>-23.5169806</v>
+      </c>
+      <c r="H379" t="n">
+        <v>-46.4171725</v>
+      </c>
+      <c r="L379" t="inlineStr">
+        <is>
+          <t>PDF Ordem de Serviço</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>agua_md</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>AVMD-PI-002</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>PID-10.2</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>7398448.072</v>
+      </c>
+      <c r="F380" t="n">
+        <v>355375.319</v>
+      </c>
+      <c r="G380" t="n">
+        <v>-23.517768</v>
+      </c>
+      <c r="H380" t="n">
+        <v>-46.4165888</v>
+      </c>
+      <c r="L380" t="inlineStr">
+        <is>
+          <t>PDF Ordem de Serviço</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>agua_md</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>AVMD-PV-022</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>PVE-2.1</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>7398845.706</v>
+      </c>
+      <c r="F381" t="n">
+        <v>355274.528</v>
+      </c>
+      <c r="G381" t="n">
+        <v>-23.5141683</v>
+      </c>
+      <c r="H381" t="n">
+        <v>-46.4175373</v>
+      </c>
+      <c r="I381" t="n">
+        <v>760.746</v>
+      </c>
+      <c r="J381" t="n">
+        <v>758.736</v>
+      </c>
+      <c r="K381" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="L381" t="inlineStr">
+        <is>
+          <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
     </row>
@@ -18231,7 +18399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R393"/>
+  <dimension ref="A1:R401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -43550,53 +43718,53 @@
     <row r="363" hidden="1">
       <c r="A363" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>rce</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>AVMD-001</t>
+          <t>FSM-001</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>PV-D04 - PV-D03</t>
+          <t>PI-4.3 - PI-4.2</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>PV-D04</t>
+          <t>PI-4.3</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>PV-D03</t>
+          <t>PI-4.2</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>PEAD</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="G363" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Método Não Destrutivo - MND</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I363" t="n">
-        <v>60.39</v>
+        <v>34.65</v>
       </c>
       <c r="J363" t="n">
-        <v>5.3</v>
+        <v>0.77</v>
       </c>
       <c r="K363" t="n">
-        <v>4.88</v>
+        <v>1.31</v>
       </c>
       <c r="L363" t="n">
-        <v>5.3</v>
+        <v>1.31</v>
       </c>
       <c r="M363" t="inlineStr">
         <is>
@@ -43605,72 +43773,72 @@
       </c>
       <c r="N363" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
         </is>
       </c>
       <c r="O363" t="n">
-        <v>-23.5152883</v>
+        <v>-23.523716</v>
       </c>
       <c r="P363" t="n">
-        <v>-46.4172866</v>
+        <v>-46.3856041</v>
       </c>
       <c r="Q363" t="n">
-        <v>-23.5147632</v>
+        <v>-23.5237554</v>
       </c>
       <c r="R363" t="n">
-        <v>-46.4174463</v>
+        <v>-46.3859408</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>rce</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>AVMD-002</t>
+          <t>FSM-002</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>PV-D03 - PV-D02</t>
+          <t>PI-4.2 - PVE-4.1</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>PV-D03</t>
+          <t>PI-4.2</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>PV-D02</t>
+          <t>PVE-4.1</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>PEAD</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="G364" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Método Não Destrutivo - MND</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I364" t="n">
-        <v>53.99</v>
+        <v>63.91</v>
       </c>
       <c r="J364" t="n">
-        <v>4.88</v>
+        <v>1.31</v>
       </c>
       <c r="K364" t="n">
-        <v>4.57</v>
+        <v>3.05</v>
       </c>
       <c r="L364" t="n">
-        <v>4.88</v>
+        <v>3.05</v>
       </c>
       <c r="M364" t="inlineStr">
         <is>
@@ -43679,72 +43847,72 @@
       </c>
       <c r="N364" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
         </is>
       </c>
       <c r="O364" t="n">
-        <v>-23.5147632</v>
+        <v>-23.5237554</v>
       </c>
       <c r="P364" t="n">
-        <v>-46.4174463</v>
+        <v>-46.3859408</v>
       </c>
       <c r="Q364" t="n">
-        <v>-23.5143137</v>
+        <v>-23.5235762</v>
       </c>
       <c r="R364" t="n">
-        <v>-46.4176511</v>
+        <v>-46.3865357</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>rce</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>AVMD-003</t>
+          <t>FSM-003</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>PV-D05 - PV-D04</t>
+          <t>PI-4.4 - PI-4.5</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>PV-D05</t>
+          <t>PI-4.4</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>PV-D04</t>
+          <t>PI-4.5</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>PEAD</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="G365" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>Método Não Destrutivo - MND</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I365" t="n">
-        <v>55.74</v>
+        <v>32.29</v>
       </c>
       <c r="J365" t="n">
-        <v>5.72</v>
+        <v>1.15</v>
       </c>
       <c r="K365" t="n">
-        <v>5.3</v>
+        <v>1.23</v>
       </c>
       <c r="L365" t="n">
-        <v>5.72</v>
+        <v>1.23</v>
       </c>
       <c r="M365" t="inlineStr">
         <is>
@@ -43753,72 +43921,72 @@
       </c>
       <c r="N365" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
         </is>
       </c>
       <c r="O365" t="n">
-        <v>-23.5157581</v>
+        <v>-23.5237085</v>
       </c>
       <c r="P365" t="n">
-        <v>-46.4170907</v>
+        <v>-46.3855499</v>
       </c>
       <c r="Q365" t="n">
-        <v>-23.5152883</v>
+        <v>-23.5234978</v>
       </c>
       <c r="R365" t="n">
-        <v>-46.4172866</v>
+        <v>-46.3853313</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>rce</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>AVMD-004</t>
+          <t>FSM-004</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>PV-D06 - PV-D05</t>
+          <t>PI-4.5 - PV-4.6</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>PV-D06</t>
+          <t>PI-4.5</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>PV-D05</t>
+          <t>PV-4.6</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>PEAD</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="G366" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>Método Não Destrutivo - MND</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I366" t="n">
-        <v>51.7</v>
+        <v>25.58</v>
       </c>
       <c r="J366" t="n">
-        <v>5.65</v>
+        <v>1.23</v>
       </c>
       <c r="K366" t="n">
-        <v>5.72</v>
+        <v>1.6</v>
       </c>
       <c r="L366" t="n">
-        <v>5.72</v>
+        <v>1.6</v>
       </c>
       <c r="M366" t="inlineStr">
         <is>
@@ -43827,72 +43995,72 @@
       </c>
       <c r="N366" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
         </is>
       </c>
       <c r="O366" t="n">
-        <v>-23.5161942</v>
+        <v>-23.5234978</v>
       </c>
       <c r="P366" t="n">
-        <v>-46.4169097</v>
+        <v>-46.3853313</v>
       </c>
       <c r="Q366" t="n">
-        <v>-23.5157581</v>
+        <v>-23.5232957</v>
       </c>
       <c r="R366" t="n">
-        <v>-46.4170907</v>
+        <v>-46.3852099</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>rce</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>AVMD-005</t>
+          <t>FSM-005</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>PV-D07 - PV-D06</t>
+          <t>PV-4.6 - PIE-12</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>PV-D07</t>
+          <t>PV-4.6</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
         <is>
-          <t>PV-D06</t>
+          <t>PIE-12</t>
         </is>
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>PEAD</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="G367" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>Método Não Destrutivo - MND</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I367" t="n">
-        <v>67.13</v>
+        <v>11.34</v>
       </c>
       <c r="J367" t="n">
-        <v>5.18</v>
+        <v>1.6</v>
       </c>
       <c r="K367" t="n">
-        <v>5.65</v>
+        <v>1.04</v>
       </c>
       <c r="L367" t="n">
-        <v>5.65</v>
+        <v>1.6</v>
       </c>
       <c r="M367" t="inlineStr">
         <is>
@@ -43901,72 +44069,72 @@
       </c>
       <c r="N367" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
         </is>
       </c>
       <c r="O367" t="n">
-        <v>-23.5167619</v>
+        <v>-23.5232957</v>
       </c>
       <c r="P367" t="n">
-        <v>-46.416679</v>
+        <v>-46.3852099</v>
       </c>
       <c r="Q367" t="n">
-        <v>-23.5161942</v>
+        <v>-23.5232865</v>
       </c>
       <c r="R367" t="n">
-        <v>-46.4169097</v>
+        <v>-46.3850993</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>AVMD-006</t>
+          <t>MDC-001</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>PV-D02 - PV-D0</t>
+          <t>PV-5.14 - PV-5.15</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>PV-D02</t>
+          <t>PV-5.14</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
         <is>
-          <t>PV-D0</t>
+          <t>PV-5.15</t>
         </is>
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>PEAD</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="G368" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Método Não Destrutivo - MND</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I368" t="n">
-        <v>40.87</v>
+        <v>8.81</v>
       </c>
       <c r="J368" t="n">
-        <v>4.57</v>
+        <v>2.66</v>
       </c>
       <c r="K368" t="n">
-        <v>4.88</v>
+        <v>3.27</v>
       </c>
       <c r="L368" t="n">
-        <v>4.88</v>
+        <v>3.27</v>
       </c>
       <c r="M368" t="inlineStr">
         <is>
@@ -43975,72 +44143,72 @@
       </c>
       <c r="N368" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
       <c r="O368" t="n">
-        <v>-23.5143137</v>
+        <v>-23.526254</v>
       </c>
       <c r="P368" t="n">
-        <v>-46.4176511</v>
+        <v>-46.3958686</v>
       </c>
       <c r="Q368" t="n">
-        <v>-23.5141947</v>
+        <v>-23.5262782</v>
       </c>
       <c r="R368" t="n">
-        <v>-46.4180299</v>
+        <v>-46.3959507</v>
       </c>
     </row>
     <row r="369" hidden="1">
       <c r="A369" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>AVMD-007</t>
+          <t>MDC-002</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>PVE-2.1 - PV-D02</t>
+          <t>PV-5.15 - PV-5.16</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>PVE-2.1</t>
+          <t>PV-5.15</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
         <is>
-          <t>PV-D02</t>
+          <t>PV-5.16</t>
         </is>
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD</t>
         </is>
       </c>
       <c r="G369" t="n">
-        <v>400</v>
+        <v>355</v>
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Método Não Destrutivo - MND</t>
         </is>
       </c>
       <c r="I369" t="n">
-        <v>19.84</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="J369" t="n">
-        <v>2.01</v>
+        <v>3.34</v>
       </c>
       <c r="K369" t="n">
-        <v>4.57</v>
+        <v>3.41</v>
       </c>
       <c r="L369" t="n">
-        <v>4.57</v>
+        <v>3.41</v>
       </c>
       <c r="M369" t="inlineStr">
         <is>
@@ -44049,46 +44217,46 @@
       </c>
       <c r="N369" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
       <c r="O369" t="n">
-        <v>-23.5141683</v>
+        <v>-23.5262782</v>
       </c>
       <c r="P369" t="n">
-        <v>-46.4175373</v>
+        <v>-46.3959507</v>
       </c>
       <c r="Q369" t="n">
-        <v>-23.5143137</v>
+        <v>-23.5263146</v>
       </c>
       <c r="R369" t="n">
-        <v>-46.4176511</v>
+        <v>-46.3960326</v>
       </c>
     </row>
     <row r="370" hidden="1">
       <c r="A370" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>AVMD-008</t>
+          <t>MDC-003</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>PV-D19 - PV-D17</t>
+          <t>PV-5.16 - PV-5.17</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>PV-D19</t>
+          <t>PV-5.16</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>PV-D17</t>
+          <t>PV-5.17</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
@@ -44097,7 +44265,7 @@
         </is>
       </c>
       <c r="G370" t="n">
-        <v>450</v>
+        <v>355</v>
       </c>
       <c r="H370" t="inlineStr">
         <is>
@@ -44105,16 +44273,16 @@
         </is>
       </c>
       <c r="I370" t="n">
-        <v>63.76</v>
+        <v>58.75</v>
       </c>
       <c r="J370" t="n">
-        <v>3.23</v>
+        <v>3.41</v>
       </c>
       <c r="K370" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="L370" t="n">
-        <v>4.75</v>
+        <v>3.41</v>
       </c>
       <c r="M370" t="inlineStr">
         <is>
@@ -44123,46 +44291,46 @@
       </c>
       <c r="N370" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
       <c r="O370" t="n">
-        <v>-23.5200479</v>
+        <v>-23.5263146</v>
       </c>
       <c r="P370" t="n">
-        <v>-46.4153913</v>
+        <v>-46.3960326</v>
       </c>
       <c r="Q370" t="n">
-        <v>-23.5195653</v>
+        <v>-23.5260174</v>
       </c>
       <c r="R370" t="n">
-        <v>-46.4150506</v>
+        <v>-46.3965092</v>
       </c>
     </row>
     <row r="371" hidden="1">
       <c r="A371" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>AVMD-009</t>
+          <t>MDC-004</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>PV-D17 - PV-D16</t>
+          <t>PV-5.17 - PVE-43</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>PV-D17</t>
+          <t>PV-5.17</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>PV-D16</t>
+          <t>PVE-43</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
@@ -44171,7 +44339,7 @@
         </is>
       </c>
       <c r="G371" t="n">
-        <v>450</v>
+        <v>355</v>
       </c>
       <c r="H371" t="inlineStr">
         <is>
@@ -44179,16 +44347,16 @@
         </is>
       </c>
       <c r="I371" t="n">
-        <v>64.95</v>
+        <v>2.21</v>
       </c>
       <c r="J371" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="K371" t="n">
-        <v>5.46</v>
+        <v>3.42</v>
       </c>
       <c r="L371" t="n">
-        <v>5.46</v>
+        <v>3.42</v>
       </c>
       <c r="M371" t="inlineStr">
         <is>
@@ -44197,72 +44365,72 @@
       </c>
       <c r="N371" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
       <c r="O371" t="n">
-        <v>-23.5195653</v>
+        <v>-23.5260174</v>
       </c>
       <c r="P371" t="n">
-        <v>-46.4150506</v>
+        <v>-46.3965092</v>
       </c>
       <c r="Q371" t="n">
-        <v>-23.5191107</v>
+        <v>-23.5260163</v>
       </c>
       <c r="R371" t="n">
-        <v>-46.4146487</v>
+        <v>-46.3965309</v>
       </c>
     </row>
     <row r="372" hidden="1">
       <c r="A372" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>AVMD-010</t>
+          <t>MDC-005</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>PV-D16 - PV-D14</t>
+          <t>PI-5.13 - PI-5.12</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>PV-D16</t>
+          <t>PI-5.13</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>PV-D14</t>
+          <t>PI-5.12</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>PEAD</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="G372" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>Método Não Destrutivo - MND</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I372" t="n">
-        <v>82.75</v>
+        <v>23.31</v>
       </c>
       <c r="J372" t="n">
-        <v>5.46</v>
+        <v>1.05</v>
       </c>
       <c r="K372" t="n">
-        <v>5.45</v>
+        <v>1.46</v>
       </c>
       <c r="L372" t="n">
-        <v>5.46</v>
+        <v>1.46</v>
       </c>
       <c r="M372" t="inlineStr">
         <is>
@@ -44271,72 +44439,72 @@
       </c>
       <c r="N372" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
       <c r="O372" t="n">
-        <v>-23.5191107</v>
+        <v>-23.5251114</v>
       </c>
       <c r="P372" t="n">
-        <v>-46.4146487</v>
+        <v>-46.3967997</v>
       </c>
       <c r="Q372" t="n">
-        <v>-23.5187039</v>
+        <v>-23.5251139</v>
       </c>
       <c r="R372" t="n">
-        <v>-46.4153284</v>
+        <v>-46.397028</v>
       </c>
     </row>
     <row r="373" hidden="1">
       <c r="A373" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>AVMD-011</t>
+          <t>MDC-006</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>PV-D14 - PV-D13</t>
+          <t>PI-5.12 - PV-5.11</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>PV-D14</t>
+          <t>PI-5.12</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>PV-D13</t>
+          <t>PV-5.11</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>PEAD</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="G373" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Método Não Destrutivo - MND</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I373" t="n">
-        <v>47.48</v>
+        <v>38.87</v>
       </c>
       <c r="J373" t="n">
-        <v>5.45</v>
+        <v>1.46</v>
       </c>
       <c r="K373" t="n">
-        <v>5.5</v>
+        <v>2.28</v>
       </c>
       <c r="L373" t="n">
-        <v>5.5</v>
+        <v>2.28</v>
       </c>
       <c r="M373" t="inlineStr">
         <is>
@@ -44345,72 +44513,72 @@
       </c>
       <c r="N373" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
       <c r="O373" t="n">
-        <v>-23.5187039</v>
+        <v>-23.5251139</v>
       </c>
       <c r="P373" t="n">
-        <v>-46.4153284</v>
+        <v>-46.397028</v>
       </c>
       <c r="Q373" t="n">
-        <v>-23.5183779</v>
+        <v>-23.5247642</v>
       </c>
       <c r="R373" t="n">
-        <v>-46.4156304</v>
+        <v>-46.3969956</v>
       </c>
     </row>
     <row r="374" hidden="1">
       <c r="A374" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>AVMD-012</t>
+          <t>MDC-007</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>PV-D13 - PV-D12</t>
+          <t>PV-5.11 - PV-5.10</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>PV-D13</t>
+          <t>PV-5.11</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>PV-D12</t>
+          <t>PV-5.10</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>PEAD</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="G374" t="n">
-        <v>450</v>
+        <v>200</v>
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Método Não Destrutivo - MND</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I374" t="n">
-        <v>36.2</v>
+        <v>14.84</v>
       </c>
       <c r="J374" t="n">
-        <v>5.5</v>
+        <v>2.28</v>
       </c>
       <c r="K374" t="n">
-        <v>5.5</v>
+        <v>2.72</v>
       </c>
       <c r="L374" t="n">
-        <v>5.5</v>
+        <v>2.72</v>
       </c>
       <c r="M374" t="inlineStr">
         <is>
@@ -44419,46 +44587,46 @@
       </c>
       <c r="N374" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
       <c r="O374" t="n">
-        <v>-23.5183779</v>
+        <v>-23.5247642</v>
       </c>
       <c r="P374" t="n">
-        <v>-46.4156304</v>
+        <v>-46.3969956</v>
       </c>
       <c r="Q374" t="n">
-        <v>-23.5180987</v>
+        <v>-23.5246986</v>
       </c>
       <c r="R374" t="n">
-        <v>-46.4158149</v>
+        <v>-46.3968688</v>
       </c>
     </row>
     <row r="375" hidden="1">
       <c r="A375" t="inlineStr">
         <is>
-          <t>agua_md</t>
+          <t>cts_mar_de_coral</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>AVMD-013</t>
+          <t>MDC-008</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>PV-D12 - PV-D10</t>
+          <t>PV-5.10 - PV-05</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>PV-D12</t>
+          <t>PV-5.10</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>PV-D10</t>
+          <t>PV-05</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
@@ -44467,7 +44635,7 @@
         </is>
       </c>
       <c r="G375" t="n">
-        <v>450</v>
+        <v>355</v>
       </c>
       <c r="H375" t="inlineStr">
         <is>
@@ -44475,16 +44643,16 @@
         </is>
       </c>
       <c r="I375" t="n">
-        <v>69.84999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="J375" t="n">
-        <v>5.55</v>
+        <v>2.76</v>
       </c>
       <c r="K375" t="n">
-        <v>5.5</v>
+        <v>5.24</v>
       </c>
       <c r="L375" t="n">
-        <v>5.55</v>
+        <v>5.24</v>
       </c>
       <c r="M375" t="inlineStr">
         <is>
@@ -44493,20 +44661,20 @@
       </c>
       <c r="N375" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
         </is>
       </c>
       <c r="O375" t="n">
-        <v>-23.5180987</v>
+        <v>-23.5246986</v>
       </c>
       <c r="P375" t="n">
-        <v>-46.4158149</v>
+        <v>-46.3968688</v>
       </c>
       <c r="Q375" t="n">
-        <v>-23.5175575</v>
+        <v>-23.5245404</v>
       </c>
       <c r="R375" t="n">
-        <v>-46.4161664</v>
+        <v>-46.3962347</v>
       </c>
     </row>
     <row r="376" hidden="1">
@@ -44517,22 +44685,22 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>AVMD-014</t>
+          <t>AVMD-001</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>PV-D10 - PV-D9</t>
+          <t>PVD-03 - PVD-02</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>PV-D10</t>
+          <t>PVD-03</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
         <is>
-          <t>PV-D9</t>
+          <t>PVD-02</t>
         </is>
       </c>
       <c r="F376" t="inlineStr">
@@ -44541,7 +44709,7 @@
         </is>
       </c>
       <c r="G376" t="n">
-        <v>450</v>
+        <v>355</v>
       </c>
       <c r="H376" t="inlineStr">
         <is>
@@ -44549,16 +44717,16 @@
         </is>
       </c>
       <c r="I376" t="n">
-        <v>34.04</v>
+        <v>53.99</v>
       </c>
       <c r="J376" t="n">
-        <v>5.5</v>
+        <v>4.88</v>
       </c>
       <c r="K376" t="n">
-        <v>5.48</v>
+        <v>4.57</v>
       </c>
       <c r="L376" t="n">
-        <v>5.5</v>
+        <v>4.88</v>
       </c>
       <c r="M376" t="inlineStr">
         <is>
@@ -44567,20 +44735,20 @@
       </c>
       <c r="N376" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; Cadastro Rede - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
       <c r="O376" t="n">
-        <v>-23.5175575</v>
+        <v>-23.5147632</v>
       </c>
       <c r="P376" t="n">
-        <v>-46.4161664</v>
+        <v>-46.4174463</v>
       </c>
       <c r="Q376" t="n">
-        <v>-23.5172967</v>
+        <v>-23.5143137</v>
       </c>
       <c r="R376" t="n">
-        <v>-46.4163427</v>
+        <v>-46.4176511</v>
       </c>
     </row>
     <row r="377" hidden="1">
@@ -44591,22 +44759,22 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>AVMD-015</t>
+          <t>AVMD-002</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>PV-D9 - PV-D07</t>
+          <t>PVD-04 - PVD-03</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>PV-D9</t>
+          <t>PVD-04</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>PV-D07</t>
+          <t>PVD-03</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
@@ -44615,7 +44783,7 @@
         </is>
       </c>
       <c r="G377" t="n">
-        <v>450</v>
+        <v>355</v>
       </c>
       <c r="H377" t="inlineStr">
         <is>
@@ -44623,16 +44791,16 @@
         </is>
       </c>
       <c r="I377" t="n">
-        <v>68.45999999999999</v>
+        <v>60.39</v>
       </c>
       <c r="J377" t="n">
-        <v>5.48</v>
+        <v>5.3</v>
       </c>
       <c r="K377" t="n">
-        <v>5.18</v>
+        <v>4.88</v>
       </c>
       <c r="L377" t="n">
-        <v>5.48</v>
+        <v>5.3</v>
       </c>
       <c r="M377" t="inlineStr">
         <is>
@@ -44641,20 +44809,20 @@
       </c>
       <c r="N377" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; Cadastro Rede - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
       <c r="O377" t="n">
-        <v>-23.5172967</v>
+        <v>-23.5152883</v>
       </c>
       <c r="P377" t="n">
-        <v>-46.4163427</v>
+        <v>-46.4172866</v>
       </c>
       <c r="Q377" t="n">
-        <v>-23.5167619</v>
+        <v>-23.5147632</v>
       </c>
       <c r="R377" t="n">
-        <v>-46.416679</v>
+        <v>-46.4174463</v>
       </c>
     </row>
     <row r="378" hidden="1">
@@ -44665,22 +44833,22 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>AVMD-016</t>
+          <t>AVMD-003</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>PV-D10.1 - PV-D10</t>
+          <t>PVD-05 - PVD-04</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>PV-D10.1</t>
+          <t>PVD-05</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>PV-D10</t>
+          <t>PVD-04</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
@@ -44689,7 +44857,7 @@
         </is>
       </c>
       <c r="G378" t="n">
-        <v>225</v>
+        <v>355</v>
       </c>
       <c r="H378" t="inlineStr">
         <is>
@@ -44697,16 +44865,16 @@
         </is>
       </c>
       <c r="I378" t="n">
-        <v>47.7</v>
+        <v>55.74</v>
       </c>
       <c r="J378" t="n">
-        <v>1.66</v>
+        <v>5.72</v>
       </c>
       <c r="K378" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L378" t="n">
-        <v>5.5</v>
+        <v>5.72</v>
       </c>
       <c r="M378" t="inlineStr">
         <is>
@@ -44715,20 +44883,20 @@
       </c>
       <c r="N378" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; Cadastro Rede - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
       <c r="O378" t="n">
-        <v>-23.5177629</v>
+        <v>-23.5157581</v>
       </c>
       <c r="P378" t="n">
-        <v>-46.416577</v>
+        <v>-46.4170907</v>
       </c>
       <c r="Q378" t="n">
-        <v>-23.5175575</v>
+        <v>-23.5152883</v>
       </c>
       <c r="R378" t="n">
-        <v>-46.4161664</v>
+        <v>-46.4172866</v>
       </c>
     </row>
     <row r="379" hidden="1">
@@ -44739,22 +44907,22 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>AVMD-017</t>
+          <t>AVMD-004</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>PI-D7.1 - PV-D07</t>
+          <t>PVD-02 - PVD-0</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>PI-D7.1</t>
+          <t>PVD-02</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>PV-D07</t>
+          <t>PVD-0</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
@@ -44763,7 +44931,7 @@
         </is>
       </c>
       <c r="G379" t="n">
-        <v>225</v>
+        <v>355</v>
       </c>
       <c r="H379" t="inlineStr">
         <is>
@@ -44771,16 +44939,16 @@
         </is>
       </c>
       <c r="I379" t="n">
-        <v>34.86</v>
+        <v>40.87</v>
       </c>
       <c r="J379" t="n">
-        <v>1.24</v>
+        <v>4.57</v>
       </c>
       <c r="K379" t="n">
-        <v>5.18</v>
+        <v>4.88</v>
       </c>
       <c r="L379" t="n">
-        <v>5.18</v>
+        <v>4.88</v>
       </c>
       <c r="M379" t="inlineStr">
         <is>
@@ -44789,20 +44957,20 @@
       </c>
       <c r="N379" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; Cadastro Rede - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
       <c r="O379" t="n">
-        <v>-23.5168893</v>
+        <v>-23.5143137</v>
       </c>
       <c r="P379" t="n">
-        <v>-46.4169912</v>
+        <v>-46.4176511</v>
       </c>
       <c r="Q379" t="n">
-        <v>-23.5167619</v>
+        <v>-23.5141947</v>
       </c>
       <c r="R379" t="n">
-        <v>-46.416679</v>
+        <v>-46.4180299</v>
       </c>
     </row>
     <row r="380" hidden="1">
@@ -44813,48 +44981,48 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>AVMD-018</t>
+          <t>AVMD-005</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>PV-D19.1 - PV-D19</t>
+          <t>PVD-06 - PVD-05</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>PV-D19.1</t>
+          <t>PVD-06</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
         <is>
-          <t>PV-D19</t>
+          <t>PVD-05</t>
         </is>
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD</t>
         </is>
       </c>
       <c r="G380" t="n">
-        <v>300</v>
+        <v>355</v>
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Método Não Destrutivo - MND</t>
         </is>
       </c>
       <c r="I380" t="n">
-        <v>3.04</v>
+        <v>51.4</v>
       </c>
       <c r="J380" t="n">
-        <v>1.09</v>
+        <v>5.65</v>
       </c>
       <c r="K380" t="n">
-        <v>3.23</v>
+        <v>5.72</v>
       </c>
       <c r="L380" t="n">
-        <v>3.23</v>
+        <v>5.72</v>
       </c>
       <c r="M380" t="inlineStr">
         <is>
@@ -44863,72 +45031,72 @@
       </c>
       <c r="N380" t="inlineStr">
         <is>
-          <t>Substituído pelo shape CTS Água Vermelha MD REV 01; atualizado pelo shape de 08/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; Cadastro Rede - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
       <c r="O380" t="n">
-        <v>-23.5200733</v>
+        <v>-23.5161942</v>
       </c>
       <c r="P380" t="n">
-        <v>-46.4154038</v>
+        <v>-46.4169097</v>
       </c>
       <c r="Q380" t="n">
-        <v>-23.5200479</v>
+        <v>-23.5157581</v>
       </c>
       <c r="R380" t="n">
-        <v>-46.4153913</v>
+        <v>-46.4170907</v>
       </c>
     </row>
     <row r="381" hidden="1">
       <c r="A381" t="inlineStr">
         <is>
-          <t>rce</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>FSM-001</t>
+          <t>AVMD-006</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>PI-4.3 - PI-4.2</t>
+          <t>PVD-07 - PVD-06</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>PI-4.3</t>
+          <t>PVD-07</t>
         </is>
       </c>
       <c r="E381" t="inlineStr">
         <is>
-          <t>PI-4.2</t>
+          <t>PVD-06</t>
         </is>
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD</t>
         </is>
       </c>
       <c r="G381" t="n">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Método Não Destrutivo - MND</t>
         </is>
       </c>
       <c r="I381" t="n">
-        <v>34.65</v>
+        <v>65.88</v>
       </c>
       <c r="J381" t="n">
-        <v>0.77</v>
+        <v>5.18</v>
       </c>
       <c r="K381" t="n">
-        <v>1.31</v>
+        <v>5.65</v>
       </c>
       <c r="L381" t="n">
-        <v>1.31</v>
+        <v>5.65</v>
       </c>
       <c r="M381" t="inlineStr">
         <is>
@@ -44937,72 +45105,72 @@
       </c>
       <c r="N381" t="inlineStr">
         <is>
-          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; Cadastro Rede - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
       <c r="O381" t="n">
-        <v>-23.523716</v>
+        <v>-23.5167619</v>
       </c>
       <c r="P381" t="n">
-        <v>-46.3856041</v>
+        <v>-46.416679</v>
       </c>
       <c r="Q381" t="n">
-        <v>-23.5237554</v>
+        <v>-23.5161942</v>
       </c>
       <c r="R381" t="n">
-        <v>-46.3859408</v>
+        <v>-46.4169097</v>
       </c>
     </row>
     <row r="382" hidden="1">
       <c r="A382" t="inlineStr">
         <is>
-          <t>rce</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>FSM-002</t>
+          <t>AVMD-007</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>PI-4.2 - PVE-4.1</t>
+          <t>PVD-07 - PVD-08</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>PI-4.2</t>
+          <t>PVD-07</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>PVE-4.1</t>
+          <t>PVD-08</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD</t>
         </is>
       </c>
       <c r="G382" t="n">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Método Não Destrutivo - MND</t>
         </is>
       </c>
       <c r="I382" t="n">
-        <v>63.91</v>
+        <v>32.99</v>
       </c>
       <c r="J382" t="n">
-        <v>1.31</v>
+        <v>5.3</v>
       </c>
       <c r="K382" t="n">
-        <v>3.05</v>
+        <v>5.45</v>
       </c>
       <c r="L382" t="n">
-        <v>3.05</v>
+        <v>5.46</v>
       </c>
       <c r="M382" t="inlineStr">
         <is>
@@ -45011,72 +45179,72 @@
       </c>
       <c r="N382" t="inlineStr">
         <is>
-          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
+          <t>07.CT AGUA VERMELHA MD_PVD-07 AO PVD-08.pdf</t>
         </is>
       </c>
       <c r="O382" t="n">
-        <v>-23.5237554</v>
+        <v>-23.5167619</v>
       </c>
       <c r="P382" t="n">
-        <v>-46.3859408</v>
+        <v>-46.416679</v>
       </c>
       <c r="Q382" t="n">
-        <v>-23.5235762</v>
+        <v>-23.5170236</v>
       </c>
       <c r="R382" t="n">
-        <v>-46.3865357</v>
+        <v>-46.4165246</v>
       </c>
     </row>
     <row r="383" hidden="1">
       <c r="A383" t="inlineStr">
         <is>
-          <t>rce</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>FSM-003</t>
+          <t>AVMD-008</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>PI-4.4 - PI-4.5</t>
+          <t>PVD-08 - PVD-09</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>PI-4.4</t>
+          <t>PVD-08</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>PI-4.5</t>
+          <t>PVD-09</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD</t>
         </is>
       </c>
       <c r="G383" t="n">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Método Não Destrutivo - MND</t>
         </is>
       </c>
       <c r="I383" t="n">
-        <v>32.29</v>
+        <v>35.48</v>
       </c>
       <c r="J383" t="n">
-        <v>1.15</v>
+        <v>5.45</v>
       </c>
       <c r="K383" t="n">
-        <v>1.23</v>
+        <v>5.5</v>
       </c>
       <c r="L383" t="n">
-        <v>1.23</v>
+        <v>5.55</v>
       </c>
       <c r="M383" t="inlineStr">
         <is>
@@ -45085,72 +45253,72 @@
       </c>
       <c r="N383" t="inlineStr">
         <is>
-          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
+          <t>08.CT AGUA VERMELHA MD_PVD-08 AO PVD-09.pdf</t>
         </is>
       </c>
       <c r="O383" t="n">
-        <v>-23.5237085</v>
+        <v>-23.5170236</v>
       </c>
       <c r="P383" t="n">
-        <v>-46.3855499</v>
+        <v>-46.4165246</v>
       </c>
       <c r="Q383" t="n">
-        <v>-23.5234978</v>
+        <v>-23.5172967</v>
       </c>
       <c r="R383" t="n">
-        <v>-46.3853313</v>
+        <v>-46.4163427</v>
       </c>
     </row>
     <row r="384" hidden="1">
       <c r="A384" t="inlineStr">
         <is>
-          <t>rce</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>FSM-004</t>
+          <t>AVMD-009</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>PI-4.5 - PV-4.6</t>
+          <t>PVD-10 - PVD-9</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>PI-4.5</t>
+          <t>PVD-10</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
         <is>
-          <t>PV-4.6</t>
+          <t>PVD-9</t>
         </is>
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD</t>
         </is>
       </c>
       <c r="G384" t="n">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Método Não Destrutivo - MND</t>
         </is>
       </c>
       <c r="I384" t="n">
-        <v>25.58</v>
+        <v>34.04</v>
       </c>
       <c r="J384" t="n">
-        <v>1.23</v>
+        <v>5.5</v>
       </c>
       <c r="K384" t="n">
-        <v>1.6</v>
+        <v>5.48</v>
       </c>
       <c r="L384" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="M384" t="inlineStr">
         <is>
@@ -45159,72 +45327,72 @@
       </c>
       <c r="N384" t="inlineStr">
         <is>
-          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; Cadastro Rede - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
       <c r="O384" t="n">
-        <v>-23.5234978</v>
+        <v>-23.5175575</v>
       </c>
       <c r="P384" t="n">
-        <v>-46.3853313</v>
+        <v>-46.4161664</v>
       </c>
       <c r="Q384" t="n">
-        <v>-23.5232957</v>
+        <v>-23.5172967</v>
       </c>
       <c r="R384" t="n">
-        <v>-46.3852099</v>
+        <v>-46.4163427</v>
       </c>
     </row>
     <row r="385" hidden="1">
       <c r="A385" t="inlineStr">
         <is>
-          <t>rce</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>FSM-005</t>
+          <t>AVMD-010</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>PV-4.6 - PIE-12</t>
+          <t>PVD-10 - PVD-11</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>PV-4.6</t>
+          <t>PVD-10</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
         <is>
-          <t>PIE-12</t>
+          <t>PVD-11</t>
         </is>
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD</t>
         </is>
       </c>
       <c r="G385" t="n">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Método Não Destrutivo - MND</t>
         </is>
       </c>
       <c r="I385" t="n">
-        <v>11.34</v>
+        <v>34.1</v>
       </c>
       <c r="J385" t="n">
-        <v>1.6</v>
+        <v>5.4</v>
       </c>
       <c r="K385" t="n">
-        <v>1.04</v>
+        <v>5.3</v>
       </c>
       <c r="L385" t="n">
-        <v>1.6</v>
+        <v>5.41</v>
       </c>
       <c r="M385" t="inlineStr">
         <is>
@@ -45233,72 +45401,72 @@
       </c>
       <c r="N385" t="inlineStr">
         <is>
-          <t>Conferido pelo pacote RCE Soutomaior Trecho II; atualizado pelo shape de 04/05/2026</t>
+          <t>10.CT AGUA VERMELHA MD_PVD-10 AO PVD-11.pdf</t>
         </is>
       </c>
       <c r="O385" t="n">
-        <v>-23.5232957</v>
+        <v>-23.5175596</v>
       </c>
       <c r="P385" t="n">
-        <v>-46.3852099</v>
+        <v>-46.4161695</v>
       </c>
       <c r="Q385" t="n">
-        <v>-23.5232865</v>
+        <v>-23.517822</v>
       </c>
       <c r="R385" t="n">
-        <v>-46.3850993</v>
+        <v>-46.4159948</v>
       </c>
     </row>
     <row r="386" hidden="1">
       <c r="A386" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>MDC-001</t>
+          <t>AVMD-011</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>PV-5.14 - PV-5.15</t>
+          <t>PVD-11 - PVD-12</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>PV-5.14</t>
+          <t>PVD-11</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>PV-5.15</t>
+          <t>PVD-12</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD</t>
         </is>
       </c>
       <c r="G386" t="n">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Método Não Destrutivo - MND</t>
         </is>
       </c>
       <c r="I386" t="n">
-        <v>8.81</v>
+        <v>35.72</v>
       </c>
       <c r="J386" t="n">
-        <v>2.66</v>
+        <v>5.3</v>
       </c>
       <c r="K386" t="n">
-        <v>3.27</v>
+        <v>5.77</v>
       </c>
       <c r="L386" t="n">
-        <v>3.27</v>
+        <v>5.77</v>
       </c>
       <c r="M386" t="inlineStr">
         <is>
@@ -45307,46 +45475,46 @@
       </c>
       <c r="N386" t="inlineStr">
         <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+          <t>10.CT AGUA VERMELHA MD_PVD-11 AO PVD-12.pdf</t>
         </is>
       </c>
       <c r="O386" t="n">
-        <v>-23.526254</v>
+        <v>-23.517822</v>
       </c>
       <c r="P386" t="n">
-        <v>-46.3958686</v>
+        <v>-46.4159948</v>
       </c>
       <c r="Q386" t="n">
-        <v>-23.5262782</v>
+        <v>-23.5180987</v>
       </c>
       <c r="R386" t="n">
-        <v>-46.3959507</v>
+        <v>-46.4158149</v>
       </c>
     </row>
     <row r="387" hidden="1">
       <c r="A387" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>MDC-002</t>
+          <t>AVMD-012</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>PV-5.15 - PV-5.16</t>
+          <t>PVD-13 - PVD-12</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>PV-5.15</t>
+          <t>PVD-13</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>PV-5.16</t>
+          <t>PVD-12</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
@@ -45363,16 +45531,16 @@
         </is>
       </c>
       <c r="I387" t="n">
-        <v>9.279999999999999</v>
+        <v>36.2</v>
       </c>
       <c r="J387" t="n">
-        <v>3.34</v>
+        <v>5.5</v>
       </c>
       <c r="K387" t="n">
-        <v>3.41</v>
+        <v>5.5</v>
       </c>
       <c r="L387" t="n">
-        <v>3.41</v>
+        <v>5.5</v>
       </c>
       <c r="M387" t="inlineStr">
         <is>
@@ -45381,46 +45549,46 @@
       </c>
       <c r="N387" t="inlineStr">
         <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; Cadastro Rede - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
       <c r="O387" t="n">
-        <v>-23.5262782</v>
+        <v>-23.5183779</v>
       </c>
       <c r="P387" t="n">
-        <v>-46.3959507</v>
+        <v>-46.4156304</v>
       </c>
       <c r="Q387" t="n">
-        <v>-23.5263146</v>
+        <v>-23.5180987</v>
       </c>
       <c r="R387" t="n">
-        <v>-46.3960326</v>
+        <v>-46.4158149</v>
       </c>
     </row>
     <row r="388" hidden="1">
       <c r="A388" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>MDC-003</t>
+          <t>AVMD-013</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>PV-5.16 - PV-5.17</t>
+          <t>PVD-14 - PVD-13</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>PV-5.16</t>
+          <t>PVD-14</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>PV-5.17</t>
+          <t>PVD-13</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -45437,16 +45605,16 @@
         </is>
       </c>
       <c r="I388" t="n">
-        <v>58.75</v>
+        <v>47.48</v>
       </c>
       <c r="J388" t="n">
-        <v>3.41</v>
+        <v>5.45</v>
       </c>
       <c r="K388" t="n">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="L388" t="n">
-        <v>3.41</v>
+        <v>5.5</v>
       </c>
       <c r="M388" t="inlineStr">
         <is>
@@ -45455,46 +45623,46 @@
       </c>
       <c r="N388" t="inlineStr">
         <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; Cadastro Rede - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
       <c r="O388" t="n">
-        <v>-23.5263146</v>
+        <v>-23.5187039</v>
       </c>
       <c r="P388" t="n">
-        <v>-46.3960326</v>
+        <v>-46.4153284</v>
       </c>
       <c r="Q388" t="n">
-        <v>-23.5260174</v>
+        <v>-23.5183779</v>
       </c>
       <c r="R388" t="n">
-        <v>-46.3965092</v>
+        <v>-46.4156304</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>MDC-004</t>
+          <t>AVMD-014</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>PV-5.17 - PVE-43</t>
+          <t>PVD-16 - PVD-14</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>PV-5.17</t>
+          <t>PVD-16</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>PVE-43</t>
+          <t>PVD-14</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -45511,16 +45679,16 @@
         </is>
       </c>
       <c r="I389" t="n">
-        <v>2.21</v>
+        <v>82.75</v>
       </c>
       <c r="J389" t="n">
-        <v>3.4</v>
+        <v>5.46</v>
       </c>
       <c r="K389" t="n">
-        <v>3.42</v>
+        <v>5.45</v>
       </c>
       <c r="L389" t="n">
-        <v>3.42</v>
+        <v>5.46</v>
       </c>
       <c r="M389" t="inlineStr">
         <is>
@@ -45529,72 +45697,72 @@
       </c>
       <c r="N389" t="inlineStr">
         <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; Cadastro Rede - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
       <c r="O389" t="n">
-        <v>-23.5260174</v>
+        <v>-23.5191107</v>
       </c>
       <c r="P389" t="n">
-        <v>-46.3965092</v>
+        <v>-46.4146487</v>
       </c>
       <c r="Q389" t="n">
-        <v>-23.5260163</v>
+        <v>-23.5187039</v>
       </c>
       <c r="R389" t="n">
-        <v>-46.3965309</v>
+        <v>-46.4153284</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>MDC-005</t>
+          <t>AVMD-015</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>PI-5.13 - PI-5.12</t>
+          <t>PVD-17 - PVD-16</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>PI-5.13</t>
+          <t>PVD-17</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>PI-5.12</t>
+          <t>PVD-16</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD</t>
         </is>
       </c>
       <c r="G390" t="n">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Método Não Destrutivo - MND</t>
         </is>
       </c>
       <c r="I390" t="n">
-        <v>23.31</v>
+        <v>64.95</v>
       </c>
       <c r="J390" t="n">
-        <v>1.05</v>
+        <v>4.75</v>
       </c>
       <c r="K390" t="n">
-        <v>1.46</v>
+        <v>5.46</v>
       </c>
       <c r="L390" t="n">
-        <v>1.46</v>
+        <v>5.46</v>
       </c>
       <c r="M390" t="inlineStr">
         <is>
@@ -45603,72 +45771,72 @@
       </c>
       <c r="N390" t="inlineStr">
         <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+          <t>Atualizado via shape em 04/05/2026; Cadastro Rede - CT ÁGUA VERMELHA - MD</t>
         </is>
       </c>
       <c r="O390" t="n">
-        <v>-23.5251114</v>
+        <v>-23.5195653</v>
       </c>
       <c r="P390" t="n">
-        <v>-46.3967997</v>
+        <v>-46.4150506</v>
       </c>
       <c r="Q390" t="n">
-        <v>-23.5251139</v>
+        <v>-23.5191107</v>
       </c>
       <c r="R390" t="n">
-        <v>-46.397028</v>
+        <v>-46.4146487</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>MDC-006</t>
+          <t>AVMD-016</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>PI-5.12 - PV-5.11</t>
+          <t>PVD-17 - PVD-18</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>PI-5.12</t>
+          <t>PVD-17</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
         <is>
-          <t>PV-5.11</t>
+          <t>PVD-18</t>
         </is>
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD</t>
         </is>
       </c>
       <c r="G391" t="n">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Método Não Destrutivo - MND</t>
         </is>
       </c>
       <c r="I391" t="n">
-        <v>38.87</v>
+        <v>20.35</v>
       </c>
       <c r="J391" t="n">
-        <v>1.46</v>
+        <v>4.75</v>
       </c>
       <c r="K391" t="n">
-        <v>2.28</v>
+        <v>4.15</v>
       </c>
       <c r="L391" t="n">
-        <v>2.28</v>
+        <v>4.75</v>
       </c>
       <c r="M391" t="inlineStr">
         <is>
@@ -45677,72 +45845,72 @@
       </c>
       <c r="N391" t="inlineStr">
         <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+          <t>12.CT AGUA VERMELHA MD_PVD-17 AO PVD-18.pdf</t>
         </is>
       </c>
       <c r="O391" t="n">
-        <v>-23.5251139</v>
+        <v>-23.5195629</v>
       </c>
       <c r="P391" t="n">
-        <v>-46.397028</v>
+        <v>-46.4150489</v>
       </c>
       <c r="Q391" t="n">
-        <v>-23.5247642</v>
+        <v>-23.5197067</v>
       </c>
       <c r="R391" t="n">
-        <v>-46.3969956</v>
+        <v>-46.4151731</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>MDC-007</t>
+          <t>AVMD-017</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>PV-5.11 - PV-5.10</t>
+          <t>PVD-18 - PVD-19</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>PV-5.11</t>
+          <t>PVD-18</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>PV-5.10</t>
+          <t>PVD-19</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD</t>
         </is>
       </c>
       <c r="G392" t="n">
-        <v>200</v>
+        <v>450</v>
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Método Não Destrutivo - MND</t>
         </is>
       </c>
       <c r="I392" t="n">
-        <v>14.84</v>
+        <v>43.87</v>
       </c>
       <c r="J392" t="n">
-        <v>2.28</v>
+        <v>4.2</v>
       </c>
       <c r="K392" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="L392" t="n">
-        <v>2.72</v>
+        <v>4.2</v>
       </c>
       <c r="M392" t="inlineStr">
         <is>
@@ -45751,46 +45919,46 @@
       </c>
       <c r="N392" t="inlineStr">
         <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
+          <t>12.CT AGUA VERMELHA MD_PVD-18 AO PVD-19.pdf</t>
         </is>
       </c>
       <c r="O392" t="n">
-        <v>-23.5247642</v>
+        <v>-23.5197067</v>
       </c>
       <c r="P392" t="n">
-        <v>-46.3969956</v>
+        <v>-46.4151731</v>
       </c>
       <c r="Q392" t="n">
-        <v>-23.5246986</v>
+        <v>-23.5200465</v>
       </c>
       <c r="R392" t="n">
-        <v>-46.3968688</v>
+        <v>-46.4153941</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>cts_mar_de_coral</t>
+          <t>agua_md</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>MDC-008</t>
+          <t>AVMD-018</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>PV-5.10 - PV-05</t>
+          <t>PVD-07 - PI-D7.3</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>PV-5.10</t>
+          <t>PVD-07</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>PV-05</t>
+          <t>PI-D7.3</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
@@ -45799,46 +45967,638 @@
         </is>
       </c>
       <c r="G393" t="n">
+        <v>225</v>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>Método Não Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I393" t="n">
+        <v>56.06</v>
+      </c>
+      <c r="J393" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K393" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L393" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>concluída</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>13.CT AGUA VERMELHA MD_PVD-07 AO PI-D07.3.pdf</t>
+        </is>
+      </c>
+      <c r="O393" t="n">
+        <v>-23.5167619</v>
+      </c>
+      <c r="P393" t="n">
+        <v>-46.416679</v>
+      </c>
+      <c r="Q393" t="n">
+        <v>-23.5169806</v>
+      </c>
+      <c r="R393" t="n">
+        <v>-46.4171725</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>agua_md</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>AVMD-019</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>PVD-10 - PV-D10.1</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>PVD-10</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>PV-D10.1</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>PEAD</t>
+        </is>
+      </c>
+      <c r="G394" t="n">
+        <v>225</v>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>Método Não Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I394" t="n">
+        <v>28.69</v>
+      </c>
+      <c r="J394" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K394" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L394" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>concluída</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>FL.19.CT AGUA VERMELHA MD_PVD-10 AO PVD-10.1.pdf</t>
+        </is>
+      </c>
+      <c r="O394" t="n">
+        <v>-23.5175596</v>
+      </c>
+      <c r="P394" t="n">
+        <v>-46.4161695</v>
+      </c>
+      <c r="Q394" t="n">
+        <v>-23.5176744</v>
+      </c>
+      <c r="R394" t="n">
+        <v>-46.4164241</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>agua_md</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>AVMD-020</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>PV-D10.1 - PID-10.2</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>PV-D10.1</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>PID-10.2</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>PEAD</t>
+        </is>
+      </c>
+      <c r="G395" t="n">
+        <v>225</v>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>Método Não Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I395" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="J395" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K395" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L395" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>concluída</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>FL.20.CT AGUA VERMELHA MD_PVD-10.1 AO PID-10.2.pdf</t>
+        </is>
+      </c>
+      <c r="O395" t="n">
+        <v>-23.5176744</v>
+      </c>
+      <c r="P395" t="n">
+        <v>-46.4164241</v>
+      </c>
+      <c r="Q395" t="n">
+        <v>-23.517768</v>
+      </c>
+      <c r="R395" t="n">
+        <v>-46.4165888</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>agua_md</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>AVMD-021</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>PVD-13 - PVD-13.1</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>PVD-13</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>PVD-13.1</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>PEAD</t>
+        </is>
+      </c>
+      <c r="G396" t="n">
+        <v>225</v>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>Método Não Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I396" t="n">
+        <v>27.71</v>
+      </c>
+      <c r="J396" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K396" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L396" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>concluída</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>FL.21.CT AGUA VERMELHA MD_PVD-13 AO PVD-13.1.pdf</t>
+        </is>
+      </c>
+      <c r="O396" t="n">
+        <v>-23.5183638</v>
+      </c>
+      <c r="P396" t="n">
+        <v>-46.4156391</v>
+      </c>
+      <c r="Q396" t="n">
+        <v>-23.5184887</v>
+      </c>
+      <c r="R396" t="n">
+        <v>-46.4158784</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>agua_md</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>AVMD-022</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>PVD-06 - PVD-06.1</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>PVD-06</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>PVD-06.1</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>PEAD</t>
+        </is>
+      </c>
+      <c r="G397" t="n">
+        <v>225</v>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>Método Não Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I397" t="n">
+        <v>34.29</v>
+      </c>
+      <c r="J397" t="n">
+        <v>3</v>
+      </c>
+      <c r="K397" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L397" t="n">
+        <v>3</v>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>concluída</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>FL.22.CT AGUA VERMELHA MD_PVD-06 AO PVD-06.1.pdf</t>
+        </is>
+      </c>
+      <c r="O397" t="n">
+        <v>-23.5161952</v>
+      </c>
+      <c r="P397" t="n">
+        <v>-46.4169114</v>
+      </c>
+      <c r="Q397" t="n">
+        <v>-23.5163277</v>
+      </c>
+      <c r="R397" t="n">
+        <v>-46.417215</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>agua_md</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>AVMD-023</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>PVE-2.1 - PVD-02</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>PVE-2.1</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>PVD-02</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G398" t="n">
+        <v>200</v>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>Vala a Céu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I398" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="J398" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="K398" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="L398" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>concluída</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>Atualizado via shape em 04/05/2026; Cadastro Rede - CT ÁGUA VERMELHA - MD</t>
+        </is>
+      </c>
+      <c r="O398" t="n">
+        <v>-23.5141683</v>
+      </c>
+      <c r="P398" t="n">
+        <v>-46.4175373</v>
+      </c>
+      <c r="Q398" t="n">
+        <v>-23.5143137</v>
+      </c>
+      <c r="R398" t="n">
+        <v>-46.4176511</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>agua_md</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>AVMD-024</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>PVD-19 - PVD-17</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>PVD-19</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>PVD-17</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>PEAD</t>
+        </is>
+      </c>
+      <c r="G399" t="n">
         <v>355</v>
       </c>
-      <c r="H393" t="inlineStr">
+      <c r="H399" t="inlineStr">
         <is>
           <t>Método Não Destrutivo - MND</t>
         </is>
       </c>
-      <c r="I393" t="n">
-        <v>67.06999999999999</v>
-      </c>
-      <c r="J393" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="K393" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="L393" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="M393" t="inlineStr">
+      <c r="I399" t="n">
+        <v>63.83</v>
+      </c>
+      <c r="J399" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="K399" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L399" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="M399" t="inlineStr">
         <is>
           <t>concluída</t>
         </is>
       </c>
-      <c r="N393" t="inlineStr">
-        <is>
-          <t>Atualizado pelo trecho PV-05 ao PV-05.13; atualizado pelo shape de 14/05/2026</t>
-        </is>
-      </c>
-      <c r="O393" t="n">
-        <v>-23.5246986</v>
-      </c>
-      <c r="P393" t="n">
-        <v>-46.3968688</v>
-      </c>
-      <c r="Q393" t="n">
-        <v>-23.5245404</v>
-      </c>
-      <c r="R393" t="n">
-        <v>-46.3962347</v>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>Atualizado via shape em 04/05/2026; Cadastro Rede - CT ÁGUA VERMELHA - MD</t>
+        </is>
+      </c>
+      <c r="O399" t="n">
+        <v>-23.520048</v>
+      </c>
+      <c r="P399" t="n">
+        <v>-46.4153923</v>
+      </c>
+      <c r="Q399" t="n">
+        <v>-23.5195653</v>
+      </c>
+      <c r="R399" t="n">
+        <v>-46.4150506</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>agua_md</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>AVMD-025</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>PVD-12 - PVD-10</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>PVD-12</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>PVD-10</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>PEAD</t>
+        </is>
+      </c>
+      <c r="G400" t="n">
+        <v>355</v>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>Método Não Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I400" t="n">
+        <v>69.84999999999999</v>
+      </c>
+      <c r="J400" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="K400" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L400" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="M400" t="inlineStr">
+        <is>
+          <t>concluída</t>
+        </is>
+      </c>
+      <c r="N400" t="inlineStr">
+        <is>
+          <t>Atualizado via shape em 04/05/2026; Cadastro Rede - CT ÁGUA VERMELHA - MD</t>
+        </is>
+      </c>
+      <c r="O400" t="n">
+        <v>-23.5180987</v>
+      </c>
+      <c r="P400" t="n">
+        <v>-46.4158149</v>
+      </c>
+      <c r="Q400" t="n">
+        <v>-23.5175575</v>
+      </c>
+      <c r="R400" t="n">
+        <v>-46.4161664</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>agua_md</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>AVMD-026</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>PVD-9 - PVD-07</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>PVD-9</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>PVD-07</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>PEAD</t>
+        </is>
+      </c>
+      <c r="G401" t="n">
+        <v>355</v>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>Método Não Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I401" t="n">
+        <v>68.45999999999999</v>
+      </c>
+      <c r="J401" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="K401" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="L401" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="M401" t="inlineStr">
+        <is>
+          <t>concluída</t>
+        </is>
+      </c>
+      <c r="N401" t="inlineStr">
+        <is>
+          <t>Atualizado via shape em 04/05/2026; Cadastro Rede - CT ÁGUA VERMELHA - MD</t>
+        </is>
+      </c>
+      <c r="O401" t="n">
+        <v>-23.5172967</v>
+      </c>
+      <c r="P401" t="n">
+        <v>-46.4163427</v>
+      </c>
+      <c r="Q401" t="n">
+        <v>-23.5167619</v>
+      </c>
+      <c r="R401" t="n">
+        <v>-46.416679</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -1200,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L381"/>
+  <dimension ref="A1:L383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -18385,6 +18385,102 @@
       <c r="L381" t="inlineStr">
         <is>
           <t>Atualizado via shape em 04/05/2026; CADASTRO PV - CT ÁGUA VERMELHA - MD</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>JC-PV-09</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>PV-09</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>7396914.814</v>
+      </c>
+      <c r="F382" t="n">
+        <v>358382.74</v>
+      </c>
+      <c r="G382" t="n">
+        <v>-23.5318788</v>
+      </c>
+      <c r="H382" t="n">
+        <v>-46.3872832</v>
+      </c>
+      <c r="I382" t="n">
+        <v>768.775</v>
+      </c>
+      <c r="J382" t="n">
+        <v>766.275</v>
+      </c>
+      <c r="K382" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L382" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-03/FL-04 versao 01, 11.MAI.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>JC-PV-10</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>PV-10</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>7396932.164</v>
+      </c>
+      <c r="F383" t="n">
+        <v>358437.094</v>
+      </c>
+      <c r="G383" t="n">
+        <v>-23.5317269</v>
+      </c>
+      <c r="H383" t="n">
+        <v>-46.3867492</v>
+      </c>
+      <c r="I383" t="n">
+        <v>770.008</v>
+      </c>
+      <c r="J383" t="n">
+        <v>767.008</v>
+      </c>
+      <c r="K383" t="n">
+        <v>3</v>
+      </c>
+      <c r="L383" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-04 versao 01, 11.MAI.2026</t>
         </is>
       </c>
     </row>
@@ -18399,7 +18495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R401"/>
+  <dimension ref="A1:R403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -46599,6 +46695,154 @@
       </c>
       <c r="R401" t="n">
         <v>-46.416679</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>JC-003</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>PV-08 - PV-09</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>PV-08</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>PV-09</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G402" t="n">
+        <v>355</v>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I402" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="J402" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K402" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L402" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="M402" t="inlineStr">
+        <is>
+          <t>em planejamento</t>
+        </is>
+      </c>
+      <c r="N402" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-03 versao 01, 11.MAI.2026; GALPAO INTERNO RUA GENI GOMES; taxa 0,0311.</t>
+        </is>
+      </c>
+      <c r="O402" t="n">
+        <v>-23.5320183</v>
+      </c>
+      <c r="P402" t="n">
+        <v>-46.3877736</v>
+      </c>
+      <c r="Q402" t="n">
+        <v>-23.5318788</v>
+      </c>
+      <c r="R402" t="n">
+        <v>-46.3872832</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>JC-004</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>PV-09 - PV-10</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>PV-09</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>PV-10</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G403" t="n">
+        <v>355</v>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I403" t="n">
+        <v>56.92</v>
+      </c>
+      <c r="J403" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K403" t="n">
+        <v>3</v>
+      </c>
+      <c r="L403" t="n">
+        <v>3</v>
+      </c>
+      <c r="M403" t="inlineStr">
+        <is>
+          <t>em planejamento</t>
+        </is>
+      </c>
+      <c r="N403" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-04 versao 01, 11.MAI.2026; GALPAO INTERNO RUA GENI GOMES; taxa 0,0129.</t>
+        </is>
+      </c>
+      <c r="O403" t="n">
+        <v>-23.5318788</v>
+      </c>
+      <c r="P403" t="n">
+        <v>-46.3872832</v>
+      </c>
+      <c r="Q403" t="n">
+        <v>-23.5317269</v>
+      </c>
+      <c r="R403" t="n">
+        <v>-46.3867492</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -588,7 +588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="31.109375" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1184,6 +1184,33 @@
         </is>
       </c>
       <c r="E22" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cts_lourdes_complementar</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>CTS Lourdes Complementar</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CTS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Base criada a partir do plano de furo CT LOURDES FL-01 PV-01 ao PV-02, 14.MAI.2026.</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1200,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L383"/>
+  <dimension ref="A1:L386"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -18481,6 +18508,150 @@
       <c r="L383" t="inlineStr">
         <is>
           <t>Plano de furo FL-04 versao 01, 11.MAI.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>cts_lourdes_complementar</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>LOUR-PV-01</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>PV-01</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>7397151.558</v>
+      </c>
+      <c r="F384" t="n">
+        <v>357586.89</v>
+      </c>
+      <c r="G384" t="n">
+        <v>-23.5296713</v>
+      </c>
+      <c r="H384" t="n">
+        <v>-46.395055</v>
+      </c>
+      <c r="I384" t="n">
+        <v>754.7190000000001</v>
+      </c>
+      <c r="J384" t="n">
+        <v>751.2190000000001</v>
+      </c>
+      <c r="K384" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L384" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-01 versao 01, 14.MAI.2026; ALARGADOR 700mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>cts_lourdes_complementar</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>LOUR-PV-02</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>PV-02</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>7397168.003</v>
+      </c>
+      <c r="F385" t="n">
+        <v>357669.586</v>
+      </c>
+      <c r="G385" t="n">
+        <v>-23.52953</v>
+      </c>
+      <c r="H385" t="n">
+        <v>-46.3942436</v>
+      </c>
+      <c r="I385" t="n">
+        <v>756.086</v>
+      </c>
+      <c r="J385" t="n">
+        <v>752.086</v>
+      </c>
+      <c r="K385" t="n">
+        <v>4</v>
+      </c>
+      <c r="L385" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-01 versao 01, 14.MAI.2026; ALARGADOR 700mm.</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>JC-PV-02</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>PV-02</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>7396941.756</v>
+      </c>
+      <c r="F386" t="n">
+        <v>358324.032</v>
+      </c>
+      <c r="G386" t="n">
+        <v>-23.5316304</v>
+      </c>
+      <c r="H386" t="n">
+        <v>-46.3878556</v>
+      </c>
+      <c r="I386" t="n">
+        <v>767.318</v>
+      </c>
+      <c r="J386" t="n">
+        <v>763.468</v>
+      </c>
+      <c r="K386" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L386" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-06 versao 01, 15.MAI.2026; RUA ELVIRA DE ARAUJO.</t>
         </is>
       </c>
     </row>
@@ -18495,7 +18666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R403"/>
+  <dimension ref="A1:R405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -46843,6 +47014,154 @@
       </c>
       <c r="R403" t="n">
         <v>-46.3867492</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>cts_lourdes_complementar</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>LOUR-001</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>PV-01 - PV-02</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>PV-01</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>PV-02</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G404" t="n">
+        <v>450</v>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I404" t="n">
+        <v>84.31999999999999</v>
+      </c>
+      <c r="J404" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K404" t="n">
+        <v>4</v>
+      </c>
+      <c r="L404" t="n">
+        <v>4</v>
+      </c>
+      <c r="M404" t="inlineStr">
+        <is>
+          <t>em planejamento</t>
+        </is>
+      </c>
+      <c r="N404" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-01 versao 01, 14.MAI.2026; RUA GONCALVES CASTELAO; ALARGADOR 700mm; taxa 0,0103.</t>
+        </is>
+      </c>
+      <c r="O404" t="n">
+        <v>-23.5296713</v>
+      </c>
+      <c r="P404" t="n">
+        <v>-46.395055</v>
+      </c>
+      <c r="Q404" t="n">
+        <v>-23.52953</v>
+      </c>
+      <c r="R404" t="n">
+        <v>-46.3942436</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>JC-005</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>PV-08 - PV-02</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>PV-08</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>PV-02</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G405" t="n">
+        <v>355</v>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I405" t="n">
+        <v>43.66</v>
+      </c>
+      <c r="J405" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="K405" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L405" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="M405" t="inlineStr">
+        <is>
+          <t>em planejamento</t>
+        </is>
+      </c>
+      <c r="N405" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-06 versao 01, 15.MAI.2026; RUA ELVIRA DE ARAUJO; taxa 0,0108.</t>
+        </is>
+      </c>
+      <c r="O405" t="n">
+        <v>-23.5320183</v>
+      </c>
+      <c r="P405" t="n">
+        <v>-46.3877736</v>
+      </c>
+      <c r="Q405" t="n">
+        <v>-23.5316304</v>
+      </c>
+      <c r="R405" t="n">
+        <v>-46.3878556</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L386"/>
+  <dimension ref="A1:L388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -18652,6 +18652,102 @@
       <c r="L386" t="inlineStr">
         <is>
           <t>Plano de furo FL-06 versao 01, 15.MAI.2026; RUA ELVIRA DE ARAUJO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>JC-PV-11</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>PV-11</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>7396951.048</v>
+      </c>
+      <c r="F387" t="n">
+        <v>358496.854</v>
+      </c>
+      <c r="G387" t="n">
+        <v>-23.5315615</v>
+      </c>
+      <c r="H387" t="n">
+        <v>-46.3861622</v>
+      </c>
+      <c r="I387" t="n">
+        <v>774.981</v>
+      </c>
+      <c r="J387" t="n">
+        <v>768.881</v>
+      </c>
+      <c r="K387" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="L387" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; trecho PV-11 ao PV-13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>JC-PV-13</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>PV-13</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>7397011.057</v>
+      </c>
+      <c r="F388" t="n">
+        <v>358478.68</v>
+      </c>
+      <c r="G388" t="n">
+        <v>-23.5310181</v>
+      </c>
+      <c r="H388" t="n">
+        <v>-46.3863345</v>
+      </c>
+      <c r="I388" t="n">
+        <v>771.8630000000001</v>
+      </c>
+      <c r="J388" t="n">
+        <v>769.8630000000001</v>
+      </c>
+      <c r="K388" t="n">
+        <v>2</v>
+      </c>
+      <c r="L388" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; trecho PV-11 ao PV-13.</t>
         </is>
       </c>
     </row>
@@ -18666,7 +18762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R405"/>
+  <dimension ref="A1:R406"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -47162,6 +47258,80 @@
       </c>
       <c r="R405" t="n">
         <v>-46.3878556</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>JC-006</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>PV-11 - PV-13</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>PV-11</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>PV-13</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G406" t="n">
+        <v>355</v>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I406" t="n">
+        <v>62.701</v>
+      </c>
+      <c r="J406" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K406" t="n">
+        <v>2</v>
+      </c>
+      <c r="L406" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="M406" t="inlineStr">
+        <is>
+          <t>concluída</t>
+        </is>
+      </c>
+      <c r="N406" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; PV-11 ao PV-13; arquivo: planos_furo/cts_joao_canzi_fl07_pv11_pv13.pdf.</t>
+        </is>
+      </c>
+      <c r="O406" t="n">
+        <v>-23.5315615</v>
+      </c>
+      <c r="P406" t="n">
+        <v>-46.3861622</v>
+      </c>
+      <c r="Q406" t="n">
+        <v>-23.5310181</v>
+      </c>
+      <c r="R406" t="n">
+        <v>-46.3863345</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L388"/>
+  <dimension ref="A1:L389"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -18748,6 +18748,54 @@
       <c r="L388" t="inlineStr">
         <is>
           <t>Plano de furo FL-07 versao 01, 20.MAI.2026; trecho PV-11 ao PV-13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>JC-PV-14</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>PV-14</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>7397049.125</v>
+      </c>
+      <c r="F389" t="n">
+        <v>358549.221</v>
+      </c>
+      <c r="G389" t="n">
+        <v>-23.5306805</v>
+      </c>
+      <c r="H389" t="n">
+        <v>-46.38564</v>
+      </c>
+      <c r="I389" t="n">
+        <v>777.573</v>
+      </c>
+      <c r="J389" t="n">
+        <v>773.073</v>
+      </c>
+      <c r="K389" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L389" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; trecho PV-13 ao PV-14.</t>
         </is>
       </c>
     </row>
@@ -18762,7 +18810,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R406"/>
+  <dimension ref="A1:R407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -47332,6 +47380,80 @@
       </c>
       <c r="R406" t="n">
         <v>-46.3863345</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>JC-007</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>PV-13 - PV-14</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>PV-13</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>PV-14</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G407" t="n">
+        <v>355</v>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I407" t="n">
+        <v>80.157</v>
+      </c>
+      <c r="J407" t="n">
+        <v>2</v>
+      </c>
+      <c r="K407" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L407" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="M407" t="inlineStr">
+        <is>
+          <t>em planejamento</t>
+        </is>
+      </c>
+      <c r="N407" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; PV-13 ao PV-14; arquivo: planos_furo/cts_joao_canzi_fl07_pv13_pv14.pdf; taxa 0,0400.</t>
+        </is>
+      </c>
+      <c r="O407" t="n">
+        <v>-23.5310181</v>
+      </c>
+      <c r="P407" t="n">
+        <v>-46.3863345</v>
+      </c>
+      <c r="Q407" t="n">
+        <v>-23.5306805</v>
+      </c>
+      <c r="R407" t="n">
+        <v>-46.38564</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L389"/>
+  <dimension ref="A1:L390"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -18796,6 +18796,54 @@
       <c r="L389" t="inlineStr">
         <is>
           <t>Plano de furo FL-07 versao 01, 20.MAI.2026; trecho PV-13 ao PV-14.</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>cts_lourdes_complementar</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>LOUR-PV-03</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>PV-03</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>7397125.283</v>
+      </c>
+      <c r="F390" t="n">
+        <v>357735.541</v>
+      </c>
+      <c r="G390" t="n">
+        <v>-23.5299216</v>
+      </c>
+      <c r="H390" t="n">
+        <v>-46.3936017</v>
+      </c>
+      <c r="I390" t="n">
+        <v>756.346</v>
+      </c>
+      <c r="J390" t="n">
+        <v>752.946</v>
+      </c>
+      <c r="K390" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-02 versao 01, 14.MAI.2026.</t>
         </is>
       </c>
     </row>
@@ -18810,7 +18858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R407"/>
+  <dimension ref="A1:R408"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -25679,7 +25727,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O97" t="n">
@@ -25748,7 +25796,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O98" t="n">
@@ -25817,7 +25865,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O99" t="n">
@@ -25886,7 +25934,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O100" t="n">
@@ -25955,7 +26003,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O101" t="n">
@@ -26024,7 +26072,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O102" t="n">
@@ -26093,7 +26141,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O103" t="n">
@@ -26162,7 +26210,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O104" t="n">
@@ -26231,7 +26279,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O105" t="n">
@@ -26300,7 +26348,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O106" t="n">
@@ -26369,7 +26417,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O107" t="n">
@@ -26438,7 +26486,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O108" t="n">
@@ -26507,7 +26555,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O109" t="n">
@@ -26576,7 +26624,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O110" t="n">
@@ -26645,7 +26693,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O111" t="n">
@@ -26714,7 +26762,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O112" t="n">
@@ -26783,7 +26831,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O113" t="n">
@@ -26852,7 +26900,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O114" t="n">
@@ -26921,7 +26969,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O115" t="n">
@@ -26990,7 +27038,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O116" t="n">
@@ -27059,7 +27107,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O117" t="n">
@@ -27128,7 +27176,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O118" t="n">
@@ -27197,7 +27245,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O119" t="n">
@@ -27266,7 +27314,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O120" t="n">
@@ -27335,7 +27383,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O121" t="n">
@@ -27404,7 +27452,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O122" t="n">
@@ -27473,7 +27521,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O123" t="n">
@@ -27542,7 +27590,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O124" t="n">
@@ -27611,7 +27659,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O125" t="n">
@@ -27680,7 +27728,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O126" t="n">
@@ -27749,7 +27797,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O127" t="n">
@@ -27818,7 +27866,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O128" t="n">
@@ -27887,7 +27935,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O129" t="n">
@@ -27956,7 +28004,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O130" t="n">
@@ -28025,7 +28073,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O131" t="n">
@@ -33758,7 +33806,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O215" t="n">
@@ -33827,7 +33875,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O216" t="n">
@@ -33896,7 +33944,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O217" t="n">
@@ -33965,7 +34013,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O218" t="n">
@@ -34034,7 +34082,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O219" t="n">
@@ -34103,7 +34151,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O220" t="n">
@@ -34172,7 +34220,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O221" t="n">
@@ -34241,7 +34289,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O222" t="n">
@@ -34310,7 +34358,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O223" t="n">
@@ -34379,7 +34427,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O224" t="n">
@@ -34448,7 +34496,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O225" t="n">
@@ -34517,7 +34565,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O226" t="n">
@@ -34586,7 +34634,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O227" t="n">
@@ -34655,7 +34703,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O228" t="n">
@@ -34724,7 +34772,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O229" t="n">
@@ -34793,7 +34841,7 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O230" t="n">
@@ -34862,7 +34910,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O231" t="n">
@@ -34931,7 +34979,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O232" t="n">
@@ -35000,7 +35048,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O233" t="n">
@@ -35069,7 +35117,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O234" t="n">
@@ -35138,7 +35186,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O235" t="n">
@@ -35207,7 +35255,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O236" t="n">
@@ -35276,7 +35324,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O237" t="n">
@@ -35345,7 +35393,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O238" t="n">
@@ -35414,7 +35462,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O239" t="n">
@@ -35483,7 +35531,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O240" t="n">
@@ -35552,7 +35600,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O241" t="n">
@@ -35621,7 +35669,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O242" t="n">
@@ -35690,7 +35738,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O243" t="n">
@@ -35759,7 +35807,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O244" t="n">
@@ -35828,7 +35876,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O245" t="n">
@@ -35897,7 +35945,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O246" t="n">
@@ -35966,7 +36014,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O247" t="n">
@@ -36035,7 +36083,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O248" t="n">
@@ -36104,7 +36152,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O249" t="n">
@@ -36173,7 +36221,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O250" t="n">
@@ -36242,7 +36290,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O251" t="n">
@@ -36311,7 +36359,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O252" t="n">
@@ -36380,7 +36428,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O253" t="n">
@@ -36449,7 +36497,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O254" t="n">
@@ -36518,7 +36566,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O255" t="n">
@@ -36587,7 +36635,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O256" t="n">
@@ -36656,7 +36704,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O257" t="n">
@@ -36725,7 +36773,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O258" t="n">
@@ -36794,7 +36842,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O259" t="n">
@@ -36863,7 +36911,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O260" t="n">
@@ -36932,7 +36980,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O261" t="n">
@@ -37001,7 +37049,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O262" t="n">
@@ -37070,7 +37118,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O263" t="n">
@@ -37139,7 +37187,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O264" t="n">
@@ -37208,7 +37256,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O265" t="n">
@@ -37277,7 +37325,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O266" t="n">
@@ -37346,7 +37394,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O267" t="n">
@@ -37415,7 +37463,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O268" t="n">
@@ -37484,7 +37532,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O269" t="n">
@@ -37553,7 +37601,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O270" t="n">
@@ -37622,7 +37670,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O271" t="n">
@@ -37691,7 +37739,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O272" t="n">
@@ -37760,7 +37808,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O273" t="n">
@@ -37829,7 +37877,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O274" t="n">
@@ -37898,7 +37946,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O275" t="n">
@@ -37967,7 +38015,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O276" t="n">
@@ -38036,7 +38084,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O277" t="n">
@@ -38105,7 +38153,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O278" t="n">
@@ -38174,7 +38222,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O279" t="n">
@@ -38243,7 +38291,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O280" t="n">
@@ -38312,7 +38360,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O281" t="n">
@@ -38381,7 +38429,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O282" t="n">
@@ -38450,7 +38498,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O283" t="n">
@@ -38519,7 +38567,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O284" t="n">
@@ -38588,7 +38636,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O285" t="n">
@@ -38657,7 +38705,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O286" t="n">
@@ -38726,7 +38774,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O287" t="n">
@@ -38795,7 +38843,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O288" t="n">
@@ -38864,7 +38912,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O289" t="n">
@@ -38933,7 +38981,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O290" t="n">
@@ -39002,7 +39050,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="O291" t="n">
@@ -40553,7 +40601,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -40627,7 +40675,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -40849,7 +40897,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -40923,7 +40971,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -40997,7 +41045,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>em andamento</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -41071,7 +41119,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>em planejamento</t>
+          <t>em andamento</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -41145,7 +41193,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -41219,7 +41267,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -41293,7 +41341,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -41367,7 +41415,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -41441,7 +41489,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -41515,7 +41563,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -41589,7 +41637,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -44549,7 +44597,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -44623,7 +44671,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -44697,7 +44745,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -44771,7 +44819,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -44845,7 +44893,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -44919,7 +44967,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -44993,7 +45041,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -45067,7 +45115,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -47065,7 +47113,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>em planejamento</t>
+          <t>em andamento</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -47139,7 +47187,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>em planejamento</t>
+          <t>em andamento</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -47213,7 +47261,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>em planejamento</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -47287,7 +47335,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>em planejamento</t>
+          <t>em andamento</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -47361,7 +47409,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>concluída</t>
+          <t>em andamento</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -47435,7 +47483,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>em planejamento</t>
+          <t>em andamento</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -47454,6 +47502,80 @@
       </c>
       <c r="R407" t="n">
         <v>-46.38564</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>cts_lourdes_complementar</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>LOUR-002</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>PV-02 - PV-03</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>PV-02</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>PV-03</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G408" t="n">
+        <v>450</v>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I408" t="n">
+        <v>78.58</v>
+      </c>
+      <c r="J408" t="n">
+        <v>4</v>
+      </c>
+      <c r="K408" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L408" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M408" t="inlineStr">
+        <is>
+          <t>concluído</t>
+        </is>
+      </c>
+      <c r="N408" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-02 versao 01, 14.MAI.2026; RUA GONCALVES CASTELAO; PV-02 ao PV-03; arquivo: planos_furo/CT LOURDES - FL.02.PLANO DE FURO_PV-02 AO PV-03.pdf; taxa 0,0109.</t>
+        </is>
+      </c>
+      <c r="O408" t="n">
+        <v>-23.52953</v>
+      </c>
+      <c r="P408" t="n">
+        <v>-46.3942436</v>
+      </c>
+      <c r="Q408" t="n">
+        <v>-23.5299216</v>
+      </c>
+      <c r="R408" t="n">
+        <v>-46.3936017</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L390"/>
+  <dimension ref="A1:L392"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -18844,6 +18844,102 @@
       <c r="L390" t="inlineStr">
         <is>
           <t>Plano de furo FL-02 versao 01, 14.MAI.2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>JC-PV-15</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>PV-15</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>7397079.185</v>
+      </c>
+      <c r="F391" t="n">
+        <v>358592.41</v>
+      </c>
+      <c r="G391" t="n">
+        <v>-23.5304128</v>
+      </c>
+      <c r="H391" t="n">
+        <v>-46.3852142</v>
+      </c>
+      <c r="I391" t="n">
+        <v>779.073</v>
+      </c>
+      <c r="J391" t="n">
+        <v>773.574</v>
+      </c>
+      <c r="K391" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; trecho PV-14 ao PV-15; arquivo: planos_furo/cts_joao_canzi_fl07_pv14_pv15.pdf.</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>JC-PV-16</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>PV-16</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>7397127.313</v>
+      </c>
+      <c r="F392" t="n">
+        <v>358662.509</v>
+      </c>
+      <c r="G392" t="n">
+        <v>-23.5299843</v>
+      </c>
+      <c r="H392" t="n">
+        <v>-46.3845231</v>
+      </c>
+      <c r="I392" t="n">
+        <v>777.73</v>
+      </c>
+      <c r="J392" t="n">
+        <v>774.633</v>
+      </c>
+      <c r="K392" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-01 versao 01, 26.MAI.2026; trecho PV-15 ao PV-16; arquivo: planos_furo/cts_joao_canzi_fl01_pv15_pv16.pdf.</t>
         </is>
       </c>
     </row>
@@ -18858,7 +18954,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R408"/>
+  <dimension ref="A1:R410"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -47576,6 +47672,154 @@
       </c>
       <c r="R408" t="n">
         <v>-46.3936017</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>JC-008</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>PV-14 - PV-15</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>PV-14</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>PV-15</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G409" t="n">
+        <v>355</v>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I409" t="n">
+        <v>52.62</v>
+      </c>
+      <c r="J409" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K409" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L409" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M409" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N409" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; PV-14 ao PV-15; arquivo: planos_furo/cts_joao_canzi_fl07_pv14_pv15.pdf; taxa 0,0095.</t>
+        </is>
+      </c>
+      <c r="O409" t="n">
+        <v>-23.5306805</v>
+      </c>
+      <c r="P409" t="n">
+        <v>-46.38564</v>
+      </c>
+      <c r="Q409" t="n">
+        <v>-23.5304128</v>
+      </c>
+      <c r="R409" t="n">
+        <v>-46.3852142</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>JC-009</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>PV-15 - PV-16</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>PV-15</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>PV-16</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G410" t="n">
+        <v>355</v>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I410" t="n">
+        <v>85.03</v>
+      </c>
+      <c r="J410" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K410" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L410" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M410" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N410" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-01 versao 01, 26.MAI.2026; PV-15 ao PV-16; arquivo: planos_furo/cts_joao_canzi_fl01_pv15_pv16.pdf; taxa 0,0125.</t>
+        </is>
+      </c>
+      <c r="O410" t="n">
+        <v>-23.5304128</v>
+      </c>
+      <c r="P410" t="n">
+        <v>-46.3852142</v>
+      </c>
+      <c r="Q410" t="n">
+        <v>-23.5299843</v>
+      </c>
+      <c r="R410" t="n">
+        <v>-46.3845231</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -18850,7 +18850,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>cts_lourdes_complementar</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -18860,45 +18860,45 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>JC-PV-15</t>
+          <t>LOUR-PV-04</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>PV-15</t>
+          <t>PV-04</t>
         </is>
       </c>
       <c r="E391" t="n">
-        <v>7397079.185</v>
+        <v>7397095.58</v>
       </c>
       <c r="F391" t="n">
-        <v>358592.41</v>
+        <v>357808.575</v>
       </c>
       <c r="G391" t="n">
-        <v>-23.5304128</v>
+        <v>-23.5301962</v>
       </c>
       <c r="H391" t="n">
-        <v>-46.3852142</v>
+        <v>-46.3928893</v>
       </c>
       <c r="I391" t="n">
-        <v>779.073</v>
+        <v>759.482</v>
       </c>
       <c r="J391" t="n">
-        <v>773.574</v>
+        <v>754.482</v>
       </c>
       <c r="K391" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="L391" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; trecho PV-14 ao PV-15; arquivo: planos_furo/cts_joao_canzi_fl07_pv14_pv15.pdf.</t>
+          <t>Plano de furo FL-02 versao 01, 26.MAI.2026; PV-03 ao PV-04.</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>cts_lourdes_complementar</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -18908,38 +18908,38 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>JC-PV-16</t>
+          <t>LOUR-PV-05</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>PV-16</t>
+          <t>PV-05</t>
         </is>
       </c>
       <c r="E392" t="n">
-        <v>7397127.313</v>
+        <v>7397066.391</v>
       </c>
       <c r="F392" t="n">
-        <v>358662.509</v>
+        <v>357868.405</v>
       </c>
       <c r="G392" t="n">
-        <v>-23.5299843</v>
+        <v>-23.530465</v>
       </c>
       <c r="H392" t="n">
-        <v>-46.3845231</v>
+        <v>-46.3923061</v>
       </c>
       <c r="I392" t="n">
-        <v>777.73</v>
+        <v>757.627</v>
       </c>
       <c r="J392" t="n">
-        <v>774.633</v>
+        <v>755.427</v>
       </c>
       <c r="K392" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="L392" t="inlineStr">
         <is>
-          <t>Plano de furo FL-01 versao 01, 26.MAI.2026; trecho PV-15 ao PV-16; arquivo: planos_furo/cts_joao_canzi_fl01_pv15_pv16.pdf.</t>
+          <t>Plano de furo FL-02 versao 01, 26.MAI.2026; PV-04 ao PV-05.</t>
         </is>
       </c>
     </row>
@@ -47677,27 +47677,27 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>cts_lourdes_complementar</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>JC-008</t>
+          <t>LOUR-003</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>PV-14 - PV-15</t>
+          <t>PV-03 - PV-04</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>PV-14</t>
+          <t>PV-03</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>PV-15</t>
+          <t>PV-04</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -47706,7 +47706,7 @@
         </is>
       </c>
       <c r="G409" t="n">
-        <v>355</v>
+        <v>450</v>
       </c>
       <c r="H409" t="inlineStr">
         <is>
@@ -47714,64 +47714,64 @@
         </is>
       </c>
       <c r="I409" t="n">
-        <v>52.62</v>
+        <v>78.843</v>
       </c>
       <c r="J409" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="K409" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="L409" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>em andamento</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; PV-14 ao PV-15; arquivo: planos_furo/cts_joao_canzi_fl07_pv14_pv15.pdf; taxa 0,0095.</t>
+          <t>Plano de furo FL-02 versao 01, 26.MAI.2026; PV-03 ao PV-04; arquivo: planos_furo/CT LOURDES - FL.02.PLANO DE FURO_PV-03 AO PV-04.pdf; taxa 0,0195.</t>
         </is>
       </c>
       <c r="O409" t="n">
-        <v>-23.5306805</v>
+        <v>-23.5299216</v>
       </c>
       <c r="P409" t="n">
-        <v>-46.38564</v>
+        <v>-46.3936017</v>
       </c>
       <c r="Q409" t="n">
-        <v>-23.5304128</v>
+        <v>-23.5301962</v>
       </c>
       <c r="R409" t="n">
-        <v>-46.3852142</v>
+        <v>-46.3928893</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>cts_lourdes_complementar</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>JC-009</t>
+          <t>LOUR-004</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>PV-15 - PV-16</t>
+          <t>PV-04 - PV-05</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>PV-15</t>
+          <t>PV-04</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>PV-16</t>
+          <t>PV-05</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -47780,7 +47780,7 @@
         </is>
       </c>
       <c r="G410" t="n">
-        <v>355</v>
+        <v>450</v>
       </c>
       <c r="H410" t="inlineStr">
         <is>
@@ -47788,38 +47788,38 @@
         </is>
       </c>
       <c r="I410" t="n">
-        <v>85.03</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="J410" t="n">
+        <v>5</v>
+      </c>
+      <c r="K410" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L410" t="n">
         <v>5.5</v>
       </c>
-      <c r="K410" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L410" t="n">
-        <v>5.9</v>
-      </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>em andamento</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
         <is>
-          <t>Plano de furo FL-01 versao 01, 26.MAI.2026; PV-15 ao PV-16; arquivo: planos_furo/cts_joao_canzi_fl01_pv15_pv16.pdf; taxa 0,0125.</t>
+          <t>Plano de furo FL-02 versao 01, 26.MAI.2026; PV-04 ao PV-05; arquivo: planos_furo/CT LOURDES - FL.02.PLANO DE FURO_PV-04 AO PV-05.pdf; taxa 0,0142.</t>
         </is>
       </c>
       <c r="O410" t="n">
-        <v>-23.5304128</v>
+        <v>-23.5301962</v>
       </c>
       <c r="P410" t="n">
-        <v>-46.3852142</v>
+        <v>-46.3928893</v>
       </c>
       <c r="Q410" t="n">
-        <v>-23.5299843</v>
+        <v>-23.530465</v>
       </c>
       <c r="R410" t="n">
-        <v>-46.3845231</v>
+        <v>-46.3923061</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L392"/>
+  <dimension ref="A1:L394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -18940,6 +18940,102 @@
       <c r="L392" t="inlineStr">
         <is>
           <t>Plano de furo FL-02 versao 01, 26.MAI.2026; PV-04 ao PV-05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>JC-PV-15</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>PV-15</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>7397079.185</v>
+      </c>
+      <c r="F393" t="n">
+        <v>358592.41</v>
+      </c>
+      <c r="G393" t="n">
+        <v>-23.5304128</v>
+      </c>
+      <c r="H393" t="n">
+        <v>-46.3852142</v>
+      </c>
+      <c r="I393" t="n">
+        <v>779.073</v>
+      </c>
+      <c r="J393" t="n">
+        <v>773.574</v>
+      </c>
+      <c r="K393" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-08 versao 01, 26.MAI.2026; trecho PV-15 ao PV-16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>JC-PV-16</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>PV-16</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>7397127.313</v>
+      </c>
+      <c r="F394" t="n">
+        <v>358662.509</v>
+      </c>
+      <c r="G394" t="n">
+        <v>-23.5299843</v>
+      </c>
+      <c r="H394" t="n">
+        <v>-46.3845231</v>
+      </c>
+      <c r="I394" t="n">
+        <v>777.73</v>
+      </c>
+      <c r="J394" t="n">
+        <v>774.633</v>
+      </c>
+      <c r="K394" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-08 versao 01, 26.MAI.2026; trecho PV-15 ao PV-16.</t>
         </is>
       </c>
     </row>
@@ -18954,7 +19050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R410"/>
+  <dimension ref="A1:R411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -47820,6 +47916,80 @@
       </c>
       <c r="R410" t="n">
         <v>-46.3923061</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>JC-008</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>PV-15 - PV-16</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>PV-15</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>PV-16</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G411" t="n">
+        <v>355</v>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I411" t="n">
+        <v>85.03</v>
+      </c>
+      <c r="J411" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K411" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L411" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-08 versao 01, 26.MAI.2026; PV-15 ao PV-16; arquivo: planos_furo/cts_joao_canzi_fl08_pv15_pv16.pdf; taxa 0,0125.</t>
+        </is>
+      </c>
+      <c r="O411" t="n">
+        <v>-23.5304128</v>
+      </c>
+      <c r="P411" t="n">
+        <v>-46.3852142</v>
+      </c>
+      <c r="Q411" t="n">
+        <v>-23.5299843</v>
+      </c>
+      <c r="R411" t="n">
+        <v>-46.3845231</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -18795,7 +18795,7 @@
       </c>
       <c r="L389" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; trecho PV-13 ao PV-14.</t>
+          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; trechos PV-13 ao PV-14 e PV-14 ao PV-15.</t>
         </is>
       </c>
     </row>
@@ -18987,7 +18987,7 @@
       </c>
       <c r="L393" t="inlineStr">
         <is>
-          <t>Plano de furo FL-08 versao 01, 26.MAI.2026; trecho PV-15 ao PV-16.</t>
+          <t>Planos de furo FL-07 versao 01, 20.MAI.2026 e FL-08 versao 01, 26.MAI.2026; trechos PV-14 ao PV-15 e PV-15 ao PV-16.</t>
         </is>
       </c>
     </row>
@@ -19050,7 +19050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R411"/>
+  <dimension ref="A1:R412"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -47990,6 +47990,80 @@
       </c>
       <c r="R411" t="n">
         <v>-46.3845231</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>JC-009</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>PV-14 - PV-15</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>PV-14</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>PV-15</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G412" t="n">
+        <v>355</v>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I412" t="n">
+        <v>52.62</v>
+      </c>
+      <c r="J412" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K412" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L412" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; PV-14 ao PV-15; arquivo: planos_furo/cts_joao_canzi_fl07_pv14_pv15.pdf; taxa 0,0095.</t>
+        </is>
+      </c>
+      <c r="O412" t="n">
+        <v>-23.5306805</v>
+      </c>
+      <c r="P412" t="n">
+        <v>-46.38564</v>
+      </c>
+      <c r="Q412" t="n">
+        <v>-23.5304128</v>
+      </c>
+      <c r="R412" t="n">
+        <v>-46.3852142</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -1227,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L394"/>
+  <dimension ref="A1:L396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -19036,6 +19036,102 @@
       <c r="L394" t="inlineStr">
         <is>
           <t>Plano de furo FL-08 versao 01, 26.MAI.2026; trecho PV-15 ao PV-16.</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>JC-PV-17-FL07</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>PV-17</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>7397122.275</v>
+      </c>
+      <c r="F395" t="n">
+        <v>358726.884</v>
+      </c>
+      <c r="G395" t="n">
+        <v>-23.5300354</v>
+      </c>
+      <c r="H395" t="n">
+        <v>-46.3838931</v>
+      </c>
+      <c r="I395" t="n">
+        <v>782.299</v>
+      </c>
+      <c r="J395" t="n">
+        <v>779.199</v>
+      </c>
+      <c r="K395" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; trechos PV-16 ao PV-17 e PV-17 ao PV-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>JC-PV-18</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>PV-18</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>7397124.485</v>
+      </c>
+      <c r="F396" t="n">
+        <v>358806.429</v>
+      </c>
+      <c r="G396" t="n">
+        <v>-23.5300223</v>
+      </c>
+      <c r="H396" t="n">
+        <v>-46.3831139</v>
+      </c>
+      <c r="I396" t="n">
+        <v>783.619</v>
+      </c>
+      <c r="J396" t="n">
+        <v>780.119</v>
+      </c>
+      <c r="K396" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; trecho PV-17 ao PV-18.</t>
         </is>
       </c>
     </row>
@@ -19050,7 +19146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R412"/>
+  <dimension ref="A1:R414"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -48064,6 +48160,154 @@
       </c>
       <c r="R412" t="n">
         <v>-46.3852142</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>JC-010</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>PV-16 - PV-17</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>PV-16</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>PV-17</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G413" t="n">
+        <v>355</v>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I413" t="n">
+        <v>64.572</v>
+      </c>
+      <c r="J413" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K413" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L413" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-16 ao PV-17; arquivo: planos_furo/cts_joao_canzi_fl07_pv16_pv17.pdf; taxa 0,0707.</t>
+        </is>
+      </c>
+      <c r="O413" t="n">
+        <v>-23.5299843</v>
+      </c>
+      <c r="P413" t="n">
+        <v>-46.3845231</v>
+      </c>
+      <c r="Q413" t="n">
+        <v>-23.5300354</v>
+      </c>
+      <c r="R413" t="n">
+        <v>-46.3838931</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>JC-011</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>PV-17 - PV-18</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>PV-17</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>PV-18</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G414" t="n">
+        <v>355</v>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I414" t="n">
+        <v>79.57599999999999</v>
+      </c>
+      <c r="J414" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K414" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L414" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-17 ao PV-18; arquivo: planos_furo/cts_joao_canzi_fl07_pv17_pv18.pdf; taxa 0,0116.</t>
+        </is>
+      </c>
+      <c r="O414" t="n">
+        <v>-23.5300354</v>
+      </c>
+      <c r="P414" t="n">
+        <v>-46.3838931</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>-23.5300223</v>
+      </c>
+      <c r="R414" t="n">
+        <v>-46.3831139</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -2,9 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEIA-ME" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OBRAS" sheetId="2" state="visible" r:id="rId2"/>
@@ -17,10 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACAO_SHAPE_LUIS_0505" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACAO_SUBST_AGUA_BOA_0505" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TRECHOS'!$A$1:$R$388</definedName>
-  </definedNames>
-  <calcPr calcId="191029" fullCalcOnLoad="1" forceFullCalc="1"/>
+  <definedNames/>
 </workbook>
 </file>
 
@@ -30,15 +24,13 @@
   <fonts count="2">
     <font>
       <name val="Calibri"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -51,23 +43,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D4ED8"/>
+        <fgColor rgb="001D4ED8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF334155"/>
+        <fgColor rgb="00334155"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -80,9 +66,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -155,7 +140,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -197,72 +182,14 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -270,55 +197,15 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
+        <a:solidFill>
+          <a:schemeClr val="dk1"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="accent1"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
@@ -327,13 +214,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -367,24 +254,13 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -410,7 +286,7 @@
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -432,8 +308,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -444,7 +318,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -503,7 +377,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -514,7 +388,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -578,7 +452,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -588,11 +462,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <cols>
-    <col width="31.109375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="35.44140625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="31.109375" customWidth="1" min="1" max="1"/>
+    <col width="35.44140625" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1216,8 +1090,62 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>RCE Elias Sleiman</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>RCE</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Base criada a partir do print enviado: coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>rce_elvira_de_araujo</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>RCE Elvira de Araújo</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>RCE</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Base criada a partir do print enviado: pontos PI-1.1 e PI-1.2 em VCA; interligação mantida com CTS João Canzi.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1227,11 +1155,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L396"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:L405"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <cols>
-    <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="12.5546875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="30.21875" customWidth="1" min="1" max="1"/>
+    <col width="12.5546875" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19052,38 +18980,38 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>JC-PV-17-FL07</t>
+          <t>JC-PV-01</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>PV-17</t>
+          <t>PV-01</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>7397122.275</v>
+        <v>7396903.634</v>
       </c>
       <c r="F395" t="n">
-        <v>358726.884</v>
+        <v>358332.744</v>
       </c>
       <c r="G395" t="n">
-        <v>-23.5300354</v>
+        <v>-23.5319754</v>
       </c>
       <c r="H395" t="n">
-        <v>-46.3838931</v>
+        <v>-46.3877739</v>
       </c>
       <c r="I395" t="n">
-        <v>782.299</v>
+        <v>767.2910000000001</v>
       </c>
       <c r="J395" t="n">
-        <v>779.199</v>
+        <v>763.0069999999999</v>
       </c>
       <c r="K395" t="n">
-        <v>3.1</v>
+        <v>4.28</v>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; trechos PV-16 ao PV-17 e PV-17 ao PV-18.</t>
+          <t>Adicionado via print do projeto RCE Elvira de Araujo; complemento em VCA.</t>
         </is>
       </c>
     </row>
@@ -19095,62 +19023,494 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>JC-PI-1.1</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>PI-1.1</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>7396905.886</v>
+      </c>
+      <c r="F396" t="n">
+        <v>358329.956</v>
+      </c>
+      <c r="G396" t="n">
+        <v>-23.5319548</v>
+      </c>
+      <c r="H396" t="n">
+        <v>-46.387801</v>
+      </c>
+      <c r="I396" t="n">
+        <v>767.159</v>
+      </c>
+      <c r="J396" t="n">
+        <v>765.927</v>
+      </c>
+      <c r="K396" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>Adicionado via print do projeto RCE Elvira de Araujo; complemento em VCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>JC-PI-1.2</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>PI-1.2</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>7396922.192</v>
+      </c>
+      <c r="F397" t="n">
+        <v>358327.004</v>
+      </c>
+      <c r="G397" t="n">
+        <v>-23.5318073</v>
+      </c>
+      <c r="H397" t="n">
+        <v>-46.3878284</v>
+      </c>
+      <c r="I397" t="n">
+        <v>767.21</v>
+      </c>
+      <c r="J397" t="n">
+        <v>766.01</v>
+      </c>
+      <c r="K397" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>Adicionado via print do projeto RCE Elvira de Araujo; complemento em VCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
           <t>PV</t>
         </is>
       </c>
-      <c r="C396" t="inlineStr">
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>ELIAS-PV-21</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>PV-21</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>7397111.065</v>
+      </c>
+      <c r="F398" t="n">
+        <v>358747.317</v>
+      </c>
+      <c r="G398" t="n">
+        <v>-23.5301384</v>
+      </c>
+      <c r="H398" t="n">
+        <v>-46.3836941</v>
+      </c>
+      <c r="I398" t="n">
+        <v>784.299</v>
+      </c>
+      <c r="J398" t="n">
+        <v>782.215</v>
+      </c>
+      <c r="K398" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="L398" t="inlineStr">
+        <is>
+          <t>Adicionado via print do projeto RCE Elias Sleiman; lancamento completo em VCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>ELIAS-PV-22</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>PV-22</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>7397048.086</v>
+      </c>
+      <c r="F399" t="n">
+        <v>358777.873</v>
+      </c>
+      <c r="G399" t="n">
+        <v>-23.5307098</v>
+      </c>
+      <c r="H399" t="n">
+        <v>-46.3834008</v>
+      </c>
+      <c r="I399" t="n">
+        <v>794.057</v>
+      </c>
+      <c r="J399" t="n">
+        <v>791.972</v>
+      </c>
+      <c r="K399" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="L399" t="inlineStr">
+        <is>
+          <t>Adicionado via print do projeto RCE Elias Sleiman; lancamento completo em VCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>ELIAS-PV-23</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>PV-23</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>7397018.372</v>
+      </c>
+      <c r="F400" t="n">
+        <v>358792.29</v>
+      </c>
+      <c r="G400" t="n">
+        <v>-23.5309793</v>
+      </c>
+      <c r="H400" t="n">
+        <v>-46.3832624</v>
+      </c>
+      <c r="I400" t="n">
+        <v>796.528</v>
+      </c>
+      <c r="J400" t="n">
+        <v>792.947</v>
+      </c>
+      <c r="K400" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="L400" t="inlineStr">
+        <is>
+          <t>Adicionado via print do projeto RCE Elias Sleiman; lancamento completo em VCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>rce_elvira_de_araujo</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>ELVIRA-PI-1.1</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>PI-1.1</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>7396905.886</v>
+      </c>
+      <c r="F401" t="n">
+        <v>358329.956</v>
+      </c>
+      <c r="G401" t="n">
+        <v>-23.5319548</v>
+      </c>
+      <c r="H401" t="n">
+        <v>-46.387801</v>
+      </c>
+      <c r="I401" t="n">
+        <v>767.159</v>
+      </c>
+      <c r="J401" t="n">
+        <v>765.927</v>
+      </c>
+      <c r="K401" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L401" t="inlineStr">
+        <is>
+          <t>Adicionado conforme solicitação: PI da RCE Elvira de Araujo; interligacao com CTS Joao Canzi mantida sem alterar registros existentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>rce_elvira_de_araujo</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>ELVIRA-PI-1.2</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>PI-1.2</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>7396922.192</v>
+      </c>
+      <c r="F402" t="n">
+        <v>358327.004</v>
+      </c>
+      <c r="G402" t="n">
+        <v>-23.5318073</v>
+      </c>
+      <c r="H402" t="n">
+        <v>-46.3878284</v>
+      </c>
+      <c r="I402" t="n">
+        <v>767.21</v>
+      </c>
+      <c r="J402" t="n">
+        <v>766.01</v>
+      </c>
+      <c r="K402" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L402" t="inlineStr">
+        <is>
+          <t>Adicionado conforme solicitação: PI da RCE Elvira de Araujo; interligacao com CTS Joao Canzi mantida sem alterar registros existentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
         <is>
           <t>JC-PV-18</t>
         </is>
       </c>
-      <c r="D396" t="inlineStr">
+      <c r="D403" t="inlineStr">
         <is>
           <t>PV-18</t>
         </is>
       </c>
-      <c r="E396" t="n">
+      <c r="E403" t="n">
         <v>7397124.485</v>
       </c>
-      <c r="F396" t="n">
+      <c r="F403" t="n">
         <v>358806.429</v>
       </c>
-      <c r="G396" t="n">
-        <v>-23.5300223</v>
-      </c>
-      <c r="H396" t="n">
+      <c r="G403" t="n">
+        <v>-23.5300224</v>
+      </c>
+      <c r="H403" t="n">
         <v>-46.3831139</v>
       </c>
-      <c r="I396" t="n">
+      <c r="I403" t="n">
         <v>783.619</v>
       </c>
-      <c r="J396" t="n">
+      <c r="J403" t="n">
         <v>780.119</v>
       </c>
-      <c r="K396" t="n">
+      <c r="K403" t="n">
         <v>3.5</v>
       </c>
-      <c r="L396" t="inlineStr">
-        <is>
-          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; trecho PV-17 ao PV-18.</t>
+      <c r="L403" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-18 ao PV-19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>JC-PV-19</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>PV-19</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>7397141.155</v>
+      </c>
+      <c r="F404" t="n">
+        <v>358871.038</v>
+      </c>
+      <c r="G404" t="n">
+        <v>-23.5298774</v>
+      </c>
+      <c r="H404" t="n">
+        <v>-46.3824796</v>
+      </c>
+      <c r="I404" t="n">
+        <v>787.357</v>
+      </c>
+      <c r="J404" t="n">
+        <v>783.357</v>
+      </c>
+      <c r="K404" t="n">
+        <v>4</v>
+      </c>
+      <c r="L404" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-18 ao PV-19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>JC-PV-17-FL07</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>PV-17</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>7397122.275</v>
+      </c>
+      <c r="F405" t="n">
+        <v>358726.884</v>
+      </c>
+      <c r="G405" t="n">
+        <v>-23.5300354</v>
+      </c>
+      <c r="H405" t="n">
+        <v>-46.3838931</v>
+      </c>
+      <c r="I405" t="n">
+        <v>782.299</v>
+      </c>
+      <c r="J405" t="n">
+        <v>779.199</v>
+      </c>
+      <c r="K405" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L405" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; trechos PV-16 ao PV-17 e PV-17 ao PV-18.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R414"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:R420"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <cols>
-    <col width="30.21875" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="17.44140625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="30.21875" customWidth="1" min="1" max="1"/>
+    <col width="17.44140625" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -48175,43 +48535,43 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>PV-16 - PV-17</t>
+          <t>PV-01 - PI-1.1</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>PV-16</t>
+          <t>PV-01</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>PV-17</t>
+          <t>PI-1.1</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>PEAD LISO</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="G413" t="n">
-        <v>355</v>
+        <v>200</v>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Metodo Nao Destrutivo - MND</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I413" t="n">
-        <v>64.572</v>
+        <v>3.58</v>
       </c>
       <c r="J413" t="n">
-        <v>3.1</v>
+        <v>4.28</v>
       </c>
       <c r="K413" t="n">
-        <v>3.1</v>
+        <v>1.23</v>
       </c>
       <c r="L413" t="n">
-        <v>5.48</v>
+        <v>4.28</v>
       </c>
       <c r="M413" t="inlineStr">
         <is>
@@ -48220,20 +48580,20 @@
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-16 ao PV-17; arquivo: planos_furo/cts_joao_canzi_fl07_pv16_pv17.pdf; taxa 0,0707.</t>
+          <t>Adicionado via print do projeto RCE Elvira de Araujo; complemento em VCA.</t>
         </is>
       </c>
       <c r="O413" t="n">
-        <v>-23.5299843</v>
+        <v>-23.5319754</v>
       </c>
       <c r="P413" t="n">
-        <v>-46.3845231</v>
+        <v>-46.3877739</v>
       </c>
       <c r="Q413" t="n">
-        <v>-23.5300354</v>
+        <v>-23.5319548</v>
       </c>
       <c r="R413" t="n">
-        <v>-46.3838931</v>
+        <v>-46.387801</v>
       </c>
     </row>
     <row r="414">
@@ -48249,76 +48609,513 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
+          <t>PI-1.1 - PI-1.2</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>PI-1.1</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>PI-1.2</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G414" t="n">
+        <v>200</v>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>Vala a Céu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I414" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="J414" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="K414" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L414" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>Adicionado via print do projeto RCE Elvira de Araujo; complemento em VCA.</t>
+        </is>
+      </c>
+      <c r="O414" t="n">
+        <v>-23.5319548</v>
+      </c>
+      <c r="P414" t="n">
+        <v>-46.387801</v>
+      </c>
+      <c r="Q414" t="n">
+        <v>-23.5318073</v>
+      </c>
+      <c r="R414" t="n">
+        <v>-46.3878284</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>JC-012</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>PI-1.2 - PV-02</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>PI-1.2</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>PV-02</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G415" t="n">
+        <v>200</v>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>Vala a Céu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I415" t="n">
+        <v>5</v>
+      </c>
+      <c r="J415" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K415" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="L415" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>Adicionado via print do projeto RCE Elvira de Araujo; complemento em VCA.</t>
+        </is>
+      </c>
+      <c r="O415" t="n">
+        <v>-23.5318073</v>
+      </c>
+      <c r="P415" t="n">
+        <v>-46.3878284</v>
+      </c>
+      <c r="Q415" t="n">
+        <v>-23.5317625</v>
+      </c>
+      <c r="R415" t="n">
+        <v>-46.3878221</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>ELIAS-001</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>PV-21 - PV-22</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>PV-21</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>PV-22</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G416" t="n">
+        <v>200</v>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>Vala a Céu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I416" t="n">
+        <v>70</v>
+      </c>
+      <c r="J416" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="K416" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="L416" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>Adicionado via print do projeto RCE Elias Sleiman; lancamento completo em VCA.</t>
+        </is>
+      </c>
+      <c r="O416" t="n">
+        <v>-23.5301384</v>
+      </c>
+      <c r="P416" t="n">
+        <v>-46.3836941</v>
+      </c>
+      <c r="Q416" t="n">
+        <v>-23.5307098</v>
+      </c>
+      <c r="R416" t="n">
+        <v>-46.3834008</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>ELIAS-002</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>PV-22 - PV-23</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>PV-22</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>PV-23</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G417" t="n">
+        <v>200</v>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>Vala a Céu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I417" t="n">
+        <v>33.03</v>
+      </c>
+      <c r="J417" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="K417" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="L417" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>Adicionado via print do projeto RCE Elias Sleiman; lancamento completo em VCA.</t>
+        </is>
+      </c>
+      <c r="O417" t="n">
+        <v>-23.5307098</v>
+      </c>
+      <c r="P417" t="n">
+        <v>-46.3834008</v>
+      </c>
+      <c r="Q417" t="n">
+        <v>-23.5309793</v>
+      </c>
+      <c r="R417" t="n">
+        <v>-46.3832624</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>JC-013</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>PV-18 - PV-19</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>PV-18</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>PV-19</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G418" t="n">
+        <v>355</v>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I418" t="n">
+        <v>66.72499999999999</v>
+      </c>
+      <c r="J418" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K418" t="n">
+        <v>4</v>
+      </c>
+      <c r="L418" t="n">
+        <v>4</v>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; PV-18 ao PV-19; arquivo: planos_furo/cts_joao_canzi_fl07_pv18_pv19.pdf; taxa 0,0485.</t>
+        </is>
+      </c>
+      <c r="O418" t="n">
+        <v>-23.5300224</v>
+      </c>
+      <c r="P418" t="n">
+        <v>-46.3831139</v>
+      </c>
+      <c r="Q418" t="n">
+        <v>-23.5298774</v>
+      </c>
+      <c r="R418" t="n">
+        <v>-46.3824796</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>JC-014</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>PV-16 - PV-17</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>PV-16</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>PV-17</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G419" t="n">
+        <v>355</v>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I419" t="n">
+        <v>64.572</v>
+      </c>
+      <c r="J419" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K419" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L419" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-16 ao PV-17; arquivo: planos_furo/cts_joao_canzi_fl07_pv16_pv17.pdf; taxa 0,0707.</t>
+        </is>
+      </c>
+      <c r="O419" t="n">
+        <v>-23.5299843</v>
+      </c>
+      <c r="P419" t="n">
+        <v>-46.3845231</v>
+      </c>
+      <c r="Q419" t="n">
+        <v>-23.5300354</v>
+      </c>
+      <c r="R419" t="n">
+        <v>-46.3838931</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>JC-015</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
           <t>PV-17 - PV-18</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr">
+      <c r="D420" t="inlineStr">
         <is>
           <t>PV-17</t>
         </is>
       </c>
-      <c r="E414" t="inlineStr">
+      <c r="E420" t="inlineStr">
         <is>
           <t>PV-18</t>
         </is>
       </c>
-      <c r="F414" t="inlineStr">
+      <c r="F420" t="inlineStr">
         <is>
           <t>PEAD LISO</t>
         </is>
       </c>
-      <c r="G414" t="n">
+      <c r="G420" t="n">
         <v>355</v>
       </c>
-      <c r="H414" t="inlineStr">
+      <c r="H420" t="inlineStr">
         <is>
           <t>Metodo Nao Destrutivo - MND</t>
         </is>
       </c>
-      <c r="I414" t="n">
+      <c r="I420" t="n">
         <v>79.57599999999999</v>
       </c>
-      <c r="J414" t="n">
+      <c r="J420" t="n">
         <v>3.1</v>
       </c>
-      <c r="K414" t="n">
+      <c r="K420" t="n">
         <v>3.5</v>
       </c>
-      <c r="L414" t="n">
+      <c r="L420" t="n">
         <v>3.56</v>
       </c>
-      <c r="M414" t="inlineStr">
+      <c r="M420" t="inlineStr">
         <is>
           <t>em andamento</t>
         </is>
       </c>
-      <c r="N414" t="inlineStr">
+      <c r="N420" t="inlineStr">
         <is>
           <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-17 ao PV-18; arquivo: planos_furo/cts_joao_canzi_fl07_pv17_pv18.pdf; taxa 0,0116.</t>
         </is>
       </c>
-      <c r="O414" t="n">
+      <c r="O420" t="n">
         <v>-23.5300354</v>
       </c>
-      <c r="P414" t="n">
+      <c r="P420" t="n">
         <v>-46.3838931</v>
       </c>
-      <c r="Q414" t="n">
+      <c r="Q420" t="n">
         <v>-23.5300223</v>
       </c>
-      <c r="R414" t="n">
+      <c r="R420" t="n">
         <v>-46.3831139</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R388">
-    <filterColumn colId="0" hiddenButton="0" showButton="1">
-      <filters>
-        <filter val="conceicao"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -48329,7 +49126,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -48437,7 +49234,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -48448,7 +49245,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -49174,7 +49971,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -49185,7 +49982,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="5"/>
   </cols>
@@ -49282,7 +50079,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -49293,7 +50090,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -49538,7 +50335,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -49549,7 +50346,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -49634,6 +50431,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -18970,7 +18970,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_elias_sleiman</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -18980,237 +18980,237 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>JC-PV-01</t>
+          <t>ELIAS-PV-21</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>PV-01</t>
+          <t>PV-21</t>
         </is>
       </c>
       <c r="E395" t="n">
-        <v>7396903.634</v>
+        <v>7397111.065</v>
       </c>
       <c r="F395" t="n">
-        <v>358332.744</v>
+        <v>358747.317</v>
       </c>
       <c r="G395" t="n">
-        <v>-23.5319754</v>
+        <v>-23.5301384</v>
       </c>
       <c r="H395" t="n">
-        <v>-46.3877739</v>
+        <v>-46.3836941</v>
       </c>
       <c r="I395" t="n">
-        <v>767.2910000000001</v>
+        <v>784.299</v>
       </c>
       <c r="J395" t="n">
-        <v>763.0069999999999</v>
+        <v>782.215</v>
       </c>
       <c r="K395" t="n">
-        <v>4.28</v>
+        <v>2.08</v>
       </c>
       <c r="L395" t="inlineStr">
         <is>
-          <t>Adicionado via print do projeto RCE Elvira de Araujo; complemento em VCA.</t>
+          <t>Adicionado via print do projeto RCE Elias Sleiman; lancamento completo em VCA.</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_elias_sleiman</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>JC-PI-1.1</t>
+          <t>ELIAS-PV-22</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>PI-1.1</t>
+          <t>PV-22</t>
         </is>
       </c>
       <c r="E396" t="n">
-        <v>7396905.886</v>
+        <v>7397048.086</v>
       </c>
       <c r="F396" t="n">
-        <v>358329.956</v>
+        <v>358777.873</v>
       </c>
       <c r="G396" t="n">
-        <v>-23.5319548</v>
+        <v>-23.5307098</v>
       </c>
       <c r="H396" t="n">
-        <v>-46.387801</v>
+        <v>-46.3834008</v>
       </c>
       <c r="I396" t="n">
-        <v>767.159</v>
+        <v>794.057</v>
       </c>
       <c r="J396" t="n">
-        <v>765.927</v>
+        <v>791.972</v>
       </c>
       <c r="K396" t="n">
-        <v>1.23</v>
+        <v>2.08</v>
       </c>
       <c r="L396" t="inlineStr">
         <is>
-          <t>Adicionado via print do projeto RCE Elvira de Araujo; complemento em VCA.</t>
+          <t>Adicionado via print do projeto RCE Elias Sleiman; lancamento completo em VCA.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_elias_sleiman</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>JC-PI-1.2</t>
+          <t>ELIAS-PV-23</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>PI-1.2</t>
+          <t>PV-23</t>
         </is>
       </c>
       <c r="E397" t="n">
-        <v>7396922.192</v>
+        <v>7397018.372</v>
       </c>
       <c r="F397" t="n">
-        <v>358327.004</v>
+        <v>358792.29</v>
       </c>
       <c r="G397" t="n">
-        <v>-23.5318073</v>
+        <v>-23.5309793</v>
       </c>
       <c r="H397" t="n">
-        <v>-46.3878284</v>
+        <v>-46.3832624</v>
       </c>
       <c r="I397" t="n">
-        <v>767.21</v>
+        <v>796.528</v>
       </c>
       <c r="J397" t="n">
-        <v>766.01</v>
+        <v>792.947</v>
       </c>
       <c r="K397" t="n">
-        <v>1.2</v>
+        <v>3.58</v>
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>Adicionado via print do projeto RCE Elvira de Araujo; complemento em VCA.</t>
+          <t>Adicionado via print do projeto RCE Elias Sleiman; lancamento completo em VCA.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>rce_elias_sleiman</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>ELIAS-PV-21</t>
+          <t>ELVIRA-PI-1.1</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>PV-21</t>
+          <t>PI-1.1</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>7397111.065</v>
+        <v>7396905.886</v>
       </c>
       <c r="F398" t="n">
-        <v>358747.317</v>
+        <v>358329.956</v>
       </c>
       <c r="G398" t="n">
-        <v>-23.5301384</v>
+        <v>-23.5319548</v>
       </c>
       <c r="H398" t="n">
-        <v>-46.3836941</v>
+        <v>-46.387801</v>
       </c>
       <c r="I398" t="n">
-        <v>784.299</v>
+        <v>767.159</v>
       </c>
       <c r="J398" t="n">
-        <v>782.215</v>
+        <v>765.927</v>
       </c>
       <c r="K398" t="n">
-        <v>2.08</v>
+        <v>1.23</v>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>Adicionado via print do projeto RCE Elias Sleiman; lancamento completo em VCA.</t>
+          <t>Adicionado conforme solicitação: PI da RCE Elvira de Araujo; interligacao com CTS Joao Canzi mantida sem alterar registros existentes.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>rce_elias_sleiman</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>ELIAS-PV-22</t>
+          <t>ELVIRA-PI-1.2</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>PV-22</t>
+          <t>PI-1.2</t>
         </is>
       </c>
       <c r="E399" t="n">
-        <v>7397048.086</v>
+        <v>7396922.192</v>
       </c>
       <c r="F399" t="n">
-        <v>358777.873</v>
+        <v>358327.004</v>
       </c>
       <c r="G399" t="n">
-        <v>-23.5307098</v>
+        <v>-23.5318073</v>
       </c>
       <c r="H399" t="n">
-        <v>-46.3834008</v>
+        <v>-46.3878284</v>
       </c>
       <c r="I399" t="n">
-        <v>794.057</v>
+        <v>767.21</v>
       </c>
       <c r="J399" t="n">
-        <v>791.972</v>
+        <v>766.01</v>
       </c>
       <c r="K399" t="n">
-        <v>2.08</v>
+        <v>1.2</v>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>Adicionado via print do projeto RCE Elias Sleiman; lancamento completo em VCA.</t>
+          <t>Adicionado conforme solicitação: PI da RCE Elvira de Araujo; interligacao com CTS Joao Canzi mantida sem alterar registros existentes.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>rce_elias_sleiman</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -19220,141 +19220,141 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>ELIAS-PV-23</t>
+          <t>JC-PV-18</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>PV-23</t>
+          <t>PV-18</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>7397018.372</v>
+        <v>7397124.485</v>
       </c>
       <c r="F400" t="n">
-        <v>358792.29</v>
+        <v>358806.429</v>
       </c>
       <c r="G400" t="n">
-        <v>-23.5309793</v>
+        <v>-23.5300224</v>
       </c>
       <c r="H400" t="n">
-        <v>-46.3832624</v>
+        <v>-46.3831139</v>
       </c>
       <c r="I400" t="n">
-        <v>796.528</v>
+        <v>783.619</v>
       </c>
       <c r="J400" t="n">
-        <v>792.947</v>
+        <v>780.119</v>
       </c>
       <c r="K400" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>Adicionado via print do projeto RCE Elias Sleiman; lancamento completo em VCA.</t>
+          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-18 ao PV-19.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>rce_elvira_de_araujo</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>ELVIRA-PI-1.1</t>
+          <t>JC-PV-19</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>PI-1.1</t>
+          <t>PV-19</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>7396905.886</v>
+        <v>7397141.155</v>
       </c>
       <c r="F401" t="n">
-        <v>358329.956</v>
+        <v>358871.038</v>
       </c>
       <c r="G401" t="n">
-        <v>-23.5319548</v>
+        <v>-23.5298774</v>
       </c>
       <c r="H401" t="n">
-        <v>-46.387801</v>
+        <v>-46.3824796</v>
       </c>
       <c r="I401" t="n">
-        <v>767.159</v>
+        <v>787.357</v>
       </c>
       <c r="J401" t="n">
-        <v>765.927</v>
+        <v>783.357</v>
       </c>
       <c r="K401" t="n">
-        <v>1.23</v>
+        <v>4</v>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>Adicionado conforme solicitação: PI da RCE Elvira de Araujo; interligacao com CTS Joao Canzi mantida sem alterar registros existentes.</t>
+          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-18 ao PV-19.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>rce_elvira_de_araujo</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>ELVIRA-PI-1.2</t>
+          <t>JC-PV-17-FL07</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>PI-1.2</t>
+          <t>PV-17</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>7396922.192</v>
+        <v>7397122.275</v>
       </c>
       <c r="F402" t="n">
-        <v>358327.004</v>
+        <v>358726.884</v>
       </c>
       <c r="G402" t="n">
-        <v>-23.5318073</v>
+        <v>-23.5300354</v>
       </c>
       <c r="H402" t="n">
-        <v>-46.3878284</v>
+        <v>-46.3838931</v>
       </c>
       <c r="I402" t="n">
-        <v>767.21</v>
+        <v>782.299</v>
       </c>
       <c r="J402" t="n">
-        <v>766.01</v>
+        <v>779.199</v>
       </c>
       <c r="K402" t="n">
-        <v>1.2</v>
+        <v>3.1</v>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>Adicionado conforme solicitação: PI da RCE Elvira de Araujo; interligacao com CTS Joao Canzi mantida sem alterar registros existentes.</t>
+          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; trechos PV-16 ao PV-17 e PV-17 ao PV-18.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -19364,45 +19364,45 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>JC-PV-18</t>
+          <t>ELVIRA-PV-08</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>PV-18</t>
+          <t>PV-08</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>7397124.485</v>
+        <v>7396899.021</v>
       </c>
       <c r="F403" t="n">
-        <v>358806.429</v>
+        <v>358332.965</v>
       </c>
       <c r="G403" t="n">
-        <v>-23.5300224</v>
+        <v>-23.532017</v>
       </c>
       <c r="H403" t="n">
-        <v>-46.3831139</v>
+        <v>-46.3877722</v>
       </c>
       <c r="I403" t="n">
-        <v>783.619</v>
+        <v>767.145</v>
       </c>
       <c r="J403" t="n">
-        <v>780.119</v>
+        <v>762.845</v>
       </c>
       <c r="K403" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-18 ao PV-19.</t>
+          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -19412,45 +19412,45 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>JC-PV-19</t>
+          <t>ELVIRA-PV-02</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>PV-19</t>
+          <t>PV-02</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>7397141.155</v>
+        <v>7396941.756</v>
       </c>
       <c r="F404" t="n">
-        <v>358871.038</v>
+        <v>358324.032</v>
       </c>
       <c r="G404" t="n">
-        <v>-23.5298774</v>
+        <v>-23.5316304</v>
       </c>
       <c r="H404" t="n">
-        <v>-46.3824796</v>
+        <v>-46.3878556</v>
       </c>
       <c r="I404" t="n">
-        <v>787.357</v>
+        <v>767.318</v>
       </c>
       <c r="J404" t="n">
-        <v>783.357</v>
+        <v>763.468</v>
       </c>
       <c r="K404" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-18 ao PV-19.</t>
+          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -19460,38 +19460,38 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>JC-PV-17-FL07</t>
+          <t>ELVIRA-PV-01</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>PV-17</t>
+          <t>PV-01</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>7397122.275</v>
+        <v>7396903.634</v>
       </c>
       <c r="F405" t="n">
-        <v>358726.884</v>
+        <v>358332.744</v>
       </c>
       <c r="G405" t="n">
-        <v>-23.5300354</v>
+        <v>-23.5319754</v>
       </c>
       <c r="H405" t="n">
-        <v>-46.3838931</v>
+        <v>-46.3877739</v>
       </c>
       <c r="I405" t="n">
-        <v>782.299</v>
+        <v>767.2910000000001</v>
       </c>
       <c r="J405" t="n">
-        <v>779.199</v>
+        <v>763.0069999999999</v>
       </c>
       <c r="K405" t="n">
-        <v>3.1</v>
+        <v>4.28</v>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; trechos PV-16 ao PV-17 e PV-17 ao PV-18.</t>
+          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
         </is>
       </c>
     </row>
@@ -47933,12 +47933,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>JC-005</t>
+          <t>ELVIRA-001</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -47988,7 +47988,7 @@
       </c>
       <c r="N405" t="inlineStr">
         <is>
-          <t>Plano de furo FL-06 versao 01, 15.MAI.2026; RUA ELVIRA DE ARAUJO; taxa 0,0108.</t>
+          <t>Plano de furo FL-06 versao 01, 15.MAI.2026; PV-08 ao PV-02; RUA ELVIRA DE ARAUJO; arquivo: planos_furo/rce_elvira_fl06_pv08_pv02.pdf; taxa 0,0108. Movido do CTS Joao Canzi para RCE Elvira de Araujo em 09.JUN.2026.</t>
         </is>
       </c>
       <c r="O405" t="n">
@@ -48525,12 +48525,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>JC-010</t>
+          <t>ELVIRA-002</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -48580,7 +48580,7 @@
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t>Adicionado via print do projeto RCE Elvira de Araujo; complemento em VCA.</t>
+          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
         </is>
       </c>
       <c r="O413" t="n">
@@ -48599,12 +48599,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>JC-011</t>
+          <t>ELVIRA-003</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -48654,7 +48654,7 @@
       </c>
       <c r="N414" t="inlineStr">
         <is>
-          <t>Adicionado via print do projeto RCE Elvira de Araujo; complemento em VCA.</t>
+          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
         </is>
       </c>
       <c r="O414" t="n">
@@ -48673,12 +48673,12 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>JC-012</t>
+          <t>ELVIRA-004</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -48728,7 +48728,7 @@
       </c>
       <c r="N415" t="inlineStr">
         <is>
-          <t>Adicionado via print do projeto RCE Elvira de Araujo; complemento em VCA.</t>
+          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
         </is>
       </c>
       <c r="O415" t="n">

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEIA-ME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OBRAS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PONTOS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRECHOS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMO" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACAO" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACAO_SHAPE" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACAO_SHAPE_0505" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACAO_SHAPE_LUIS_0505" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACAO_SUBST_AGUA_BOA_0505" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="LEIA-ME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OBRAS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="PONTOS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="TRECHOS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="RESUMO" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="VALIDACAO" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="VALIDACAO_SHAPE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="VALIDACAO_SHAPE_0505" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="VALIDACAO_SHAPE_LUIS_0505" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="VALIDACAO_SUBST_AGUA_BOA_0505" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TRECHOS'!$A$1:$R$445</definedName>
@@ -21171,7 +21171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R452"/>
+  <dimension ref="A1:R453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -53094,6 +53094,80 @@
       </c>
       <c r="R452" t="n">
         <v>-46.3831139</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>JC-005</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>PV-10 - PV-11</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>PV-10</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>PV-11</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G453" t="n">
+        <v>355</v>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I453" t="n">
+        <v>62.673</v>
+      </c>
+      <c r="J453" t="n">
+        <v>3</v>
+      </c>
+      <c r="K453" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="L453" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-05; PV-10 ao PV-11; arquivo: planos_furo/cts_joao_canzi_fl05_pv10_pv11.pdf.</t>
+        </is>
+      </c>
+      <c r="O453" t="n">
+        <v>-23.5317269</v>
+      </c>
+      <c r="P453" t="n">
+        <v>-46.3867492</v>
+      </c>
+      <c r="Q453" t="n">
+        <v>-23.5315615</v>
+      </c>
+      <c r="R453" t="n">
+        <v>-46.3861622</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="LEIA-ME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="OBRAS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PONTOS" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="TRECHOS" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="RESUMO" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="VALIDACAO" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="VALIDACAO_SHAPE" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="VALIDACAO_SHAPE_0505" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="VALIDACAO_SHAPE_LUIS_0505" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="VALIDACAO_SUBST_AGUA_BOA_0505" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEIA-ME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OBRAS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PONTOS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TRECHOS" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMO" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACAO" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACAO_SHAPE" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACAO_SHAPE_0505" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACAO_SHAPE_LUIS_0505" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACAO_SUBST_AGUA_BOA_0505" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TRECHOS'!$A$1:$R$445</definedName>
@@ -1197,7 +1197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L440"/>
+  <dimension ref="A1:L441"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -21157,6 +21157,54 @@
       <c r="L440" t="inlineStr">
         <is>
           <t>Plano de furo FL-07 versao 01, 02.JUN.2026; trechos PV-16 ao PV-17 e PV-17 ao PV-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>JC-PV-20</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>PV-20</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>7397174.5</v>
+      </c>
+      <c r="F441" t="n">
+        <v>358918.3</v>
+      </c>
+      <c r="G441" t="n">
+        <v>-23.5295804</v>
+      </c>
+      <c r="H441" t="n">
+        <v>-46.3820136</v>
+      </c>
+      <c r="I441" t="n">
+        <v>794.6</v>
+      </c>
+      <c r="J441" t="n">
+        <v>790.638</v>
+      </c>
+      <c r="K441" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-19 ao PV-20.</t>
         </is>
       </c>
     </row>
@@ -53104,22 +53152,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>JC-005</t>
+          <t>JC-016</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>PV-10 - PV-11</t>
+          <t>PV-19 - PV-20</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>PV-10</t>
+          <t>PV-19</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>PV-11</t>
+          <t>PV-20</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
@@ -53136,16 +53184,16 @@
         </is>
       </c>
       <c r="I453" t="n">
-        <v>62.673</v>
+        <v>57.846</v>
       </c>
       <c r="J453" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K453" t="n">
-        <v>6.1</v>
+        <v>3.96</v>
       </c>
       <c r="L453" t="n">
-        <v>6.1</v>
+        <v>4</v>
       </c>
       <c r="M453" t="inlineStr">
         <is>
@@ -53154,20 +53202,20 @@
       </c>
       <c r="N453" t="inlineStr">
         <is>
-          <t>Plano de furo FL-05; PV-10 ao PV-11; arquivo: planos_furo/cts_joao_canzi_fl05_pv10_pv11.pdf.</t>
+          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; PV-19 ao PV-20; arquivo: planos_furo/cts_joao_canzi_fl07_pv19_pv20.pdf; taxa 0,1224.</t>
         </is>
       </c>
       <c r="O453" t="n">
-        <v>-23.5317269</v>
+        <v>-23.529877</v>
       </c>
       <c r="P453" t="n">
-        <v>-46.3867492</v>
+        <v>-46.3824799</v>
       </c>
       <c r="Q453" t="n">
-        <v>-23.5315615</v>
+        <v>-23.5295804</v>
       </c>
       <c r="R453" t="n">
-        <v>-46.3861622</v>
+        <v>-46.3820136</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -21219,7 +21219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R453"/>
+  <dimension ref="A1:R454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -49725,22 +49725,22 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>JC-006</t>
+          <t>JC-005</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>PV-11 - PV-13</t>
+          <t>PV-10 - PV-11</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
+          <t>PV-10</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
           <t>PV-11</t>
-        </is>
-      </c>
-      <c r="E406" t="inlineStr">
-        <is>
-          <t>PV-13</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
@@ -49757,13 +49757,13 @@
         </is>
       </c>
       <c r="I406" t="n">
-        <v>62.701</v>
+        <v>62.673</v>
       </c>
       <c r="J406" t="n">
+        <v>3</v>
+      </c>
+      <c r="K406" t="n">
         <v>6.1</v>
-      </c>
-      <c r="K406" t="n">
-        <v>2</v>
       </c>
       <c r="L406" t="n">
         <v>6.1</v>
@@ -49775,20 +49775,20 @@
       </c>
       <c r="N406" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; PV-11 ao PV-13; arquivo: planos_furo/cts_joao_canzi_fl07_pv11_pv13.pdf.</t>
+          <t>Plano de furo FL-05; PV-10 ao PV-11; arquivo: planos_furo/cts_joao_canzi_fl05_pv10_pv11.pdf.</t>
         </is>
       </c>
       <c r="O406" t="n">
+        <v>-23.5317269</v>
+      </c>
+      <c r="P406" t="n">
+        <v>-46.3867492</v>
+      </c>
+      <c r="Q406" t="n">
         <v>-23.5315615</v>
       </c>
-      <c r="P406" t="n">
+      <c r="R406" t="n">
         <v>-46.3861622</v>
-      </c>
-      <c r="Q406" t="n">
-        <v>-23.5310181</v>
-      </c>
-      <c r="R406" t="n">
-        <v>-46.3863345</v>
       </c>
     </row>
     <row r="407" hidden="1">
@@ -49799,22 +49799,22 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>JC-007</t>
+          <t>JC-006</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>PV-13 - PV-14</t>
+          <t>PV-11 - PV-13</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
+          <t>PV-11</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
           <t>PV-13</t>
-        </is>
-      </c>
-      <c r="E407" t="inlineStr">
-        <is>
-          <t>PV-14</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
@@ -49831,16 +49831,16 @@
         </is>
       </c>
       <c r="I407" t="n">
-        <v>80.157</v>
+        <v>62.701</v>
       </c>
       <c r="J407" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K407" t="n">
         <v>2</v>
       </c>
-      <c r="K407" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L407" t="n">
-        <v>4.5</v>
+        <v>6.1</v>
       </c>
       <c r="M407" t="inlineStr">
         <is>
@@ -49849,46 +49849,46 @@
       </c>
       <c r="N407" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; PV-13 ao PV-14; arquivo: planos_furo/cts_joao_canzi_fl07_pv13_pv14.pdf; taxa 0,0400.</t>
+          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; PV-11 ao PV-13; arquivo: planos_furo/cts_joao_canzi_fl07_pv11_pv13.pdf.</t>
         </is>
       </c>
       <c r="O407" t="n">
+        <v>-23.5315615</v>
+      </c>
+      <c r="P407" t="n">
+        <v>-46.3861622</v>
+      </c>
+      <c r="Q407" t="n">
         <v>-23.5310181</v>
       </c>
-      <c r="P407" t="n">
+      <c r="R407" t="n">
         <v>-46.3863345</v>
-      </c>
-      <c r="Q407" t="n">
-        <v>-23.5306805</v>
-      </c>
-      <c r="R407" t="n">
-        <v>-46.38564</v>
       </c>
     </row>
     <row r="408" hidden="1">
       <c r="A408" t="inlineStr">
         <is>
-          <t>cts_lourdes_complementar</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>LOUR-002</t>
+          <t>JC-007</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>PV-02 - PV-03</t>
+          <t>PV-13 - PV-14</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>PV-02</t>
+          <t>PV-13</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>PV-03</t>
+          <t>PV-14</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
@@ -49897,7 +49897,7 @@
         </is>
       </c>
       <c r="G408" t="n">
-        <v>450</v>
+        <v>355</v>
       </c>
       <c r="H408" t="inlineStr">
         <is>
@@ -49905,38 +49905,38 @@
         </is>
       </c>
       <c r="I408" t="n">
-        <v>78.58</v>
+        <v>80.157</v>
       </c>
       <c r="J408" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K408" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="L408" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>concluído</t>
+          <t>em andamento</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
         <is>
-          <t>Plano de furo FL-02 versao 01, 14.MAI.2026; RUA GONCALVES CASTELAO; PV-02 ao PV-03; arquivo: planos_furo/CT LOURDES - FL.02.PLANO DE FURO_PV-02 AO PV-03.pdf; taxa 0,0109.</t>
+          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; PV-13 ao PV-14; arquivo: planos_furo/cts_joao_canzi_fl07_pv13_pv14.pdf; taxa 0,0400.</t>
         </is>
       </c>
       <c r="O408" t="n">
-        <v>-23.52953</v>
+        <v>-23.5310181</v>
       </c>
       <c r="P408" t="n">
-        <v>-46.3942436</v>
+        <v>-46.3863345</v>
       </c>
       <c r="Q408" t="n">
-        <v>-23.5299216</v>
+        <v>-23.5306805</v>
       </c>
       <c r="R408" t="n">
-        <v>-46.3936017</v>
+        <v>-46.38564</v>
       </c>
     </row>
     <row r="409" hidden="1">
@@ -49947,22 +49947,22 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>LOUR-003</t>
+          <t>LOUR-002</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>PV-03 - PV-04</t>
+          <t>PV-02 - PV-03</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
+          <t>PV-02</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
           <t>PV-03</t>
-        </is>
-      </c>
-      <c r="E409" t="inlineStr">
-        <is>
-          <t>PV-04</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -49979,16 +49979,16 @@
         </is>
       </c>
       <c r="I409" t="n">
-        <v>78.843</v>
+        <v>78.58</v>
       </c>
       <c r="J409" t="n">
+        <v>4</v>
+      </c>
+      <c r="K409" t="n">
         <v>3.4</v>
       </c>
-      <c r="K409" t="n">
-        <v>5</v>
-      </c>
       <c r="L409" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="M409" t="inlineStr">
         <is>
@@ -49997,20 +49997,20 @@
       </c>
       <c r="N409" t="inlineStr">
         <is>
-          <t>Plano de furo FL-02 versao 01, 26.MAI.2026; PV-03 ao PV-04; arquivo: planos_furo/CT LOURDES - FL.02.PLANO DE FURO_PV-03 AO PV-04.pdf; taxa 0,0195.</t>
+          <t>Plano de furo FL-02 versao 01, 14.MAI.2026; RUA GONCALVES CASTELAO; PV-02 ao PV-03; arquivo: planos_furo/CT LOURDES - FL.02.PLANO DE FURO_PV-02 AO PV-03.pdf; taxa 0,0109.</t>
         </is>
       </c>
       <c r="O409" t="n">
+        <v>-23.52953</v>
+      </c>
+      <c r="P409" t="n">
+        <v>-46.3942436</v>
+      </c>
+      <c r="Q409" t="n">
         <v>-23.5299216</v>
       </c>
-      <c r="P409" t="n">
+      <c r="R409" t="n">
         <v>-46.3936017</v>
-      </c>
-      <c r="Q409" t="n">
-        <v>-23.5301962</v>
-      </c>
-      <c r="R409" t="n">
-        <v>-46.3928893</v>
       </c>
     </row>
     <row r="410" hidden="1">
@@ -50021,22 +50021,22 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>LOUR-004</t>
+          <t>LOUR-003</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>PV-04 - PV-05</t>
+          <t>PV-03 - PV-04</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
+          <t>PV-03</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
           <t>PV-04</t>
-        </is>
-      </c>
-      <c r="E410" t="inlineStr">
-        <is>
-          <t>PV-05</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -50053,16 +50053,16 @@
         </is>
       </c>
       <c r="I410" t="n">
-        <v>66.56999999999999</v>
+        <v>78.843</v>
       </c>
       <c r="J410" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K410" t="n">
         <v>5</v>
       </c>
-      <c r="K410" t="n">
-        <v>2.2</v>
-      </c>
       <c r="L410" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="M410" t="inlineStr">
         <is>
@@ -50071,46 +50071,46 @@
       </c>
       <c r="N410" t="inlineStr">
         <is>
-          <t>Plano de furo FL-02 versao 01, 26.MAI.2026; PV-04 ao PV-05; arquivo: planos_furo/CT LOURDES - FL.02.PLANO DE FURO_PV-04 AO PV-05.pdf; taxa 0,0142.</t>
+          <t>Plano de furo FL-02 versao 01, 26.MAI.2026; PV-03 ao PV-04; arquivo: planos_furo/CT LOURDES - FL.02.PLANO DE FURO_PV-03 AO PV-04.pdf; taxa 0,0195.</t>
         </is>
       </c>
       <c r="O410" t="n">
+        <v>-23.5299216</v>
+      </c>
+      <c r="P410" t="n">
+        <v>-46.3936017</v>
+      </c>
+      <c r="Q410" t="n">
         <v>-23.5301962</v>
       </c>
-      <c r="P410" t="n">
+      <c r="R410" t="n">
         <v>-46.3928893</v>
-      </c>
-      <c r="Q410" t="n">
-        <v>-23.530465</v>
-      </c>
-      <c r="R410" t="n">
-        <v>-46.3923061</v>
       </c>
     </row>
     <row r="411" hidden="1">
       <c r="A411" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>cts_lourdes_complementar</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>JC-008</t>
+          <t>LOUR-004</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>PV-15 - PV-16</t>
+          <t>PV-04 - PV-05</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>PV-15</t>
+          <t>PV-04</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>PV-16</t>
+          <t>PV-05</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
@@ -50119,7 +50119,7 @@
         </is>
       </c>
       <c r="G411" t="n">
-        <v>355</v>
+        <v>450</v>
       </c>
       <c r="H411" t="inlineStr">
         <is>
@@ -50127,38 +50127,38 @@
         </is>
       </c>
       <c r="I411" t="n">
-        <v>85.03</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="J411" t="n">
+        <v>5</v>
+      </c>
+      <c r="K411" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L411" t="n">
         <v>5.5</v>
       </c>
-      <c r="K411" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L411" t="n">
-        <v>5.9</v>
-      </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>em andamento</t>
+          <t>concluído</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
         <is>
-          <t>Plano de furo FL-08 versao 01, 26.MAI.2026; PV-15 ao PV-16; arquivo: planos_furo/cts_joao_canzi_fl08_pv15_pv16.pdf; taxa 0,0125.</t>
+          <t>Plano de furo FL-02 versao 01, 26.MAI.2026; PV-04 ao PV-05; arquivo: planos_furo/CT LOURDES - FL.02.PLANO DE FURO_PV-04 AO PV-05.pdf; taxa 0,0142.</t>
         </is>
       </c>
       <c r="O411" t="n">
-        <v>-23.5304128</v>
+        <v>-23.5301962</v>
       </c>
       <c r="P411" t="n">
-        <v>-46.3852142</v>
+        <v>-46.3928893</v>
       </c>
       <c r="Q411" t="n">
-        <v>-23.5299843</v>
+        <v>-23.530465</v>
       </c>
       <c r="R411" t="n">
-        <v>-46.3845231</v>
+        <v>-46.3923061</v>
       </c>
     </row>
     <row r="412" hidden="1">
@@ -50169,22 +50169,22 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>JC-009</t>
+          <t>JC-008</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>PV-14 - PV-15</t>
+          <t>PV-15 - PV-16</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>PV-14</t>
+          <t>PV-15</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>PV-15</t>
+          <t>PV-16</t>
         </is>
       </c>
       <c r="F412" t="inlineStr">
@@ -50201,16 +50201,16 @@
         </is>
       </c>
       <c r="I412" t="n">
-        <v>52.62</v>
+        <v>85.03</v>
       </c>
       <c r="J412" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="K412" t="n">
-        <v>5.5</v>
+        <v>3.1</v>
       </c>
       <c r="L412" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="M412" t="inlineStr">
         <is>
@@ -50219,72 +50219,72 @@
       </c>
       <c r="N412" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; PV-14 ao PV-15; arquivo: planos_furo/cts_joao_canzi_fl07_pv14_pv15.pdf; taxa 0,0095.</t>
+          <t>Plano de furo FL-08 versao 01, 26.MAI.2026; PV-15 ao PV-16; arquivo: planos_furo/cts_joao_canzi_fl08_pv15_pv16.pdf; taxa 0,0125.</t>
         </is>
       </c>
       <c r="O412" t="n">
-        <v>-23.5306805</v>
+        <v>-23.5304128</v>
       </c>
       <c r="P412" t="n">
-        <v>-46.38564</v>
+        <v>-46.3852142</v>
       </c>
       <c r="Q412" t="n">
-        <v>-23.5304128</v>
+        <v>-23.5299843</v>
       </c>
       <c r="R412" t="n">
-        <v>-46.3852142</v>
+        <v>-46.3845231</v>
       </c>
     </row>
     <row r="413" hidden="1">
       <c r="A413" t="inlineStr">
         <is>
-          <t>rce_elvira_de_araujo</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>ELVIRA-002</t>
+          <t>JC-009</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>PV-01 - PI-1.1</t>
+          <t>PV-14 - PV-15</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>PV-01</t>
+          <t>PV-14</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>PI-1.1</t>
+          <t>PV-15</t>
         </is>
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD LISO</t>
         </is>
       </c>
       <c r="G413" t="n">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Metodo Nao Destrutivo - MND</t>
         </is>
       </c>
       <c r="I413" t="n">
-        <v>3.58</v>
+        <v>52.62</v>
       </c>
       <c r="J413" t="n">
-        <v>4.28</v>
+        <v>4.5</v>
       </c>
       <c r="K413" t="n">
-        <v>1.23</v>
+        <v>5.5</v>
       </c>
       <c r="L413" t="n">
-        <v>4.28</v>
+        <v>5.5</v>
       </c>
       <c r="M413" t="inlineStr">
         <is>
@@ -50293,20 +50293,20 @@
       </c>
       <c r="N413" t="inlineStr">
         <is>
-          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
+          <t>Plano de furo FL-07 versao 01, 20.MAI.2026; PV-14 ao PV-15; arquivo: planos_furo/cts_joao_canzi_fl07_pv14_pv15.pdf; taxa 0,0095.</t>
         </is>
       </c>
       <c r="O413" t="n">
-        <v>-23.5319754</v>
+        <v>-23.5306805</v>
       </c>
       <c r="P413" t="n">
-        <v>-46.3877739</v>
+        <v>-46.38564</v>
       </c>
       <c r="Q413" t="n">
-        <v>-23.5319548</v>
+        <v>-23.5304128</v>
       </c>
       <c r="R413" t="n">
-        <v>-46.387801</v>
+        <v>-46.3852142</v>
       </c>
     </row>
     <row r="414" hidden="1">
@@ -50317,22 +50317,22 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>ELVIRA-003</t>
+          <t>ELVIRA-002</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>PI-1.1 - PI-1.2</t>
+          <t>PV-01 - PI-1.1</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
+          <t>PV-01</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
           <t>PI-1.1</t>
-        </is>
-      </c>
-      <c r="E414" t="inlineStr">
-        <is>
-          <t>PI-1.2</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
@@ -50349,16 +50349,16 @@
         </is>
       </c>
       <c r="I414" t="n">
-        <v>16.62</v>
+        <v>3.58</v>
       </c>
       <c r="J414" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="K414" t="n">
         <v>1.23</v>
       </c>
-      <c r="K414" t="n">
-        <v>1.2</v>
-      </c>
       <c r="L414" t="n">
-        <v>1.23</v>
+        <v>4.28</v>
       </c>
       <c r="M414" t="inlineStr">
         <is>
@@ -50371,16 +50371,16 @@
         </is>
       </c>
       <c r="O414" t="n">
+        <v>-23.5319754</v>
+      </c>
+      <c r="P414" t="n">
+        <v>-46.3877739</v>
+      </c>
+      <c r="Q414" t="n">
         <v>-23.5319548</v>
       </c>
-      <c r="P414" t="n">
+      <c r="R414" t="n">
         <v>-46.387801</v>
-      </c>
-      <c r="Q414" t="n">
-        <v>-23.5318073</v>
-      </c>
-      <c r="R414" t="n">
-        <v>-46.3878284</v>
       </c>
     </row>
     <row r="415" hidden="1">
@@ -50391,22 +50391,22 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>ELVIRA-004</t>
+          <t>ELVIRA-003</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>PI-1.2 - PV-02</t>
+          <t>PI-1.1 - PI-1.2</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
+          <t>PI-1.1</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
           <t>PI-1.2</t>
-        </is>
-      </c>
-      <c r="E415" t="inlineStr">
-        <is>
-          <t>PV-02</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
@@ -50423,16 +50423,16 @@
         </is>
       </c>
       <c r="I415" t="n">
-        <v>5</v>
+        <v>16.62</v>
       </c>
       <c r="J415" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="K415" t="n">
         <v>1.2</v>
       </c>
-      <c r="K415" t="n">
-        <v>4.01</v>
-      </c>
       <c r="L415" t="n">
-        <v>4.01</v>
+        <v>1.23</v>
       </c>
       <c r="M415" t="inlineStr">
         <is>
@@ -50445,42 +50445,42 @@
         </is>
       </c>
       <c r="O415" t="n">
+        <v>-23.5319548</v>
+      </c>
+      <c r="P415" t="n">
+        <v>-46.387801</v>
+      </c>
+      <c r="Q415" t="n">
         <v>-23.5318073</v>
       </c>
-      <c r="P415" t="n">
+      <c r="R415" t="n">
         <v>-46.3878284</v>
-      </c>
-      <c r="Q415" t="n">
-        <v>-23.5317625</v>
-      </c>
-      <c r="R415" t="n">
-        <v>-46.3878221</v>
       </c>
     </row>
     <row r="416" hidden="1">
       <c r="A416" t="inlineStr">
         <is>
-          <t>rce_elias_sleiman</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>ELIAS-001</t>
+          <t>ELVIRA-004</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>PV-21 - PV-22</t>
+          <t>PI-1.2 - PV-02</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>PV-21</t>
+          <t>PI-1.2</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>PV-22</t>
+          <t>PV-02</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -50497,16 +50497,16 @@
         </is>
       </c>
       <c r="I416" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="J416" t="n">
-        <v>2.08</v>
+        <v>1.2</v>
       </c>
       <c r="K416" t="n">
-        <v>2.08</v>
+        <v>4.01</v>
       </c>
       <c r="L416" t="n">
-        <v>2.08</v>
+        <v>4.01</v>
       </c>
       <c r="M416" t="inlineStr">
         <is>
@@ -50515,20 +50515,20 @@
       </c>
       <c r="N416" t="inlineStr">
         <is>
-          <t>Adicionado via print do projeto RCE Elias Sleiman; lancamento completo em VCA.</t>
+          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
         </is>
       </c>
       <c r="O416" t="n">
-        <v>-23.5301384</v>
+        <v>-23.5318073</v>
       </c>
       <c r="P416" t="n">
-        <v>-46.3836941</v>
+        <v>-46.3878284</v>
       </c>
       <c r="Q416" t="n">
-        <v>-23.5307098</v>
+        <v>-23.5317625</v>
       </c>
       <c r="R416" t="n">
-        <v>-46.3834008</v>
+        <v>-46.3878221</v>
       </c>
     </row>
     <row r="417" hidden="1">
@@ -50539,22 +50539,22 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>ELIAS-002</t>
+          <t>ELIAS-001</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>PV-22 - PV-23</t>
+          <t>PV-21 - PV-22</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
+          <t>PV-21</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
           <t>PV-22</t>
-        </is>
-      </c>
-      <c r="E417" t="inlineStr">
-        <is>
-          <t>PV-23</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -50571,16 +50571,16 @@
         </is>
       </c>
       <c r="I417" t="n">
-        <v>33.03</v>
+        <v>70</v>
       </c>
       <c r="J417" t="n">
         <v>2.08</v>
       </c>
       <c r="K417" t="n">
-        <v>3.58</v>
+        <v>2.08</v>
       </c>
       <c r="L417" t="n">
-        <v>3.58</v>
+        <v>2.08</v>
       </c>
       <c r="M417" t="inlineStr">
         <is>
@@ -50593,68 +50593,68 @@
         </is>
       </c>
       <c r="O417" t="n">
+        <v>-23.5301384</v>
+      </c>
+      <c r="P417" t="n">
+        <v>-46.3836941</v>
+      </c>
+      <c r="Q417" t="n">
         <v>-23.5307098</v>
       </c>
-      <c r="P417" t="n">
+      <c r="R417" t="n">
         <v>-46.3834008</v>
-      </c>
-      <c r="Q417" t="n">
-        <v>-23.5309793</v>
-      </c>
-      <c r="R417" t="n">
-        <v>-46.3832624</v>
       </c>
     </row>
     <row r="418" hidden="1">
       <c r="A418" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_elias_sleiman</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>JC-013</t>
+          <t>ELIAS-002</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>PV-18 - PV-19</t>
+          <t>PV-22 - PV-23</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>PV-18</t>
+          <t>PV-22</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>PV-19</t>
+          <t>PV-23</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>PEAD LISO</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="G418" t="n">
-        <v>355</v>
+        <v>200</v>
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Metodo Nao Destrutivo - MND</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I418" t="n">
-        <v>66.72499999999999</v>
+        <v>33.03</v>
       </c>
       <c r="J418" t="n">
-        <v>3.5</v>
+        <v>2.08</v>
       </c>
       <c r="K418" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="L418" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="M418" t="inlineStr">
         <is>
@@ -50663,72 +50663,72 @@
       </c>
       <c r="N418" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; PV-18 ao PV-19; arquivo: planos_furo/cts_joao_canzi_fl07_pv18_pv19.pdf; taxa 0,0485.</t>
+          <t>Adicionado via print do projeto RCE Elias Sleiman; lancamento completo em VCA.</t>
         </is>
       </c>
       <c r="O418" t="n">
-        <v>-23.5300224</v>
+        <v>-23.5307098</v>
       </c>
       <c r="P418" t="n">
-        <v>-46.3831139</v>
+        <v>-46.3834008</v>
       </c>
       <c r="Q418" t="n">
-        <v>-23.5298774</v>
+        <v>-23.5309793</v>
       </c>
       <c r="R418" t="n">
-        <v>-46.3824796</v>
+        <v>-46.3832624</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>SL-001</t>
+          <t>JC-013</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>PV-26 - PV-27</t>
+          <t>PV-18 - PV-19</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>PV-26</t>
+          <t>PV-18</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>PV-27</t>
+          <t>PV-19</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD LISO</t>
         </is>
       </c>
       <c r="G419" t="n">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Metodo Nao Destrutivo - MND</t>
         </is>
       </c>
       <c r="I419" t="n">
-        <v>14.74</v>
+        <v>66.72499999999999</v>
       </c>
       <c r="J419" t="n">
-        <v>3.04</v>
+        <v>3.5</v>
       </c>
       <c r="K419" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="L419" t="n">
-        <v>3.57</v>
+        <v>4</v>
       </c>
       <c r="M419" t="inlineStr">
         <is>
@@ -50737,20 +50737,20 @@
       </c>
       <c r="N419" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
+          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; PV-18 ao PV-19; arquivo: planos_furo/cts_joao_canzi_fl07_pv18_pv19.pdf; taxa 0,0485.</t>
         </is>
       </c>
       <c r="O419" t="n">
-        <v>-23.5236471</v>
+        <v>-23.5300224</v>
       </c>
       <c r="P419" t="n">
-        <v>-46.3767998</v>
+        <v>-46.3831139</v>
       </c>
       <c r="Q419" t="n">
-        <v>-23.5237798</v>
+        <v>-23.5298774</v>
       </c>
       <c r="R419" t="n">
-        <v>-46.3767878</v>
+        <v>-46.3824796</v>
       </c>
     </row>
     <row r="420">
@@ -50761,22 +50761,22 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>SL-002</t>
+          <t>SL-001</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>PV-27 - PV-28</t>
+          <t>PV-26 - PV-27</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
+          <t>PV-26</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
           <t>PV-27</t>
-        </is>
-      </c>
-      <c r="E420" t="inlineStr">
-        <is>
-          <t>PV-28</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -50793,13 +50793,13 @@
         </is>
       </c>
       <c r="I420" t="n">
-        <v>3.63</v>
+        <v>14.74</v>
       </c>
       <c r="J420" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="K420" t="n">
         <v>3.57</v>
-      </c>
-      <c r="K420" t="n">
-        <v>3.34</v>
       </c>
       <c r="L420" t="n">
         <v>3.57</v>
@@ -50815,16 +50815,16 @@
         </is>
       </c>
       <c r="O420" t="n">
+        <v>-23.5236471</v>
+      </c>
+      <c r="P420" t="n">
+        <v>-46.3767998</v>
+      </c>
+      <c r="Q420" t="n">
         <v>-23.5237798</v>
       </c>
-      <c r="P420" t="n">
+      <c r="R420" t="n">
         <v>-46.3767878</v>
-      </c>
-      <c r="Q420" t="n">
-        <v>-23.5238121</v>
-      </c>
-      <c r="R420" t="n">
-        <v>-46.3767936</v>
       </c>
     </row>
     <row r="421">
@@ -50835,22 +50835,22 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>SL-003</t>
+          <t>SL-002</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>PV-28 - PV-29</t>
+          <t>PV-27 - PV-28</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
+          <t>PV-27</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
           <t>PV-28</t>
-        </is>
-      </c>
-      <c r="E421" t="inlineStr">
-        <is>
-          <t>PV-29</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -50867,16 +50867,16 @@
         </is>
       </c>
       <c r="I421" t="n">
-        <v>7.51</v>
+        <v>3.63</v>
       </c>
       <c r="J421" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="K421" t="n">
         <v>3.34</v>
       </c>
-      <c r="K421" t="n">
-        <v>1.81</v>
-      </c>
       <c r="L421" t="n">
-        <v>3.34</v>
+        <v>3.57</v>
       </c>
       <c r="M421" t="inlineStr">
         <is>
@@ -50889,16 +50889,16 @@
         </is>
       </c>
       <c r="O421" t="n">
+        <v>-23.5237798</v>
+      </c>
+      <c r="P421" t="n">
+        <v>-46.3767878</v>
+      </c>
+      <c r="Q421" t="n">
         <v>-23.5238121</v>
       </c>
-      <c r="P421" t="n">
+      <c r="R421" t="n">
         <v>-46.3767936</v>
-      </c>
-      <c r="Q421" t="n">
-        <v>-23.5238331</v>
-      </c>
-      <c r="R421" t="n">
-        <v>-46.3768636</v>
       </c>
     </row>
     <row r="422">
@@ -50909,22 +50909,22 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>SL-004</t>
+          <t>SL-003</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>PV-29 - PV-30</t>
+          <t>PV-28 - PV-29</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
+          <t>PV-28</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
           <t>PV-29</t>
-        </is>
-      </c>
-      <c r="E422" t="inlineStr">
-        <is>
-          <t>PV-30</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -50941,16 +50941,16 @@
         </is>
       </c>
       <c r="I422" t="n">
-        <v>13.61</v>
+        <v>7.51</v>
       </c>
       <c r="J422" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="K422" t="n">
         <v>1.81</v>
       </c>
-      <c r="K422" t="n">
-        <v>1.4</v>
-      </c>
       <c r="L422" t="n">
-        <v>1.81</v>
+        <v>3.34</v>
       </c>
       <c r="M422" t="inlineStr">
         <is>
@@ -50963,16 +50963,16 @@
         </is>
       </c>
       <c r="O422" t="n">
+        <v>-23.5238121</v>
+      </c>
+      <c r="P422" t="n">
+        <v>-46.3767936</v>
+      </c>
+      <c r="Q422" t="n">
         <v>-23.5238331</v>
       </c>
-      <c r="P422" t="n">
+      <c r="R422" t="n">
         <v>-46.3768636</v>
-      </c>
-      <c r="Q422" t="n">
-        <v>-23.5237849</v>
-      </c>
-      <c r="R422" t="n">
-        <v>-46.3769862</v>
       </c>
     </row>
     <row r="423">
@@ -50983,22 +50983,22 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>SL-005</t>
+          <t>SL-004</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>PV-30 - PV-31</t>
+          <t>PV-29 - PV-30</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
+          <t>PV-29</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
           <t>PV-30</t>
-        </is>
-      </c>
-      <c r="E423" t="inlineStr">
-        <is>
-          <t>PV-31</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -51015,16 +51015,16 @@
         </is>
       </c>
       <c r="I423" t="n">
-        <v>6.62</v>
+        <v>13.61</v>
       </c>
       <c r="J423" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="K423" t="n">
         <v>1.4</v>
       </c>
-      <c r="K423" t="n">
-        <v>1.43</v>
-      </c>
       <c r="L423" t="n">
-        <v>1.43</v>
+        <v>1.81</v>
       </c>
       <c r="M423" t="inlineStr">
         <is>
@@ -51037,16 +51037,16 @@
         </is>
       </c>
       <c r="O423" t="n">
+        <v>-23.5238331</v>
+      </c>
+      <c r="P423" t="n">
+        <v>-46.3768636</v>
+      </c>
+      <c r="Q423" t="n">
         <v>-23.5237849</v>
       </c>
-      <c r="P423" t="n">
+      <c r="R423" t="n">
         <v>-46.3769862</v>
-      </c>
-      <c r="Q423" t="n">
-        <v>-23.5237689</v>
-      </c>
-      <c r="R423" t="n">
-        <v>-46.3770487</v>
       </c>
     </row>
     <row r="424">
@@ -51057,22 +51057,22 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>SL-006</t>
+          <t>SL-005</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>PV-31 - PV-32</t>
+          <t>PV-30 - PV-31</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
+          <t>PV-30</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
           <t>PV-31</t>
-        </is>
-      </c>
-      <c r="E424" t="inlineStr">
-        <is>
-          <t>PV-32</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -51089,16 +51089,16 @@
         </is>
       </c>
       <c r="I424" t="n">
-        <v>70.89</v>
+        <v>6.62</v>
       </c>
       <c r="J424" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="K424" t="n">
         <v>1.43</v>
       </c>
-      <c r="K424" t="n">
-        <v>2.18</v>
-      </c>
       <c r="L424" t="n">
-        <v>2.18</v>
+        <v>1.43</v>
       </c>
       <c r="M424" t="inlineStr">
         <is>
@@ -51111,16 +51111,16 @@
         </is>
       </c>
       <c r="O424" t="n">
+        <v>-23.5237849</v>
+      </c>
+      <c r="P424" t="n">
+        <v>-46.3769862</v>
+      </c>
+      <c r="Q424" t="n">
         <v>-23.5237689</v>
       </c>
-      <c r="P424" t="n">
+      <c r="R424" t="n">
         <v>-46.3770487</v>
-      </c>
-      <c r="Q424" t="n">
-        <v>-23.5233519</v>
-      </c>
-      <c r="R424" t="n">
-        <v>-46.3775754</v>
       </c>
     </row>
     <row r="425">
@@ -51131,22 +51131,22 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>SL-007</t>
+          <t>SL-006</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>PV-32 - PV-33</t>
+          <t>PV-31 - PV-32</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
+          <t>PV-31</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
           <t>PV-32</t>
-        </is>
-      </c>
-      <c r="E425" t="inlineStr">
-        <is>
-          <t>PV-33</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -51163,13 +51163,13 @@
         </is>
       </c>
       <c r="I425" t="n">
-        <v>62.56</v>
+        <v>70.89</v>
       </c>
       <c r="J425" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="K425" t="n">
         <v>2.18</v>
-      </c>
-      <c r="K425" t="n">
-        <v>2.16</v>
       </c>
       <c r="L425" t="n">
         <v>2.18</v>
@@ -51185,16 +51185,16 @@
         </is>
       </c>
       <c r="O425" t="n">
+        <v>-23.5237689</v>
+      </c>
+      <c r="P425" t="n">
+        <v>-46.3770487</v>
+      </c>
+      <c r="Q425" t="n">
         <v>-23.5233519</v>
       </c>
-      <c r="P425" t="n">
+      <c r="R425" t="n">
         <v>-46.3775754</v>
-      </c>
-      <c r="Q425" t="n">
-        <v>-23.5230626</v>
-      </c>
-      <c r="R425" t="n">
-        <v>-46.3781017</v>
       </c>
     </row>
     <row r="426">
@@ -51205,22 +51205,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>SL-008</t>
+          <t>SL-007</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>PV-33 - PV-34</t>
+          <t>PV-32 - PV-33</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
+          <t>PV-32</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
           <t>PV-33</t>
-        </is>
-      </c>
-      <c r="E426" t="inlineStr">
-        <is>
-          <t>PV-34</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -51237,16 +51237,16 @@
         </is>
       </c>
       <c r="I426" t="n">
-        <v>55.46</v>
+        <v>62.56</v>
       </c>
       <c r="J426" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="K426" t="n">
         <v>2.16</v>
       </c>
-      <c r="K426" t="n">
-        <v>2.45</v>
-      </c>
       <c r="L426" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="M426" t="inlineStr">
         <is>
@@ -51259,16 +51259,16 @@
         </is>
       </c>
       <c r="O426" t="n">
+        <v>-23.5233519</v>
+      </c>
+      <c r="P426" t="n">
+        <v>-46.3775754</v>
+      </c>
+      <c r="Q426" t="n">
         <v>-23.5230626</v>
       </c>
-      <c r="P426" t="n">
+      <c r="R426" t="n">
         <v>-46.3781017</v>
-      </c>
-      <c r="Q426" t="n">
-        <v>-23.5226874</v>
-      </c>
-      <c r="R426" t="n">
-        <v>-46.3784614</v>
       </c>
     </row>
     <row r="427">
@@ -51279,22 +51279,22 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>SL-009</t>
+          <t>SL-008</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>PV-34 - PV-35</t>
+          <t>PV-33 - PV-34</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
+          <t>PV-33</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
           <t>PV-34</t>
-        </is>
-      </c>
-      <c r="E427" t="inlineStr">
-        <is>
-          <t>PV-35</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -51311,16 +51311,16 @@
         </is>
       </c>
       <c r="I427" t="n">
-        <v>57.62</v>
+        <v>55.46</v>
       </c>
       <c r="J427" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K427" t="n">
         <v>2.45</v>
       </c>
-      <c r="K427" t="n">
-        <v>3.88</v>
-      </c>
       <c r="L427" t="n">
-        <v>3.88</v>
+        <v>2.45</v>
       </c>
       <c r="M427" t="inlineStr">
         <is>
@@ -51333,16 +51333,16 @@
         </is>
       </c>
       <c r="O427" t="n">
+        <v>-23.5230626</v>
+      </c>
+      <c r="P427" t="n">
+        <v>-46.3781017</v>
+      </c>
+      <c r="Q427" t="n">
         <v>-23.5226874</v>
       </c>
-      <c r="P427" t="n">
+      <c r="R427" t="n">
         <v>-46.3784614</v>
-      </c>
-      <c r="Q427" t="n">
-        <v>-23.5223561</v>
-      </c>
-      <c r="R427" t="n">
-        <v>-46.3788967</v>
       </c>
     </row>
     <row r="428">
@@ -51353,22 +51353,22 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>SL-010</t>
+          <t>SL-009</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>PV-35 - PV-36</t>
+          <t>PV-34 - PV-35</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
+          <t>PV-34</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
           <t>PV-35</t>
-        </is>
-      </c>
-      <c r="E428" t="inlineStr">
-        <is>
-          <t>PV-36</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -51385,16 +51385,16 @@
         </is>
       </c>
       <c r="I428" t="n">
-        <v>27.35</v>
+        <v>57.62</v>
       </c>
       <c r="J428" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K428" t="n">
         <v>3.88</v>
       </c>
-      <c r="K428" t="n">
-        <v>3.97</v>
-      </c>
       <c r="L428" t="n">
-        <v>3.97</v>
+        <v>3.88</v>
       </c>
       <c r="M428" t="inlineStr">
         <is>
@@ -51407,16 +51407,16 @@
         </is>
       </c>
       <c r="O428" t="n">
+        <v>-23.5226874</v>
+      </c>
+      <c r="P428" t="n">
+        <v>-46.3784614</v>
+      </c>
+      <c r="Q428" t="n">
         <v>-23.5223561</v>
       </c>
-      <c r="P428" t="n">
+      <c r="R428" t="n">
         <v>-46.3788967</v>
-      </c>
-      <c r="Q428" t="n">
-        <v>-23.5221552</v>
-      </c>
-      <c r="R428" t="n">
-        <v>-46.3790525</v>
       </c>
     </row>
     <row r="429">
@@ -51427,22 +51427,22 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>SL-011</t>
+          <t>SL-010</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>PV-36 - PV-37</t>
+          <t>PV-35 - PV-36</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
+          <t>PV-35</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
           <t>PV-36</t>
-        </is>
-      </c>
-      <c r="E429" t="inlineStr">
-        <is>
-          <t>PV-37</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -51459,13 +51459,13 @@
         </is>
       </c>
       <c r="I429" t="n">
-        <v>10.49</v>
+        <v>27.35</v>
       </c>
       <c r="J429" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K429" t="n">
         <v>3.97</v>
-      </c>
-      <c r="K429" t="n">
-        <v>3.75</v>
       </c>
       <c r="L429" t="n">
         <v>3.97</v>
@@ -51481,16 +51481,16 @@
         </is>
       </c>
       <c r="O429" t="n">
+        <v>-23.5223561</v>
+      </c>
+      <c r="P429" t="n">
+        <v>-46.3788967</v>
+      </c>
+      <c r="Q429" t="n">
         <v>-23.5221552</v>
       </c>
-      <c r="P429" t="n">
+      <c r="R429" t="n">
         <v>-46.3790525</v>
-      </c>
-      <c r="Q429" t="n">
-        <v>-23.5220801</v>
-      </c>
-      <c r="R429" t="n">
-        <v>-46.379115</v>
       </c>
     </row>
     <row r="430">
@@ -51501,22 +51501,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>SL-012</t>
+          <t>SL-011</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>PV-37 - PV-38</t>
+          <t>PV-36 - PV-37</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
+          <t>PV-36</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
           <t>PV-37</t>
-        </is>
-      </c>
-      <c r="E430" t="inlineStr">
-        <is>
-          <t>PV-38</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -51529,20 +51529,20 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I430" t="n">
-        <v>16.89</v>
+        <v>10.49</v>
       </c>
       <c r="J430" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="K430" t="n">
         <v>3.75</v>
       </c>
-      <c r="K430" t="n">
-        <v>3.92</v>
-      </c>
       <c r="L430" t="n">
-        <v>3.92</v>
+        <v>3.97</v>
       </c>
       <c r="M430" t="inlineStr">
         <is>
@@ -51551,20 +51551,20 @@
       </c>
       <c r="N430" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. PV-38 incluido conforme novo print.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
         </is>
       </c>
       <c r="O430" t="n">
+        <v>-23.5221552</v>
+      </c>
+      <c r="P430" t="n">
+        <v>-46.3790525</v>
+      </c>
+      <c r="Q430" t="n">
         <v>-23.5220801</v>
       </c>
-      <c r="P430" t="n">
+      <c r="R430" t="n">
         <v>-46.379115</v>
-      </c>
-      <c r="Q430" t="n">
-        <v>-23.5220422</v>
-      </c>
-      <c r="R430" t="n">
-        <v>-46.3789548</v>
       </c>
     </row>
     <row r="431">
@@ -51575,22 +51575,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>SL-013</t>
+          <t>SL-012</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>PV-38 - PV-39</t>
+          <t>PV-37 - PV-38</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
+          <t>PV-37</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
           <t>PV-38</t>
-        </is>
-      </c>
-      <c r="E431" t="inlineStr">
-        <is>
-          <t>PV-39</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -51607,13 +51607,13 @@
         </is>
       </c>
       <c r="I431" t="n">
-        <v>46.47</v>
+        <v>16.89</v>
       </c>
       <c r="J431" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K431" t="n">
         <v>3.92</v>
-      </c>
-      <c r="K431" t="n">
-        <v>3.64</v>
       </c>
       <c r="L431" t="n">
         <v>3.92</v>
@@ -51629,16 +51629,16 @@
         </is>
       </c>
       <c r="O431" t="n">
+        <v>-23.5220801</v>
+      </c>
+      <c r="P431" t="n">
+        <v>-46.379115</v>
+      </c>
+      <c r="Q431" t="n">
         <v>-23.5220422</v>
       </c>
-      <c r="P431" t="n">
+      <c r="R431" t="n">
         <v>-46.3789548</v>
-      </c>
-      <c r="Q431" t="n">
-        <v>-23.5222906</v>
-      </c>
-      <c r="R431" t="n">
-        <v>-46.378588</v>
       </c>
     </row>
     <row r="432">
@@ -51649,22 +51649,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>SL-014</t>
+          <t>SL-013</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>PV-40 - PV-41</t>
+          <t>PV-38 - PV-39</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>PV-40</t>
+          <t>PV-38</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>PV-41</t>
+          <t>PV-39</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -51677,20 +51677,20 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I432" t="n">
-        <v>48.64</v>
+        <v>46.47</v>
       </c>
       <c r="J432" t="n">
-        <v>4.31</v>
+        <v>3.92</v>
       </c>
       <c r="K432" t="n">
-        <v>2.58</v>
+        <v>3.64</v>
       </c>
       <c r="L432" t="n">
-        <v>4.31</v>
+        <v>3.92</v>
       </c>
       <c r="M432" t="inlineStr">
         <is>
@@ -51699,20 +51699,20 @@
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. PV-38 incluido conforme novo print.</t>
         </is>
       </c>
       <c r="O432" t="n">
-        <v>-23.5224137</v>
+        <v>-23.5220422</v>
       </c>
       <c r="P432" t="n">
-        <v>-46.3783767</v>
+        <v>-46.3789548</v>
       </c>
       <c r="Q432" t="n">
-        <v>-23.5227141</v>
+        <v>-23.5222906</v>
       </c>
       <c r="R432" t="n">
-        <v>-46.378029</v>
+        <v>-46.378588</v>
       </c>
     </row>
     <row r="433">
@@ -51723,22 +51723,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>SL-015</t>
+          <t>SL-014</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>PV-41 - PV-42</t>
+          <t>PV-40 - PV-41</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
+          <t>PV-40</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
           <t>PV-41</t>
-        </is>
-      </c>
-      <c r="E433" t="inlineStr">
-        <is>
-          <t>PV-42</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -51755,16 +51755,16 @@
         </is>
       </c>
       <c r="I433" t="n">
-        <v>38.45</v>
+        <v>48.64</v>
       </c>
       <c r="J433" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="K433" t="n">
         <v>2.58</v>
       </c>
-      <c r="K433" t="n">
-        <v>1.41</v>
-      </c>
       <c r="L433" t="n">
-        <v>2.58</v>
+        <v>4.31</v>
       </c>
       <c r="M433" t="inlineStr">
         <is>
@@ -51777,16 +51777,16 @@
         </is>
       </c>
       <c r="O433" t="n">
+        <v>-23.5224137</v>
+      </c>
+      <c r="P433" t="n">
+        <v>-46.3783767</v>
+      </c>
+      <c r="Q433" t="n">
         <v>-23.5227141</v>
       </c>
-      <c r="P433" t="n">
+      <c r="R433" t="n">
         <v>-46.378029</v>
-      </c>
-      <c r="Q433" t="n">
-        <v>-23.52298</v>
-      </c>
-      <c r="R433" t="n">
-        <v>-46.3777869</v>
       </c>
     </row>
     <row r="434">
@@ -51797,22 +51797,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>SL-016</t>
+          <t>SL-015</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>PV-39 - PV-40</t>
+          <t>PV-41 - PV-42</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>PV-39</t>
+          <t>PV-41</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>PV-40</t>
+          <t>PV-42</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -51825,20 +51825,20 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I434" t="n">
-        <v>24.53</v>
+        <v>38.45</v>
       </c>
       <c r="J434" t="n">
-        <v>3.64</v>
+        <v>2.58</v>
       </c>
       <c r="K434" t="n">
-        <v>4.31</v>
+        <v>1.41</v>
       </c>
       <c r="L434" t="n">
-        <v>4.31</v>
+        <v>2.58</v>
       </c>
       <c r="M434" t="inlineStr">
         <is>
@@ -51847,20 +51847,20 @@
       </c>
       <c r="N434" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. Extensao lida no print.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
         </is>
       </c>
       <c r="O434" t="n">
-        <v>-23.5222906</v>
+        <v>-23.5227141</v>
       </c>
       <c r="P434" t="n">
-        <v>-46.378588</v>
+        <v>-46.378029</v>
       </c>
       <c r="Q434" t="n">
-        <v>-23.5224137</v>
+        <v>-23.52298</v>
       </c>
       <c r="R434" t="n">
-        <v>-46.3783767</v>
+        <v>-46.3777869</v>
       </c>
     </row>
     <row r="435">
@@ -51871,22 +51871,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>SL-017</t>
+          <t>SL-016</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>PV-40 - PV-69</t>
+          <t>PV-39 - PV-40</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
+          <t>PV-39</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
           <t>PV-40</t>
-        </is>
-      </c>
-      <c r="E435" t="inlineStr">
-        <is>
-          <t>PV-69</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -51903,13 +51903,13 @@
         </is>
       </c>
       <c r="I435" t="n">
-        <v>13.08</v>
+        <v>24.53</v>
       </c>
       <c r="J435" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="K435" t="n">
         <v>4.31</v>
-      </c>
-      <c r="K435" t="n">
-        <v>1.93</v>
       </c>
       <c r="L435" t="n">
         <v>4.31</v>
@@ -51925,16 +51925,16 @@
         </is>
       </c>
       <c r="O435" t="n">
+        <v>-23.5222906</v>
+      </c>
+      <c r="P435" t="n">
+        <v>-46.378588</v>
+      </c>
+      <c r="Q435" t="n">
         <v>-23.5224137</v>
       </c>
-      <c r="P435" t="n">
+      <c r="R435" t="n">
         <v>-46.3783767</v>
-      </c>
-      <c r="Q435" t="n">
-        <v>-23.5224631</v>
-      </c>
-      <c r="R435" t="n">
-        <v>-46.3782535</v>
       </c>
     </row>
     <row r="436">
@@ -51945,22 +51945,22 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>SL-018</t>
+          <t>SL-017</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>PV-69 - PV-70</t>
+          <t>PV-40 - PV-69</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
+          <t>PV-40</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
           <t>PV-69</t>
-        </is>
-      </c>
-      <c r="E436" t="inlineStr">
-        <is>
-          <t>PV-70</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -51977,16 +51977,16 @@
         </is>
       </c>
       <c r="I436" t="n">
-        <v>20.55</v>
+        <v>13.08</v>
       </c>
       <c r="J436" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="K436" t="n">
         <v>1.93</v>
       </c>
-      <c r="K436" t="n">
-        <v>1.41</v>
-      </c>
       <c r="L436" t="n">
-        <v>1.93</v>
+        <v>4.31</v>
       </c>
       <c r="M436" t="inlineStr">
         <is>
@@ -51999,16 +51999,16 @@
         </is>
       </c>
       <c r="O436" t="n">
+        <v>-23.5224137</v>
+      </c>
+      <c r="P436" t="n">
+        <v>-46.3783767</v>
+      </c>
+      <c r="Q436" t="n">
         <v>-23.5224631</v>
       </c>
-      <c r="P436" t="n">
+      <c r="R436" t="n">
         <v>-46.3782535</v>
-      </c>
-      <c r="Q436" t="n">
-        <v>-23.5224276</v>
-      </c>
-      <c r="R436" t="n">
-        <v>-46.378053</v>
       </c>
     </row>
     <row r="437">
@@ -52019,22 +52019,22 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>SL-019</t>
+          <t>SL-018</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>PV-64 - PV-65</t>
+          <t>PV-69 - PV-70</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>PV-64</t>
+          <t>PV-69</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>PV-65</t>
+          <t>PV-70</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -52047,42 +52047,42 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>VCA</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I437" t="n">
-        <v>39.5</v>
+        <v>20.55</v>
       </c>
       <c r="J437" t="n">
-        <v>2.84</v>
+        <v>1.93</v>
       </c>
       <c r="K437" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="L437" t="n">
-        <v>2.84</v>
+        <v>1.93</v>
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>em andamento</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
         <is>
-          <t>Interligação corrigida PV-64 -&gt; PV-65 conforme projeto.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. Extensao lida no print.</t>
         </is>
       </c>
       <c r="O437" t="n">
-        <v>-23.522</v>
+        <v>-23.5224631</v>
       </c>
       <c r="P437" t="n">
-        <v>-46.378</v>
+        <v>-46.3782535</v>
       </c>
       <c r="Q437" t="n">
-        <v>-23.5224</v>
+        <v>-23.5224276</v>
       </c>
       <c r="R437" t="n">
-        <v>-46.378</v>
+        <v>-46.378053</v>
       </c>
     </row>
     <row r="438">
@@ -52093,22 +52093,22 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>SL-020</t>
+          <t>SL-019</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>PV-65 - PV-70</t>
+          <t>PV-64 - PV-65</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
+          <t>PV-64</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
           <t>PV-65</t>
-        </is>
-      </c>
-      <c r="E438" t="inlineStr">
-        <is>
-          <t>PV-70</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -52125,16 +52125,16 @@
         </is>
       </c>
       <c r="I438" t="n">
-        <v>2.88</v>
+        <v>39.5</v>
       </c>
       <c r="J438" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="K438" t="n">
         <v>1.6</v>
       </c>
-      <c r="K438" t="n">
-        <v>1.41</v>
-      </c>
       <c r="L438" t="n">
-        <v>1.6</v>
+        <v>2.84</v>
       </c>
       <c r="M438" t="inlineStr">
         <is>
@@ -52143,11 +52143,11 @@
       </c>
       <c r="N438" t="inlineStr">
         <is>
-          <t>Interligação corrigida PV-65 -&gt; PV-70 conforme projeto.</t>
+          <t>Interligação corrigida PV-64 -&gt; PV-65 conforme projeto.</t>
         </is>
       </c>
       <c r="O438" t="n">
-        <v>-23.5224</v>
+        <v>-23.522</v>
       </c>
       <c r="P438" t="n">
         <v>-46.378</v>
@@ -52167,22 +52167,22 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>SL-021</t>
+          <t>SL-020</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>PVE-32 - PV-02</t>
+          <t>PV-65 - PV-70</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>PVE-32</t>
+          <t>PV-65</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>PV-02</t>
+          <t>PV-70</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -52195,42 +52195,42 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>VCA</t>
         </is>
       </c>
       <c r="I439" t="n">
-        <v>12.61</v>
+        <v>2.88</v>
       </c>
       <c r="J439" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="K439" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="L439" t="n">
-        <v>2.05</v>
+        <v>1.6</v>
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>em andamento</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
+          <t>Interligação corrigida PV-65 -&gt; PV-70 conforme projeto.</t>
         </is>
       </c>
       <c r="O439" t="n">
-        <v>-23.5199037</v>
+        <v>-23.5224</v>
       </c>
       <c r="P439" t="n">
-        <v>-46.3771453</v>
+        <v>-46.378</v>
       </c>
       <c r="Q439" t="n">
-        <v>-23.5200098</v>
+        <v>-23.5224</v>
       </c>
       <c r="R439" t="n">
-        <v>-46.3771007</v>
+        <v>-46.378</v>
       </c>
     </row>
     <row r="440">
@@ -52241,22 +52241,22 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>SL-022</t>
+          <t>SL-021</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>PV-02 - PV-03</t>
+          <t>PVE-32 - PV-02</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
+          <t>PVE-32</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
           <t>PV-02</t>
-        </is>
-      </c>
-      <c r="E440" t="inlineStr">
-        <is>
-          <t>PV-03</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
@@ -52273,16 +52273,16 @@
         </is>
       </c>
       <c r="I440" t="n">
-        <v>21</v>
+        <v>12.61</v>
       </c>
       <c r="J440" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="K440" t="n">
         <v>1.48</v>
       </c>
-      <c r="K440" t="n">
-        <v>2.04</v>
-      </c>
       <c r="L440" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="M440" t="inlineStr">
         <is>
@@ -52295,16 +52295,16 @@
         </is>
       </c>
       <c r="O440" t="n">
+        <v>-23.5199037</v>
+      </c>
+      <c r="P440" t="n">
+        <v>-46.3771453</v>
+      </c>
+      <c r="Q440" t="n">
         <v>-23.5200098</v>
       </c>
-      <c r="P440" t="n">
+      <c r="R440" t="n">
         <v>-46.3771007</v>
-      </c>
-      <c r="Q440" t="n">
-        <v>-23.5200681</v>
-      </c>
-      <c r="R440" t="n">
-        <v>-46.376905</v>
       </c>
     </row>
     <row r="441">
@@ -52315,22 +52315,22 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>SL-023</t>
+          <t>SL-022</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>PV-03 - PV-04</t>
+          <t>PV-02 - PV-03</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
+          <t>PV-02</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
           <t>PV-03</t>
-        </is>
-      </c>
-      <c r="E441" t="inlineStr">
-        <is>
-          <t>PV-04</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -52347,13 +52347,13 @@
         </is>
       </c>
       <c r="I441" t="n">
-        <v>46.15</v>
+        <v>21</v>
       </c>
       <c r="J441" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="K441" t="n">
         <v>2.04</v>
-      </c>
-      <c r="K441" t="n">
-        <v>1.68</v>
       </c>
       <c r="L441" t="n">
         <v>2.04</v>
@@ -52369,16 +52369,16 @@
         </is>
       </c>
       <c r="O441" t="n">
+        <v>-23.5200098</v>
+      </c>
+      <c r="P441" t="n">
+        <v>-46.3771007</v>
+      </c>
+      <c r="Q441" t="n">
         <v>-23.5200681</v>
       </c>
-      <c r="P441" t="n">
+      <c r="R441" t="n">
         <v>-46.376905</v>
-      </c>
-      <c r="Q441" t="n">
-        <v>-23.5204836</v>
-      </c>
-      <c r="R441" t="n">
-        <v>-46.3768696</v>
       </c>
     </row>
     <row r="442">
@@ -52389,22 +52389,22 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>SL-024</t>
+          <t>SL-023</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>PV-04 - PV-05</t>
+          <t>PV-03 - PV-04</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
+          <t>PV-03</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
           <t>PV-04</t>
-        </is>
-      </c>
-      <c r="E442" t="inlineStr">
-        <is>
-          <t>PV-05</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -52421,16 +52421,16 @@
         </is>
       </c>
       <c r="I442" t="n">
-        <v>38.98</v>
+        <v>46.15</v>
       </c>
       <c r="J442" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K442" t="n">
         <v>1.68</v>
       </c>
-      <c r="K442" t="n">
-        <v>1.76</v>
-      </c>
       <c r="L442" t="n">
-        <v>1.76</v>
+        <v>2.04</v>
       </c>
       <c r="M442" t="inlineStr">
         <is>
@@ -52443,16 +52443,16 @@
         </is>
       </c>
       <c r="O442" t="n">
+        <v>-23.5200681</v>
+      </c>
+      <c r="P442" t="n">
+        <v>-46.376905</v>
+      </c>
+      <c r="Q442" t="n">
         <v>-23.5204836</v>
       </c>
-      <c r="P442" t="n">
+      <c r="R442" t="n">
         <v>-46.3768696</v>
-      </c>
-      <c r="Q442" t="n">
-        <v>-23.5208354</v>
-      </c>
-      <c r="R442" t="n">
-        <v>-46.3768848</v>
       </c>
     </row>
     <row r="443">
@@ -52463,22 +52463,22 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>SL-025</t>
+          <t>SL-024</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>PV-05 - PV-06</t>
+          <t>PV-04 - PV-05</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
+          <t>PV-04</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
           <t>PV-05</t>
-        </is>
-      </c>
-      <c r="E443" t="inlineStr">
-        <is>
-          <t>PV-06</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -52495,16 +52495,16 @@
         </is>
       </c>
       <c r="I443" t="n">
-        <v>37.7</v>
+        <v>38.98</v>
       </c>
       <c r="J443" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="K443" t="n">
         <v>1.76</v>
       </c>
-      <c r="K443" t="n">
-        <v>1.85</v>
-      </c>
       <c r="L443" t="n">
-        <v>1.85</v>
+        <v>1.76</v>
       </c>
       <c r="M443" t="inlineStr">
         <is>
@@ -52517,16 +52517,16 @@
         </is>
       </c>
       <c r="O443" t="n">
+        <v>-23.5204836</v>
+      </c>
+      <c r="P443" t="n">
+        <v>-46.3768696</v>
+      </c>
+      <c r="Q443" t="n">
         <v>-23.5208354</v>
       </c>
-      <c r="P443" t="n">
+      <c r="R443" t="n">
         <v>-46.3768848</v>
-      </c>
-      <c r="Q443" t="n">
-        <v>-23.5211749</v>
-      </c>
-      <c r="R443" t="n">
-        <v>-46.3768575</v>
       </c>
     </row>
     <row r="444">
@@ -52537,22 +52537,22 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>SL-026</t>
+          <t>SL-025</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>PV-06 - PV-07</t>
+          <t>PV-05 - PV-06</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
+          <t>PV-05</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
           <t>PV-06</t>
-        </is>
-      </c>
-      <c r="E444" t="inlineStr">
-        <is>
-          <t>PV-07</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -52569,13 +52569,13 @@
         </is>
       </c>
       <c r="I444" t="n">
-        <v>34.53</v>
+        <v>37.7</v>
       </c>
       <c r="J444" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="K444" t="n">
         <v>1.85</v>
-      </c>
-      <c r="K444" t="n">
-        <v>1.44</v>
       </c>
       <c r="L444" t="n">
         <v>1.85</v>
@@ -52591,16 +52591,16 @@
         </is>
       </c>
       <c r="O444" t="n">
+        <v>-23.5208354</v>
+      </c>
+      <c r="P444" t="n">
+        <v>-46.3768848</v>
+      </c>
+      <c r="Q444" t="n">
         <v>-23.5211749</v>
       </c>
-      <c r="P444" t="n">
+      <c r="R444" t="n">
         <v>-46.3768575</v>
-      </c>
-      <c r="Q444" t="n">
-        <v>-23.5214649</v>
-      </c>
-      <c r="R444" t="n">
-        <v>-46.3767334</v>
       </c>
     </row>
     <row r="445">
@@ -52611,22 +52611,22 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>SL-027</t>
+          <t>SL-026</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>PV-07 - PV-08</t>
+          <t>PV-06 - PV-07</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
+          <t>PV-06</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
           <t>PV-07</t>
-        </is>
-      </c>
-      <c r="E445" t="inlineStr">
-        <is>
-          <t>PV-08</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -52643,16 +52643,16 @@
         </is>
       </c>
       <c r="I445" t="n">
-        <v>8.17</v>
+        <v>34.53</v>
       </c>
       <c r="J445" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="K445" t="n">
         <v>1.44</v>
       </c>
-      <c r="K445" t="n">
-        <v>1.41</v>
-      </c>
       <c r="L445" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="M445" t="inlineStr">
         <is>
@@ -52665,16 +52665,16 @@
         </is>
       </c>
       <c r="O445" t="n">
+        <v>-23.5211749</v>
+      </c>
+      <c r="P445" t="n">
+        <v>-46.3768575</v>
+      </c>
+      <c r="Q445" t="n">
         <v>-23.5214649</v>
       </c>
-      <c r="P445" t="n">
+      <c r="R445" t="n">
         <v>-46.3767334</v>
-      </c>
-      <c r="Q445" t="n">
-        <v>-23.5215374</v>
-      </c>
-      <c r="R445" t="n">
-        <v>-46.3767183</v>
       </c>
     </row>
     <row r="446">
@@ -52685,22 +52685,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>SL-028</t>
+          <t>SL-027</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>PVE-31 - PV-37</t>
+          <t>PV-07 - PV-08</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>PVE-31</t>
+          <t>PV-07</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>PV-37</t>
+          <t>PV-08</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -52717,16 +52717,16 @@
         </is>
       </c>
       <c r="I446" t="n">
-        <v>10.11</v>
+        <v>8.17</v>
       </c>
       <c r="J446" t="n">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="K446" t="n">
-        <v>3.75</v>
+        <v>1.41</v>
       </c>
       <c r="L446" t="n">
-        <v>3.75</v>
+        <v>1.44</v>
       </c>
       <c r="M446" t="inlineStr">
         <is>
@@ -52735,8 +52735,20 @@
       </c>
       <c r="N446" t="inlineStr">
         <is>
-          <t>Interligacao adicionada conforme projeto.</t>
-        </is>
+          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
+        </is>
+      </c>
+      <c r="O446" t="n">
+        <v>-23.5214649</v>
+      </c>
+      <c r="P446" t="n">
+        <v>-46.3767334</v>
+      </c>
+      <c r="Q446" t="n">
+        <v>-23.5215374</v>
+      </c>
+      <c r="R446" t="n">
+        <v>-46.3767183</v>
       </c>
     </row>
     <row r="447">
@@ -52747,22 +52759,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>SL-029</t>
+          <t>SL-028</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>PV-75 - PV-76</t>
+          <t>PVE-31 - PV-37</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>PV-75</t>
+          <t>PVE-31</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>PV-76</t>
+          <t>PV-37</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -52779,16 +52791,16 @@
         </is>
       </c>
       <c r="I447" t="n">
-        <v>2.09</v>
+        <v>10.11</v>
       </c>
       <c r="J447" t="n">
-        <v>1.35</v>
+        <v>2.4</v>
       </c>
       <c r="K447" t="n">
-        <v>1.25</v>
+        <v>3.75</v>
       </c>
       <c r="L447" t="n">
-        <v>1.35</v>
+        <v>3.75</v>
       </c>
       <c r="M447" t="inlineStr">
         <is>
@@ -52797,7 +52809,7 @@
       </c>
       <c r="N447" t="inlineStr">
         <is>
-          <t>Interligação adicionada conforme projeto.</t>
+          <t>Interligacao adicionada conforme projeto.</t>
         </is>
       </c>
     </row>
@@ -52809,22 +52821,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>SL-030</t>
+          <t>SL-029</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>PV-76 - PV-77</t>
+          <t>PV-75 - PV-76</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
+          <t>PV-75</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
           <t>PV-76</t>
-        </is>
-      </c>
-      <c r="E448" t="inlineStr">
-        <is>
-          <t>PV-77</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -52841,16 +52853,16 @@
         </is>
       </c>
       <c r="I448" t="n">
-        <v>18.02</v>
+        <v>2.09</v>
       </c>
       <c r="J448" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K448" t="n">
         <v>1.25</v>
       </c>
-      <c r="K448" t="n">
-        <v>1.58</v>
-      </c>
       <c r="L448" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="M448" t="inlineStr">
         <is>
@@ -52871,22 +52883,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>SL-031</t>
+          <t>SL-030</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>PV-77 - PV-78</t>
+          <t>PV-76 - PV-77</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
+          <t>PV-76</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
           <t>PV-77</t>
-        </is>
-      </c>
-      <c r="E449" t="inlineStr">
-        <is>
-          <t>PV-78</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -52903,10 +52915,10 @@
         </is>
       </c>
       <c r="I449" t="n">
-        <v>21.33</v>
+        <v>18.02</v>
       </c>
       <c r="J449" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="K449" t="n">
         <v>1.58</v>
@@ -52933,22 +52945,22 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>SL-032</t>
+          <t>SL-031</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>PV-75.1 - PV-75</t>
+          <t>PV-77 - PV-78</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>PV-75.1</t>
+          <t>PV-77</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>PV-75</t>
+          <t>PV-78</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -52965,13 +52977,16 @@
         </is>
       </c>
       <c r="I450" t="n">
-        <v>5</v>
+        <v>21.33</v>
+      </c>
+      <c r="J450" t="n">
+        <v>1.58</v>
       </c>
       <c r="K450" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="L450" t="n">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="M450" t="inlineStr">
         <is>
@@ -52980,72 +52995,57 @@
       </c>
       <c r="N450" t="inlineStr">
         <is>
-          <t>Interligacao PV-75.1 -&gt; PV-75 adicionada via Google Earth.</t>
-        </is>
-      </c>
-      <c r="O450" t="n">
-        <v>-23.5198222</v>
-      </c>
-      <c r="P450" t="n">
-        <v>-46.3768722</v>
-      </c>
-      <c r="Q450" t="n">
-        <v>-23.5198</v>
-      </c>
-      <c r="R450" t="n">
-        <v>-46.3763</v>
+          <t>Interligação adicionada conforme projeto.</t>
+        </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_comunidade_sao_lucas</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>JC-014</t>
+          <t>SL-032</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>PV-16 - PV-17</t>
+          <t>PV-75.1 - PV-75</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>PV-16</t>
+          <t>PV-75.1</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>PV-17</t>
+          <t>PV-75</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>PEAD LISO</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="G451" t="n">
-        <v>355</v>
+        <v>200</v>
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>Metodo Nao Destrutivo - MND</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I451" t="n">
-        <v>64.572</v>
-      </c>
-      <c r="J451" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="K451" t="n">
-        <v>3.1</v>
+        <v>1.35</v>
       </c>
       <c r="L451" t="n">
-        <v>5.48</v>
+        <v>1.35</v>
       </c>
       <c r="M451" t="inlineStr">
         <is>
@@ -53054,20 +53054,20 @@
       </c>
       <c r="N451" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-16 ao PV-17; arquivo: planos_furo/cts_joao_canzi_fl07_pv16_pv17.pdf; taxa 0,0707.</t>
+          <t>Interligacao PV-75.1 -&gt; PV-75 adicionada via Google Earth.</t>
         </is>
       </c>
       <c r="O451" t="n">
-        <v>-23.5299843</v>
+        <v>-23.5198222</v>
       </c>
       <c r="P451" t="n">
-        <v>-46.3845231</v>
+        <v>-46.3768722</v>
       </c>
       <c r="Q451" t="n">
-        <v>-23.5300354</v>
+        <v>-23.5198</v>
       </c>
       <c r="R451" t="n">
-        <v>-46.3838931</v>
+        <v>-46.3763</v>
       </c>
     </row>
     <row r="452">
@@ -53078,22 +53078,22 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>JC-015</t>
+          <t>JC-014</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>PV-17 - PV-18</t>
+          <t>PV-16 - PV-17</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
+          <t>PV-16</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
           <t>PV-17</t>
-        </is>
-      </c>
-      <c r="E452" t="inlineStr">
-        <is>
-          <t>PV-18</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
@@ -53110,16 +53110,16 @@
         </is>
       </c>
       <c r="I452" t="n">
-        <v>79.57599999999999</v>
+        <v>64.572</v>
       </c>
       <c r="J452" t="n">
         <v>3.1</v>
       </c>
       <c r="K452" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="L452" t="n">
-        <v>3.56</v>
+        <v>5.48</v>
       </c>
       <c r="M452" t="inlineStr">
         <is>
@@ -53128,20 +53128,20 @@
       </c>
       <c r="N452" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-17 ao PV-18; arquivo: planos_furo/cts_joao_canzi_fl07_pv17_pv18.pdf; taxa 0,0116.</t>
+          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-16 ao PV-17; arquivo: planos_furo/cts_joao_canzi_fl07_pv16_pv17.pdf; taxa 0,0707.</t>
         </is>
       </c>
       <c r="O452" t="n">
+        <v>-23.5299843</v>
+      </c>
+      <c r="P452" t="n">
+        <v>-46.3845231</v>
+      </c>
+      <c r="Q452" t="n">
         <v>-23.5300354</v>
       </c>
-      <c r="P452" t="n">
+      <c r="R452" t="n">
         <v>-46.3838931</v>
-      </c>
-      <c r="Q452" t="n">
-        <v>-23.5300223</v>
-      </c>
-      <c r="R452" t="n">
-        <v>-46.3831139</v>
       </c>
     </row>
     <row r="453">
@@ -53152,22 +53152,22 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>JC-016</t>
+          <t>JC-015</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>PV-19 - PV-20</t>
+          <t>PV-17 - PV-18</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>PV-19</t>
+          <t>PV-17</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>PV-20</t>
+          <t>PV-18</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
@@ -53184,37 +53184,111 @@
         </is>
       </c>
       <c r="I453" t="n">
+        <v>79.57599999999999</v>
+      </c>
+      <c r="J453" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K453" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L453" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="M453" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N453" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-17 ao PV-18; arquivo: planos_furo/cts_joao_canzi_fl07_pv17_pv18.pdf; taxa 0,0116.</t>
+        </is>
+      </c>
+      <c r="O453" t="n">
+        <v>-23.5300354</v>
+      </c>
+      <c r="P453" t="n">
+        <v>-46.3838931</v>
+      </c>
+      <c r="Q453" t="n">
+        <v>-23.5300223</v>
+      </c>
+      <c r="R453" t="n">
+        <v>-46.3831139</v>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>JC-016</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>PV-19 - PV-20</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>PV-19</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>PV-20</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G454" t="n">
+        <v>355</v>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I454" t="n">
         <v>57.846</v>
       </c>
-      <c r="J453" t="n">
+      <c r="J454" t="n">
         <v>4</v>
       </c>
-      <c r="K453" t="n">
+      <c r="K454" t="n">
         <v>3.96</v>
       </c>
-      <c r="L453" t="n">
+      <c r="L454" t="n">
         <v>4</v>
       </c>
-      <c r="M453" t="inlineStr">
+      <c r="M454" t="inlineStr">
         <is>
           <t>em andamento</t>
         </is>
       </c>
-      <c r="N453" t="inlineStr">
+      <c r="N454" t="inlineStr">
         <is>
           <t>Plano de furo FL-07 versao 01, 05.JUN.2026; PV-19 ao PV-20; arquivo: planos_furo/cts_joao_canzi_fl07_pv19_pv20.pdf; taxa 0,1224.</t>
         </is>
       </c>
-      <c r="O453" t="n">
+      <c r="O454" t="n">
         <v>-23.529877</v>
       </c>
-      <c r="P453" t="n">
+      <c r="P454" t="n">
         <v>-46.3824799</v>
       </c>
-      <c r="Q453" t="n">
+      <c r="Q454" t="n">
         <v>-23.5295804</v>
       </c>
-      <c r="R453" t="n">
+      <c r="R454" t="n">
         <v>-46.3820136</v>
       </c>
     </row>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -2,9 +2,6 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEIA-ME" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OBRAS" sheetId="2" state="visible" r:id="rId2"/>
@@ -17,10 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACAO_SHAPE_LUIS_0505" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACAO_SUBST_AGUA_BOA_0505" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TRECHOS'!$A$1:$R$445</definedName>
-  </definedNames>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <definedNames/>
 </workbook>
 </file>
 
@@ -59,13 +53,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -78,9 +66,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -321,8 +308,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -333,7 +318,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -403,7 +388,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -478,7 +463,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <cols>
     <col width="31.109375" customWidth="1" min="1" max="1"/>
     <col width="35.44140625" customWidth="1" min="2" max="2"/>
@@ -1197,8 +1182,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L441"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:L447"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
     <col width="12.5546875" customWidth="1" min="3" max="3"/>
@@ -19149,110 +19134,110 @@
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>Adicionado via print do projeto RCE Elias Sleiman; lancamento completo em VCA.</t>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>rce_elvira_de_araujo</t>
+          <t>rce_elias_sleiman</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>ELVIRA-PI-1.1</t>
+          <t>ELIAS-PV-24</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>PI-1.1</t>
+          <t>PV-24</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>7396905.886</v>
+        <v>7397047.32</v>
       </c>
       <c r="F398" t="n">
-        <v>358329.956</v>
+        <v>358826.273</v>
       </c>
       <c r="G398" t="n">
-        <v>-23.5319548</v>
+        <v>-23.5307209</v>
       </c>
       <c r="H398" t="n">
-        <v>-46.387801</v>
+        <v>-46.3829268</v>
       </c>
       <c r="I398" t="n">
-        <v>767.159</v>
+        <v>795.659</v>
       </c>
       <c r="J398" t="n">
-        <v>765.927</v>
+        <v>793.298</v>
       </c>
       <c r="K398" t="n">
-        <v>1.23</v>
+        <v>2.36</v>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>Adicionado conforme solicitação: PI da RCE Elvira de Araujo; interligacao com CTS Joao Canzi mantida sem alterar registros existentes.</t>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>rce_elvira_de_araujo</t>
+          <t>rce_elias_sleiman</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>ELVIRA-PI-1.2</t>
+          <t>ELIAS-PV-25</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>PI-1.2</t>
+          <t>PV-25</t>
         </is>
       </c>
       <c r="E399" t="n">
-        <v>7396922.192</v>
+        <v>7397044.193</v>
       </c>
       <c r="F399" t="n">
-        <v>358327.004</v>
+        <v>358909.128</v>
       </c>
       <c r="G399" t="n">
-        <v>-23.5318073</v>
+        <v>-23.5307563</v>
       </c>
       <c r="H399" t="n">
-        <v>-46.3878284</v>
+        <v>-46.3821157</v>
       </c>
       <c r="I399" t="n">
-        <v>767.21</v>
+        <v>798.554</v>
       </c>
       <c r="J399" t="n">
-        <v>766.01</v>
+        <v>795.832</v>
       </c>
       <c r="K399" t="n">
-        <v>1.2</v>
+        <v>2.72</v>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>Adicionado conforme solicitação: PI da RCE Elvira de Araujo; interligacao com CTS Joao Canzi mantida sem alterar registros existentes.</t>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_elias_sleiman</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -19262,45 +19247,45 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>JC-PV-18</t>
+          <t>ELIAS-PV-26</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>PV-18</t>
+          <t>PV-26</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>7397124.485</v>
+        <v>7397000.312</v>
       </c>
       <c r="F400" t="n">
-        <v>358806.429</v>
+        <v>358903.103</v>
       </c>
       <c r="G400" t="n">
-        <v>-23.5300224</v>
+        <v>-23.5311521</v>
       </c>
       <c r="H400" t="n">
-        <v>-46.3831139</v>
+        <v>-46.3821788</v>
       </c>
       <c r="I400" t="n">
-        <v>783.619</v>
+        <v>803.849</v>
       </c>
       <c r="J400" t="n">
-        <v>780.119</v>
+        <v>801.227</v>
       </c>
       <c r="K400" t="n">
-        <v>3.5</v>
+        <v>2.62</v>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-18 ao PV-19.</t>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_elias_sleiman</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -19310,45 +19295,45 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>JC-PV-19</t>
+          <t>ELIAS-PV-27</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>PV-19</t>
+          <t>PV-27</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>7397141.155</v>
+        <v>7396952.046</v>
       </c>
       <c r="F401" t="n">
-        <v>358871.038</v>
+        <v>358919.472</v>
       </c>
       <c r="G401" t="n">
-        <v>-23.5298774</v>
+        <v>-23.5315893</v>
       </c>
       <c r="H401" t="n">
-        <v>-46.3824796</v>
+        <v>-46.3820231</v>
       </c>
       <c r="I401" t="n">
-        <v>787.357</v>
+        <v>810.896</v>
       </c>
       <c r="J401" t="n">
-        <v>783.357</v>
+        <v>808.804</v>
       </c>
       <c r="K401" t="n">
-        <v>4</v>
+        <v>2.09</v>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-18 ao PV-19.</t>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>rce_elvira_de_araujo</t>
+          <t>rce_elias_sleiman</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -19358,45 +19343,45 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>ELVIRA-PV-08</t>
+          <t>ELIAS-PV-28</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>PV-08</t>
+          <t>PV-28</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>7396899.021</v>
+        <v>7396913.479</v>
       </c>
       <c r="F402" t="n">
-        <v>358332.965</v>
+        <v>358940.543</v>
       </c>
       <c r="G402" t="n">
-        <v>-23.532017</v>
+        <v>-23.5319394</v>
       </c>
       <c r="H402" t="n">
-        <v>-46.3877722</v>
+        <v>-46.3818203</v>
       </c>
       <c r="I402" t="n">
-        <v>767.145</v>
+        <v>813.813</v>
       </c>
       <c r="J402" t="n">
-        <v>762.845</v>
+        <v>811.614</v>
       </c>
       <c r="K402" t="n">
-        <v>4.3</v>
+        <v>2.2</v>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>rce_elvira_de_araujo</t>
+          <t>rce_elias_sleiman</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -19406,38 +19391,38 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>ELVIRA-PV-02</t>
+          <t>ELIAS-PV-29</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>PV-02</t>
+          <t>PV-29</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>7396941.756</v>
+        <v>7396888.957</v>
       </c>
       <c r="F403" t="n">
-        <v>358324.032</v>
+        <v>358954.374</v>
       </c>
       <c r="G403" t="n">
-        <v>-23.5316304</v>
+        <v>-23.5321621</v>
       </c>
       <c r="H403" t="n">
-        <v>-46.3878556</v>
+        <v>-46.3816872</v>
       </c>
       <c r="I403" t="n">
-        <v>767.318</v>
+        <v>815.335</v>
       </c>
       <c r="J403" t="n">
-        <v>763.468</v>
+        <v>813.135</v>
       </c>
       <c r="K403" t="n">
-        <v>3.85</v>
+        <v>2.2</v>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
         </is>
       </c>
     </row>
@@ -19449,98 +19434,98 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>ELVIRA-PV-01</t>
+          <t>ELVIRA-PI-1.1</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>PV-01</t>
+          <t>PI-1.1</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>7396903.634</v>
+        <v>7396905.886</v>
       </c>
       <c r="F404" t="n">
-        <v>358332.744</v>
+        <v>358329.956</v>
       </c>
       <c r="G404" t="n">
-        <v>-23.5319754</v>
+        <v>-23.5319548</v>
       </c>
       <c r="H404" t="n">
-        <v>-46.3877739</v>
+        <v>-46.387801</v>
       </c>
       <c r="I404" t="n">
-        <v>767.2910000000001</v>
+        <v>767.159</v>
       </c>
       <c r="J404" t="n">
-        <v>763.0069999999999</v>
+        <v>765.927</v>
       </c>
       <c r="K404" t="n">
-        <v>4.28</v>
+        <v>1.23</v>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
+          <t>Adicionado conforme solicitação: PI da RCE Elvira de Araujo; interligacao com CTS Joao Canzi mantida sem alterar registros existentes.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>SL-PV-26</t>
+          <t>ELVIRA-PI-1.2</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>PV-26</t>
+          <t>PI-1.2</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>7397836.606</v>
+        <v>7396922.192</v>
       </c>
       <c r="F405" t="n">
-        <v>359444.31</v>
+        <v>358327.004</v>
       </c>
       <c r="G405" t="n">
-        <v>-23.5236471</v>
+        <v>-23.5318073</v>
       </c>
       <c r="H405" t="n">
-        <v>-46.3767998</v>
+        <v>-46.3878284</v>
       </c>
       <c r="I405" t="n">
-        <v>765.833</v>
+        <v>767.21</v>
       </c>
       <c r="J405" t="n">
-        <v>762.795</v>
+        <v>766.01</v>
       </c>
       <c r="K405" t="n">
-        <v>3.04</v>
+        <v>1.2</v>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
+          <t>Adicionado conforme solicitação: PI da RCE Elvira de Araujo; interligacao com CTS Joao Canzi mantida sem alterar registros existentes.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -19550,45 +19535,45 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>SL-PV-27</t>
+          <t>JC-PV-18</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>PV-27</t>
+          <t>PV-18</t>
         </is>
       </c>
       <c r="E406" t="n">
-        <v>7397821.933</v>
+        <v>7397124.485</v>
       </c>
       <c r="F406" t="n">
-        <v>359445.676</v>
+        <v>358806.429</v>
       </c>
       <c r="G406" t="n">
-        <v>-23.5237798</v>
+        <v>-23.5300224</v>
       </c>
       <c r="H406" t="n">
-        <v>-46.3767878</v>
+        <v>-46.3831139</v>
       </c>
       <c r="I406" t="n">
-        <v>766.55</v>
+        <v>783.619</v>
       </c>
       <c r="J406" t="n">
-        <v>762.985</v>
+        <v>780.119</v>
       </c>
       <c r="K406" t="n">
-        <v>3.57</v>
+        <v>3.5</v>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
+          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-18 ao PV-19.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -19598,45 +19583,45 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>SL-PV-28</t>
+          <t>JC-PV-19</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>PV-28</t>
+          <t>PV-19</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>7397818.346</v>
+        <v>7397141.155</v>
       </c>
       <c r="F407" t="n">
-        <v>359445.113</v>
+        <v>358871.038</v>
       </c>
       <c r="G407" t="n">
-        <v>-23.5238121</v>
+        <v>-23.5298774</v>
       </c>
       <c r="H407" t="n">
-        <v>-46.3767936</v>
+        <v>-46.3824796</v>
       </c>
       <c r="I407" t="n">
-        <v>766.3390000000001</v>
+        <v>787.357</v>
       </c>
       <c r="J407" t="n">
-        <v>763.003</v>
+        <v>783.357</v>
       </c>
       <c r="K407" t="n">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
+          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-18 ao PV-19.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -19646,45 +19631,45 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>SL-PV-29</t>
+          <t>ELVIRA-PV-08</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>PV-29</t>
+          <t>PV-08</t>
         </is>
       </c>
       <c r="E408" t="n">
-        <v>7397815.955</v>
+        <v>7396899.021</v>
       </c>
       <c r="F408" t="n">
-        <v>359437.991</v>
+        <v>358332.965</v>
       </c>
       <c r="G408" t="n">
-        <v>-23.5238331</v>
+        <v>-23.532017</v>
       </c>
       <c r="H408" t="n">
-        <v>-46.3768636</v>
+        <v>-46.3877722</v>
       </c>
       <c r="I408" t="n">
-        <v>767.119</v>
+        <v>767.145</v>
       </c>
       <c r="J408" t="n">
-        <v>765.308</v>
+        <v>762.845</v>
       </c>
       <c r="K408" t="n">
-        <v>1.81</v>
+        <v>4.3</v>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
+          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -19694,45 +19679,45 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>SL-PV-30</t>
+          <t>ELVIRA-PV-02</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>PV-30</t>
+          <t>PV-02</t>
         </is>
       </c>
       <c r="E409" t="n">
-        <v>7397821.17</v>
+        <v>7396941.756</v>
       </c>
       <c r="F409" t="n">
-        <v>359425.424</v>
+        <v>358324.032</v>
       </c>
       <c r="G409" t="n">
-        <v>-23.5237849</v>
+        <v>-23.5316304</v>
       </c>
       <c r="H409" t="n">
-        <v>-46.3769862</v>
+        <v>-46.3878556</v>
       </c>
       <c r="I409" t="n">
-        <v>768.3</v>
+        <v>767.318</v>
       </c>
       <c r="J409" t="n">
-        <v>766.9</v>
+        <v>763.468</v>
       </c>
       <c r="K409" t="n">
-        <v>1.4</v>
+        <v>3.85</v>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
+          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -19742,38 +19727,38 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>SL-PV-31</t>
+          <t>ELVIRA-PV-01</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>PV-31</t>
+          <t>PV-01</t>
         </is>
       </c>
       <c r="E410" t="n">
-        <v>7397822.876</v>
+        <v>7396903.634</v>
       </c>
       <c r="F410" t="n">
-        <v>359419.03</v>
+        <v>358332.744</v>
       </c>
       <c r="G410" t="n">
-        <v>-23.5237689</v>
+        <v>-23.5319754</v>
       </c>
       <c r="H410" t="n">
-        <v>-46.3770487</v>
+        <v>-46.3877739</v>
       </c>
       <c r="I410" t="n">
-        <v>768.978</v>
+        <v>767.2910000000001</v>
       </c>
       <c r="J410" t="n">
-        <v>767.552</v>
+        <v>763.0069999999999</v>
       </c>
       <c r="K410" t="n">
-        <v>1.43</v>
+        <v>4.28</v>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
+          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
         </is>
       </c>
     </row>
@@ -19790,34 +19775,34 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>SL-PV-32</t>
+          <t>SL-PV-26</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>PV-32</t>
+          <t>PV-26</t>
         </is>
       </c>
       <c r="E411" t="n">
-        <v>7397868.541</v>
+        <v>7397836.606</v>
       </c>
       <c r="F411" t="n">
-        <v>359364.806</v>
+        <v>359444.31</v>
       </c>
       <c r="G411" t="n">
-        <v>-23.5233519</v>
+        <v>-23.5236471</v>
       </c>
       <c r="H411" t="n">
-        <v>-46.3775754</v>
+        <v>-46.3767998</v>
       </c>
       <c r="I411" t="n">
-        <v>778.292</v>
+        <v>765.833</v>
       </c>
       <c r="J411" t="n">
-        <v>776.111</v>
+        <v>762.795</v>
       </c>
       <c r="K411" t="n">
-        <v>2.18</v>
+        <v>3.04</v>
       </c>
       <c r="L411" t="inlineStr">
         <is>
@@ -19838,34 +19823,34 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>SL-PV-33</t>
+          <t>SL-PV-27</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>PV-33</t>
+          <t>PV-27</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>7397900.057</v>
+        <v>7397821.933</v>
       </c>
       <c r="F412" t="n">
-        <v>359310.764</v>
+        <v>359445.676</v>
       </c>
       <c r="G412" t="n">
-        <v>-23.5230626</v>
+        <v>-23.5237798</v>
       </c>
       <c r="H412" t="n">
-        <v>-46.3781017</v>
+        <v>-46.3767878</v>
       </c>
       <c r="I412" t="n">
-        <v>784.273</v>
+        <v>766.55</v>
       </c>
       <c r="J412" t="n">
-        <v>782.111</v>
+        <v>762.985</v>
       </c>
       <c r="K412" t="n">
-        <v>2.16</v>
+        <v>3.57</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
@@ -19886,34 +19871,34 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>SL-PV-34</t>
+          <t>SL-PV-28</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>PV-34</t>
+          <t>PV-28</t>
         </is>
       </c>
       <c r="E413" t="n">
-        <v>7397941.252</v>
+        <v>7397818.346</v>
       </c>
       <c r="F413" t="n">
-        <v>359273.636</v>
+        <v>359445.113</v>
       </c>
       <c r="G413" t="n">
-        <v>-23.5226874</v>
+        <v>-23.5238121</v>
       </c>
       <c r="H413" t="n">
-        <v>-46.3784614</v>
+        <v>-46.3767936</v>
       </c>
       <c r="I413" t="n">
-        <v>787.202</v>
+        <v>766.3390000000001</v>
       </c>
       <c r="J413" t="n">
-        <v>784.7569999999999</v>
+        <v>763.003</v>
       </c>
       <c r="K413" t="n">
-        <v>2.45</v>
+        <v>3.34</v>
       </c>
       <c r="L413" t="inlineStr">
         <is>
@@ -19934,34 +19919,34 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>SL-PV-35</t>
+          <t>SL-PV-29</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>PV-35</t>
+          <t>PV-29</t>
         </is>
       </c>
       <c r="E414" t="n">
-        <v>7397977.503</v>
+        <v>7397815.955</v>
       </c>
       <c r="F414" t="n">
-        <v>359228.842</v>
+        <v>359437.991</v>
       </c>
       <c r="G414" t="n">
-        <v>-23.5223561</v>
+        <v>-23.5238331</v>
       </c>
       <c r="H414" t="n">
-        <v>-46.3788967</v>
+        <v>-46.3768636</v>
       </c>
       <c r="I414" t="n">
-        <v>788.938</v>
+        <v>767.119</v>
       </c>
       <c r="J414" t="n">
-        <v>785.057</v>
+        <v>765.308</v>
       </c>
       <c r="K414" t="n">
-        <v>3.88</v>
+        <v>1.81</v>
       </c>
       <c r="L414" t="inlineStr">
         <is>
@@ -19982,34 +19967,34 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>SL-PV-36</t>
+          <t>SL-PV-30</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>PV-36</t>
+          <t>PV-30</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>7397999.594</v>
+        <v>7397821.17</v>
       </c>
       <c r="F415" t="n">
-        <v>359212.718</v>
+        <v>359425.424</v>
       </c>
       <c r="G415" t="n">
-        <v>-23.5221552</v>
+        <v>-23.5237849</v>
       </c>
       <c r="H415" t="n">
-        <v>-46.3790525</v>
+        <v>-46.3769862</v>
       </c>
       <c r="I415" t="n">
-        <v>789.169</v>
+        <v>768.3</v>
       </c>
       <c r="J415" t="n">
-        <v>785.2</v>
+        <v>766.9</v>
       </c>
       <c r="K415" t="n">
-        <v>3.97</v>
+        <v>1.4</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
@@ -20030,34 +20015,34 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>SL-PV-37</t>
+          <t>SL-PV-31</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>PV-37</t>
+          <t>PV-31</t>
         </is>
       </c>
       <c r="E416" t="n">
-        <v>7398007.858</v>
+        <v>7397822.876</v>
       </c>
       <c r="F416" t="n">
-        <v>359206.253</v>
+        <v>359419.03</v>
       </c>
       <c r="G416" t="n">
-        <v>-23.5220801</v>
+        <v>-23.5237689</v>
       </c>
       <c r="H416" t="n">
-        <v>-46.379115</v>
+        <v>-46.3770487</v>
       </c>
       <c r="I416" t="n">
-        <v>788.999</v>
+        <v>768.978</v>
       </c>
       <c r="J416" t="n">
-        <v>785.249</v>
+        <v>767.552</v>
       </c>
       <c r="K416" t="n">
-        <v>3.75</v>
+        <v>1.43</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
@@ -20078,34 +20063,34 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>SL-PV-39</t>
+          <t>SL-PV-32</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>PV-39</t>
+          <t>PV-32</t>
         </is>
       </c>
       <c r="E417" t="n">
-        <v>7397985.065</v>
+        <v>7397868.541</v>
       </c>
       <c r="F417" t="n">
-        <v>359260.286</v>
+        <v>359364.806</v>
       </c>
       <c r="G417" t="n">
-        <v>-23.5222906</v>
+        <v>-23.5233519</v>
       </c>
       <c r="H417" t="n">
-        <v>-46.378588</v>
+        <v>-46.3775754</v>
       </c>
       <c r="I417" t="n">
-        <v>790.049</v>
+        <v>778.292</v>
       </c>
       <c r="J417" t="n">
-        <v>786.409</v>
+        <v>776.111</v>
       </c>
       <c r="K417" t="n">
-        <v>3.64</v>
+        <v>2.18</v>
       </c>
       <c r="L417" t="inlineStr">
         <is>
@@ -20126,34 +20111,34 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>SL-PV-40</t>
+          <t>SL-PV-33</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>PV-40</t>
+          <t>PV-33</t>
         </is>
       </c>
       <c r="E418" t="n">
-        <v>7397971.64</v>
+        <v>7397900.057</v>
       </c>
       <c r="F418" t="n">
-        <v>359281.997</v>
+        <v>359310.764</v>
       </c>
       <c r="G418" t="n">
-        <v>-23.5224137</v>
+        <v>-23.5230626</v>
       </c>
       <c r="H418" t="n">
-        <v>-46.3783767</v>
+        <v>-46.3781017</v>
       </c>
       <c r="I418" t="n">
-        <v>790.846</v>
+        <v>784.273</v>
       </c>
       <c r="J418" t="n">
-        <v>786.551</v>
+        <v>782.111</v>
       </c>
       <c r="K418" t="n">
-        <v>4.31</v>
+        <v>2.16</v>
       </c>
       <c r="L418" t="inlineStr">
         <is>
@@ -20174,34 +20159,34 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>SL-PV-41</t>
+          <t>SL-PV-34</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>PV-41</t>
+          <t>PV-34</t>
         </is>
       </c>
       <c r="E419" t="n">
-        <v>7397938.72</v>
+        <v>7397941.252</v>
       </c>
       <c r="F419" t="n">
-        <v>359317.81</v>
+        <v>359273.636</v>
       </c>
       <c r="G419" t="n">
-        <v>-23.5227141</v>
+        <v>-23.5226874</v>
       </c>
       <c r="H419" t="n">
-        <v>-46.378029</v>
+        <v>-46.3784614</v>
       </c>
       <c r="I419" t="n">
-        <v>789.352</v>
+        <v>787.202</v>
       </c>
       <c r="J419" t="n">
-        <v>786.775</v>
+        <v>784.7569999999999</v>
       </c>
       <c r="K419" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="L419" t="inlineStr">
         <is>
@@ -20222,34 +20207,34 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>SL-PV-42</t>
+          <t>SL-PV-35</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>PV-42</t>
+          <t>PV-35</t>
         </is>
       </c>
       <c r="E420" t="n">
-        <v>7397909.511</v>
+        <v>7397977.503</v>
       </c>
       <c r="F420" t="n">
-        <v>359342.82</v>
+        <v>359228.842</v>
       </c>
       <c r="G420" t="n">
-        <v>-23.52298</v>
+        <v>-23.5223561</v>
       </c>
       <c r="H420" t="n">
-        <v>-46.3777869</v>
+        <v>-46.3788967</v>
       </c>
       <c r="I420" t="n">
-        <v>788.374</v>
+        <v>788.938</v>
       </c>
       <c r="J420" t="n">
-        <v>786.967</v>
+        <v>785.057</v>
       </c>
       <c r="K420" t="n">
-        <v>1.41</v>
+        <v>3.88</v>
       </c>
       <c r="L420" t="inlineStr">
         <is>
@@ -20270,38 +20255,38 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>SL-PV-38</t>
+          <t>SL-PV-36</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>PV-38</t>
+          <t>PV-36</t>
         </is>
       </c>
       <c r="E421" t="n">
-        <v>7398012.211</v>
+        <v>7397999.594</v>
       </c>
       <c r="F421" t="n">
-        <v>359222.572</v>
+        <v>359212.718</v>
       </c>
       <c r="G421" t="n">
-        <v>-23.5220422</v>
+        <v>-23.5221552</v>
       </c>
       <c r="H421" t="n">
-        <v>-46.3789548</v>
+        <v>-46.3790525</v>
       </c>
       <c r="I421" t="n">
-        <v>789.247</v>
+        <v>789.169</v>
       </c>
       <c r="J421" t="n">
-        <v>785.327</v>
+        <v>785.2</v>
       </c>
       <c r="K421" t="n">
-        <v>3.92</v>
+        <v>3.97</v>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
         </is>
       </c>
     </row>
@@ -20318,38 +20303,38 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>SL-PV-69</t>
+          <t>SL-PV-37</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>PV-69</t>
+          <t>PV-37</t>
         </is>
       </c>
       <c r="E422" t="n">
-        <v>7397966.291</v>
+        <v>7398007.858</v>
       </c>
       <c r="F422" t="n">
-        <v>359294.62</v>
+        <v>359206.253</v>
       </c>
       <c r="G422" t="n">
-        <v>-23.5224631</v>
+        <v>-23.5220801</v>
       </c>
       <c r="H422" t="n">
-        <v>-46.3782535</v>
+        <v>-46.379115</v>
       </c>
       <c r="I422" t="n">
-        <v>789.657</v>
+        <v>788.999</v>
       </c>
       <c r="J422" t="n">
-        <v>787.726</v>
+        <v>785.249</v>
       </c>
       <c r="K422" t="n">
-        <v>1.93</v>
+        <v>3.75</v>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
         </is>
       </c>
     </row>
@@ -20366,38 +20351,38 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>SL-PV-70</t>
+          <t>SL-PV-39</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>PV-70</t>
+          <t>PV-39</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>7397970.42</v>
+        <v>7397985.065</v>
       </c>
       <c r="F423" t="n">
-        <v>359315.057</v>
+        <v>359260.286</v>
       </c>
       <c r="G423" t="n">
-        <v>-23.5224276</v>
+        <v>-23.5222906</v>
       </c>
       <c r="H423" t="n">
-        <v>-46.378053</v>
+        <v>-46.378588</v>
       </c>
       <c r="I423" t="n">
-        <v>789.236</v>
+        <v>790.049</v>
       </c>
       <c r="J423" t="n">
-        <v>787.629</v>
+        <v>786.409</v>
       </c>
       <c r="K423" t="n">
-        <v>1.41</v>
+        <v>3.64</v>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
         </is>
       </c>
     </row>
@@ -20414,32 +20399,38 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>SL-PV-64</t>
+          <t>SL-PV-40</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>PV-64</t>
+          <t>PV-40</t>
         </is>
       </c>
       <c r="E424" t="n">
-        <v>7398010.193</v>
+        <v>7397971.64</v>
       </c>
       <c r="F424" t="n">
-        <v>359316.45</v>
+        <v>359281.997</v>
+      </c>
+      <c r="G424" t="n">
+        <v>-23.5224137</v>
+      </c>
+      <c r="H424" t="n">
+        <v>-46.3783767</v>
       </c>
       <c r="I424" t="n">
-        <v>788.654</v>
+        <v>790.846</v>
       </c>
       <c r="J424" t="n">
-        <v>785.813</v>
+        <v>786.551</v>
       </c>
       <c r="K424" t="n">
-        <v>2.84</v>
+        <v>4.31</v>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
         </is>
       </c>
     </row>
@@ -20456,32 +20447,38 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>SL-PV-65</t>
+          <t>SL-PV-41</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>PV-65</t>
+          <t>PV-41</t>
         </is>
       </c>
       <c r="E425" t="n">
-        <v>7397970.718</v>
+        <v>7397938.72</v>
       </c>
       <c r="F425" t="n">
-        <v>359317.925</v>
+        <v>359317.81</v>
+      </c>
+      <c r="G425" t="n">
+        <v>-23.5227141</v>
+      </c>
+      <c r="H425" t="n">
+        <v>-46.378029</v>
       </c>
       <c r="I425" t="n">
-        <v>789.213</v>
+        <v>789.352</v>
       </c>
       <c r="J425" t="n">
-        <v>787.615</v>
+        <v>786.775</v>
       </c>
       <c r="K425" t="n">
-        <v>1.6</v>
+        <v>2.58</v>
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
         </is>
       </c>
     </row>
@@ -20493,43 +20490,43 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>PVE</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>SL-PVE-32</t>
+          <t>SL-PV-42</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>PVE-32</t>
+          <t>PV-42</t>
         </is>
       </c>
       <c r="E426" t="n">
-        <v>7398250.778</v>
+        <v>7397909.511</v>
       </c>
       <c r="F426" t="n">
-        <v>359405.052</v>
+        <v>359342.82</v>
       </c>
       <c r="G426" t="n">
-        <v>-23.5199037</v>
+        <v>-23.52298</v>
       </c>
       <c r="H426" t="n">
-        <v>-46.3771453</v>
+        <v>-46.3777869</v>
       </c>
       <c r="I426" t="n">
-        <v>760.912</v>
+        <v>788.374</v>
       </c>
       <c r="J426" t="n">
-        <v>758.865</v>
+        <v>786.967</v>
       </c>
       <c r="K426" t="n">
-        <v>2.05</v>
+        <v>1.41</v>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
         </is>
       </c>
     </row>
@@ -20546,34 +20543,34 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>SL-PV-04</t>
+          <t>SL-PV-38</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>PV-04</t>
+          <t>PV-38</t>
         </is>
       </c>
       <c r="E427" t="n">
-        <v>7398186.83</v>
+        <v>7398012.211</v>
       </c>
       <c r="F427" t="n">
-        <v>359433.819</v>
+        <v>359222.572</v>
       </c>
       <c r="G427" t="n">
-        <v>-23.5204836</v>
+        <v>-23.5220422</v>
       </c>
       <c r="H427" t="n">
-        <v>-46.3768696</v>
+        <v>-46.3789548</v>
       </c>
       <c r="I427" t="n">
-        <v>761.346</v>
+        <v>789.247</v>
       </c>
       <c r="J427" t="n">
-        <v>759.662</v>
+        <v>785.327</v>
       </c>
       <c r="K427" t="n">
-        <v>1.68</v>
+        <v>3.92</v>
       </c>
       <c r="L427" t="inlineStr">
         <is>
@@ -20594,34 +20591,34 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>SL-PV-05</t>
+          <t>SL-PV-69</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>PV-05</t>
+          <t>PV-69</t>
         </is>
       </c>
       <c r="E428" t="n">
-        <v>7398147.868</v>
+        <v>7397966.291</v>
       </c>
       <c r="F428" t="n">
-        <v>359432.639</v>
+        <v>359294.62</v>
       </c>
       <c r="G428" t="n">
-        <v>-23.5208354</v>
+        <v>-23.5224631</v>
       </c>
       <c r="H428" t="n">
-        <v>-46.3768848</v>
+        <v>-46.3782535</v>
       </c>
       <c r="I428" t="n">
-        <v>761.62</v>
+        <v>789.657</v>
       </c>
       <c r="J428" t="n">
-        <v>759.857</v>
+        <v>787.726</v>
       </c>
       <c r="K428" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="L428" t="inlineStr">
         <is>
@@ -20642,34 +20639,34 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>SL-PV-06</t>
+          <t>SL-PV-70</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>PV-06</t>
+          <t>PV-70</t>
         </is>
       </c>
       <c r="E429" t="n">
-        <v>7398110.3</v>
+        <v>7397970.42</v>
       </c>
       <c r="F429" t="n">
-        <v>359435.788</v>
+        <v>359315.057</v>
       </c>
       <c r="G429" t="n">
-        <v>-23.5211749</v>
+        <v>-23.5224276</v>
       </c>
       <c r="H429" t="n">
-        <v>-46.3768575</v>
+        <v>-46.378053</v>
       </c>
       <c r="I429" t="n">
-        <v>761.895</v>
+        <v>789.236</v>
       </c>
       <c r="J429" t="n">
-        <v>760.046</v>
+        <v>787.629</v>
       </c>
       <c r="K429" t="n">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="L429" t="inlineStr">
         <is>
@@ -20690,34 +20687,28 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>SL-PV-07</t>
+          <t>SL-PV-64</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>PV-07</t>
+          <t>PV-64</t>
         </is>
       </c>
       <c r="E430" t="n">
-        <v>7398078.311</v>
+        <v>7398010.193</v>
       </c>
       <c r="F430" t="n">
-        <v>359448.771</v>
-      </c>
-      <c r="G430" t="n">
-        <v>-23.5214649</v>
-      </c>
-      <c r="H430" t="n">
-        <v>-46.3767334</v>
+        <v>359316.45</v>
       </c>
       <c r="I430" t="n">
-        <v>761.657</v>
+        <v>788.654</v>
       </c>
       <c r="J430" t="n">
-        <v>760.218</v>
+        <v>785.813</v>
       </c>
       <c r="K430" t="n">
-        <v>1.44</v>
+        <v>2.84</v>
       </c>
       <c r="L430" t="inlineStr">
         <is>
@@ -20738,34 +20729,28 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>SL-PV-08</t>
+          <t>SL-PV-65</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>PV-08</t>
+          <t>PV-65</t>
         </is>
       </c>
       <c r="E431" t="n">
-        <v>7398070.299</v>
+        <v>7397970.718</v>
       </c>
       <c r="F431" t="n">
-        <v>359450.392</v>
-      </c>
-      <c r="G431" t="n">
-        <v>-23.5215374</v>
-      </c>
-      <c r="H431" t="n">
-        <v>-46.3767183</v>
+        <v>359317.925</v>
       </c>
       <c r="I431" t="n">
-        <v>762.054</v>
+        <v>789.213</v>
       </c>
       <c r="J431" t="n">
-        <v>760.647</v>
+        <v>787.615</v>
       </c>
       <c r="K431" t="n">
-        <v>1.41</v>
+        <v>1.6</v>
       </c>
       <c r="L431" t="inlineStr">
         <is>
@@ -20781,39 +20766,39 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PVE</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>SL-PV-02</t>
+          <t>SL-PVE-32</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>PV-02</t>
+          <t>PVE-32</t>
         </is>
       </c>
       <c r="E432" t="n">
-        <v>7398239.066</v>
+        <v>7398250.778</v>
       </c>
       <c r="F432" t="n">
-        <v>359409.719</v>
+        <v>359405.052</v>
       </c>
       <c r="G432" t="n">
-        <v>-23.5200098</v>
+        <v>-23.5199037</v>
       </c>
       <c r="H432" t="n">
-        <v>-46.3771007</v>
+        <v>-46.3771453</v>
       </c>
       <c r="I432" t="n">
-        <v>760.8099999999999</v>
+        <v>760.912</v>
       </c>
       <c r="J432" t="n">
-        <v>759.326</v>
+        <v>758.865</v>
       </c>
       <c r="K432" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="L432" t="inlineStr">
         <is>
@@ -20834,34 +20819,34 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>SL-PV-03</t>
+          <t>SL-PV-04</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>PV-03</t>
+          <t>PV-04</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>7398232.807</v>
+        <v>7398186.83</v>
       </c>
       <c r="F433" t="n">
-        <v>359429.767</v>
+        <v>359433.819</v>
       </c>
       <c r="G433" t="n">
-        <v>-23.5200681</v>
+        <v>-23.5204836</v>
       </c>
       <c r="H433" t="n">
-        <v>-46.376905</v>
+        <v>-46.3768696</v>
       </c>
       <c r="I433" t="n">
-        <v>761.472</v>
+        <v>761.346</v>
       </c>
       <c r="J433" t="n">
-        <v>759.431</v>
+        <v>759.662</v>
       </c>
       <c r="K433" t="n">
-        <v>2.04</v>
+        <v>1.68</v>
       </c>
       <c r="L433" t="inlineStr">
         <is>
@@ -20877,37 +20862,43 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PVE</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>SL-PVE-31</t>
+          <t>SL-PV-05</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>PVE-31</t>
+          <t>PV-05</t>
         </is>
       </c>
       <c r="E434" t="n">
-        <v>7398016.07</v>
+        <v>7398147.868</v>
       </c>
       <c r="F434" t="n">
-        <v>359202.358</v>
+        <v>359432.639</v>
+      </c>
+      <c r="G434" t="n">
+        <v>-23.5208354</v>
+      </c>
+      <c r="H434" t="n">
+        <v>-46.3768848</v>
       </c>
       <c r="I434" t="n">
-        <v>788.763</v>
+        <v>761.62</v>
       </c>
       <c r="J434" t="n">
-        <v>786.3630000000001</v>
+        <v>759.857</v>
       </c>
       <c r="K434" t="n">
-        <v>2.4</v>
+        <v>1.76</v>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>Adicionado via projeto RCE Comunidade Sao Lucas; interligado ao PV-37.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
         </is>
       </c>
     </row>
@@ -20924,32 +20915,38 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>SL-PV-75</t>
+          <t>SL-PV-06</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>PV-75</t>
+          <t>PV-06</t>
         </is>
       </c>
       <c r="E435" t="n">
-        <v>7398253.374</v>
+        <v>7398110.3</v>
       </c>
       <c r="F435" t="n">
-        <v>359465.776</v>
+        <v>359435.788</v>
+      </c>
+      <c r="G435" t="n">
+        <v>-23.5211749</v>
+      </c>
+      <c r="H435" t="n">
+        <v>-46.3768575</v>
       </c>
       <c r="I435" t="n">
-        <v>761.765</v>
+        <v>761.895</v>
       </c>
       <c r="J435" t="n">
-        <v>760.415</v>
+        <v>760.046</v>
       </c>
       <c r="K435" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>Adicionado via projeto São Lucas</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
         </is>
       </c>
     </row>
@@ -20966,32 +20963,38 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>SL-PV-76</t>
+          <t>SL-PV-07</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>PV-76</t>
+          <t>PV-07</t>
         </is>
       </c>
       <c r="E436" t="n">
-        <v>7398255.262</v>
+        <v>7398078.311</v>
       </c>
       <c r="F436" t="n">
-        <v>359466.421</v>
+        <v>359448.771</v>
+      </c>
+      <c r="G436" t="n">
+        <v>-23.5214649</v>
+      </c>
+      <c r="H436" t="n">
+        <v>-46.3767334</v>
       </c>
       <c r="I436" t="n">
-        <v>761.674</v>
+        <v>761.657</v>
       </c>
       <c r="J436" t="n">
-        <v>760.426</v>
+        <v>760.218</v>
       </c>
       <c r="K436" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>Adicionado via projeto São Lucas</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
         </is>
       </c>
     </row>
@@ -21008,32 +21011,38 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>SL-PV-77</t>
+          <t>SL-PV-08</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>PV-77</t>
+          <t>PV-08</t>
         </is>
       </c>
       <c r="E437" t="n">
-        <v>7398249.797</v>
+        <v>7398070.299</v>
       </c>
       <c r="F437" t="n">
-        <v>359483.592</v>
+        <v>359450.392</v>
+      </c>
+      <c r="G437" t="n">
+        <v>-23.5215374</v>
+      </c>
+      <c r="H437" t="n">
+        <v>-46.3767183</v>
       </c>
       <c r="I437" t="n">
-        <v>762.967</v>
+        <v>762.054</v>
       </c>
       <c r="J437" t="n">
-        <v>761.376</v>
+        <v>760.647</v>
       </c>
       <c r="K437" t="n">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>Adicionado via projeto São Lucas</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
         </is>
       </c>
     </row>
@@ -21050,32 +21059,38 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>SL-PV-78</t>
+          <t>SL-PV-02</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>PV-78</t>
+          <t>PV-02</t>
         </is>
       </c>
       <c r="E438" t="n">
-        <v>7398238.573</v>
+        <v>7398239.066</v>
       </c>
       <c r="F438" t="n">
-        <v>359501.728</v>
+        <v>359409.719</v>
+      </c>
+      <c r="G438" t="n">
+        <v>-23.5200098</v>
+      </c>
+      <c r="H438" t="n">
+        <v>-46.3771007</v>
       </c>
       <c r="I438" t="n">
-        <v>765.659</v>
+        <v>760.8099999999999</v>
       </c>
       <c r="J438" t="n">
-        <v>764.275</v>
+        <v>759.326</v>
       </c>
       <c r="K438" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>Adicionado via projeto São Lucas</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
         </is>
       </c>
     </row>
@@ -21092,117 +21107,375 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>SL-PV-75.1</t>
+          <t>SL-PV-03</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>PV-75.1</t>
-        </is>
+          <t>PV-03</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>7398232.807</v>
+      </c>
+      <c r="F439" t="n">
+        <v>359429.767</v>
       </c>
       <c r="G439" t="n">
-        <v>-23.5198222</v>
+        <v>-23.5200681</v>
       </c>
       <c r="H439" t="n">
-        <v>-46.3768722</v>
+        <v>-46.376905</v>
+      </c>
+      <c r="I439" t="n">
+        <v>761.472</v>
+      </c>
+      <c r="J439" t="n">
+        <v>759.431</v>
+      </c>
+      <c r="K439" t="n">
+        <v>2.04</v>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>Ponto auxiliar obtido via Google Earth.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_comunidade_sao_lucas</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PVE</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>JC-PV-17-FL07</t>
+          <t>SL-PVE-31</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>PV-17</t>
+          <t>PVE-31</t>
         </is>
       </c>
       <c r="E440" t="n">
-        <v>7397122.275</v>
+        <v>7398016.07</v>
       </c>
       <c r="F440" t="n">
-        <v>358726.884</v>
-      </c>
-      <c r="G440" t="n">
-        <v>-23.5300354</v>
-      </c>
-      <c r="H440" t="n">
-        <v>-46.3838931</v>
+        <v>359202.358</v>
       </c>
       <c r="I440" t="n">
-        <v>782.299</v>
+        <v>788.763</v>
       </c>
       <c r="J440" t="n">
-        <v>779.199</v>
+        <v>786.3630000000001</v>
       </c>
       <c r="K440" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; trechos PV-16 ao PV-17 e PV-17 ao PV-18.</t>
+          <t>Adicionado via projeto RCE Comunidade Sao Lucas; interligado ao PV-37.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
+          <t>rce_comunidade_sao_lucas</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>SL-PV-75</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>PV-75</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>7398253.374</v>
+      </c>
+      <c r="F441" t="n">
+        <v>359465.776</v>
+      </c>
+      <c r="I441" t="n">
+        <v>761.765</v>
+      </c>
+      <c r="J441" t="n">
+        <v>760.415</v>
+      </c>
+      <c r="K441" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L441" t="inlineStr">
+        <is>
+          <t>Adicionado via projeto São Lucas</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>rce_comunidade_sao_lucas</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>SL-PV-76</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>PV-76</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>7398255.262</v>
+      </c>
+      <c r="F442" t="n">
+        <v>359466.421</v>
+      </c>
+      <c r="I442" t="n">
+        <v>761.674</v>
+      </c>
+      <c r="J442" t="n">
+        <v>760.426</v>
+      </c>
+      <c r="K442" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Adicionado via projeto São Lucas</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>rce_comunidade_sao_lucas</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>SL-PV-77</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>PV-77</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>7398249.797</v>
+      </c>
+      <c r="F443" t="n">
+        <v>359483.592</v>
+      </c>
+      <c r="I443" t="n">
+        <v>762.967</v>
+      </c>
+      <c r="J443" t="n">
+        <v>761.376</v>
+      </c>
+      <c r="K443" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Adicionado via projeto São Lucas</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>rce_comunidade_sao_lucas</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>SL-PV-78</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>PV-78</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>7398238.573</v>
+      </c>
+      <c r="F444" t="n">
+        <v>359501.728</v>
+      </c>
+      <c r="I444" t="n">
+        <v>765.659</v>
+      </c>
+      <c r="J444" t="n">
+        <v>764.275</v>
+      </c>
+      <c r="K444" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Adicionado via projeto São Lucas</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>rce_comunidade_sao_lucas</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>SL-PV-75.1</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>PV-75.1</t>
+        </is>
+      </c>
+      <c r="G445" t="n">
+        <v>-23.5198222</v>
+      </c>
+      <c r="H445" t="n">
+        <v>-46.3768722</v>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Ponto auxiliar obtido via Google Earth.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
           <t>cts_joao_canzi</t>
         </is>
       </c>
-      <c r="B441" t="inlineStr">
+      <c r="B446" t="inlineStr">
         <is>
           <t>PV</t>
         </is>
       </c>
-      <c r="C441" t="inlineStr">
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>JC-PV-17-FL07</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>PV-17</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>7397122.275</v>
+      </c>
+      <c r="F446" t="n">
+        <v>358726.884</v>
+      </c>
+      <c r="G446" t="n">
+        <v>-23.5300354</v>
+      </c>
+      <c r="H446" t="n">
+        <v>-46.3838931</v>
+      </c>
+      <c r="I446" t="n">
+        <v>782.299</v>
+      </c>
+      <c r="J446" t="n">
+        <v>779.199</v>
+      </c>
+      <c r="K446" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; trechos PV-16 ao PV-17 e PV-17 ao PV-18.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
         <is>
           <t>JC-PV-20</t>
         </is>
       </c>
-      <c r="D441" t="inlineStr">
+      <c r="D447" t="inlineStr">
         <is>
           <t>PV-20</t>
         </is>
       </c>
-      <c r="E441" t="n">
+      <c r="E447" t="n">
         <v>7397174.5</v>
       </c>
-      <c r="F441" t="n">
+      <c r="F447" t="n">
         <v>358918.3</v>
       </c>
-      <c r="G441" t="n">
+      <c r="G447" t="n">
         <v>-23.5295804</v>
       </c>
-      <c r="H441" t="n">
+      <c r="H447" t="n">
         <v>-46.3820136</v>
       </c>
-      <c r="I441" t="n">
+      <c r="I447" t="n">
         <v>794.6</v>
       </c>
-      <c r="J441" t="n">
+      <c r="J447" t="n">
         <v>790.638</v>
       </c>
-      <c r="K441" t="n">
+      <c r="K447" t="n">
         <v>3.96</v>
       </c>
-      <c r="L441" t="inlineStr">
+      <c r="L447" t="inlineStr">
         <is>
           <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-19 ao PV-20.</t>
         </is>
@@ -21215,12 +21488,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="1">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R454"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <dimension ref="A1:R460"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
     <col width="17.44140625" customWidth="1" min="3" max="3"/>
@@ -50682,53 +50955,53 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_elias_sleiman</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>JC-013</t>
+          <t>ELIAS-003</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>PV-18 - PV-19</t>
+          <t>PV-23 - PV-24</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>PV-18</t>
+          <t>PV-23</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>PV-19</t>
+          <t>PV-24</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>PEAD LISO</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="G419" t="n">
-        <v>355</v>
+        <v>200</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Metodo Nao Destrutivo - MND</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I419" t="n">
-        <v>66.72499999999999</v>
+        <v>44.64</v>
       </c>
       <c r="J419" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="K419" t="n">
-        <v>4</v>
+        <v>2.36</v>
       </c>
       <c r="L419" t="n">
-        <v>4</v>
+        <v>3.58</v>
       </c>
       <c r="M419" t="inlineStr">
         <is>
@@ -50737,46 +51010,46 @@
       </c>
       <c r="N419" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; PV-18 ao PV-19; arquivo: planos_furo/cts_joao_canzi_fl07_pv18_pv19.pdf; taxa 0,0485.</t>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
         </is>
       </c>
       <c r="O419" t="n">
-        <v>-23.5300224</v>
+        <v>-23.5309793</v>
       </c>
       <c r="P419" t="n">
-        <v>-46.3831139</v>
+        <v>-46.3832624</v>
       </c>
       <c r="Q419" t="n">
-        <v>-23.5298774</v>
+        <v>-23.5307209</v>
       </c>
       <c r="R419" t="n">
-        <v>-46.3824796</v>
+        <v>-46.3829268</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>rce_elias_sleiman</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>SL-001</t>
+          <t>ELIAS-004</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>PV-26 - PV-27</t>
+          <t>PV-24 - PV-25</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>PV-26</t>
+          <t>PV-24</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>PV-27</t>
+          <t>PV-25</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -50789,20 +51062,20 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I420" t="n">
-        <v>14.74</v>
+        <v>82.91</v>
       </c>
       <c r="J420" t="n">
-        <v>3.04</v>
+        <v>2.36</v>
       </c>
       <c r="K420" t="n">
-        <v>3.57</v>
+        <v>2.72</v>
       </c>
       <c r="L420" t="n">
-        <v>3.57</v>
+        <v>2.72</v>
       </c>
       <c r="M420" t="inlineStr">
         <is>
@@ -50811,46 +51084,46 @@
       </c>
       <c r="N420" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
         </is>
       </c>
       <c r="O420" t="n">
-        <v>-23.5236471</v>
+        <v>-23.5307209</v>
       </c>
       <c r="P420" t="n">
-        <v>-46.3767998</v>
+        <v>-46.3829268</v>
       </c>
       <c r="Q420" t="n">
-        <v>-23.5237798</v>
+        <v>-23.5307563</v>
       </c>
       <c r="R420" t="n">
-        <v>-46.3767878</v>
+        <v>-46.3821157</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>rce_elias_sleiman</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>SL-002</t>
+          <t>ELIAS-005</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>PV-27 - PV-28</t>
+          <t>PV-25 - PV-26</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>PV-27</t>
+          <t>PV-25</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>PV-28</t>
+          <t>PV-26</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -50863,20 +51136,20 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I421" t="n">
-        <v>3.63</v>
+        <v>44.29</v>
       </c>
       <c r="J421" t="n">
-        <v>3.57</v>
+        <v>2.72</v>
       </c>
       <c r="K421" t="n">
-        <v>3.34</v>
+        <v>2.62</v>
       </c>
       <c r="L421" t="n">
-        <v>3.57</v>
+        <v>2.72</v>
       </c>
       <c r="M421" t="inlineStr">
         <is>
@@ -50885,46 +51158,46 @@
       </c>
       <c r="N421" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
         </is>
       </c>
       <c r="O421" t="n">
-        <v>-23.5237798</v>
+        <v>-23.5307563</v>
       </c>
       <c r="P421" t="n">
-        <v>-46.3767878</v>
+        <v>-46.3821157</v>
       </c>
       <c r="Q421" t="n">
-        <v>-23.5238121</v>
+        <v>-23.5311521</v>
       </c>
       <c r="R421" t="n">
-        <v>-46.3767936</v>
+        <v>-46.3821788</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>rce_elias_sleiman</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>SL-003</t>
+          <t>ELIAS-006</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>PV-28 - PV-29</t>
+          <t>PV-26 - PV-27</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>PV-28</t>
+          <t>PV-26</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>PV-29</t>
+          <t>PV-27</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -50937,20 +51210,20 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I422" t="n">
-        <v>7.51</v>
+        <v>50.97</v>
       </c>
       <c r="J422" t="n">
-        <v>3.34</v>
+        <v>2.62</v>
       </c>
       <c r="K422" t="n">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="L422" t="n">
-        <v>3.34</v>
+        <v>2.62</v>
       </c>
       <c r="M422" t="inlineStr">
         <is>
@@ -50959,46 +51232,46 @@
       </c>
       <c r="N422" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
         </is>
       </c>
       <c r="O422" t="n">
-        <v>-23.5238121</v>
+        <v>-23.5311521</v>
       </c>
       <c r="P422" t="n">
-        <v>-46.3767936</v>
+        <v>-46.3821788</v>
       </c>
       <c r="Q422" t="n">
-        <v>-23.5238331</v>
+        <v>-23.5315893</v>
       </c>
       <c r="R422" t="n">
-        <v>-46.3768636</v>
+        <v>-46.3820231</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>rce_elias_sleiman</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>SL-004</t>
+          <t>ELIAS-007</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>PV-29 - PV-30</t>
+          <t>PV-27 - PV-28</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>PV-29</t>
+          <t>PV-27</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>PV-30</t>
+          <t>PV-28</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -51011,20 +51284,20 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I423" t="n">
-        <v>13.61</v>
+        <v>43.95</v>
       </c>
       <c r="J423" t="n">
-        <v>1.81</v>
+        <v>2.09</v>
       </c>
       <c r="K423" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="L423" t="n">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="M423" t="inlineStr">
         <is>
@@ -51033,46 +51306,46 @@
       </c>
       <c r="N423" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
         </is>
       </c>
       <c r="O423" t="n">
-        <v>-23.5238331</v>
+        <v>-23.5315893</v>
       </c>
       <c r="P423" t="n">
-        <v>-46.3768636</v>
+        <v>-46.3820231</v>
       </c>
       <c r="Q423" t="n">
-        <v>-23.5237849</v>
+        <v>-23.5319394</v>
       </c>
       <c r="R423" t="n">
-        <v>-46.3769862</v>
+        <v>-46.3818203</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>rce_elias_sleiman</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>SL-005</t>
+          <t>ELIAS-008</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>PV-30 - PV-31</t>
+          <t>PV-28 - PV-29</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>PV-30</t>
+          <t>PV-28</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>PV-31</t>
+          <t>PV-29</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -51085,20 +51358,20 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I424" t="n">
-        <v>6.62</v>
+        <v>28.15</v>
       </c>
       <c r="J424" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="K424" t="n">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="L424" t="n">
-        <v>1.43</v>
+        <v>2.2</v>
       </c>
       <c r="M424" t="inlineStr">
         <is>
@@ -51107,72 +51380,72 @@
       </c>
       <c r="N424" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
         </is>
       </c>
       <c r="O424" t="n">
-        <v>-23.5237849</v>
+        <v>-23.5319394</v>
       </c>
       <c r="P424" t="n">
-        <v>-46.3769862</v>
+        <v>-46.3818203</v>
       </c>
       <c r="Q424" t="n">
-        <v>-23.5237689</v>
+        <v>-23.5321621</v>
       </c>
       <c r="R424" t="n">
-        <v>-46.3770487</v>
+        <v>-46.3816872</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>SL-006</t>
+          <t>JC-013</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>PV-31 - PV-32</t>
+          <t>PV-18 - PV-19</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>PV-31</t>
+          <t>PV-18</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>PV-32</t>
+          <t>PV-19</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD LISO</t>
         </is>
       </c>
       <c r="G425" t="n">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Metodo Nao Destrutivo - MND</t>
         </is>
       </c>
       <c r="I425" t="n">
-        <v>70.89</v>
+        <v>66.72499999999999</v>
       </c>
       <c r="J425" t="n">
-        <v>1.43</v>
+        <v>3.5</v>
       </c>
       <c r="K425" t="n">
-        <v>2.18</v>
+        <v>4</v>
       </c>
       <c r="L425" t="n">
-        <v>2.18</v>
+        <v>4</v>
       </c>
       <c r="M425" t="inlineStr">
         <is>
@@ -51181,20 +51454,20 @@
       </c>
       <c r="N425" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
+          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; PV-18 ao PV-19; arquivo: planos_furo/cts_joao_canzi_fl07_pv18_pv19.pdf; taxa 0,0485.</t>
         </is>
       </c>
       <c r="O425" t="n">
-        <v>-23.5237689</v>
+        <v>-23.5300224</v>
       </c>
       <c r="P425" t="n">
-        <v>-46.3770487</v>
+        <v>-46.3831139</v>
       </c>
       <c r="Q425" t="n">
-        <v>-23.5233519</v>
+        <v>-23.5298774</v>
       </c>
       <c r="R425" t="n">
-        <v>-46.3775754</v>
+        <v>-46.3824796</v>
       </c>
     </row>
     <row r="426">
@@ -51205,22 +51478,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>SL-007</t>
+          <t>SL-001</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>PV-32 - PV-33</t>
+          <t>PV-26 - PV-27</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>PV-32</t>
+          <t>PV-26</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>PV-33</t>
+          <t>PV-27</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -51237,16 +51510,16 @@
         </is>
       </c>
       <c r="I426" t="n">
-        <v>62.56</v>
+        <v>14.74</v>
       </c>
       <c r="J426" t="n">
-        <v>2.18</v>
+        <v>3.04</v>
       </c>
       <c r="K426" t="n">
-        <v>2.16</v>
+        <v>3.57</v>
       </c>
       <c r="L426" t="n">
-        <v>2.18</v>
+        <v>3.57</v>
       </c>
       <c r="M426" t="inlineStr">
         <is>
@@ -51259,16 +51532,16 @@
         </is>
       </c>
       <c r="O426" t="n">
-        <v>-23.5233519</v>
+        <v>-23.5236471</v>
       </c>
       <c r="P426" t="n">
-        <v>-46.3775754</v>
+        <v>-46.3767998</v>
       </c>
       <c r="Q426" t="n">
-        <v>-23.5230626</v>
+        <v>-23.5237798</v>
       </c>
       <c r="R426" t="n">
-        <v>-46.3781017</v>
+        <v>-46.3767878</v>
       </c>
     </row>
     <row r="427">
@@ -51279,22 +51552,22 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>SL-008</t>
+          <t>SL-002</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>PV-33 - PV-34</t>
+          <t>PV-27 - PV-28</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>PV-33</t>
+          <t>PV-27</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>PV-34</t>
+          <t>PV-28</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -51311,16 +51584,16 @@
         </is>
       </c>
       <c r="I427" t="n">
-        <v>55.46</v>
+        <v>3.63</v>
       </c>
       <c r="J427" t="n">
-        <v>2.16</v>
+        <v>3.57</v>
       </c>
       <c r="K427" t="n">
-        <v>2.45</v>
+        <v>3.34</v>
       </c>
       <c r="L427" t="n">
-        <v>2.45</v>
+        <v>3.57</v>
       </c>
       <c r="M427" t="inlineStr">
         <is>
@@ -51333,16 +51606,16 @@
         </is>
       </c>
       <c r="O427" t="n">
-        <v>-23.5230626</v>
+        <v>-23.5237798</v>
       </c>
       <c r="P427" t="n">
-        <v>-46.3781017</v>
+        <v>-46.3767878</v>
       </c>
       <c r="Q427" t="n">
-        <v>-23.5226874</v>
+        <v>-23.5238121</v>
       </c>
       <c r="R427" t="n">
-        <v>-46.3784614</v>
+        <v>-46.3767936</v>
       </c>
     </row>
     <row r="428">
@@ -51353,22 +51626,22 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>SL-009</t>
+          <t>SL-003</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>PV-34 - PV-35</t>
+          <t>PV-28 - PV-29</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>PV-34</t>
+          <t>PV-28</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>PV-35</t>
+          <t>PV-29</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -51385,16 +51658,16 @@
         </is>
       </c>
       <c r="I428" t="n">
-        <v>57.62</v>
+        <v>7.51</v>
       </c>
       <c r="J428" t="n">
-        <v>2.45</v>
+        <v>3.34</v>
       </c>
       <c r="K428" t="n">
-        <v>3.88</v>
+        <v>1.81</v>
       </c>
       <c r="L428" t="n">
-        <v>3.88</v>
+        <v>3.34</v>
       </c>
       <c r="M428" t="inlineStr">
         <is>
@@ -51407,16 +51680,16 @@
         </is>
       </c>
       <c r="O428" t="n">
-        <v>-23.5226874</v>
+        <v>-23.5238121</v>
       </c>
       <c r="P428" t="n">
-        <v>-46.3784614</v>
+        <v>-46.3767936</v>
       </c>
       <c r="Q428" t="n">
-        <v>-23.5223561</v>
+        <v>-23.5238331</v>
       </c>
       <c r="R428" t="n">
-        <v>-46.3788967</v>
+        <v>-46.3768636</v>
       </c>
     </row>
     <row r="429">
@@ -51427,22 +51700,22 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>SL-010</t>
+          <t>SL-004</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>PV-35 - PV-36</t>
+          <t>PV-29 - PV-30</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>PV-35</t>
+          <t>PV-29</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>PV-36</t>
+          <t>PV-30</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -51459,16 +51732,16 @@
         </is>
       </c>
       <c r="I429" t="n">
-        <v>27.35</v>
+        <v>13.61</v>
       </c>
       <c r="J429" t="n">
-        <v>3.88</v>
+        <v>1.81</v>
       </c>
       <c r="K429" t="n">
-        <v>3.97</v>
+        <v>1.4</v>
       </c>
       <c r="L429" t="n">
-        <v>3.97</v>
+        <v>1.81</v>
       </c>
       <c r="M429" t="inlineStr">
         <is>
@@ -51481,16 +51754,16 @@
         </is>
       </c>
       <c r="O429" t="n">
-        <v>-23.5223561</v>
+        <v>-23.5238331</v>
       </c>
       <c r="P429" t="n">
-        <v>-46.3788967</v>
+        <v>-46.3768636</v>
       </c>
       <c r="Q429" t="n">
-        <v>-23.5221552</v>
+        <v>-23.5237849</v>
       </c>
       <c r="R429" t="n">
-        <v>-46.3790525</v>
+        <v>-46.3769862</v>
       </c>
     </row>
     <row r="430">
@@ -51501,22 +51774,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>SL-011</t>
+          <t>SL-005</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>PV-36 - PV-37</t>
+          <t>PV-30 - PV-31</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>PV-36</t>
+          <t>PV-30</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>PV-37</t>
+          <t>PV-31</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -51533,16 +51806,16 @@
         </is>
       </c>
       <c r="I430" t="n">
-        <v>10.49</v>
+        <v>6.62</v>
       </c>
       <c r="J430" t="n">
-        <v>3.97</v>
+        <v>1.4</v>
       </c>
       <c r="K430" t="n">
-        <v>3.75</v>
+        <v>1.43</v>
       </c>
       <c r="L430" t="n">
-        <v>3.97</v>
+        <v>1.43</v>
       </c>
       <c r="M430" t="inlineStr">
         <is>
@@ -51555,16 +51828,16 @@
         </is>
       </c>
       <c r="O430" t="n">
-        <v>-23.5221552</v>
+        <v>-23.5237849</v>
       </c>
       <c r="P430" t="n">
-        <v>-46.3790525</v>
+        <v>-46.3769862</v>
       </c>
       <c r="Q430" t="n">
-        <v>-23.5220801</v>
+        <v>-23.5237689</v>
       </c>
       <c r="R430" t="n">
-        <v>-46.379115</v>
+        <v>-46.3770487</v>
       </c>
     </row>
     <row r="431">
@@ -51575,22 +51848,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>SL-012</t>
+          <t>SL-006</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>PV-37 - PV-38</t>
+          <t>PV-31 - PV-32</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>PV-37</t>
+          <t>PV-31</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>PV-38</t>
+          <t>PV-32</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -51603,20 +51876,20 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I431" t="n">
-        <v>16.89</v>
+        <v>70.89</v>
       </c>
       <c r="J431" t="n">
-        <v>3.75</v>
+        <v>1.43</v>
       </c>
       <c r="K431" t="n">
-        <v>3.92</v>
+        <v>2.18</v>
       </c>
       <c r="L431" t="n">
-        <v>3.92</v>
+        <v>2.18</v>
       </c>
       <c r="M431" t="inlineStr">
         <is>
@@ -51625,20 +51898,20 @@
       </c>
       <c r="N431" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. PV-38 incluido conforme novo print.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
         </is>
       </c>
       <c r="O431" t="n">
-        <v>-23.5220801</v>
+        <v>-23.5237689</v>
       </c>
       <c r="P431" t="n">
-        <v>-46.379115</v>
+        <v>-46.3770487</v>
       </c>
       <c r="Q431" t="n">
-        <v>-23.5220422</v>
+        <v>-23.5233519</v>
       </c>
       <c r="R431" t="n">
-        <v>-46.3789548</v>
+        <v>-46.3775754</v>
       </c>
     </row>
     <row r="432">
@@ -51649,22 +51922,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>SL-013</t>
+          <t>SL-007</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>PV-38 - PV-39</t>
+          <t>PV-32 - PV-33</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>PV-38</t>
+          <t>PV-32</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>PV-39</t>
+          <t>PV-33</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -51677,20 +51950,20 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I432" t="n">
-        <v>46.47</v>
+        <v>62.56</v>
       </c>
       <c r="J432" t="n">
-        <v>3.92</v>
+        <v>2.18</v>
       </c>
       <c r="K432" t="n">
-        <v>3.64</v>
+        <v>2.16</v>
       </c>
       <c r="L432" t="n">
-        <v>3.92</v>
+        <v>2.18</v>
       </c>
       <c r="M432" t="inlineStr">
         <is>
@@ -51699,20 +51972,20 @@
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. PV-38 incluido conforme novo print.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
         </is>
       </c>
       <c r="O432" t="n">
-        <v>-23.5220422</v>
+        <v>-23.5233519</v>
       </c>
       <c r="P432" t="n">
-        <v>-46.3789548</v>
+        <v>-46.3775754</v>
       </c>
       <c r="Q432" t="n">
-        <v>-23.5222906</v>
+        <v>-23.5230626</v>
       </c>
       <c r="R432" t="n">
-        <v>-46.378588</v>
+        <v>-46.3781017</v>
       </c>
     </row>
     <row r="433">
@@ -51723,22 +51996,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>SL-014</t>
+          <t>SL-008</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>PV-40 - PV-41</t>
+          <t>PV-33 - PV-34</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>PV-40</t>
+          <t>PV-33</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>PV-41</t>
+          <t>PV-34</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -51755,16 +52028,16 @@
         </is>
       </c>
       <c r="I433" t="n">
-        <v>48.64</v>
+        <v>55.46</v>
       </c>
       <c r="J433" t="n">
-        <v>4.31</v>
+        <v>2.16</v>
       </c>
       <c r="K433" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="L433" t="n">
-        <v>4.31</v>
+        <v>2.45</v>
       </c>
       <c r="M433" t="inlineStr">
         <is>
@@ -51777,16 +52050,16 @@
         </is>
       </c>
       <c r="O433" t="n">
-        <v>-23.5224137</v>
+        <v>-23.5230626</v>
       </c>
       <c r="P433" t="n">
-        <v>-46.3783767</v>
+        <v>-46.3781017</v>
       </c>
       <c r="Q433" t="n">
-        <v>-23.5227141</v>
+        <v>-23.5226874</v>
       </c>
       <c r="R433" t="n">
-        <v>-46.378029</v>
+        <v>-46.3784614</v>
       </c>
     </row>
     <row r="434">
@@ -51797,22 +52070,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>SL-015</t>
+          <t>SL-009</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>PV-41 - PV-42</t>
+          <t>PV-34 - PV-35</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>PV-41</t>
+          <t>PV-34</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>PV-42</t>
+          <t>PV-35</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -51829,16 +52102,16 @@
         </is>
       </c>
       <c r="I434" t="n">
-        <v>38.45</v>
+        <v>57.62</v>
       </c>
       <c r="J434" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="K434" t="n">
-        <v>1.41</v>
+        <v>3.88</v>
       </c>
       <c r="L434" t="n">
-        <v>2.58</v>
+        <v>3.88</v>
       </c>
       <c r="M434" t="inlineStr">
         <is>
@@ -51851,16 +52124,16 @@
         </is>
       </c>
       <c r="O434" t="n">
-        <v>-23.5227141</v>
+        <v>-23.5226874</v>
       </c>
       <c r="P434" t="n">
-        <v>-46.378029</v>
+        <v>-46.3784614</v>
       </c>
       <c r="Q434" t="n">
-        <v>-23.52298</v>
+        <v>-23.5223561</v>
       </c>
       <c r="R434" t="n">
-        <v>-46.3777869</v>
+        <v>-46.3788967</v>
       </c>
     </row>
     <row r="435">
@@ -51871,22 +52144,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>SL-016</t>
+          <t>SL-010</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>PV-39 - PV-40</t>
+          <t>PV-35 - PV-36</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>PV-39</t>
+          <t>PV-35</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>PV-40</t>
+          <t>PV-36</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -51899,20 +52172,20 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I435" t="n">
-        <v>24.53</v>
+        <v>27.35</v>
       </c>
       <c r="J435" t="n">
-        <v>3.64</v>
+        <v>3.88</v>
       </c>
       <c r="K435" t="n">
-        <v>4.31</v>
+        <v>3.97</v>
       </c>
       <c r="L435" t="n">
-        <v>4.31</v>
+        <v>3.97</v>
       </c>
       <c r="M435" t="inlineStr">
         <is>
@@ -51921,20 +52194,20 @@
       </c>
       <c r="N435" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. Extensao lida no print.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
         </is>
       </c>
       <c r="O435" t="n">
-        <v>-23.5222906</v>
+        <v>-23.5223561</v>
       </c>
       <c r="P435" t="n">
-        <v>-46.378588</v>
+        <v>-46.3788967</v>
       </c>
       <c r="Q435" t="n">
-        <v>-23.5224137</v>
+        <v>-23.5221552</v>
       </c>
       <c r="R435" t="n">
-        <v>-46.3783767</v>
+        <v>-46.3790525</v>
       </c>
     </row>
     <row r="436">
@@ -51945,22 +52218,22 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>SL-017</t>
+          <t>SL-011</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>PV-40 - PV-69</t>
+          <t>PV-36 - PV-37</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>PV-40</t>
+          <t>PV-36</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>PV-69</t>
+          <t>PV-37</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -51973,20 +52246,20 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I436" t="n">
-        <v>13.08</v>
+        <v>10.49</v>
       </c>
       <c r="J436" t="n">
-        <v>4.31</v>
+        <v>3.97</v>
       </c>
       <c r="K436" t="n">
-        <v>1.93</v>
+        <v>3.75</v>
       </c>
       <c r="L436" t="n">
-        <v>4.31</v>
+        <v>3.97</v>
       </c>
       <c r="M436" t="inlineStr">
         <is>
@@ -51995,20 +52268,20 @@
       </c>
       <c r="N436" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. Extensao lida no print.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
         </is>
       </c>
       <c r="O436" t="n">
-        <v>-23.5224137</v>
+        <v>-23.5221552</v>
       </c>
       <c r="P436" t="n">
-        <v>-46.3783767</v>
+        <v>-46.3790525</v>
       </c>
       <c r="Q436" t="n">
-        <v>-23.5224631</v>
+        <v>-23.5220801</v>
       </c>
       <c r="R436" t="n">
-        <v>-46.3782535</v>
+        <v>-46.379115</v>
       </c>
     </row>
     <row r="437">
@@ -52019,22 +52292,22 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>SL-018</t>
+          <t>SL-012</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>PV-69 - PV-70</t>
+          <t>PV-37 - PV-38</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>PV-69</t>
+          <t>PV-37</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>PV-70</t>
+          <t>PV-38</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -52051,16 +52324,16 @@
         </is>
       </c>
       <c r="I437" t="n">
-        <v>20.55</v>
+        <v>16.89</v>
       </c>
       <c r="J437" t="n">
-        <v>1.93</v>
+        <v>3.75</v>
       </c>
       <c r="K437" t="n">
-        <v>1.41</v>
+        <v>3.92</v>
       </c>
       <c r="L437" t="n">
-        <v>1.93</v>
+        <v>3.92</v>
       </c>
       <c r="M437" t="inlineStr">
         <is>
@@ -52069,20 +52342,20 @@
       </c>
       <c r="N437" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. Extensao lida no print.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. PV-38 incluido conforme novo print.</t>
         </is>
       </c>
       <c r="O437" t="n">
-        <v>-23.5224631</v>
+        <v>-23.5220801</v>
       </c>
       <c r="P437" t="n">
-        <v>-46.3782535</v>
+        <v>-46.379115</v>
       </c>
       <c r="Q437" t="n">
-        <v>-23.5224276</v>
+        <v>-23.5220422</v>
       </c>
       <c r="R437" t="n">
-        <v>-46.378053</v>
+        <v>-46.3789548</v>
       </c>
     </row>
     <row r="438">
@@ -52093,22 +52366,22 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>SL-019</t>
+          <t>SL-013</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>PV-64 - PV-65</t>
+          <t>PV-38 - PV-39</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>PV-64</t>
+          <t>PV-38</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>PV-65</t>
+          <t>PV-39</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -52121,42 +52394,42 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>VCA</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I438" t="n">
-        <v>39.5</v>
+        <v>46.47</v>
       </c>
       <c r="J438" t="n">
-        <v>2.84</v>
+        <v>3.92</v>
       </c>
       <c r="K438" t="n">
-        <v>1.6</v>
+        <v>3.64</v>
       </c>
       <c r="L438" t="n">
-        <v>2.84</v>
+        <v>3.92</v>
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>em andamento</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
         <is>
-          <t>Interligação corrigida PV-64 -&gt; PV-65 conforme projeto.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. PV-38 incluido conforme novo print.</t>
         </is>
       </c>
       <c r="O438" t="n">
-        <v>-23.522</v>
+        <v>-23.5220422</v>
       </c>
       <c r="P438" t="n">
-        <v>-46.378</v>
+        <v>-46.3789548</v>
       </c>
       <c r="Q438" t="n">
-        <v>-23.5224</v>
+        <v>-23.5222906</v>
       </c>
       <c r="R438" t="n">
-        <v>-46.378</v>
+        <v>-46.378588</v>
       </c>
     </row>
     <row r="439">
@@ -52167,22 +52440,22 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>SL-020</t>
+          <t>SL-014</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>PV-65 - PV-70</t>
+          <t>PV-40 - PV-41</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>PV-65</t>
+          <t>PV-40</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>PV-70</t>
+          <t>PV-41</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -52195,42 +52468,42 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>VCA</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I439" t="n">
-        <v>2.88</v>
+        <v>48.64</v>
       </c>
       <c r="J439" t="n">
-        <v>1.6</v>
+        <v>4.31</v>
       </c>
       <c r="K439" t="n">
-        <v>1.41</v>
+        <v>2.58</v>
       </c>
       <c r="L439" t="n">
-        <v>1.6</v>
+        <v>4.31</v>
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>em andamento</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t>Interligação corrigida PV-65 -&gt; PV-70 conforme projeto.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
         </is>
       </c>
       <c r="O439" t="n">
-        <v>-23.5224</v>
+        <v>-23.5224137</v>
       </c>
       <c r="P439" t="n">
-        <v>-46.378</v>
+        <v>-46.3783767</v>
       </c>
       <c r="Q439" t="n">
-        <v>-23.5224</v>
+        <v>-23.5227141</v>
       </c>
       <c r="R439" t="n">
-        <v>-46.378</v>
+        <v>-46.378029</v>
       </c>
     </row>
     <row r="440">
@@ -52241,22 +52514,22 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>SL-021</t>
+          <t>SL-015</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>PVE-32 - PV-02</t>
+          <t>PV-41 - PV-42</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>PVE-32</t>
+          <t>PV-41</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>PV-02</t>
+          <t>PV-42</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
@@ -52269,20 +52542,20 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I440" t="n">
-        <v>12.61</v>
+        <v>38.45</v>
       </c>
       <c r="J440" t="n">
-        <v>2.05</v>
+        <v>2.58</v>
       </c>
       <c r="K440" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="L440" t="n">
-        <v>2.05</v>
+        <v>2.58</v>
       </c>
       <c r="M440" t="inlineStr">
         <is>
@@ -52291,20 +52564,20 @@
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
         </is>
       </c>
       <c r="O440" t="n">
-        <v>-23.5199037</v>
+        <v>-23.5227141</v>
       </c>
       <c r="P440" t="n">
-        <v>-46.3771453</v>
+        <v>-46.378029</v>
       </c>
       <c r="Q440" t="n">
-        <v>-23.5200098</v>
+        <v>-23.52298</v>
       </c>
       <c r="R440" t="n">
-        <v>-46.3771007</v>
+        <v>-46.3777869</v>
       </c>
     </row>
     <row r="441">
@@ -52315,22 +52588,22 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>SL-022</t>
+          <t>SL-016</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>PV-02 - PV-03</t>
+          <t>PV-39 - PV-40</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>PV-02</t>
+          <t>PV-39</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>PV-03</t>
+          <t>PV-40</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -52347,16 +52620,16 @@
         </is>
       </c>
       <c r="I441" t="n">
-        <v>21</v>
+        <v>24.53</v>
       </c>
       <c r="J441" t="n">
-        <v>1.48</v>
+        <v>3.64</v>
       </c>
       <c r="K441" t="n">
-        <v>2.04</v>
+        <v>4.31</v>
       </c>
       <c r="L441" t="n">
-        <v>2.04</v>
+        <v>4.31</v>
       </c>
       <c r="M441" t="inlineStr">
         <is>
@@ -52365,20 +52638,20 @@
       </c>
       <c r="N441" t="inlineStr">
         <is>
-          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. Extensao lida no print.</t>
         </is>
       </c>
       <c r="O441" t="n">
-        <v>-23.5200098</v>
+        <v>-23.5222906</v>
       </c>
       <c r="P441" t="n">
-        <v>-46.3771007</v>
+        <v>-46.378588</v>
       </c>
       <c r="Q441" t="n">
-        <v>-23.5200681</v>
+        <v>-23.5224137</v>
       </c>
       <c r="R441" t="n">
-        <v>-46.376905</v>
+        <v>-46.3783767</v>
       </c>
     </row>
     <row r="442">
@@ -52389,22 +52662,22 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>SL-023</t>
+          <t>SL-017</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>PV-03 - PV-04</t>
+          <t>PV-40 - PV-69</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>PV-03</t>
+          <t>PV-40</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>PV-04</t>
+          <t>PV-69</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -52421,16 +52694,16 @@
         </is>
       </c>
       <c r="I442" t="n">
-        <v>46.15</v>
+        <v>13.08</v>
       </c>
       <c r="J442" t="n">
-        <v>2.04</v>
+        <v>4.31</v>
       </c>
       <c r="K442" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="L442" t="n">
-        <v>2.04</v>
+        <v>4.31</v>
       </c>
       <c r="M442" t="inlineStr">
         <is>
@@ -52439,20 +52712,20 @@
       </c>
       <c r="N442" t="inlineStr">
         <is>
-          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. Extensao lida no print.</t>
         </is>
       </c>
       <c r="O442" t="n">
-        <v>-23.5200681</v>
+        <v>-23.5224137</v>
       </c>
       <c r="P442" t="n">
-        <v>-46.376905</v>
+        <v>-46.3783767</v>
       </c>
       <c r="Q442" t="n">
-        <v>-23.5204836</v>
+        <v>-23.5224631</v>
       </c>
       <c r="R442" t="n">
-        <v>-46.3768696</v>
+        <v>-46.3782535</v>
       </c>
     </row>
     <row r="443">
@@ -52463,22 +52736,22 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>SL-024</t>
+          <t>SL-018</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>PV-04 - PV-05</t>
+          <t>PV-69 - PV-70</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>PV-04</t>
+          <t>PV-69</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>PV-05</t>
+          <t>PV-70</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -52495,16 +52768,16 @@
         </is>
       </c>
       <c r="I443" t="n">
-        <v>38.98</v>
+        <v>20.55</v>
       </c>
       <c r="J443" t="n">
-        <v>1.68</v>
+        <v>1.93</v>
       </c>
       <c r="K443" t="n">
-        <v>1.76</v>
+        <v>1.41</v>
       </c>
       <c r="L443" t="n">
-        <v>1.76</v>
+        <v>1.93</v>
       </c>
       <c r="M443" t="inlineStr">
         <is>
@@ -52513,20 +52786,20 @@
       </c>
       <c r="N443" t="inlineStr">
         <is>
-          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. Extensao lida no print.</t>
         </is>
       </c>
       <c r="O443" t="n">
-        <v>-23.5204836</v>
+        <v>-23.5224631</v>
       </c>
       <c r="P443" t="n">
-        <v>-46.3768696</v>
+        <v>-46.3782535</v>
       </c>
       <c r="Q443" t="n">
-        <v>-23.5208354</v>
+        <v>-23.5224276</v>
       </c>
       <c r="R443" t="n">
-        <v>-46.3768848</v>
+        <v>-46.378053</v>
       </c>
     </row>
     <row r="444">
@@ -52537,22 +52810,22 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>SL-025</t>
+          <t>SL-019</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>PV-05 - PV-06</t>
+          <t>PV-64 - PV-65</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>PV-05</t>
+          <t>PV-64</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>PV-06</t>
+          <t>PV-65</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -52565,42 +52838,42 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>VCA</t>
         </is>
       </c>
       <c r="I444" t="n">
-        <v>37.7</v>
+        <v>39.5</v>
       </c>
       <c r="J444" t="n">
-        <v>1.76</v>
+        <v>2.84</v>
       </c>
       <c r="K444" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="L444" t="n">
-        <v>1.85</v>
+        <v>2.84</v>
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>em andamento</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
         <is>
-          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
+          <t>Interligação corrigida PV-64 -&gt; PV-65 conforme projeto.</t>
         </is>
       </c>
       <c r="O444" t="n">
-        <v>-23.5208354</v>
+        <v>-23.522</v>
       </c>
       <c r="P444" t="n">
-        <v>-46.3768848</v>
+        <v>-46.378</v>
       </c>
       <c r="Q444" t="n">
-        <v>-23.5211749</v>
+        <v>-23.5224</v>
       </c>
       <c r="R444" t="n">
-        <v>-46.3768575</v>
+        <v>-46.378</v>
       </c>
     </row>
     <row r="445">
@@ -52611,22 +52884,22 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>SL-026</t>
+          <t>SL-020</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>PV-06 - PV-07</t>
+          <t>PV-65 - PV-70</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>PV-06</t>
+          <t>PV-65</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>PV-07</t>
+          <t>PV-70</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -52639,42 +52912,42 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>VCA</t>
         </is>
       </c>
       <c r="I445" t="n">
-        <v>34.53</v>
+        <v>2.88</v>
       </c>
       <c r="J445" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="K445" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="L445" t="n">
-        <v>1.85</v>
+        <v>1.6</v>
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>em andamento</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
         <is>
-          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
+          <t>Interligação corrigida PV-65 -&gt; PV-70 conforme projeto.</t>
         </is>
       </c>
       <c r="O445" t="n">
-        <v>-23.5211749</v>
+        <v>-23.5224</v>
       </c>
       <c r="P445" t="n">
-        <v>-46.3768575</v>
+        <v>-46.378</v>
       </c>
       <c r="Q445" t="n">
-        <v>-23.5214649</v>
+        <v>-23.5224</v>
       </c>
       <c r="R445" t="n">
-        <v>-46.3767334</v>
+        <v>-46.378</v>
       </c>
     </row>
     <row r="446">
@@ -52685,22 +52958,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>SL-027</t>
+          <t>SL-021</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>PV-07 - PV-08</t>
+          <t>PVE-32 - PV-02</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>PV-07</t>
+          <t>PVE-32</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>PV-08</t>
+          <t>PV-02</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -52717,16 +52990,16 @@
         </is>
       </c>
       <c r="I446" t="n">
-        <v>8.17</v>
+        <v>12.61</v>
       </c>
       <c r="J446" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="K446" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="L446" t="n">
-        <v>1.44</v>
+        <v>2.05</v>
       </c>
       <c r="M446" t="inlineStr">
         <is>
@@ -52739,16 +53012,16 @@
         </is>
       </c>
       <c r="O446" t="n">
-        <v>-23.5214649</v>
+        <v>-23.5199037</v>
       </c>
       <c r="P446" t="n">
-        <v>-46.3767334</v>
+        <v>-46.3771453</v>
       </c>
       <c r="Q446" t="n">
-        <v>-23.5215374</v>
+        <v>-23.5200098</v>
       </c>
       <c r="R446" t="n">
-        <v>-46.3767183</v>
+        <v>-46.3771007</v>
       </c>
     </row>
     <row r="447">
@@ -52759,22 +53032,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>SL-028</t>
+          <t>SL-022</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>PVE-31 - PV-37</t>
+          <t>PV-02 - PV-03</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>PVE-31</t>
+          <t>PV-02</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>PV-37</t>
+          <t>PV-03</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -52791,16 +53064,16 @@
         </is>
       </c>
       <c r="I447" t="n">
-        <v>10.11</v>
+        <v>21</v>
       </c>
       <c r="J447" t="n">
-        <v>2.4</v>
+        <v>1.48</v>
       </c>
       <c r="K447" t="n">
-        <v>3.75</v>
+        <v>2.04</v>
       </c>
       <c r="L447" t="n">
-        <v>3.75</v>
+        <v>2.04</v>
       </c>
       <c r="M447" t="inlineStr">
         <is>
@@ -52809,8 +53082,20 @@
       </c>
       <c r="N447" t="inlineStr">
         <is>
-          <t>Interligacao adicionada conforme projeto.</t>
-        </is>
+          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
+        </is>
+      </c>
+      <c r="O447" t="n">
+        <v>-23.5200098</v>
+      </c>
+      <c r="P447" t="n">
+        <v>-46.3771007</v>
+      </c>
+      <c r="Q447" t="n">
+        <v>-23.5200681</v>
+      </c>
+      <c r="R447" t="n">
+        <v>-46.376905</v>
       </c>
     </row>
     <row r="448">
@@ -52821,22 +53106,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>SL-029</t>
+          <t>SL-023</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>PV-75 - PV-76</t>
+          <t>PV-03 - PV-04</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>PV-75</t>
+          <t>PV-03</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>PV-76</t>
+          <t>PV-04</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -52853,16 +53138,16 @@
         </is>
       </c>
       <c r="I448" t="n">
-        <v>2.09</v>
+        <v>46.15</v>
       </c>
       <c r="J448" t="n">
-        <v>1.35</v>
+        <v>2.04</v>
       </c>
       <c r="K448" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="L448" t="n">
-        <v>1.35</v>
+        <v>2.04</v>
       </c>
       <c r="M448" t="inlineStr">
         <is>
@@ -52871,8 +53156,20 @@
       </c>
       <c r="N448" t="inlineStr">
         <is>
-          <t>Interligação adicionada conforme projeto.</t>
-        </is>
+          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
+        </is>
+      </c>
+      <c r="O448" t="n">
+        <v>-23.5200681</v>
+      </c>
+      <c r="P448" t="n">
+        <v>-46.376905</v>
+      </c>
+      <c r="Q448" t="n">
+        <v>-23.5204836</v>
+      </c>
+      <c r="R448" t="n">
+        <v>-46.3768696</v>
       </c>
     </row>
     <row r="449">
@@ -52883,22 +53180,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>SL-030</t>
+          <t>SL-024</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>PV-76 - PV-77</t>
+          <t>PV-04 - PV-05</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>PV-76</t>
+          <t>PV-04</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>PV-77</t>
+          <t>PV-05</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -52915,16 +53212,16 @@
         </is>
       </c>
       <c r="I449" t="n">
-        <v>18.02</v>
+        <v>38.98</v>
       </c>
       <c r="J449" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="K449" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="L449" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="M449" t="inlineStr">
         <is>
@@ -52933,8 +53230,20 @@
       </c>
       <c r="N449" t="inlineStr">
         <is>
-          <t>Interligação adicionada conforme projeto.</t>
-        </is>
+          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
+        </is>
+      </c>
+      <c r="O449" t="n">
+        <v>-23.5204836</v>
+      </c>
+      <c r="P449" t="n">
+        <v>-46.3768696</v>
+      </c>
+      <c r="Q449" t="n">
+        <v>-23.5208354</v>
+      </c>
+      <c r="R449" t="n">
+        <v>-46.3768848</v>
       </c>
     </row>
     <row r="450">
@@ -52945,22 +53254,22 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>SL-031</t>
+          <t>SL-025</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>PV-77 - PV-78</t>
+          <t>PV-05 - PV-06</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>PV-77</t>
+          <t>PV-05</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>PV-78</t>
+          <t>PV-06</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -52977,16 +53286,16 @@
         </is>
       </c>
       <c r="I450" t="n">
-        <v>21.33</v>
+        <v>37.7</v>
       </c>
       <c r="J450" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="K450" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="L450" t="n">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="M450" t="inlineStr">
         <is>
@@ -52995,8 +53304,20 @@
       </c>
       <c r="N450" t="inlineStr">
         <is>
-          <t>Interligação adicionada conforme projeto.</t>
-        </is>
+          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
+        </is>
+      </c>
+      <c r="O450" t="n">
+        <v>-23.5208354</v>
+      </c>
+      <c r="P450" t="n">
+        <v>-46.3768848</v>
+      </c>
+      <c r="Q450" t="n">
+        <v>-23.5211749</v>
+      </c>
+      <c r="R450" t="n">
+        <v>-46.3768575</v>
       </c>
     </row>
     <row r="451">
@@ -53007,22 +53328,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>SL-032</t>
+          <t>SL-026</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>PV-75.1 - PV-75</t>
+          <t>PV-06 - PV-07</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>PV-75.1</t>
+          <t>PV-06</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>PV-75</t>
+          <t>PV-07</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
@@ -53039,13 +53360,16 @@
         </is>
       </c>
       <c r="I451" t="n">
-        <v>5</v>
+        <v>34.53</v>
+      </c>
+      <c r="J451" t="n">
+        <v>1.85</v>
       </c>
       <c r="K451" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="L451" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="M451" t="inlineStr">
         <is>
@@ -53054,72 +53378,72 @@
       </c>
       <c r="N451" t="inlineStr">
         <is>
-          <t>Interligacao PV-75.1 -&gt; PV-75 adicionada via Google Earth.</t>
+          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
         </is>
       </c>
       <c r="O451" t="n">
-        <v>-23.5198222</v>
+        <v>-23.5211749</v>
       </c>
       <c r="P451" t="n">
-        <v>-46.3768722</v>
+        <v>-46.3768575</v>
       </c>
       <c r="Q451" t="n">
-        <v>-23.5198</v>
+        <v>-23.5214649</v>
       </c>
       <c r="R451" t="n">
-        <v>-46.3763</v>
+        <v>-46.3767334</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_comunidade_sao_lucas</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>JC-014</t>
+          <t>SL-027</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>PV-16 - PV-17</t>
+          <t>PV-07 - PV-08</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>PV-16</t>
+          <t>PV-07</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>PV-17</t>
+          <t>PV-08</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>PEAD LISO</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="G452" t="n">
-        <v>355</v>
+        <v>200</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Metodo Nao Destrutivo - MND</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I452" t="n">
-        <v>64.572</v>
+        <v>8.17</v>
       </c>
       <c r="J452" t="n">
-        <v>3.1</v>
+        <v>1.44</v>
       </c>
       <c r="K452" t="n">
-        <v>3.1</v>
+        <v>1.41</v>
       </c>
       <c r="L452" t="n">
-        <v>5.48</v>
+        <v>1.44</v>
       </c>
       <c r="M452" t="inlineStr">
         <is>
@@ -53128,72 +53452,72 @@
       </c>
       <c r="N452" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-16 ao PV-17; arquivo: planos_furo/cts_joao_canzi_fl07_pv16_pv17.pdf; taxa 0,0707.</t>
+          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
         </is>
       </c>
       <c r="O452" t="n">
-        <v>-23.5299843</v>
+        <v>-23.5214649</v>
       </c>
       <c r="P452" t="n">
-        <v>-46.3845231</v>
+        <v>-46.3767334</v>
       </c>
       <c r="Q452" t="n">
-        <v>-23.5300354</v>
+        <v>-23.5215374</v>
       </c>
       <c r="R452" t="n">
-        <v>-46.3838931</v>
+        <v>-46.3767183</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_comunidade_sao_lucas</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>JC-015</t>
+          <t>SL-028</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>PV-17 - PV-18</t>
+          <t>PVE-31 - PV-37</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>PV-17</t>
+          <t>PVE-31</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>PV-18</t>
+          <t>PV-37</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>PEAD LISO</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="G453" t="n">
-        <v>355</v>
+        <v>200</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Metodo Nao Destrutivo - MND</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I453" t="n">
-        <v>79.57599999999999</v>
+        <v>10.11</v>
       </c>
       <c r="J453" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="K453" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="L453" t="n">
-        <v>3.56</v>
+        <v>3.75</v>
       </c>
       <c r="M453" t="inlineStr">
         <is>
@@ -53202,104 +53526,490 @@
       </c>
       <c r="N453" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-17 ao PV-18; arquivo: planos_furo/cts_joao_canzi_fl07_pv17_pv18.pdf; taxa 0,0116.</t>
-        </is>
-      </c>
-      <c r="O453" t="n">
-        <v>-23.5300354</v>
-      </c>
-      <c r="P453" t="n">
-        <v>-46.3838931</v>
-      </c>
-      <c r="Q453" t="n">
-        <v>-23.5300223</v>
-      </c>
-      <c r="R453" t="n">
-        <v>-46.3831139</v>
+          <t>Interligacao adicionada conforme projeto.</t>
+        </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
+          <t>rce_comunidade_sao_lucas</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>SL-029</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>PV-75 - PV-76</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>PV-75</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>PV-76</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G454" t="n">
+        <v>200</v>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I454" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="J454" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K454" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="L454" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M454" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N454" t="inlineStr">
+        <is>
+          <t>Interligação adicionada conforme projeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>rce_comunidade_sao_lucas</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>SL-030</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>PV-76 - PV-77</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>PV-76</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>PV-77</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G455" t="n">
+        <v>200</v>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I455" t="n">
+        <v>18.02</v>
+      </c>
+      <c r="J455" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="K455" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L455" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>Interligação adicionada conforme projeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>rce_comunidade_sao_lucas</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>SL-031</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>PV-77 - PV-78</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>PV-77</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>PV-78</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G456" t="n">
+        <v>200</v>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I456" t="n">
+        <v>21.33</v>
+      </c>
+      <c r="J456" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="K456" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L456" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>Interligação adicionada conforme projeto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>rce_comunidade_sao_lucas</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>SL-032</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>PV-75.1 - PV-75</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>PV-75.1</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>PV-75</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G457" t="n">
+        <v>200</v>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I457" t="n">
+        <v>5</v>
+      </c>
+      <c r="K457" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="L457" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>Interligacao PV-75.1 -&gt; PV-75 adicionada via Google Earth.</t>
+        </is>
+      </c>
+      <c r="O457" t="n">
+        <v>-23.5198222</v>
+      </c>
+      <c r="P457" t="n">
+        <v>-46.3768722</v>
+      </c>
+      <c r="Q457" t="n">
+        <v>-23.5198</v>
+      </c>
+      <c r="R457" t="n">
+        <v>-46.3763</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
           <t>cts_joao_canzi</t>
         </is>
       </c>
-      <c r="B454" t="inlineStr">
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>JC-014</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>PV-16 - PV-17</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>PV-16</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>PV-17</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G458" t="n">
+        <v>355</v>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I458" t="n">
+        <v>64.572</v>
+      </c>
+      <c r="J458" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K458" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L458" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-16 ao PV-17; arquivo: planos_furo/cts_joao_canzi_fl07_pv16_pv17.pdf; taxa 0,0707.</t>
+        </is>
+      </c>
+      <c r="O458" t="n">
+        <v>-23.5299843</v>
+      </c>
+      <c r="P458" t="n">
+        <v>-46.3845231</v>
+      </c>
+      <c r="Q458" t="n">
+        <v>-23.5300354</v>
+      </c>
+      <c r="R458" t="n">
+        <v>-46.3838931</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>JC-015</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>PV-17 - PV-18</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>PV-17</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>PV-18</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>PEAD LISO</t>
+        </is>
+      </c>
+      <c r="G459" t="n">
+        <v>355</v>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>Metodo Nao Destrutivo - MND</t>
+        </is>
+      </c>
+      <c r="I459" t="n">
+        <v>79.57599999999999</v>
+      </c>
+      <c r="J459" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K459" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L459" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-17 ao PV-18; arquivo: planos_furo/cts_joao_canzi_fl07_pv17_pv18.pdf; taxa 0,0116.</t>
+        </is>
+      </c>
+      <c r="O459" t="n">
+        <v>-23.5300354</v>
+      </c>
+      <c r="P459" t="n">
+        <v>-46.3838931</v>
+      </c>
+      <c r="Q459" t="n">
+        <v>-23.5300223</v>
+      </c>
+      <c r="R459" t="n">
+        <v>-46.3831139</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>cts_joao_canzi</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
         <is>
           <t>JC-016</t>
         </is>
       </c>
-      <c r="C454" t="inlineStr">
+      <c r="C460" t="inlineStr">
         <is>
           <t>PV-19 - PV-20</t>
         </is>
       </c>
-      <c r="D454" t="inlineStr">
+      <c r="D460" t="inlineStr">
         <is>
           <t>PV-19</t>
         </is>
       </c>
-      <c r="E454" t="inlineStr">
+      <c r="E460" t="inlineStr">
         <is>
           <t>PV-20</t>
         </is>
       </c>
-      <c r="F454" t="inlineStr">
+      <c r="F460" t="inlineStr">
         <is>
           <t>PEAD LISO</t>
         </is>
       </c>
-      <c r="G454" t="n">
+      <c r="G460" t="n">
         <v>355</v>
       </c>
-      <c r="H454" t="inlineStr">
+      <c r="H460" t="inlineStr">
         <is>
           <t>Metodo Nao Destrutivo - MND</t>
         </is>
       </c>
-      <c r="I454" t="n">
+      <c r="I460" t="n">
         <v>57.846</v>
       </c>
-      <c r="J454" t="n">
+      <c r="J460" t="n">
         <v>4</v>
       </c>
-      <c r="K454" t="n">
+      <c r="K460" t="n">
         <v>3.96</v>
       </c>
-      <c r="L454" t="n">
+      <c r="L460" t="n">
         <v>4</v>
       </c>
-      <c r="M454" t="inlineStr">
+      <c r="M460" t="inlineStr">
         <is>
           <t>em andamento</t>
         </is>
       </c>
-      <c r="N454" t="inlineStr">
+      <c r="N460" t="inlineStr">
         <is>
           <t>Plano de furo FL-07 versao 01, 05.JUN.2026; PV-19 ao PV-20; arquivo: planos_furo/cts_joao_canzi_fl07_pv19_pv20.pdf; taxa 0,1224.</t>
         </is>
       </c>
-      <c r="O454" t="n">
+      <c r="O460" t="n">
         <v>-23.529877</v>
       </c>
-      <c r="P454" t="n">
+      <c r="P460" t="n">
         <v>-46.3824799</v>
       </c>
-      <c r="Q454" t="n">
+      <c r="Q460" t="n">
         <v>-23.5295804</v>
       </c>
-      <c r="R454" t="n">
+      <c r="R460" t="n">
         <v>-46.3820136</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R445">
-    <filterColumn colId="0" hiddenButton="0" showButton="1">
-      <filters>
-        <filter val="rce_comunidade_sao_lucas"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -53311,7 +54021,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -53430,7 +54140,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -54167,7 +54877,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="5"/>
   </cols>
@@ -54275,7 +54985,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -54531,7 +55241,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -2,6 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEIA-ME" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OBRAS" sheetId="2" state="visible" r:id="rId2"/>
@@ -14,7 +17,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACAO_SHAPE_LUIS_0505" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VALIDACAO_SUBST_AGUA_BOA_0505" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'TRECHOS'!$A$1:$R$445</definedName>
+  </definedNames>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -53,7 +59,13 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -66,8 +78,9 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -308,6 +321,8 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -318,7 +333,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:A9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -388,7 +403,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -463,7 +478,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="31.109375" customWidth="1" min="1" max="1"/>
     <col width="35.44140625" customWidth="1" min="2" max="2"/>
@@ -1182,8 +1197,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L447"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
+  <dimension ref="A1:L441"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
     <col width="12.5546875" customWidth="1" min="3" max="3"/>
@@ -19134,110 +19149,110 @@
       </c>
       <c r="L397" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+          <t>Adicionado via print do projeto RCE Elias Sleiman; lancamento completo em VCA.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>rce_elias_sleiman</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>ELIAS-PV-24</t>
+          <t>ELVIRA-PI-1.1</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>PV-24</t>
+          <t>PI-1.1</t>
         </is>
       </c>
       <c r="E398" t="n">
-        <v>7397047.32</v>
+        <v>7396905.886</v>
       </c>
       <c r="F398" t="n">
-        <v>358826.273</v>
+        <v>358329.956</v>
       </c>
       <c r="G398" t="n">
-        <v>-23.5307209</v>
+        <v>-23.5319548</v>
       </c>
       <c r="H398" t="n">
-        <v>-46.3829268</v>
+        <v>-46.387801</v>
       </c>
       <c r="I398" t="n">
-        <v>795.659</v>
+        <v>767.159</v>
       </c>
       <c r="J398" t="n">
-        <v>793.298</v>
+        <v>765.927</v>
       </c>
       <c r="K398" t="n">
-        <v>2.36</v>
+        <v>1.23</v>
       </c>
       <c r="L398" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+          <t>Adicionado conforme solicitação: PI da RCE Elvira de Araujo; interligacao com CTS Joao Canzi mantida sem alterar registros existentes.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>rce_elias_sleiman</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>ELIAS-PV-25</t>
+          <t>ELVIRA-PI-1.2</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>PV-25</t>
+          <t>PI-1.2</t>
         </is>
       </c>
       <c r="E399" t="n">
-        <v>7397044.193</v>
+        <v>7396922.192</v>
       </c>
       <c r="F399" t="n">
-        <v>358909.128</v>
+        <v>358327.004</v>
       </c>
       <c r="G399" t="n">
-        <v>-23.5307563</v>
+        <v>-23.5318073</v>
       </c>
       <c r="H399" t="n">
-        <v>-46.3821157</v>
+        <v>-46.3878284</v>
       </c>
       <c r="I399" t="n">
-        <v>798.554</v>
+        <v>767.21</v>
       </c>
       <c r="J399" t="n">
-        <v>795.832</v>
+        <v>766.01</v>
       </c>
       <c r="K399" t="n">
-        <v>2.72</v>
+        <v>1.2</v>
       </c>
       <c r="L399" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+          <t>Adicionado conforme solicitação: PI da RCE Elvira de Araujo; interligacao com CTS Joao Canzi mantida sem alterar registros existentes.</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>rce_elias_sleiman</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -19247,45 +19262,45 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>ELIAS-PV-26</t>
+          <t>JC-PV-18</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>PV-26</t>
+          <t>PV-18</t>
         </is>
       </c>
       <c r="E400" t="n">
-        <v>7397000.312</v>
+        <v>7397124.485</v>
       </c>
       <c r="F400" t="n">
-        <v>358903.103</v>
+        <v>358806.429</v>
       </c>
       <c r="G400" t="n">
-        <v>-23.5311521</v>
+        <v>-23.5300224</v>
       </c>
       <c r="H400" t="n">
-        <v>-46.3821788</v>
+        <v>-46.3831139</v>
       </c>
       <c r="I400" t="n">
-        <v>803.849</v>
+        <v>783.619</v>
       </c>
       <c r="J400" t="n">
-        <v>801.227</v>
+        <v>780.119</v>
       </c>
       <c r="K400" t="n">
-        <v>2.62</v>
+        <v>3.5</v>
       </c>
       <c r="L400" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-18 ao PV-19.</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>rce_elias_sleiman</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -19295,45 +19310,45 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>ELIAS-PV-27</t>
+          <t>JC-PV-19</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>PV-27</t>
+          <t>PV-19</t>
         </is>
       </c>
       <c r="E401" t="n">
-        <v>7396952.046</v>
+        <v>7397141.155</v>
       </c>
       <c r="F401" t="n">
-        <v>358919.472</v>
+        <v>358871.038</v>
       </c>
       <c r="G401" t="n">
-        <v>-23.5315893</v>
+        <v>-23.5298774</v>
       </c>
       <c r="H401" t="n">
-        <v>-46.3820231</v>
+        <v>-46.3824796</v>
       </c>
       <c r="I401" t="n">
-        <v>810.896</v>
+        <v>787.357</v>
       </c>
       <c r="J401" t="n">
-        <v>808.804</v>
+        <v>783.357</v>
       </c>
       <c r="K401" t="n">
-        <v>2.09</v>
+        <v>4</v>
       </c>
       <c r="L401" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-18 ao PV-19.</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>rce_elias_sleiman</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -19343,45 +19358,45 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>ELIAS-PV-28</t>
+          <t>ELVIRA-PV-08</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>PV-28</t>
+          <t>PV-08</t>
         </is>
       </c>
       <c r="E402" t="n">
-        <v>7396913.479</v>
+        <v>7396899.021</v>
       </c>
       <c r="F402" t="n">
-        <v>358940.543</v>
+        <v>358332.965</v>
       </c>
       <c r="G402" t="n">
-        <v>-23.5319394</v>
+        <v>-23.532017</v>
       </c>
       <c r="H402" t="n">
-        <v>-46.3818203</v>
+        <v>-46.3877722</v>
       </c>
       <c r="I402" t="n">
-        <v>813.813</v>
+        <v>767.145</v>
       </c>
       <c r="J402" t="n">
-        <v>811.614</v>
+        <v>762.845</v>
       </c>
       <c r="K402" t="n">
-        <v>2.2</v>
+        <v>4.3</v>
       </c>
       <c r="L402" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>rce_elias_sleiman</t>
+          <t>rce_elvira_de_araujo</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -19391,38 +19406,38 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>ELIAS-PV-29</t>
+          <t>ELVIRA-PV-02</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>PV-29</t>
+          <t>PV-02</t>
         </is>
       </c>
       <c r="E403" t="n">
-        <v>7396888.957</v>
+        <v>7396941.756</v>
       </c>
       <c r="F403" t="n">
-        <v>358954.374</v>
+        <v>358324.032</v>
       </c>
       <c r="G403" t="n">
-        <v>-23.5321621</v>
+        <v>-23.5316304</v>
       </c>
       <c r="H403" t="n">
-        <v>-46.3816872</v>
+        <v>-46.3878556</v>
       </c>
       <c r="I403" t="n">
-        <v>815.335</v>
+        <v>767.318</v>
       </c>
       <c r="J403" t="n">
-        <v>813.135</v>
+        <v>763.468</v>
       </c>
       <c r="K403" t="n">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
         </is>
       </c>
     </row>
@@ -19434,98 +19449,98 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>ELVIRA-PI-1.1</t>
+          <t>ELVIRA-PV-01</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>PI-1.1</t>
+          <t>PV-01</t>
         </is>
       </c>
       <c r="E404" t="n">
-        <v>7396905.886</v>
+        <v>7396903.634</v>
       </c>
       <c r="F404" t="n">
-        <v>358329.956</v>
+        <v>358332.744</v>
       </c>
       <c r="G404" t="n">
-        <v>-23.5319548</v>
+        <v>-23.5319754</v>
       </c>
       <c r="H404" t="n">
-        <v>-46.387801</v>
+        <v>-46.3877739</v>
       </c>
       <c r="I404" t="n">
-        <v>767.159</v>
+        <v>767.2910000000001</v>
       </c>
       <c r="J404" t="n">
-        <v>765.927</v>
+        <v>763.0069999999999</v>
       </c>
       <c r="K404" t="n">
-        <v>1.23</v>
+        <v>4.28</v>
       </c>
       <c r="L404" t="inlineStr">
         <is>
-          <t>Adicionado conforme solicitação: PI da RCE Elvira de Araujo; interligacao com CTS Joao Canzi mantida sem alterar registros existentes.</t>
+          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>rce_elvira_de_araujo</t>
+          <t>rce_comunidade_sao_lucas</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>ELVIRA-PI-1.2</t>
+          <t>SL-PV-26</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>PI-1.2</t>
+          <t>PV-26</t>
         </is>
       </c>
       <c r="E405" t="n">
-        <v>7396922.192</v>
+        <v>7397836.606</v>
       </c>
       <c r="F405" t="n">
-        <v>358327.004</v>
+        <v>359444.31</v>
       </c>
       <c r="G405" t="n">
-        <v>-23.5318073</v>
+        <v>-23.5236471</v>
       </c>
       <c r="H405" t="n">
-        <v>-46.3878284</v>
+        <v>-46.3767998</v>
       </c>
       <c r="I405" t="n">
-        <v>767.21</v>
+        <v>765.833</v>
       </c>
       <c r="J405" t="n">
-        <v>766.01</v>
+        <v>762.795</v>
       </c>
       <c r="K405" t="n">
-        <v>1.2</v>
+        <v>3.04</v>
       </c>
       <c r="L405" t="inlineStr">
         <is>
-          <t>Adicionado conforme solicitação: PI da RCE Elvira de Araujo; interligacao com CTS Joao Canzi mantida sem alterar registros existentes.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_comunidade_sao_lucas</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -19535,45 +19550,45 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>JC-PV-18</t>
+          <t>SL-PV-27</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>PV-18</t>
+          <t>PV-27</t>
         </is>
       </c>
       <c r="E406" t="n">
-        <v>7397124.485</v>
+        <v>7397821.933</v>
       </c>
       <c r="F406" t="n">
-        <v>358806.429</v>
+        <v>359445.676</v>
       </c>
       <c r="G406" t="n">
-        <v>-23.5300224</v>
+        <v>-23.5237798</v>
       </c>
       <c r="H406" t="n">
-        <v>-46.3831139</v>
+        <v>-46.3767878</v>
       </c>
       <c r="I406" t="n">
-        <v>783.619</v>
+        <v>766.55</v>
       </c>
       <c r="J406" t="n">
-        <v>780.119</v>
+        <v>762.985</v>
       </c>
       <c r="K406" t="n">
-        <v>3.5</v>
+        <v>3.57</v>
       </c>
       <c r="L406" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-18 ao PV-19.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_comunidade_sao_lucas</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -19583,45 +19598,45 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>JC-PV-19</t>
+          <t>SL-PV-28</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>PV-19</t>
+          <t>PV-28</t>
         </is>
       </c>
       <c r="E407" t="n">
-        <v>7397141.155</v>
+        <v>7397818.346</v>
       </c>
       <c r="F407" t="n">
-        <v>358871.038</v>
+        <v>359445.113</v>
       </c>
       <c r="G407" t="n">
-        <v>-23.5298774</v>
+        <v>-23.5238121</v>
       </c>
       <c r="H407" t="n">
-        <v>-46.3824796</v>
+        <v>-46.3767936</v>
       </c>
       <c r="I407" t="n">
-        <v>787.357</v>
+        <v>766.3390000000001</v>
       </c>
       <c r="J407" t="n">
-        <v>783.357</v>
+        <v>763.003</v>
       </c>
       <c r="K407" t="n">
-        <v>4</v>
+        <v>3.34</v>
       </c>
       <c r="L407" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-18 ao PV-19.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>rce_elvira_de_araujo</t>
+          <t>rce_comunidade_sao_lucas</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -19631,45 +19646,45 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>ELVIRA-PV-08</t>
+          <t>SL-PV-29</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>PV-08</t>
+          <t>PV-29</t>
         </is>
       </c>
       <c r="E408" t="n">
-        <v>7396899.021</v>
+        <v>7397815.955</v>
       </c>
       <c r="F408" t="n">
-        <v>358332.965</v>
+        <v>359437.991</v>
       </c>
       <c r="G408" t="n">
-        <v>-23.532017</v>
+        <v>-23.5238331</v>
       </c>
       <c r="H408" t="n">
-        <v>-46.3877722</v>
+        <v>-46.3768636</v>
       </c>
       <c r="I408" t="n">
-        <v>767.145</v>
+        <v>767.119</v>
       </c>
       <c r="J408" t="n">
-        <v>762.845</v>
+        <v>765.308</v>
       </c>
       <c r="K408" t="n">
-        <v>4.3</v>
+        <v>1.81</v>
       </c>
       <c r="L408" t="inlineStr">
         <is>
-          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>rce_elvira_de_araujo</t>
+          <t>rce_comunidade_sao_lucas</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -19679,45 +19694,45 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>ELVIRA-PV-02</t>
+          <t>SL-PV-30</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>PV-02</t>
+          <t>PV-30</t>
         </is>
       </c>
       <c r="E409" t="n">
-        <v>7396941.756</v>
+        <v>7397821.17</v>
       </c>
       <c r="F409" t="n">
-        <v>358324.032</v>
+        <v>359425.424</v>
       </c>
       <c r="G409" t="n">
-        <v>-23.5316304</v>
+        <v>-23.5237849</v>
       </c>
       <c r="H409" t="n">
-        <v>-46.3878556</v>
+        <v>-46.3769862</v>
       </c>
       <c r="I409" t="n">
-        <v>767.318</v>
+        <v>768.3</v>
       </c>
       <c r="J409" t="n">
-        <v>763.468</v>
+        <v>766.9</v>
       </c>
       <c r="K409" t="n">
-        <v>3.85</v>
+        <v>1.4</v>
       </c>
       <c r="L409" t="inlineStr">
         <is>
-          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>rce_elvira_de_araujo</t>
+          <t>rce_comunidade_sao_lucas</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -19727,38 +19742,38 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>ELVIRA-PV-01</t>
+          <t>SL-PV-31</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>PV-01</t>
+          <t>PV-31</t>
         </is>
       </c>
       <c r="E410" t="n">
-        <v>7396903.634</v>
+        <v>7397822.876</v>
       </c>
       <c r="F410" t="n">
-        <v>358332.744</v>
+        <v>359419.03</v>
       </c>
       <c r="G410" t="n">
-        <v>-23.5319754</v>
+        <v>-23.5237689</v>
       </c>
       <c r="H410" t="n">
-        <v>-46.3877739</v>
+        <v>-46.3770487</v>
       </c>
       <c r="I410" t="n">
-        <v>767.2910000000001</v>
+        <v>768.978</v>
       </c>
       <c r="J410" t="n">
-        <v>763.0069999999999</v>
+        <v>767.552</v>
       </c>
       <c r="K410" t="n">
-        <v>4.28</v>
+        <v>1.43</v>
       </c>
       <c r="L410" t="inlineStr">
         <is>
-          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
         </is>
       </c>
     </row>
@@ -19775,34 +19790,34 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>SL-PV-26</t>
+          <t>SL-PV-32</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>PV-26</t>
+          <t>PV-32</t>
         </is>
       </c>
       <c r="E411" t="n">
-        <v>7397836.606</v>
+        <v>7397868.541</v>
       </c>
       <c r="F411" t="n">
-        <v>359444.31</v>
+        <v>359364.806</v>
       </c>
       <c r="G411" t="n">
-        <v>-23.5236471</v>
+        <v>-23.5233519</v>
       </c>
       <c r="H411" t="n">
-        <v>-46.3767998</v>
+        <v>-46.3775754</v>
       </c>
       <c r="I411" t="n">
-        <v>765.833</v>
+        <v>778.292</v>
       </c>
       <c r="J411" t="n">
-        <v>762.795</v>
+        <v>776.111</v>
       </c>
       <c r="K411" t="n">
-        <v>3.04</v>
+        <v>2.18</v>
       </c>
       <c r="L411" t="inlineStr">
         <is>
@@ -19823,34 +19838,34 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>SL-PV-27</t>
+          <t>SL-PV-33</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>PV-27</t>
+          <t>PV-33</t>
         </is>
       </c>
       <c r="E412" t="n">
-        <v>7397821.933</v>
+        <v>7397900.057</v>
       </c>
       <c r="F412" t="n">
-        <v>359445.676</v>
+        <v>359310.764</v>
       </c>
       <c r="G412" t="n">
-        <v>-23.5237798</v>
+        <v>-23.5230626</v>
       </c>
       <c r="H412" t="n">
-        <v>-46.3767878</v>
+        <v>-46.3781017</v>
       </c>
       <c r="I412" t="n">
-        <v>766.55</v>
+        <v>784.273</v>
       </c>
       <c r="J412" t="n">
-        <v>762.985</v>
+        <v>782.111</v>
       </c>
       <c r="K412" t="n">
-        <v>3.57</v>
+        <v>2.16</v>
       </c>
       <c r="L412" t="inlineStr">
         <is>
@@ -19871,34 +19886,34 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>SL-PV-28</t>
+          <t>SL-PV-34</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>PV-28</t>
+          <t>PV-34</t>
         </is>
       </c>
       <c r="E413" t="n">
-        <v>7397818.346</v>
+        <v>7397941.252</v>
       </c>
       <c r="F413" t="n">
-        <v>359445.113</v>
+        <v>359273.636</v>
       </c>
       <c r="G413" t="n">
-        <v>-23.5238121</v>
+        <v>-23.5226874</v>
       </c>
       <c r="H413" t="n">
-        <v>-46.3767936</v>
+        <v>-46.3784614</v>
       </c>
       <c r="I413" t="n">
-        <v>766.3390000000001</v>
+        <v>787.202</v>
       </c>
       <c r="J413" t="n">
-        <v>763.003</v>
+        <v>784.7569999999999</v>
       </c>
       <c r="K413" t="n">
-        <v>3.34</v>
+        <v>2.45</v>
       </c>
       <c r="L413" t="inlineStr">
         <is>
@@ -19919,34 +19934,34 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>SL-PV-29</t>
+          <t>SL-PV-35</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>PV-29</t>
+          <t>PV-35</t>
         </is>
       </c>
       <c r="E414" t="n">
-        <v>7397815.955</v>
+        <v>7397977.503</v>
       </c>
       <c r="F414" t="n">
-        <v>359437.991</v>
+        <v>359228.842</v>
       </c>
       <c r="G414" t="n">
-        <v>-23.5238331</v>
+        <v>-23.5223561</v>
       </c>
       <c r="H414" t="n">
-        <v>-46.3768636</v>
+        <v>-46.3788967</v>
       </c>
       <c r="I414" t="n">
-        <v>767.119</v>
+        <v>788.938</v>
       </c>
       <c r="J414" t="n">
-        <v>765.308</v>
+        <v>785.057</v>
       </c>
       <c r="K414" t="n">
-        <v>1.81</v>
+        <v>3.88</v>
       </c>
       <c r="L414" t="inlineStr">
         <is>
@@ -19967,34 +19982,34 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>SL-PV-30</t>
+          <t>SL-PV-36</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>PV-30</t>
+          <t>PV-36</t>
         </is>
       </c>
       <c r="E415" t="n">
-        <v>7397821.17</v>
+        <v>7397999.594</v>
       </c>
       <c r="F415" t="n">
-        <v>359425.424</v>
+        <v>359212.718</v>
       </c>
       <c r="G415" t="n">
-        <v>-23.5237849</v>
+        <v>-23.5221552</v>
       </c>
       <c r="H415" t="n">
-        <v>-46.3769862</v>
+        <v>-46.3790525</v>
       </c>
       <c r="I415" t="n">
-        <v>768.3</v>
+        <v>789.169</v>
       </c>
       <c r="J415" t="n">
-        <v>766.9</v>
+        <v>785.2</v>
       </c>
       <c r="K415" t="n">
-        <v>1.4</v>
+        <v>3.97</v>
       </c>
       <c r="L415" t="inlineStr">
         <is>
@@ -20015,34 +20030,34 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>SL-PV-31</t>
+          <t>SL-PV-37</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>PV-31</t>
+          <t>PV-37</t>
         </is>
       </c>
       <c r="E416" t="n">
-        <v>7397822.876</v>
+        <v>7398007.858</v>
       </c>
       <c r="F416" t="n">
-        <v>359419.03</v>
+        <v>359206.253</v>
       </c>
       <c r="G416" t="n">
-        <v>-23.5237689</v>
+        <v>-23.5220801</v>
       </c>
       <c r="H416" t="n">
-        <v>-46.3770487</v>
+        <v>-46.379115</v>
       </c>
       <c r="I416" t="n">
-        <v>768.978</v>
+        <v>788.999</v>
       </c>
       <c r="J416" t="n">
-        <v>767.552</v>
+        <v>785.249</v>
       </c>
       <c r="K416" t="n">
-        <v>1.43</v>
+        <v>3.75</v>
       </c>
       <c r="L416" t="inlineStr">
         <is>
@@ -20063,34 +20078,34 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>SL-PV-32</t>
+          <t>SL-PV-39</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>PV-32</t>
+          <t>PV-39</t>
         </is>
       </c>
       <c r="E417" t="n">
-        <v>7397868.541</v>
+        <v>7397985.065</v>
       </c>
       <c r="F417" t="n">
-        <v>359364.806</v>
+        <v>359260.286</v>
       </c>
       <c r="G417" t="n">
-        <v>-23.5233519</v>
+        <v>-23.5222906</v>
       </c>
       <c r="H417" t="n">
-        <v>-46.3775754</v>
+        <v>-46.378588</v>
       </c>
       <c r="I417" t="n">
-        <v>778.292</v>
+        <v>790.049</v>
       </c>
       <c r="J417" t="n">
-        <v>776.111</v>
+        <v>786.409</v>
       </c>
       <c r="K417" t="n">
-        <v>2.18</v>
+        <v>3.64</v>
       </c>
       <c r="L417" t="inlineStr">
         <is>
@@ -20111,34 +20126,34 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>SL-PV-33</t>
+          <t>SL-PV-40</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>PV-33</t>
+          <t>PV-40</t>
         </is>
       </c>
       <c r="E418" t="n">
-        <v>7397900.057</v>
+        <v>7397971.64</v>
       </c>
       <c r="F418" t="n">
-        <v>359310.764</v>
+        <v>359281.997</v>
       </c>
       <c r="G418" t="n">
-        <v>-23.5230626</v>
+        <v>-23.5224137</v>
       </c>
       <c r="H418" t="n">
-        <v>-46.3781017</v>
+        <v>-46.3783767</v>
       </c>
       <c r="I418" t="n">
-        <v>784.273</v>
+        <v>790.846</v>
       </c>
       <c r="J418" t="n">
-        <v>782.111</v>
+        <v>786.551</v>
       </c>
       <c r="K418" t="n">
-        <v>2.16</v>
+        <v>4.31</v>
       </c>
       <c r="L418" t="inlineStr">
         <is>
@@ -20159,34 +20174,34 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>SL-PV-34</t>
+          <t>SL-PV-41</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>PV-34</t>
+          <t>PV-41</t>
         </is>
       </c>
       <c r="E419" t="n">
-        <v>7397941.252</v>
+        <v>7397938.72</v>
       </c>
       <c r="F419" t="n">
-        <v>359273.636</v>
+        <v>359317.81</v>
       </c>
       <c r="G419" t="n">
-        <v>-23.5226874</v>
+        <v>-23.5227141</v>
       </c>
       <c r="H419" t="n">
-        <v>-46.3784614</v>
+        <v>-46.378029</v>
       </c>
       <c r="I419" t="n">
-        <v>787.202</v>
+        <v>789.352</v>
       </c>
       <c r="J419" t="n">
-        <v>784.7569999999999</v>
+        <v>786.775</v>
       </c>
       <c r="K419" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="L419" t="inlineStr">
         <is>
@@ -20207,34 +20222,34 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>SL-PV-35</t>
+          <t>SL-PV-42</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>PV-35</t>
+          <t>PV-42</t>
         </is>
       </c>
       <c r="E420" t="n">
-        <v>7397977.503</v>
+        <v>7397909.511</v>
       </c>
       <c r="F420" t="n">
-        <v>359228.842</v>
+        <v>359342.82</v>
       </c>
       <c r="G420" t="n">
-        <v>-23.5223561</v>
+        <v>-23.52298</v>
       </c>
       <c r="H420" t="n">
-        <v>-46.3788967</v>
+        <v>-46.3777869</v>
       </c>
       <c r="I420" t="n">
-        <v>788.938</v>
+        <v>788.374</v>
       </c>
       <c r="J420" t="n">
-        <v>785.057</v>
+        <v>786.967</v>
       </c>
       <c r="K420" t="n">
-        <v>3.88</v>
+        <v>1.41</v>
       </c>
       <c r="L420" t="inlineStr">
         <is>
@@ -20255,38 +20270,38 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>SL-PV-36</t>
+          <t>SL-PV-38</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>PV-36</t>
+          <t>PV-38</t>
         </is>
       </c>
       <c r="E421" t="n">
-        <v>7397999.594</v>
+        <v>7398012.211</v>
       </c>
       <c r="F421" t="n">
-        <v>359212.718</v>
+        <v>359222.572</v>
       </c>
       <c r="G421" t="n">
-        <v>-23.5221552</v>
+        <v>-23.5220422</v>
       </c>
       <c r="H421" t="n">
-        <v>-46.3790525</v>
+        <v>-46.3789548</v>
       </c>
       <c r="I421" t="n">
-        <v>789.169</v>
+        <v>789.247</v>
       </c>
       <c r="J421" t="n">
-        <v>785.2</v>
+        <v>785.327</v>
       </c>
       <c r="K421" t="n">
-        <v>3.97</v>
+        <v>3.92</v>
       </c>
       <c r="L421" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
         </is>
       </c>
     </row>
@@ -20303,38 +20318,38 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>SL-PV-37</t>
+          <t>SL-PV-69</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>PV-37</t>
+          <t>PV-69</t>
         </is>
       </c>
       <c r="E422" t="n">
-        <v>7398007.858</v>
+        <v>7397966.291</v>
       </c>
       <c r="F422" t="n">
-        <v>359206.253</v>
+        <v>359294.62</v>
       </c>
       <c r="G422" t="n">
-        <v>-23.5220801</v>
+        <v>-23.5224631</v>
       </c>
       <c r="H422" t="n">
-        <v>-46.379115</v>
+        <v>-46.3782535</v>
       </c>
       <c r="I422" t="n">
-        <v>788.999</v>
+        <v>789.657</v>
       </c>
       <c r="J422" t="n">
-        <v>785.249</v>
+        <v>787.726</v>
       </c>
       <c r="K422" t="n">
-        <v>3.75</v>
+        <v>1.93</v>
       </c>
       <c r="L422" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
         </is>
       </c>
     </row>
@@ -20351,38 +20366,38 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>SL-PV-39</t>
+          <t>SL-PV-70</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>PV-39</t>
+          <t>PV-70</t>
         </is>
       </c>
       <c r="E423" t="n">
-        <v>7397985.065</v>
+        <v>7397970.42</v>
       </c>
       <c r="F423" t="n">
-        <v>359260.286</v>
+        <v>359315.057</v>
       </c>
       <c r="G423" t="n">
-        <v>-23.5222906</v>
+        <v>-23.5224276</v>
       </c>
       <c r="H423" t="n">
-        <v>-46.378588</v>
+        <v>-46.378053</v>
       </c>
       <c r="I423" t="n">
-        <v>790.049</v>
+        <v>789.236</v>
       </c>
       <c r="J423" t="n">
-        <v>786.409</v>
+        <v>787.629</v>
       </c>
       <c r="K423" t="n">
-        <v>3.64</v>
+        <v>1.41</v>
       </c>
       <c r="L423" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
         </is>
       </c>
     </row>
@@ -20399,38 +20414,32 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>SL-PV-40</t>
+          <t>SL-PV-64</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>PV-40</t>
+          <t>PV-64</t>
         </is>
       </c>
       <c r="E424" t="n">
-        <v>7397971.64</v>
+        <v>7398010.193</v>
       </c>
       <c r="F424" t="n">
-        <v>359281.997</v>
-      </c>
-      <c r="G424" t="n">
-        <v>-23.5224137</v>
-      </c>
-      <c r="H424" t="n">
-        <v>-46.3783767</v>
+        <v>359316.45</v>
       </c>
       <c r="I424" t="n">
-        <v>790.846</v>
+        <v>788.654</v>
       </c>
       <c r="J424" t="n">
-        <v>786.551</v>
+        <v>785.813</v>
       </c>
       <c r="K424" t="n">
-        <v>4.31</v>
+        <v>2.84</v>
       </c>
       <c r="L424" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
         </is>
       </c>
     </row>
@@ -20447,38 +20456,32 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>SL-PV-41</t>
+          <t>SL-PV-65</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>PV-41</t>
+          <t>PV-65</t>
         </is>
       </c>
       <c r="E425" t="n">
-        <v>7397938.72</v>
+        <v>7397970.718</v>
       </c>
       <c r="F425" t="n">
-        <v>359317.81</v>
-      </c>
-      <c r="G425" t="n">
-        <v>-23.5227141</v>
-      </c>
-      <c r="H425" t="n">
-        <v>-46.378029</v>
+        <v>359317.925</v>
       </c>
       <c r="I425" t="n">
-        <v>789.352</v>
+        <v>789.213</v>
       </c>
       <c r="J425" t="n">
-        <v>786.775</v>
+        <v>787.615</v>
       </c>
       <c r="K425" t="n">
-        <v>2.58</v>
+        <v>1.6</v>
       </c>
       <c r="L425" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
         </is>
       </c>
     </row>
@@ -20490,43 +20493,43 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PVE</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>SL-PV-42</t>
+          <t>SL-PVE-32</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>PV-42</t>
+          <t>PVE-32</t>
         </is>
       </c>
       <c r="E426" t="n">
-        <v>7397909.511</v>
+        <v>7398250.778</v>
       </c>
       <c r="F426" t="n">
-        <v>359342.82</v>
+        <v>359405.052</v>
       </c>
       <c r="G426" t="n">
-        <v>-23.52298</v>
+        <v>-23.5199037</v>
       </c>
       <c r="H426" t="n">
-        <v>-46.3777869</v>
+        <v>-46.3771453</v>
       </c>
       <c r="I426" t="n">
-        <v>788.374</v>
+        <v>760.912</v>
       </c>
       <c r="J426" t="n">
-        <v>786.967</v>
+        <v>758.865</v>
       </c>
       <c r="K426" t="n">
-        <v>1.41</v>
+        <v>2.05</v>
       </c>
       <c r="L426" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA. PV-38 nao constava legivel nos prints enviados.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
         </is>
       </c>
     </row>
@@ -20543,34 +20546,34 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>SL-PV-38</t>
+          <t>SL-PV-04</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>PV-38</t>
+          <t>PV-04</t>
         </is>
       </c>
       <c r="E427" t="n">
-        <v>7398012.211</v>
+        <v>7398186.83</v>
       </c>
       <c r="F427" t="n">
-        <v>359222.572</v>
+        <v>359433.819</v>
       </c>
       <c r="G427" t="n">
-        <v>-23.5220422</v>
+        <v>-23.5204836</v>
       </c>
       <c r="H427" t="n">
-        <v>-46.3789548</v>
+        <v>-46.3768696</v>
       </c>
       <c r="I427" t="n">
-        <v>789.247</v>
+        <v>761.346</v>
       </c>
       <c r="J427" t="n">
-        <v>785.327</v>
+        <v>759.662</v>
       </c>
       <c r="K427" t="n">
-        <v>3.92</v>
+        <v>1.68</v>
       </c>
       <c r="L427" t="inlineStr">
         <is>
@@ -20591,34 +20594,34 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>SL-PV-69</t>
+          <t>SL-PV-05</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>PV-69</t>
+          <t>PV-05</t>
         </is>
       </c>
       <c r="E428" t="n">
-        <v>7397966.291</v>
+        <v>7398147.868</v>
       </c>
       <c r="F428" t="n">
-        <v>359294.62</v>
+        <v>359432.639</v>
       </c>
       <c r="G428" t="n">
-        <v>-23.5224631</v>
+        <v>-23.5208354</v>
       </c>
       <c r="H428" t="n">
-        <v>-46.3782535</v>
+        <v>-46.3768848</v>
       </c>
       <c r="I428" t="n">
-        <v>789.657</v>
+        <v>761.62</v>
       </c>
       <c r="J428" t="n">
-        <v>787.726</v>
+        <v>759.857</v>
       </c>
       <c r="K428" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="L428" t="inlineStr">
         <is>
@@ -20639,34 +20642,34 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>SL-PV-70</t>
+          <t>SL-PV-06</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>PV-70</t>
+          <t>PV-06</t>
         </is>
       </c>
       <c r="E429" t="n">
-        <v>7397970.42</v>
+        <v>7398110.3</v>
       </c>
       <c r="F429" t="n">
-        <v>359315.057</v>
+        <v>359435.788</v>
       </c>
       <c r="G429" t="n">
-        <v>-23.5224276</v>
+        <v>-23.5211749</v>
       </c>
       <c r="H429" t="n">
-        <v>-46.378053</v>
+        <v>-46.3768575</v>
       </c>
       <c r="I429" t="n">
-        <v>789.236</v>
+        <v>761.895</v>
       </c>
       <c r="J429" t="n">
-        <v>787.629</v>
+        <v>760.046</v>
       </c>
       <c r="K429" t="n">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="L429" t="inlineStr">
         <is>
@@ -20687,28 +20690,34 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>SL-PV-64</t>
+          <t>SL-PV-07</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>PV-64</t>
+          <t>PV-07</t>
         </is>
       </c>
       <c r="E430" t="n">
-        <v>7398010.193</v>
+        <v>7398078.311</v>
       </c>
       <c r="F430" t="n">
-        <v>359316.45</v>
+        <v>359448.771</v>
+      </c>
+      <c r="G430" t="n">
+        <v>-23.5214649</v>
+      </c>
+      <c r="H430" t="n">
+        <v>-46.3767334</v>
       </c>
       <c r="I430" t="n">
-        <v>788.654</v>
+        <v>761.657</v>
       </c>
       <c r="J430" t="n">
-        <v>785.813</v>
+        <v>760.218</v>
       </c>
       <c r="K430" t="n">
-        <v>2.84</v>
+        <v>1.44</v>
       </c>
       <c r="L430" t="inlineStr">
         <is>
@@ -20729,28 +20738,34 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>SL-PV-65</t>
+          <t>SL-PV-08</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>PV-65</t>
+          <t>PV-08</t>
         </is>
       </c>
       <c r="E431" t="n">
-        <v>7397970.718</v>
+        <v>7398070.299</v>
       </c>
       <c r="F431" t="n">
-        <v>359317.925</v>
+        <v>359450.392</v>
+      </c>
+      <c r="G431" t="n">
+        <v>-23.5215374</v>
+      </c>
+      <c r="H431" t="n">
+        <v>-46.3767183</v>
       </c>
       <c r="I431" t="n">
-        <v>789.213</v>
+        <v>762.054</v>
       </c>
       <c r="J431" t="n">
-        <v>787.615</v>
+        <v>760.647</v>
       </c>
       <c r="K431" t="n">
-        <v>1.6</v>
+        <v>1.41</v>
       </c>
       <c r="L431" t="inlineStr">
         <is>
@@ -20766,39 +20781,39 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>PVE</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>SL-PVE-32</t>
+          <t>SL-PV-02</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>PVE-32</t>
+          <t>PV-02</t>
         </is>
       </c>
       <c r="E432" t="n">
-        <v>7398250.778</v>
+        <v>7398239.066</v>
       </c>
       <c r="F432" t="n">
-        <v>359405.052</v>
+        <v>359409.719</v>
       </c>
       <c r="G432" t="n">
-        <v>-23.5199037</v>
+        <v>-23.5200098</v>
       </c>
       <c r="H432" t="n">
-        <v>-46.3771453</v>
+        <v>-46.3771007</v>
       </c>
       <c r="I432" t="n">
-        <v>760.912</v>
+        <v>760.8099999999999</v>
       </c>
       <c r="J432" t="n">
-        <v>758.865</v>
+        <v>759.326</v>
       </c>
       <c r="K432" t="n">
-        <v>2.05</v>
+        <v>1.48</v>
       </c>
       <c r="L432" t="inlineStr">
         <is>
@@ -20819,34 +20834,34 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>SL-PV-04</t>
+          <t>SL-PV-03</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>PV-04</t>
+          <t>PV-03</t>
         </is>
       </c>
       <c r="E433" t="n">
-        <v>7398186.83</v>
+        <v>7398232.807</v>
       </c>
       <c r="F433" t="n">
-        <v>359433.819</v>
+        <v>359429.767</v>
       </c>
       <c r="G433" t="n">
-        <v>-23.5204836</v>
+        <v>-23.5200681</v>
       </c>
       <c r="H433" t="n">
-        <v>-46.3768696</v>
+        <v>-46.376905</v>
       </c>
       <c r="I433" t="n">
-        <v>761.346</v>
+        <v>761.472</v>
       </c>
       <c r="J433" t="n">
-        <v>759.662</v>
+        <v>759.431</v>
       </c>
       <c r="K433" t="n">
-        <v>1.68</v>
+        <v>2.04</v>
       </c>
       <c r="L433" t="inlineStr">
         <is>
@@ -20862,43 +20877,37 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>PV</t>
+          <t>PVE</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>SL-PV-05</t>
+          <t>SL-PVE-31</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>PV-05</t>
+          <t>PVE-31</t>
         </is>
       </c>
       <c r="E434" t="n">
-        <v>7398147.868</v>
+        <v>7398016.07</v>
       </c>
       <c r="F434" t="n">
-        <v>359432.639</v>
-      </c>
-      <c r="G434" t="n">
-        <v>-23.5208354</v>
-      </c>
-      <c r="H434" t="n">
-        <v>-46.3768848</v>
+        <v>359202.358</v>
       </c>
       <c r="I434" t="n">
-        <v>761.62</v>
+        <v>788.763</v>
       </c>
       <c r="J434" t="n">
-        <v>759.857</v>
+        <v>786.3630000000001</v>
       </c>
       <c r="K434" t="n">
-        <v>1.76</v>
+        <v>2.4</v>
       </c>
       <c r="L434" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
+          <t>Adicionado via projeto RCE Comunidade Sao Lucas; interligado ao PV-37.</t>
         </is>
       </c>
     </row>
@@ -20915,38 +20924,32 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>SL-PV-06</t>
+          <t>SL-PV-75</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>PV-06</t>
+          <t>PV-75</t>
         </is>
       </c>
       <c r="E435" t="n">
-        <v>7398110.3</v>
+        <v>7398253.374</v>
       </c>
       <c r="F435" t="n">
-        <v>359435.788</v>
-      </c>
-      <c r="G435" t="n">
-        <v>-23.5211749</v>
-      </c>
-      <c r="H435" t="n">
-        <v>-46.3768575</v>
+        <v>359465.776</v>
       </c>
       <c r="I435" t="n">
-        <v>761.895</v>
+        <v>761.765</v>
       </c>
       <c r="J435" t="n">
-        <v>760.046</v>
+        <v>760.415</v>
       </c>
       <c r="K435" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="L435" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
+          <t>Adicionado via projeto São Lucas</t>
         </is>
       </c>
     </row>
@@ -20963,38 +20966,32 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>SL-PV-07</t>
+          <t>SL-PV-76</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>PV-07</t>
+          <t>PV-76</t>
         </is>
       </c>
       <c r="E436" t="n">
-        <v>7398078.311</v>
+        <v>7398255.262</v>
       </c>
       <c r="F436" t="n">
-        <v>359448.771</v>
-      </c>
-      <c r="G436" t="n">
-        <v>-23.5214649</v>
-      </c>
-      <c r="H436" t="n">
-        <v>-46.3767334</v>
+        <v>359466.421</v>
       </c>
       <c r="I436" t="n">
-        <v>761.657</v>
+        <v>761.674</v>
       </c>
       <c r="J436" t="n">
-        <v>760.218</v>
+        <v>760.426</v>
       </c>
       <c r="K436" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="L436" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
+          <t>Adicionado via projeto São Lucas</t>
         </is>
       </c>
     </row>
@@ -21011,38 +21008,32 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>SL-PV-08</t>
+          <t>SL-PV-77</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>PV-08</t>
+          <t>PV-77</t>
         </is>
       </c>
       <c r="E437" t="n">
-        <v>7398070.299</v>
+        <v>7398249.797</v>
       </c>
       <c r="F437" t="n">
-        <v>359450.392</v>
-      </c>
-      <c r="G437" t="n">
-        <v>-23.5215374</v>
-      </c>
-      <c r="H437" t="n">
-        <v>-46.3767183</v>
+        <v>359483.592</v>
       </c>
       <c r="I437" t="n">
-        <v>762.054</v>
+        <v>762.967</v>
       </c>
       <c r="J437" t="n">
-        <v>760.647</v>
+        <v>761.376</v>
       </c>
       <c r="K437" t="n">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="L437" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
+          <t>Adicionado via projeto São Lucas</t>
         </is>
       </c>
     </row>
@@ -21059,38 +21050,32 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>SL-PV-02</t>
+          <t>SL-PV-78</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>PV-02</t>
+          <t>PV-78</t>
         </is>
       </c>
       <c r="E438" t="n">
-        <v>7398239.066</v>
+        <v>7398238.573</v>
       </c>
       <c r="F438" t="n">
-        <v>359409.719</v>
-      </c>
-      <c r="G438" t="n">
-        <v>-23.5200098</v>
-      </c>
-      <c r="H438" t="n">
-        <v>-46.3771007</v>
+        <v>359501.728</v>
       </c>
       <c r="I438" t="n">
-        <v>760.8099999999999</v>
+        <v>765.659</v>
       </c>
       <c r="J438" t="n">
-        <v>759.326</v>
+        <v>764.275</v>
       </c>
       <c r="K438" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="L438" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
+          <t>Adicionado via projeto São Lucas</t>
         </is>
       </c>
     </row>
@@ -21107,87 +21092,78 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>SL-PV-03</t>
+          <t>SL-PV-75.1</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>PV-03</t>
-        </is>
-      </c>
-      <c r="E439" t="n">
-        <v>7398232.807</v>
-      </c>
-      <c r="F439" t="n">
-        <v>359429.767</v>
+          <t>PV-75.1</t>
+        </is>
       </c>
       <c r="G439" t="n">
-        <v>-23.5200681</v>
+        <v>-23.5198222</v>
       </c>
       <c r="H439" t="n">
-        <v>-46.376905</v>
-      </c>
-      <c r="I439" t="n">
-        <v>761.472</v>
-      </c>
-      <c r="J439" t="n">
-        <v>759.431</v>
-      </c>
-      <c r="K439" t="n">
-        <v>2.04</v>
+        <v>-46.3768722</v>
       </c>
       <c r="L439" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; lancamento em VCA.</t>
+          <t>Ponto auxiliar obtido via Google Earth.</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>PVE</t>
+          <t>PV</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>SL-PVE-31</t>
+          <t>JC-PV-17-FL07</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>PVE-31</t>
+          <t>PV-17</t>
         </is>
       </c>
       <c r="E440" t="n">
-        <v>7398016.07</v>
+        <v>7397122.275</v>
       </c>
       <c r="F440" t="n">
-        <v>359202.358</v>
+        <v>358726.884</v>
+      </c>
+      <c r="G440" t="n">
+        <v>-23.5300354</v>
+      </c>
+      <c r="H440" t="n">
+        <v>-46.3838931</v>
       </c>
       <c r="I440" t="n">
-        <v>788.763</v>
+        <v>782.299</v>
       </c>
       <c r="J440" t="n">
-        <v>786.3630000000001</v>
+        <v>779.199</v>
       </c>
       <c r="K440" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="L440" t="inlineStr">
         <is>
-          <t>Adicionado via projeto RCE Comunidade Sao Lucas; interligado ao PV-37.</t>
+          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; trechos PV-16 ao PV-17 e PV-17 ao PV-18.</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -21197,285 +21173,36 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>SL-PV-75</t>
+          <t>JC-PV-20</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>PV-75</t>
+          <t>PV-20</t>
         </is>
       </c>
       <c r="E441" t="n">
-        <v>7398253.374</v>
+        <v>7397174.5</v>
       </c>
       <c r="F441" t="n">
-        <v>359465.776</v>
+        <v>358918.3</v>
+      </c>
+      <c r="G441" t="n">
+        <v>-23.5295804</v>
+      </c>
+      <c r="H441" t="n">
+        <v>-46.3820136</v>
       </c>
       <c r="I441" t="n">
-        <v>761.765</v>
+        <v>794.6</v>
       </c>
       <c r="J441" t="n">
-        <v>760.415</v>
+        <v>790.638</v>
       </c>
       <c r="K441" t="n">
-        <v>1.35</v>
+        <v>3.96</v>
       </c>
       <c r="L441" t="inlineStr">
-        <is>
-          <t>Adicionado via projeto São Lucas</t>
-        </is>
-      </c>
-    </row>
-    <row r="442">
-      <c r="A442" t="inlineStr">
-        <is>
-          <t>rce_comunidade_sao_lucas</t>
-        </is>
-      </c>
-      <c r="B442" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="C442" t="inlineStr">
-        <is>
-          <t>SL-PV-76</t>
-        </is>
-      </c>
-      <c r="D442" t="inlineStr">
-        <is>
-          <t>PV-76</t>
-        </is>
-      </c>
-      <c r="E442" t="n">
-        <v>7398255.262</v>
-      </c>
-      <c r="F442" t="n">
-        <v>359466.421</v>
-      </c>
-      <c r="I442" t="n">
-        <v>761.674</v>
-      </c>
-      <c r="J442" t="n">
-        <v>760.426</v>
-      </c>
-      <c r="K442" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="L442" t="inlineStr">
-        <is>
-          <t>Adicionado via projeto São Lucas</t>
-        </is>
-      </c>
-    </row>
-    <row r="443">
-      <c r="A443" t="inlineStr">
-        <is>
-          <t>rce_comunidade_sao_lucas</t>
-        </is>
-      </c>
-      <c r="B443" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="C443" t="inlineStr">
-        <is>
-          <t>SL-PV-77</t>
-        </is>
-      </c>
-      <c r="D443" t="inlineStr">
-        <is>
-          <t>PV-77</t>
-        </is>
-      </c>
-      <c r="E443" t="n">
-        <v>7398249.797</v>
-      </c>
-      <c r="F443" t="n">
-        <v>359483.592</v>
-      </c>
-      <c r="I443" t="n">
-        <v>762.967</v>
-      </c>
-      <c r="J443" t="n">
-        <v>761.376</v>
-      </c>
-      <c r="K443" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="L443" t="inlineStr">
-        <is>
-          <t>Adicionado via projeto São Lucas</t>
-        </is>
-      </c>
-    </row>
-    <row r="444">
-      <c r="A444" t="inlineStr">
-        <is>
-          <t>rce_comunidade_sao_lucas</t>
-        </is>
-      </c>
-      <c r="B444" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="C444" t="inlineStr">
-        <is>
-          <t>SL-PV-78</t>
-        </is>
-      </c>
-      <c r="D444" t="inlineStr">
-        <is>
-          <t>PV-78</t>
-        </is>
-      </c>
-      <c r="E444" t="n">
-        <v>7398238.573</v>
-      </c>
-      <c r="F444" t="n">
-        <v>359501.728</v>
-      </c>
-      <c r="I444" t="n">
-        <v>765.659</v>
-      </c>
-      <c r="J444" t="n">
-        <v>764.275</v>
-      </c>
-      <c r="K444" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="L444" t="inlineStr">
-        <is>
-          <t>Adicionado via projeto São Lucas</t>
-        </is>
-      </c>
-    </row>
-    <row r="445">
-      <c r="A445" t="inlineStr">
-        <is>
-          <t>rce_comunidade_sao_lucas</t>
-        </is>
-      </c>
-      <c r="B445" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="C445" t="inlineStr">
-        <is>
-          <t>SL-PV-75.1</t>
-        </is>
-      </c>
-      <c r="D445" t="inlineStr">
-        <is>
-          <t>PV-75.1</t>
-        </is>
-      </c>
-      <c r="G445" t="n">
-        <v>-23.5198222</v>
-      </c>
-      <c r="H445" t="n">
-        <v>-46.3768722</v>
-      </c>
-      <c r="L445" t="inlineStr">
-        <is>
-          <t>Ponto auxiliar obtido via Google Earth.</t>
-        </is>
-      </c>
-    </row>
-    <row r="446">
-      <c r="A446" t="inlineStr">
-        <is>
-          <t>cts_joao_canzi</t>
-        </is>
-      </c>
-      <c r="B446" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="C446" t="inlineStr">
-        <is>
-          <t>JC-PV-17-FL07</t>
-        </is>
-      </c>
-      <c r="D446" t="inlineStr">
-        <is>
-          <t>PV-17</t>
-        </is>
-      </c>
-      <c r="E446" t="n">
-        <v>7397122.275</v>
-      </c>
-      <c r="F446" t="n">
-        <v>358726.884</v>
-      </c>
-      <c r="G446" t="n">
-        <v>-23.5300354</v>
-      </c>
-      <c r="H446" t="n">
-        <v>-46.3838931</v>
-      </c>
-      <c r="I446" t="n">
-        <v>782.299</v>
-      </c>
-      <c r="J446" t="n">
-        <v>779.199</v>
-      </c>
-      <c r="K446" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L446" t="inlineStr">
-        <is>
-          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; trechos PV-16 ao PV-17 e PV-17 ao PV-18.</t>
-        </is>
-      </c>
-    </row>
-    <row r="447">
-      <c r="A447" t="inlineStr">
-        <is>
-          <t>cts_joao_canzi</t>
-        </is>
-      </c>
-      <c r="B447" t="inlineStr">
-        <is>
-          <t>PV</t>
-        </is>
-      </c>
-      <c r="C447" t="inlineStr">
-        <is>
-          <t>JC-PV-20</t>
-        </is>
-      </c>
-      <c r="D447" t="inlineStr">
-        <is>
-          <t>PV-20</t>
-        </is>
-      </c>
-      <c r="E447" t="n">
-        <v>7397174.5</v>
-      </c>
-      <c r="F447" t="n">
-        <v>358918.3</v>
-      </c>
-      <c r="G447" t="n">
-        <v>-23.5295804</v>
-      </c>
-      <c r="H447" t="n">
-        <v>-46.3820136</v>
-      </c>
-      <c r="I447" t="n">
-        <v>794.6</v>
-      </c>
-      <c r="J447" t="n">
-        <v>790.638</v>
-      </c>
-      <c r="K447" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="L447" t="inlineStr">
         <is>
           <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-19 ao PV-20.</t>
         </is>
@@ -21488,12 +21215,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R460"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
+  <dimension ref="A1:R454"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
     <col width="17.44140625" customWidth="1" min="3" max="3"/>
@@ -50955,53 +50682,53 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>rce_elias_sleiman</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>ELIAS-003</t>
+          <t>JC-013</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>PV-23 - PV-24</t>
+          <t>PV-18 - PV-19</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>PV-23</t>
+          <t>PV-18</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>PV-24</t>
+          <t>PV-19</t>
         </is>
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD LISO</t>
         </is>
       </c>
       <c r="G419" t="n">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>Metodo Nao Destrutivo - MND</t>
         </is>
       </c>
       <c r="I419" t="n">
-        <v>44.64</v>
+        <v>66.72499999999999</v>
       </c>
       <c r="J419" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="K419" t="n">
-        <v>2.36</v>
+        <v>4</v>
       </c>
       <c r="L419" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="M419" t="inlineStr">
         <is>
@@ -51010,46 +50737,46 @@
       </c>
       <c r="N419" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; PV-18 ao PV-19; arquivo: planos_furo/cts_joao_canzi_fl07_pv18_pv19.pdf; taxa 0,0485.</t>
         </is>
       </c>
       <c r="O419" t="n">
-        <v>-23.5309793</v>
+        <v>-23.5300224</v>
       </c>
       <c r="P419" t="n">
-        <v>-46.3832624</v>
+        <v>-46.3831139</v>
       </c>
       <c r="Q419" t="n">
-        <v>-23.5307209</v>
+        <v>-23.5298774</v>
       </c>
       <c r="R419" t="n">
-        <v>-46.3829268</v>
+        <v>-46.3824796</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>rce_elias_sleiman</t>
+          <t>rce_comunidade_sao_lucas</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>ELIAS-004</t>
+          <t>SL-001</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>PV-24 - PV-25</t>
+          <t>PV-26 - PV-27</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>PV-24</t>
+          <t>PV-26</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>PV-25</t>
+          <t>PV-27</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
@@ -51062,20 +50789,20 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I420" t="n">
-        <v>82.91</v>
+        <v>14.74</v>
       </c>
       <c r="J420" t="n">
-        <v>2.36</v>
+        <v>3.04</v>
       </c>
       <c r="K420" t="n">
-        <v>2.72</v>
+        <v>3.57</v>
       </c>
       <c r="L420" t="n">
-        <v>2.72</v>
+        <v>3.57</v>
       </c>
       <c r="M420" t="inlineStr">
         <is>
@@ -51084,46 +50811,46 @@
       </c>
       <c r="N420" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
         </is>
       </c>
       <c r="O420" t="n">
-        <v>-23.5307209</v>
+        <v>-23.5236471</v>
       </c>
       <c r="P420" t="n">
-        <v>-46.3829268</v>
+        <v>-46.3767998</v>
       </c>
       <c r="Q420" t="n">
-        <v>-23.5307563</v>
+        <v>-23.5237798</v>
       </c>
       <c r="R420" t="n">
-        <v>-46.3821157</v>
+        <v>-46.3767878</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>rce_elias_sleiman</t>
+          <t>rce_comunidade_sao_lucas</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>ELIAS-005</t>
+          <t>SL-002</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>PV-25 - PV-26</t>
+          <t>PV-27 - PV-28</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>PV-25</t>
+          <t>PV-27</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>PV-26</t>
+          <t>PV-28</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -51136,20 +50863,20 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I421" t="n">
-        <v>44.29</v>
+        <v>3.63</v>
       </c>
       <c r="J421" t="n">
-        <v>2.72</v>
+        <v>3.57</v>
       </c>
       <c r="K421" t="n">
-        <v>2.62</v>
+        <v>3.34</v>
       </c>
       <c r="L421" t="n">
-        <v>2.72</v>
+        <v>3.57</v>
       </c>
       <c r="M421" t="inlineStr">
         <is>
@@ -51158,46 +50885,46 @@
       </c>
       <c r="N421" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
         </is>
       </c>
       <c r="O421" t="n">
-        <v>-23.5307563</v>
+        <v>-23.5237798</v>
       </c>
       <c r="P421" t="n">
-        <v>-46.3821157</v>
+        <v>-46.3767878</v>
       </c>
       <c r="Q421" t="n">
-        <v>-23.5311521</v>
+        <v>-23.5238121</v>
       </c>
       <c r="R421" t="n">
-        <v>-46.3821788</v>
+        <v>-46.3767936</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>rce_elias_sleiman</t>
+          <t>rce_comunidade_sao_lucas</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>ELIAS-006</t>
+          <t>SL-003</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>PV-26 - PV-27</t>
+          <t>PV-28 - PV-29</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>PV-26</t>
+          <t>PV-28</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>PV-27</t>
+          <t>PV-29</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -51210,20 +50937,20 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I422" t="n">
-        <v>50.97</v>
+        <v>7.51</v>
       </c>
       <c r="J422" t="n">
-        <v>2.62</v>
+        <v>3.34</v>
       </c>
       <c r="K422" t="n">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="L422" t="n">
-        <v>2.62</v>
+        <v>3.34</v>
       </c>
       <c r="M422" t="inlineStr">
         <is>
@@ -51232,46 +50959,46 @@
       </c>
       <c r="N422" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
         </is>
       </c>
       <c r="O422" t="n">
-        <v>-23.5311521</v>
+        <v>-23.5238121</v>
       </c>
       <c r="P422" t="n">
-        <v>-46.3821788</v>
+        <v>-46.3767936</v>
       </c>
       <c r="Q422" t="n">
-        <v>-23.5315893</v>
+        <v>-23.5238331</v>
       </c>
       <c r="R422" t="n">
-        <v>-46.3820231</v>
+        <v>-46.3768636</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>rce_elias_sleiman</t>
+          <t>rce_comunidade_sao_lucas</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>ELIAS-007</t>
+          <t>SL-004</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>PV-27 - PV-28</t>
+          <t>PV-29 - PV-30</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>PV-27</t>
+          <t>PV-29</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>PV-28</t>
+          <t>PV-30</t>
         </is>
       </c>
       <c r="F423" t="inlineStr">
@@ -51284,20 +51011,20 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I423" t="n">
-        <v>43.95</v>
+        <v>13.61</v>
       </c>
       <c r="J423" t="n">
-        <v>2.09</v>
+        <v>1.81</v>
       </c>
       <c r="K423" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="L423" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="M423" t="inlineStr">
         <is>
@@ -51306,46 +51033,46 @@
       </c>
       <c r="N423" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
         </is>
       </c>
       <c r="O423" t="n">
-        <v>-23.5315893</v>
+        <v>-23.5238331</v>
       </c>
       <c r="P423" t="n">
-        <v>-46.3820231</v>
+        <v>-46.3768636</v>
       </c>
       <c r="Q423" t="n">
-        <v>-23.5319394</v>
+        <v>-23.5237849</v>
       </c>
       <c r="R423" t="n">
-        <v>-46.3818203</v>
+        <v>-46.3769862</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>rce_elias_sleiman</t>
+          <t>rce_comunidade_sao_lucas</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>ELIAS-008</t>
+          <t>SL-005</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>PV-28 - PV-29</t>
+          <t>PV-30 - PV-31</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>PV-28</t>
+          <t>PV-30</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>PV-29</t>
+          <t>PV-31</t>
         </is>
       </c>
       <c r="F424" t="inlineStr">
@@ -51358,20 +51085,20 @@
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I424" t="n">
-        <v>28.15</v>
+        <v>6.62</v>
       </c>
       <c r="J424" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="K424" t="n">
-        <v>2.2</v>
+        <v>1.43</v>
       </c>
       <c r="L424" t="n">
-        <v>2.2</v>
+        <v>1.43</v>
       </c>
       <c r="M424" t="inlineStr">
         <is>
@@ -51380,72 +51107,72 @@
       </c>
       <c r="N424" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
         </is>
       </c>
       <c r="O424" t="n">
-        <v>-23.5319394</v>
+        <v>-23.5237849</v>
       </c>
       <c r="P424" t="n">
-        <v>-46.3818203</v>
+        <v>-46.3769862</v>
       </c>
       <c r="Q424" t="n">
-        <v>-23.5321621</v>
+        <v>-23.5237689</v>
       </c>
       <c r="R424" t="n">
-        <v>-46.3816872</v>
+        <v>-46.3770487</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>cts_joao_canzi</t>
+          <t>rce_comunidade_sao_lucas</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>JC-013</t>
+          <t>SL-006</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>PV-18 - PV-19</t>
+          <t>PV-31 - PV-32</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>PV-18</t>
+          <t>PV-31</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>PV-19</t>
+          <t>PV-32</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>PEAD LISO</t>
+          <t>PVC</t>
         </is>
       </c>
       <c r="G425" t="n">
-        <v>355</v>
+        <v>200</v>
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Metodo Nao Destrutivo - MND</t>
+          <t>Vala a Céu Aberto - VCA</t>
         </is>
       </c>
       <c r="I425" t="n">
-        <v>66.72499999999999</v>
+        <v>70.89</v>
       </c>
       <c r="J425" t="n">
-        <v>3.5</v>
+        <v>1.43</v>
       </c>
       <c r="K425" t="n">
-        <v>4</v>
+        <v>2.18</v>
       </c>
       <c r="L425" t="n">
-        <v>4</v>
+        <v>2.18</v>
       </c>
       <c r="M425" t="inlineStr">
         <is>
@@ -51454,20 +51181,20 @@
       </c>
       <c r="N425" t="inlineStr">
         <is>
-          <t>Plano de furo FL-07 versao 01, 05.JUN.2026; PV-18 ao PV-19; arquivo: planos_furo/cts_joao_canzi_fl07_pv18_pv19.pdf; taxa 0,0485.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
         </is>
       </c>
       <c r="O425" t="n">
-        <v>-23.5300224</v>
+        <v>-23.5237689</v>
       </c>
       <c r="P425" t="n">
-        <v>-46.3831139</v>
+        <v>-46.3770487</v>
       </c>
       <c r="Q425" t="n">
-        <v>-23.5298774</v>
+        <v>-23.5233519</v>
       </c>
       <c r="R425" t="n">
-        <v>-46.3824796</v>
+        <v>-46.3775754</v>
       </c>
     </row>
     <row r="426">
@@ -51478,22 +51205,22 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>SL-001</t>
+          <t>SL-007</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>PV-26 - PV-27</t>
+          <t>PV-32 - PV-33</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>PV-26</t>
+          <t>PV-32</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>PV-27</t>
+          <t>PV-33</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
@@ -51510,16 +51237,16 @@
         </is>
       </c>
       <c r="I426" t="n">
-        <v>14.74</v>
+        <v>62.56</v>
       </c>
       <c r="J426" t="n">
-        <v>3.04</v>
+        <v>2.18</v>
       </c>
       <c r="K426" t="n">
-        <v>3.57</v>
+        <v>2.16</v>
       </c>
       <c r="L426" t="n">
-        <v>3.57</v>
+        <v>2.18</v>
       </c>
       <c r="M426" t="inlineStr">
         <is>
@@ -51532,16 +51259,16 @@
         </is>
       </c>
       <c r="O426" t="n">
-        <v>-23.5236471</v>
+        <v>-23.5233519</v>
       </c>
       <c r="P426" t="n">
-        <v>-46.3767998</v>
+        <v>-46.3775754</v>
       </c>
       <c r="Q426" t="n">
-        <v>-23.5237798</v>
+        <v>-23.5230626</v>
       </c>
       <c r="R426" t="n">
-        <v>-46.3767878</v>
+        <v>-46.3781017</v>
       </c>
     </row>
     <row r="427">
@@ -51552,22 +51279,22 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>SL-002</t>
+          <t>SL-008</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>PV-27 - PV-28</t>
+          <t>PV-33 - PV-34</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>PV-27</t>
+          <t>PV-33</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>PV-28</t>
+          <t>PV-34</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
@@ -51584,16 +51311,16 @@
         </is>
       </c>
       <c r="I427" t="n">
-        <v>3.63</v>
+        <v>55.46</v>
       </c>
       <c r="J427" t="n">
-        <v>3.57</v>
+        <v>2.16</v>
       </c>
       <c r="K427" t="n">
-        <v>3.34</v>
+        <v>2.45</v>
       </c>
       <c r="L427" t="n">
-        <v>3.57</v>
+        <v>2.45</v>
       </c>
       <c r="M427" t="inlineStr">
         <is>
@@ -51606,16 +51333,16 @@
         </is>
       </c>
       <c r="O427" t="n">
-        <v>-23.5237798</v>
+        <v>-23.5230626</v>
       </c>
       <c r="P427" t="n">
-        <v>-46.3767878</v>
+        <v>-46.3781017</v>
       </c>
       <c r="Q427" t="n">
-        <v>-23.5238121</v>
+        <v>-23.5226874</v>
       </c>
       <c r="R427" t="n">
-        <v>-46.3767936</v>
+        <v>-46.3784614</v>
       </c>
     </row>
     <row r="428">
@@ -51626,22 +51353,22 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>SL-003</t>
+          <t>SL-009</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>PV-28 - PV-29</t>
+          <t>PV-34 - PV-35</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>PV-28</t>
+          <t>PV-34</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>PV-29</t>
+          <t>PV-35</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -51658,16 +51385,16 @@
         </is>
       </c>
       <c r="I428" t="n">
-        <v>7.51</v>
+        <v>57.62</v>
       </c>
       <c r="J428" t="n">
-        <v>3.34</v>
+        <v>2.45</v>
       </c>
       <c r="K428" t="n">
-        <v>1.81</v>
+        <v>3.88</v>
       </c>
       <c r="L428" t="n">
-        <v>3.34</v>
+        <v>3.88</v>
       </c>
       <c r="M428" t="inlineStr">
         <is>
@@ -51680,16 +51407,16 @@
         </is>
       </c>
       <c r="O428" t="n">
-        <v>-23.5238121</v>
+        <v>-23.5226874</v>
       </c>
       <c r="P428" t="n">
-        <v>-46.3767936</v>
+        <v>-46.3784614</v>
       </c>
       <c r="Q428" t="n">
-        <v>-23.5238331</v>
+        <v>-23.5223561</v>
       </c>
       <c r="R428" t="n">
-        <v>-46.3768636</v>
+        <v>-46.3788967</v>
       </c>
     </row>
     <row r="429">
@@ -51700,22 +51427,22 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>SL-004</t>
+          <t>SL-010</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>PV-29 - PV-30</t>
+          <t>PV-35 - PV-36</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>PV-29</t>
+          <t>PV-35</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>PV-30</t>
+          <t>PV-36</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -51732,16 +51459,16 @@
         </is>
       </c>
       <c r="I429" t="n">
-        <v>13.61</v>
+        <v>27.35</v>
       </c>
       <c r="J429" t="n">
-        <v>1.81</v>
+        <v>3.88</v>
       </c>
       <c r="K429" t="n">
-        <v>1.4</v>
+        <v>3.97</v>
       </c>
       <c r="L429" t="n">
-        <v>1.81</v>
+        <v>3.97</v>
       </c>
       <c r="M429" t="inlineStr">
         <is>
@@ -51754,16 +51481,16 @@
         </is>
       </c>
       <c r="O429" t="n">
-        <v>-23.5238331</v>
+        <v>-23.5223561</v>
       </c>
       <c r="P429" t="n">
-        <v>-46.3768636</v>
+        <v>-46.3788967</v>
       </c>
       <c r="Q429" t="n">
-        <v>-23.5237849</v>
+        <v>-23.5221552</v>
       </c>
       <c r="R429" t="n">
-        <v>-46.3769862</v>
+        <v>-46.3790525</v>
       </c>
     </row>
     <row r="430">
@@ -51774,22 +51501,22 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>SL-005</t>
+          <t>SL-011</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>PV-30 - PV-31</t>
+          <t>PV-36 - PV-37</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>PV-30</t>
+          <t>PV-36</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>PV-31</t>
+          <t>PV-37</t>
         </is>
       </c>
       <c r="F430" t="inlineStr">
@@ -51806,16 +51533,16 @@
         </is>
       </c>
       <c r="I430" t="n">
-        <v>6.62</v>
+        <v>10.49</v>
       </c>
       <c r="J430" t="n">
-        <v>1.4</v>
+        <v>3.97</v>
       </c>
       <c r="K430" t="n">
-        <v>1.43</v>
+        <v>3.75</v>
       </c>
       <c r="L430" t="n">
-        <v>1.43</v>
+        <v>3.97</v>
       </c>
       <c r="M430" t="inlineStr">
         <is>
@@ -51828,16 +51555,16 @@
         </is>
       </c>
       <c r="O430" t="n">
-        <v>-23.5237849</v>
+        <v>-23.5221552</v>
       </c>
       <c r="P430" t="n">
-        <v>-46.3769862</v>
+        <v>-46.3790525</v>
       </c>
       <c r="Q430" t="n">
-        <v>-23.5237689</v>
+        <v>-23.5220801</v>
       </c>
       <c r="R430" t="n">
-        <v>-46.3770487</v>
+        <v>-46.379115</v>
       </c>
     </row>
     <row r="431">
@@ -51848,22 +51575,22 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>SL-006</t>
+          <t>SL-012</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>PV-31 - PV-32</t>
+          <t>PV-37 - PV-38</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>PV-31</t>
+          <t>PV-37</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>PV-32</t>
+          <t>PV-38</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -51876,20 +51603,20 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I431" t="n">
-        <v>70.89</v>
+        <v>16.89</v>
       </c>
       <c r="J431" t="n">
-        <v>1.43</v>
+        <v>3.75</v>
       </c>
       <c r="K431" t="n">
-        <v>2.18</v>
+        <v>3.92</v>
       </c>
       <c r="L431" t="n">
-        <v>2.18</v>
+        <v>3.92</v>
       </c>
       <c r="M431" t="inlineStr">
         <is>
@@ -51898,20 +51625,20 @@
       </c>
       <c r="N431" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. PV-38 incluido conforme novo print.</t>
         </is>
       </c>
       <c r="O431" t="n">
-        <v>-23.5237689</v>
+        <v>-23.5220801</v>
       </c>
       <c r="P431" t="n">
-        <v>-46.3770487</v>
+        <v>-46.379115</v>
       </c>
       <c r="Q431" t="n">
-        <v>-23.5233519</v>
+        <v>-23.5220422</v>
       </c>
       <c r="R431" t="n">
-        <v>-46.3775754</v>
+        <v>-46.3789548</v>
       </c>
     </row>
     <row r="432">
@@ -51922,22 +51649,22 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>SL-007</t>
+          <t>SL-013</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>PV-32 - PV-33</t>
+          <t>PV-38 - PV-39</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>PV-32</t>
+          <t>PV-38</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>PV-33</t>
+          <t>PV-39</t>
         </is>
       </c>
       <c r="F432" t="inlineStr">
@@ -51950,20 +51677,20 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I432" t="n">
-        <v>62.56</v>
+        <v>46.47</v>
       </c>
       <c r="J432" t="n">
-        <v>2.18</v>
+        <v>3.92</v>
       </c>
       <c r="K432" t="n">
-        <v>2.16</v>
+        <v>3.64</v>
       </c>
       <c r="L432" t="n">
-        <v>2.18</v>
+        <v>3.92</v>
       </c>
       <c r="M432" t="inlineStr">
         <is>
@@ -51972,20 +51699,20 @@
       </c>
       <c r="N432" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. PV-38 incluido conforme novo print.</t>
         </is>
       </c>
       <c r="O432" t="n">
-        <v>-23.5233519</v>
+        <v>-23.5220422</v>
       </c>
       <c r="P432" t="n">
-        <v>-46.3775754</v>
+        <v>-46.3789548</v>
       </c>
       <c r="Q432" t="n">
-        <v>-23.5230626</v>
+        <v>-23.5222906</v>
       </c>
       <c r="R432" t="n">
-        <v>-46.3781017</v>
+        <v>-46.378588</v>
       </c>
     </row>
     <row r="433">
@@ -51996,22 +51723,22 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>SL-008</t>
+          <t>SL-014</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>PV-33 - PV-34</t>
+          <t>PV-40 - PV-41</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>PV-33</t>
+          <t>PV-40</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
         <is>
-          <t>PV-34</t>
+          <t>PV-41</t>
         </is>
       </c>
       <c r="F433" t="inlineStr">
@@ -52028,16 +51755,16 @@
         </is>
       </c>
       <c r="I433" t="n">
-        <v>55.46</v>
+        <v>48.64</v>
       </c>
       <c r="J433" t="n">
-        <v>2.16</v>
+        <v>4.31</v>
       </c>
       <c r="K433" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="L433" t="n">
-        <v>2.45</v>
+        <v>4.31</v>
       </c>
       <c r="M433" t="inlineStr">
         <is>
@@ -52050,16 +51777,16 @@
         </is>
       </c>
       <c r="O433" t="n">
-        <v>-23.5230626</v>
+        <v>-23.5224137</v>
       </c>
       <c r="P433" t="n">
-        <v>-46.3781017</v>
+        <v>-46.3783767</v>
       </c>
       <c r="Q433" t="n">
-        <v>-23.5226874</v>
+        <v>-23.5227141</v>
       </c>
       <c r="R433" t="n">
-        <v>-46.3784614</v>
+        <v>-46.378029</v>
       </c>
     </row>
     <row r="434">
@@ -52070,22 +51797,22 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>SL-009</t>
+          <t>SL-015</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>PV-34 - PV-35</t>
+          <t>PV-41 - PV-42</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>PV-34</t>
+          <t>PV-41</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
         <is>
-          <t>PV-35</t>
+          <t>PV-42</t>
         </is>
       </c>
       <c r="F434" t="inlineStr">
@@ -52102,16 +51829,16 @@
         </is>
       </c>
       <c r="I434" t="n">
-        <v>57.62</v>
+        <v>38.45</v>
       </c>
       <c r="J434" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="K434" t="n">
-        <v>3.88</v>
+        <v>1.41</v>
       </c>
       <c r="L434" t="n">
-        <v>3.88</v>
+        <v>2.58</v>
       </c>
       <c r="M434" t="inlineStr">
         <is>
@@ -52124,16 +51851,16 @@
         </is>
       </c>
       <c r="O434" t="n">
-        <v>-23.5226874</v>
+        <v>-23.5227141</v>
       </c>
       <c r="P434" t="n">
-        <v>-46.3784614</v>
+        <v>-46.378029</v>
       </c>
       <c r="Q434" t="n">
-        <v>-23.5223561</v>
+        <v>-23.52298</v>
       </c>
       <c r="R434" t="n">
-        <v>-46.3788967</v>
+        <v>-46.3777869</v>
       </c>
     </row>
     <row r="435">
@@ -52144,22 +51871,22 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>SL-010</t>
+          <t>SL-016</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>PV-35 - PV-36</t>
+          <t>PV-39 - PV-40</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>PV-35</t>
+          <t>PV-39</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>PV-36</t>
+          <t>PV-40</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -52172,20 +51899,20 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I435" t="n">
-        <v>27.35</v>
+        <v>24.53</v>
       </c>
       <c r="J435" t="n">
-        <v>3.88</v>
+        <v>3.64</v>
       </c>
       <c r="K435" t="n">
-        <v>3.97</v>
+        <v>4.31</v>
       </c>
       <c r="L435" t="n">
-        <v>3.97</v>
+        <v>4.31</v>
       </c>
       <c r="M435" t="inlineStr">
         <is>
@@ -52194,20 +51921,20 @@
       </c>
       <c r="N435" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. Extensao lida no print.</t>
         </is>
       </c>
       <c r="O435" t="n">
-        <v>-23.5223561</v>
+        <v>-23.5222906</v>
       </c>
       <c r="P435" t="n">
-        <v>-46.3788967</v>
+        <v>-46.378588</v>
       </c>
       <c r="Q435" t="n">
-        <v>-23.5221552</v>
+        <v>-23.5224137</v>
       </c>
       <c r="R435" t="n">
-        <v>-46.3790525</v>
+        <v>-46.3783767</v>
       </c>
     </row>
     <row r="436">
@@ -52218,22 +51945,22 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>SL-011</t>
+          <t>SL-017</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>PV-36 - PV-37</t>
+          <t>PV-40 - PV-69</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>PV-36</t>
+          <t>PV-40</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>PV-37</t>
+          <t>PV-69</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">
@@ -52246,20 +51973,20 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I436" t="n">
-        <v>10.49</v>
+        <v>13.08</v>
       </c>
       <c r="J436" t="n">
-        <v>3.97</v>
+        <v>4.31</v>
       </c>
       <c r="K436" t="n">
-        <v>3.75</v>
+        <v>1.93</v>
       </c>
       <c r="L436" t="n">
-        <v>3.97</v>
+        <v>4.31</v>
       </c>
       <c r="M436" t="inlineStr">
         <is>
@@ -52268,20 +51995,20 @@
       </c>
       <c r="N436" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. Extensao lida no print.</t>
         </is>
       </c>
       <c r="O436" t="n">
-        <v>-23.5221552</v>
+        <v>-23.5224137</v>
       </c>
       <c r="P436" t="n">
-        <v>-46.3790525</v>
+        <v>-46.3783767</v>
       </c>
       <c r="Q436" t="n">
-        <v>-23.5220801</v>
+        <v>-23.5224631</v>
       </c>
       <c r="R436" t="n">
-        <v>-46.379115</v>
+        <v>-46.3782535</v>
       </c>
     </row>
     <row r="437">
@@ -52292,22 +52019,22 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>SL-012</t>
+          <t>SL-018</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>PV-37 - PV-38</t>
+          <t>PV-69 - PV-70</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>PV-37</t>
+          <t>PV-69</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>PV-38</t>
+          <t>PV-70</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -52324,16 +52051,16 @@
         </is>
       </c>
       <c r="I437" t="n">
-        <v>16.89</v>
+        <v>20.55</v>
       </c>
       <c r="J437" t="n">
-        <v>3.75</v>
+        <v>1.93</v>
       </c>
       <c r="K437" t="n">
-        <v>3.92</v>
+        <v>1.41</v>
       </c>
       <c r="L437" t="n">
-        <v>3.92</v>
+        <v>1.93</v>
       </c>
       <c r="M437" t="inlineStr">
         <is>
@@ -52342,20 +52069,20 @@
       </c>
       <c r="N437" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. PV-38 incluido conforme novo print.</t>
+          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. Extensao lida no print.</t>
         </is>
       </c>
       <c r="O437" t="n">
-        <v>-23.5220801</v>
+        <v>-23.5224631</v>
       </c>
       <c r="P437" t="n">
-        <v>-46.379115</v>
+        <v>-46.3782535</v>
       </c>
       <c r="Q437" t="n">
-        <v>-23.5220422</v>
+        <v>-23.5224276</v>
       </c>
       <c r="R437" t="n">
-        <v>-46.3789548</v>
+        <v>-46.378053</v>
       </c>
     </row>
     <row r="438">
@@ -52366,22 +52093,22 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>SL-013</t>
+          <t>SL-019</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>PV-38 - PV-39</t>
+          <t>PV-64 - PV-65</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>PV-38</t>
+          <t>PV-64</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>PV-39</t>
+          <t>PV-65</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -52394,42 +52121,42 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>VCA</t>
         </is>
       </c>
       <c r="I438" t="n">
-        <v>46.47</v>
+        <v>39.5</v>
       </c>
       <c r="J438" t="n">
-        <v>3.92</v>
+        <v>2.84</v>
       </c>
       <c r="K438" t="n">
-        <v>3.64</v>
+        <v>1.6</v>
       </c>
       <c r="L438" t="n">
-        <v>3.92</v>
+        <v>2.84</v>
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>em andamento</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. PV-38 incluido conforme novo print.</t>
+          <t>Interligação corrigida PV-64 -&gt; PV-65 conforme projeto.</t>
         </is>
       </c>
       <c r="O438" t="n">
-        <v>-23.5220422</v>
+        <v>-23.522</v>
       </c>
       <c r="P438" t="n">
-        <v>-46.3789548</v>
+        <v>-46.378</v>
       </c>
       <c r="Q438" t="n">
-        <v>-23.5222906</v>
+        <v>-23.5224</v>
       </c>
       <c r="R438" t="n">
-        <v>-46.378588</v>
+        <v>-46.378</v>
       </c>
     </row>
     <row r="439">
@@ -52440,22 +52167,22 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>SL-014</t>
+          <t>SL-020</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>PV-40 - PV-41</t>
+          <t>PV-65 - PV-70</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>PV-40</t>
+          <t>PV-65</t>
         </is>
       </c>
       <c r="E439" t="inlineStr">
         <is>
-          <t>PV-41</t>
+          <t>PV-70</t>
         </is>
       </c>
       <c r="F439" t="inlineStr">
@@ -52468,42 +52195,42 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>VCA</t>
         </is>
       </c>
       <c r="I439" t="n">
-        <v>48.64</v>
+        <v>2.88</v>
       </c>
       <c r="J439" t="n">
-        <v>4.31</v>
+        <v>1.6</v>
       </c>
       <c r="K439" t="n">
-        <v>2.58</v>
+        <v>1.41</v>
       </c>
       <c r="L439" t="n">
-        <v>4.31</v>
+        <v>1.6</v>
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>em andamento</t>
+          <t>ATIVO</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
+          <t>Interligação corrigida PV-65 -&gt; PV-70 conforme projeto.</t>
         </is>
       </c>
       <c r="O439" t="n">
-        <v>-23.5224137</v>
+        <v>-23.5224</v>
       </c>
       <c r="P439" t="n">
-        <v>-46.3783767</v>
+        <v>-46.378</v>
       </c>
       <c r="Q439" t="n">
-        <v>-23.5227141</v>
+        <v>-23.5224</v>
       </c>
       <c r="R439" t="n">
-        <v>-46.378029</v>
+        <v>-46.378</v>
       </c>
     </row>
     <row r="440">
@@ -52514,22 +52241,22 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>SL-015</t>
+          <t>SL-021</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>PV-41 - PV-42</t>
+          <t>PVE-32 - PV-02</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>PV-41</t>
+          <t>PVE-32</t>
         </is>
       </c>
       <c r="E440" t="inlineStr">
         <is>
-          <t>PV-42</t>
+          <t>PV-02</t>
         </is>
       </c>
       <c r="F440" t="inlineStr">
@@ -52542,20 +52269,20 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Vala a Céu Aberto - VCA</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I440" t="n">
-        <v>38.45</v>
+        <v>12.61</v>
       </c>
       <c r="J440" t="n">
-        <v>2.58</v>
+        <v>2.05</v>
       </c>
       <c r="K440" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="L440" t="n">
-        <v>2.58</v>
+        <v>2.05</v>
       </c>
       <c r="M440" t="inlineStr">
         <is>
@@ -52564,20 +52291,20 @@
       </c>
       <c r="N440" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA; extensao calculada pela distancia entre coordenadas UTM.</t>
+          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
         </is>
       </c>
       <c r="O440" t="n">
-        <v>-23.5227141</v>
+        <v>-23.5199037</v>
       </c>
       <c r="P440" t="n">
-        <v>-46.378029</v>
+        <v>-46.3771453</v>
       </c>
       <c r="Q440" t="n">
-        <v>-23.52298</v>
+        <v>-23.5200098</v>
       </c>
       <c r="R440" t="n">
-        <v>-46.3777869</v>
+        <v>-46.3771007</v>
       </c>
     </row>
     <row r="441">
@@ -52588,22 +52315,22 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>SL-016</t>
+          <t>SL-022</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>PV-39 - PV-40</t>
+          <t>PV-02 - PV-03</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>PV-39</t>
+          <t>PV-02</t>
         </is>
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>PV-40</t>
+          <t>PV-03</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
@@ -52620,16 +52347,16 @@
         </is>
       </c>
       <c r="I441" t="n">
-        <v>24.53</v>
+        <v>21</v>
       </c>
       <c r="J441" t="n">
-        <v>3.64</v>
+        <v>1.48</v>
       </c>
       <c r="K441" t="n">
-        <v>4.31</v>
+        <v>2.04</v>
       </c>
       <c r="L441" t="n">
-        <v>4.31</v>
+        <v>2.04</v>
       </c>
       <c r="M441" t="inlineStr">
         <is>
@@ -52638,20 +52365,20 @@
       </c>
       <c r="N441" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. Extensao lida no print.</t>
+          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
         </is>
       </c>
       <c r="O441" t="n">
-        <v>-23.5222906</v>
+        <v>-23.5200098</v>
       </c>
       <c r="P441" t="n">
-        <v>-46.378588</v>
+        <v>-46.3771007</v>
       </c>
       <c r="Q441" t="n">
-        <v>-23.5224137</v>
+        <v>-23.5200681</v>
       </c>
       <c r="R441" t="n">
-        <v>-46.3783767</v>
+        <v>-46.376905</v>
       </c>
     </row>
     <row r="442">
@@ -52662,22 +52389,22 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>SL-017</t>
+          <t>SL-023</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>PV-40 - PV-69</t>
+          <t>PV-03 - PV-04</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>PV-40</t>
+          <t>PV-03</t>
         </is>
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>PV-69</t>
+          <t>PV-04</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
@@ -52694,16 +52421,16 @@
         </is>
       </c>
       <c r="I442" t="n">
-        <v>13.08</v>
+        <v>46.15</v>
       </c>
       <c r="J442" t="n">
-        <v>4.31</v>
+        <v>2.04</v>
       </c>
       <c r="K442" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="L442" t="n">
-        <v>4.31</v>
+        <v>2.04</v>
       </c>
       <c r="M442" t="inlineStr">
         <is>
@@ -52712,20 +52439,20 @@
       </c>
       <c r="N442" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. Extensao lida no print.</t>
+          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
         </is>
       </c>
       <c r="O442" t="n">
-        <v>-23.5224137</v>
+        <v>-23.5200681</v>
       </c>
       <c r="P442" t="n">
-        <v>-46.3783767</v>
+        <v>-46.376905</v>
       </c>
       <c r="Q442" t="n">
-        <v>-23.5224631</v>
+        <v>-23.5204836</v>
       </c>
       <c r="R442" t="n">
-        <v>-46.3782535</v>
+        <v>-46.3768696</v>
       </c>
     </row>
     <row r="443">
@@ -52736,22 +52463,22 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>SL-018</t>
+          <t>SL-024</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>PV-69 - PV-70</t>
+          <t>PV-04 - PV-05</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>PV-69</t>
+          <t>PV-04</t>
         </is>
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>PV-70</t>
+          <t>PV-05</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
@@ -52768,16 +52495,16 @@
         </is>
       </c>
       <c r="I443" t="n">
-        <v>20.55</v>
+        <v>38.98</v>
       </c>
       <c r="J443" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="K443" t="n">
-        <v>1.41</v>
+        <v>1.76</v>
       </c>
       <c r="L443" t="n">
-        <v>1.93</v>
+        <v>1.76</v>
       </c>
       <c r="M443" t="inlineStr">
         <is>
@@ -52786,20 +52513,20 @@
       </c>
       <c r="N443" t="inlineStr">
         <is>
-          <t>Adicionado via prints do projeto RCE Comunidade Sao Lucas; trecho em VCA. Extensao lida no print.</t>
+          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
         </is>
       </c>
       <c r="O443" t="n">
-        <v>-23.5224631</v>
+        <v>-23.5204836</v>
       </c>
       <c r="P443" t="n">
-        <v>-46.3782535</v>
+        <v>-46.3768696</v>
       </c>
       <c r="Q443" t="n">
-        <v>-23.5224276</v>
+        <v>-23.5208354</v>
       </c>
       <c r="R443" t="n">
-        <v>-46.378053</v>
+        <v>-46.3768848</v>
       </c>
     </row>
     <row r="444">
@@ -52810,22 +52537,22 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>SL-019</t>
+          <t>SL-025</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>PV-64 - PV-65</t>
+          <t>PV-05 - PV-06</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>PV-64</t>
+          <t>PV-05</t>
         </is>
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>PV-65</t>
+          <t>PV-06</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
@@ -52838,42 +52565,42 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>VCA</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I444" t="n">
-        <v>39.5</v>
+        <v>37.7</v>
       </c>
       <c r="J444" t="n">
-        <v>2.84</v>
+        <v>1.76</v>
       </c>
       <c r="K444" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="L444" t="n">
-        <v>2.84</v>
+        <v>1.85</v>
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>em andamento</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
         <is>
-          <t>Interligação corrigida PV-64 -&gt; PV-65 conforme projeto.</t>
+          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
         </is>
       </c>
       <c r="O444" t="n">
-        <v>-23.522</v>
+        <v>-23.5208354</v>
       </c>
       <c r="P444" t="n">
-        <v>-46.378</v>
+        <v>-46.3768848</v>
       </c>
       <c r="Q444" t="n">
-        <v>-23.5224</v>
+        <v>-23.5211749</v>
       </c>
       <c r="R444" t="n">
-        <v>-46.378</v>
+        <v>-46.3768575</v>
       </c>
     </row>
     <row r="445">
@@ -52884,22 +52611,22 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>SL-020</t>
+          <t>SL-026</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>PV-65 - PV-70</t>
+          <t>PV-06 - PV-07</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>PV-65</t>
+          <t>PV-06</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">
         <is>
-          <t>PV-70</t>
+          <t>PV-07</t>
         </is>
       </c>
       <c r="F445" t="inlineStr">
@@ -52912,42 +52639,42 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>VCA</t>
+          <t>Vala a Ceu Aberto - VCA</t>
         </is>
       </c>
       <c r="I445" t="n">
-        <v>2.88</v>
+        <v>34.53</v>
       </c>
       <c r="J445" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="K445" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="L445" t="n">
-        <v>1.6</v>
+        <v>1.85</v>
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>ATIVO</t>
+          <t>em andamento</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
         <is>
-          <t>Interligação corrigida PV-65 -&gt; PV-70 conforme projeto.</t>
+          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
         </is>
       </c>
       <c r="O445" t="n">
-        <v>-23.5224</v>
+        <v>-23.5211749</v>
       </c>
       <c r="P445" t="n">
-        <v>-46.378</v>
+        <v>-46.3768575</v>
       </c>
       <c r="Q445" t="n">
-        <v>-23.5224</v>
+        <v>-23.5214649</v>
       </c>
       <c r="R445" t="n">
-        <v>-46.378</v>
+        <v>-46.3767334</v>
       </c>
     </row>
     <row r="446">
@@ -52958,22 +52685,22 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>SL-021</t>
+          <t>SL-027</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>PVE-32 - PV-02</t>
+          <t>PV-07 - PV-08</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>PVE-32</t>
+          <t>PV-07</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
         <is>
-          <t>PV-02</t>
+          <t>PV-08</t>
         </is>
       </c>
       <c r="F446" t="inlineStr">
@@ -52990,16 +52717,16 @@
         </is>
       </c>
       <c r="I446" t="n">
-        <v>12.61</v>
+        <v>8.17</v>
       </c>
       <c r="J446" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="K446" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="L446" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="M446" t="inlineStr">
         <is>
@@ -53012,16 +52739,16 @@
         </is>
       </c>
       <c r="O446" t="n">
-        <v>-23.5199037</v>
+        <v>-23.5214649</v>
       </c>
       <c r="P446" t="n">
-        <v>-46.3771453</v>
+        <v>-46.3767334</v>
       </c>
       <c r="Q446" t="n">
-        <v>-23.5200098</v>
+        <v>-23.5215374</v>
       </c>
       <c r="R446" t="n">
-        <v>-46.3771007</v>
+        <v>-46.3767183</v>
       </c>
     </row>
     <row r="447">
@@ -53032,22 +52759,22 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>SL-022</t>
+          <t>SL-028</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>PV-02 - PV-03</t>
+          <t>PVE-31 - PV-37</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>PV-02</t>
+          <t>PVE-31</t>
         </is>
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>PV-03</t>
+          <t>PV-37</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
@@ -53064,16 +52791,16 @@
         </is>
       </c>
       <c r="I447" t="n">
-        <v>21</v>
+        <v>10.11</v>
       </c>
       <c r="J447" t="n">
-        <v>1.48</v>
+        <v>2.4</v>
       </c>
       <c r="K447" t="n">
-        <v>2.04</v>
+        <v>3.75</v>
       </c>
       <c r="L447" t="n">
-        <v>2.04</v>
+        <v>3.75</v>
       </c>
       <c r="M447" t="inlineStr">
         <is>
@@ -53082,20 +52809,8 @@
       </c>
       <c r="N447" t="inlineStr">
         <is>
-          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
-        </is>
-      </c>
-      <c r="O447" t="n">
-        <v>-23.5200098</v>
-      </c>
-      <c r="P447" t="n">
-        <v>-46.3771007</v>
-      </c>
-      <c r="Q447" t="n">
-        <v>-23.5200681</v>
-      </c>
-      <c r="R447" t="n">
-        <v>-46.376905</v>
+          <t>Interligacao adicionada conforme projeto.</t>
+        </is>
       </c>
     </row>
     <row r="448">
@@ -53106,22 +52821,22 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>SL-023</t>
+          <t>SL-029</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>PV-03 - PV-04</t>
+          <t>PV-75 - PV-76</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>PV-03</t>
+          <t>PV-75</t>
         </is>
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>PV-04</t>
+          <t>PV-76</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -53138,16 +52853,16 @@
         </is>
       </c>
       <c r="I448" t="n">
-        <v>46.15</v>
+        <v>2.09</v>
       </c>
       <c r="J448" t="n">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
       <c r="K448" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="L448" t="n">
-        <v>2.04</v>
+        <v>1.35</v>
       </c>
       <c r="M448" t="inlineStr">
         <is>
@@ -53156,20 +52871,8 @@
       </c>
       <c r="N448" t="inlineStr">
         <is>
-          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
-        </is>
-      </c>
-      <c r="O448" t="n">
-        <v>-23.5200681</v>
-      </c>
-      <c r="P448" t="n">
-        <v>-46.376905</v>
-      </c>
-      <c r="Q448" t="n">
-        <v>-23.5204836</v>
-      </c>
-      <c r="R448" t="n">
-        <v>-46.3768696</v>
+          <t>Interligação adicionada conforme projeto.</t>
+        </is>
       </c>
     </row>
     <row r="449">
@@ -53180,22 +52883,22 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>SL-024</t>
+          <t>SL-030</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>PV-04 - PV-05</t>
+          <t>PV-76 - PV-77</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>PV-04</t>
+          <t>PV-76</t>
         </is>
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>PV-05</t>
+          <t>PV-77</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -53212,16 +52915,16 @@
         </is>
       </c>
       <c r="I449" t="n">
-        <v>38.98</v>
+        <v>18.02</v>
       </c>
       <c r="J449" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="K449" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="L449" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="M449" t="inlineStr">
         <is>
@@ -53230,20 +52933,8 @@
       </c>
       <c r="N449" t="inlineStr">
         <is>
-          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
-        </is>
-      </c>
-      <c r="O449" t="n">
-        <v>-23.5204836</v>
-      </c>
-      <c r="P449" t="n">
-        <v>-46.3768696</v>
-      </c>
-      <c r="Q449" t="n">
-        <v>-23.5208354</v>
-      </c>
-      <c r="R449" t="n">
-        <v>-46.3768848</v>
+          <t>Interligação adicionada conforme projeto.</t>
+        </is>
       </c>
     </row>
     <row r="450">
@@ -53254,22 +52945,22 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>SL-025</t>
+          <t>SL-031</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>PV-05 - PV-06</t>
+          <t>PV-77 - PV-78</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>PV-05</t>
+          <t>PV-77</t>
         </is>
       </c>
       <c r="E450" t="inlineStr">
         <is>
-          <t>PV-06</t>
+          <t>PV-78</t>
         </is>
       </c>
       <c r="F450" t="inlineStr">
@@ -53286,16 +52977,16 @@
         </is>
       </c>
       <c r="I450" t="n">
-        <v>37.7</v>
+        <v>21.33</v>
       </c>
       <c r="J450" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="K450" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="L450" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="M450" t="inlineStr">
         <is>
@@ -53304,20 +52995,8 @@
       </c>
       <c r="N450" t="inlineStr">
         <is>
-          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
-        </is>
-      </c>
-      <c r="O450" t="n">
-        <v>-23.5208354</v>
-      </c>
-      <c r="P450" t="n">
-        <v>-46.3768848</v>
-      </c>
-      <c r="Q450" t="n">
-        <v>-23.5211749</v>
-      </c>
-      <c r="R450" t="n">
-        <v>-46.3768575</v>
+          <t>Interligação adicionada conforme projeto.</t>
+        </is>
       </c>
     </row>
     <row r="451">
@@ -53328,22 +53007,22 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>SL-026</t>
+          <t>SL-032</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>PV-06 - PV-07</t>
+          <t>PV-75.1 - PV-75</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>PV-06</t>
+          <t>PV-75.1</t>
         </is>
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>PV-07</t>
+          <t>PV-75</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
@@ -53360,16 +53039,13 @@
         </is>
       </c>
       <c r="I451" t="n">
-        <v>34.53</v>
-      </c>
-      <c r="J451" t="n">
-        <v>1.85</v>
+        <v>5</v>
       </c>
       <c r="K451" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="L451" t="n">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="M451" t="inlineStr">
         <is>
@@ -53378,72 +53054,72 @@
       </c>
       <c r="N451" t="inlineStr">
         <is>
-          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
+          <t>Interligacao PV-75.1 -&gt; PV-75 adicionada via Google Earth.</t>
         </is>
       </c>
       <c r="O451" t="n">
-        <v>-23.5211749</v>
+        <v>-23.5198222</v>
       </c>
       <c r="P451" t="n">
-        <v>-46.3768575</v>
+        <v>-46.3768722</v>
       </c>
       <c r="Q451" t="n">
-        <v>-23.5214649</v>
+        <v>-23.5198</v>
       </c>
       <c r="R451" t="n">
-        <v>-46.3767334</v>
+        <v>-46.3763</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>SL-027</t>
+          <t>JC-014</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>PV-07 - PV-08</t>
+          <t>PV-16 - PV-17</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>PV-07</t>
+          <t>PV-16</t>
         </is>
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>PV-08</t>
+          <t>PV-17</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD LISO</t>
         </is>
       </c>
       <c r="G452" t="n">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>Metodo Nao Destrutivo - MND</t>
         </is>
       </c>
       <c r="I452" t="n">
-        <v>8.17</v>
+        <v>64.572</v>
       </c>
       <c r="J452" t="n">
-        <v>1.44</v>
+        <v>3.1</v>
       </c>
       <c r="K452" t="n">
-        <v>1.41</v>
+        <v>3.1</v>
       </c>
       <c r="L452" t="n">
-        <v>1.44</v>
+        <v>5.48</v>
       </c>
       <c r="M452" t="inlineStr">
         <is>
@@ -53452,72 +53128,72 @@
       </c>
       <c r="N452" t="inlineStr">
         <is>
-          <t>Corrigido conforme sequencia informada: PVE-32 -&gt; PV-02 -&gt; PV-03 -&gt; PV-04 -&gt; PV-05 -&gt; PV-06 -&gt; PV-07 -&gt; PV-08; trecho em VCA.</t>
+          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-16 ao PV-17; arquivo: planos_furo/cts_joao_canzi_fl07_pv16_pv17.pdf; taxa 0,0707.</t>
         </is>
       </c>
       <c r="O452" t="n">
-        <v>-23.5214649</v>
+        <v>-23.5299843</v>
       </c>
       <c r="P452" t="n">
-        <v>-46.3767334</v>
+        <v>-46.3845231</v>
       </c>
       <c r="Q452" t="n">
-        <v>-23.5215374</v>
+        <v>-23.5300354</v>
       </c>
       <c r="R452" t="n">
-        <v>-46.3767183</v>
+        <v>-46.3838931</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>SL-028</t>
+          <t>JC-015</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>PVE-31 - PV-37</t>
+          <t>PV-17 - PV-18</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>PVE-31</t>
+          <t>PV-17</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>PV-37</t>
+          <t>PV-18</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD LISO</t>
         </is>
       </c>
       <c r="G453" t="n">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>Metodo Nao Destrutivo - MND</t>
         </is>
       </c>
       <c r="I453" t="n">
-        <v>10.11</v>
+        <v>79.57599999999999</v>
       </c>
       <c r="J453" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="K453" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="L453" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="M453" t="inlineStr">
         <is>
@@ -53526,60 +53202,72 @@
       </c>
       <c r="N453" t="inlineStr">
         <is>
-          <t>Interligacao adicionada conforme projeto.</t>
-        </is>
+          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-17 ao PV-18; arquivo: planos_furo/cts_joao_canzi_fl07_pv17_pv18.pdf; taxa 0,0116.</t>
+        </is>
+      </c>
+      <c r="O453" t="n">
+        <v>-23.5300354</v>
+      </c>
+      <c r="P453" t="n">
+        <v>-46.3838931</v>
+      </c>
+      <c r="Q453" t="n">
+        <v>-23.5300223</v>
+      </c>
+      <c r="R453" t="n">
+        <v>-46.3831139</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>cts_joao_canzi</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>SL-029</t>
+          <t>JC-016</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>PV-75 - PV-76</t>
+          <t>PV-19 - PV-20</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>PV-75</t>
+          <t>PV-19</t>
         </is>
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>PV-76</t>
+          <t>PV-20</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>PVC</t>
+          <t>PEAD LISO</t>
         </is>
       </c>
       <c r="G454" t="n">
-        <v>200</v>
+        <v>355</v>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Vala a Ceu Aberto - VCA</t>
+          <t>Metodo Nao Destrutivo - MND</t>
         </is>
       </c>
       <c r="I454" t="n">
-        <v>2.09</v>
+        <v>57.846</v>
       </c>
       <c r="J454" t="n">
-        <v>1.35</v>
+        <v>4</v>
       </c>
       <c r="K454" t="n">
-        <v>1.25</v>
+        <v>3.96</v>
       </c>
       <c r="L454" t="n">
-        <v>1.35</v>
+        <v>4</v>
       </c>
       <c r="M454" t="inlineStr">
         <is>
@@ -53588,428 +53276,30 @@
       </c>
       <c r="N454" t="inlineStr">
         <is>
-          <t>Interligação adicionada conforme projeto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="455">
-      <c r="A455" t="inlineStr">
-        <is>
-          <t>rce_comunidade_sao_lucas</t>
-        </is>
-      </c>
-      <c r="B455" t="inlineStr">
-        <is>
-          <t>SL-030</t>
-        </is>
-      </c>
-      <c r="C455" t="inlineStr">
-        <is>
-          <t>PV-76 - PV-77</t>
-        </is>
-      </c>
-      <c r="D455" t="inlineStr">
-        <is>
-          <t>PV-76</t>
-        </is>
-      </c>
-      <c r="E455" t="inlineStr">
-        <is>
-          <t>PV-77</t>
-        </is>
-      </c>
-      <c r="F455" t="inlineStr">
-        <is>
-          <t>PVC</t>
-        </is>
-      </c>
-      <c r="G455" t="n">
-        <v>200</v>
-      </c>
-      <c r="H455" t="inlineStr">
-        <is>
-          <t>Vala a Ceu Aberto - VCA</t>
-        </is>
-      </c>
-      <c r="I455" t="n">
-        <v>18.02</v>
-      </c>
-      <c r="J455" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="K455" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="L455" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M455" t="inlineStr">
-        <is>
-          <t>em andamento</t>
-        </is>
-      </c>
-      <c r="N455" t="inlineStr">
-        <is>
-          <t>Interligação adicionada conforme projeto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="456">
-      <c r="A456" t="inlineStr">
-        <is>
-          <t>rce_comunidade_sao_lucas</t>
-        </is>
-      </c>
-      <c r="B456" t="inlineStr">
-        <is>
-          <t>SL-031</t>
-        </is>
-      </c>
-      <c r="C456" t="inlineStr">
-        <is>
-          <t>PV-77 - PV-78</t>
-        </is>
-      </c>
-      <c r="D456" t="inlineStr">
-        <is>
-          <t>PV-77</t>
-        </is>
-      </c>
-      <c r="E456" t="inlineStr">
-        <is>
-          <t>PV-78</t>
-        </is>
-      </c>
-      <c r="F456" t="inlineStr">
-        <is>
-          <t>PVC</t>
-        </is>
-      </c>
-      <c r="G456" t="n">
-        <v>200</v>
-      </c>
-      <c r="H456" t="inlineStr">
-        <is>
-          <t>Vala a Ceu Aberto - VCA</t>
-        </is>
-      </c>
-      <c r="I456" t="n">
-        <v>21.33</v>
-      </c>
-      <c r="J456" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="K456" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="L456" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="M456" t="inlineStr">
-        <is>
-          <t>em andamento</t>
-        </is>
-      </c>
-      <c r="N456" t="inlineStr">
-        <is>
-          <t>Interligação adicionada conforme projeto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="457">
-      <c r="A457" t="inlineStr">
-        <is>
-          <t>rce_comunidade_sao_lucas</t>
-        </is>
-      </c>
-      <c r="B457" t="inlineStr">
-        <is>
-          <t>SL-032</t>
-        </is>
-      </c>
-      <c r="C457" t="inlineStr">
-        <is>
-          <t>PV-75.1 - PV-75</t>
-        </is>
-      </c>
-      <c r="D457" t="inlineStr">
-        <is>
-          <t>PV-75.1</t>
-        </is>
-      </c>
-      <c r="E457" t="inlineStr">
-        <is>
-          <t>PV-75</t>
-        </is>
-      </c>
-      <c r="F457" t="inlineStr">
-        <is>
-          <t>PVC</t>
-        </is>
-      </c>
-      <c r="G457" t="n">
-        <v>200</v>
-      </c>
-      <c r="H457" t="inlineStr">
-        <is>
-          <t>Vala a Ceu Aberto - VCA</t>
-        </is>
-      </c>
-      <c r="I457" t="n">
-        <v>5</v>
-      </c>
-      <c r="K457" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="L457" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="M457" t="inlineStr">
-        <is>
-          <t>em andamento</t>
-        </is>
-      </c>
-      <c r="N457" t="inlineStr">
-        <is>
-          <t>Interligacao PV-75.1 -&gt; PV-75 adicionada via Google Earth.</t>
-        </is>
-      </c>
-      <c r="O457" t="n">
-        <v>-23.5198222</v>
-      </c>
-      <c r="P457" t="n">
-        <v>-46.3768722</v>
-      </c>
-      <c r="Q457" t="n">
-        <v>-23.5198</v>
-      </c>
-      <c r="R457" t="n">
-        <v>-46.3763</v>
-      </c>
-    </row>
-    <row r="458">
-      <c r="A458" t="inlineStr">
-        <is>
-          <t>cts_joao_canzi</t>
-        </is>
-      </c>
-      <c r="B458" t="inlineStr">
-        <is>
-          <t>JC-014</t>
-        </is>
-      </c>
-      <c r="C458" t="inlineStr">
-        <is>
-          <t>PV-16 - PV-17</t>
-        </is>
-      </c>
-      <c r="D458" t="inlineStr">
-        <is>
-          <t>PV-16</t>
-        </is>
-      </c>
-      <c r="E458" t="inlineStr">
-        <is>
-          <t>PV-17</t>
-        </is>
-      </c>
-      <c r="F458" t="inlineStr">
-        <is>
-          <t>PEAD LISO</t>
-        </is>
-      </c>
-      <c r="G458" t="n">
-        <v>355</v>
-      </c>
-      <c r="H458" t="inlineStr">
-        <is>
-          <t>Metodo Nao Destrutivo - MND</t>
-        </is>
-      </c>
-      <c r="I458" t="n">
-        <v>64.572</v>
-      </c>
-      <c r="J458" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K458" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L458" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="M458" t="inlineStr">
-        <is>
-          <t>em andamento</t>
-        </is>
-      </c>
-      <c r="N458" t="inlineStr">
-        <is>
-          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-16 ao PV-17; arquivo: planos_furo/cts_joao_canzi_fl07_pv16_pv17.pdf; taxa 0,0707.</t>
-        </is>
-      </c>
-      <c r="O458" t="n">
-        <v>-23.5299843</v>
-      </c>
-      <c r="P458" t="n">
-        <v>-46.3845231</v>
-      </c>
-      <c r="Q458" t="n">
-        <v>-23.5300354</v>
-      </c>
-      <c r="R458" t="n">
-        <v>-46.3838931</v>
-      </c>
-    </row>
-    <row r="459">
-      <c r="A459" t="inlineStr">
-        <is>
-          <t>cts_joao_canzi</t>
-        </is>
-      </c>
-      <c r="B459" t="inlineStr">
-        <is>
-          <t>JC-015</t>
-        </is>
-      </c>
-      <c r="C459" t="inlineStr">
-        <is>
-          <t>PV-17 - PV-18</t>
-        </is>
-      </c>
-      <c r="D459" t="inlineStr">
-        <is>
-          <t>PV-17</t>
-        </is>
-      </c>
-      <c r="E459" t="inlineStr">
-        <is>
-          <t>PV-18</t>
-        </is>
-      </c>
-      <c r="F459" t="inlineStr">
-        <is>
-          <t>PEAD LISO</t>
-        </is>
-      </c>
-      <c r="G459" t="n">
-        <v>355</v>
-      </c>
-      <c r="H459" t="inlineStr">
-        <is>
-          <t>Metodo Nao Destrutivo - MND</t>
-        </is>
-      </c>
-      <c r="I459" t="n">
-        <v>79.57599999999999</v>
-      </c>
-      <c r="J459" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K459" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L459" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="M459" t="inlineStr">
-        <is>
-          <t>em andamento</t>
-        </is>
-      </c>
-      <c r="N459" t="inlineStr">
-        <is>
-          <t>Plano de furo FL-07 versao 01, 02.JUN.2026; PV-17 ao PV-18; arquivo: planos_furo/cts_joao_canzi_fl07_pv17_pv18.pdf; taxa 0,0116.</t>
-        </is>
-      </c>
-      <c r="O459" t="n">
-        <v>-23.5300354</v>
-      </c>
-      <c r="P459" t="n">
-        <v>-46.3838931</v>
-      </c>
-      <c r="Q459" t="n">
-        <v>-23.5300223</v>
-      </c>
-      <c r="R459" t="n">
-        <v>-46.3831139</v>
-      </c>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr">
-        <is>
-          <t>cts_joao_canzi</t>
-        </is>
-      </c>
-      <c r="B460" t="inlineStr">
-        <is>
-          <t>JC-016</t>
-        </is>
-      </c>
-      <c r="C460" t="inlineStr">
-        <is>
-          <t>PV-19 - PV-20</t>
-        </is>
-      </c>
-      <c r="D460" t="inlineStr">
-        <is>
-          <t>PV-19</t>
-        </is>
-      </c>
-      <c r="E460" t="inlineStr">
-        <is>
-          <t>PV-20</t>
-        </is>
-      </c>
-      <c r="F460" t="inlineStr">
-        <is>
-          <t>PEAD LISO</t>
-        </is>
-      </c>
-      <c r="G460" t="n">
-        <v>355</v>
-      </c>
-      <c r="H460" t="inlineStr">
-        <is>
-          <t>Metodo Nao Destrutivo - MND</t>
-        </is>
-      </c>
-      <c r="I460" t="n">
-        <v>57.846</v>
-      </c>
-      <c r="J460" t="n">
-        <v>4</v>
-      </c>
-      <c r="K460" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="L460" t="n">
-        <v>4</v>
-      </c>
-      <c r="M460" t="inlineStr">
-        <is>
-          <t>em andamento</t>
-        </is>
-      </c>
-      <c r="N460" t="inlineStr">
-        <is>
           <t>Plano de furo FL-07 versao 01, 05.JUN.2026; PV-19 ao PV-20; arquivo: planos_furo/cts_joao_canzi_fl07_pv19_pv20.pdf; taxa 0,1224.</t>
         </is>
       </c>
-      <c r="O460" t="n">
+      <c r="O454" t="n">
         <v>-23.529877</v>
       </c>
-      <c r="P460" t="n">
+      <c r="P454" t="n">
         <v>-46.3824799</v>
       </c>
-      <c r="Q460" t="n">
+      <c r="Q454" t="n">
         <v>-23.5295804</v>
       </c>
-      <c r="R460" t="n">
+      <c r="R454" t="n">
         <v>-46.3820136</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R445">
+    <filterColumn colId="0" hiddenButton="0" showButton="1">
+      <filters>
+        <filter val="rce_comunidade_sao_lucas"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -54021,7 +53311,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -54140,7 +53430,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -54877,7 +54167,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="5"/>
   </cols>
@@ -54985,7 +54275,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -55241,7 +54531,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -1197,7 +1197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L441"/>
+  <dimension ref="A1:L447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -21205,6 +21205,294 @@
       <c r="L441" t="inlineStr">
         <is>
           <t>Plano de furo FL-07 versao 01, 05.JUN.2026; trecho PV-19 ao PV-20.</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>ELIAS-PV-24</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>PV-24</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>7397047.32</v>
+      </c>
+      <c r="F442" t="n">
+        <v>358826.273</v>
+      </c>
+      <c r="G442" t="n">
+        <v>-23.5307209</v>
+      </c>
+      <c r="H442" t="n">
+        <v>-46.3829268</v>
+      </c>
+      <c r="I442" t="n">
+        <v>795.659</v>
+      </c>
+      <c r="J442" t="n">
+        <v>793.298</v>
+      </c>
+      <c r="K442" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="L442" t="inlineStr">
+        <is>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>ELIAS-PV-25</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>PV-25</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>7397044.193</v>
+      </c>
+      <c r="F443" t="n">
+        <v>358909.128</v>
+      </c>
+      <c r="G443" t="n">
+        <v>-23.5307563</v>
+      </c>
+      <c r="H443" t="n">
+        <v>-46.3821157</v>
+      </c>
+      <c r="I443" t="n">
+        <v>798.554</v>
+      </c>
+      <c r="J443" t="n">
+        <v>795.832</v>
+      </c>
+      <c r="K443" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L443" t="inlineStr">
+        <is>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>ELIAS-PV-26</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>PV-26</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>7397000.312</v>
+      </c>
+      <c r="F444" t="n">
+        <v>358903.103</v>
+      </c>
+      <c r="G444" t="n">
+        <v>-23.5311521</v>
+      </c>
+      <c r="H444" t="n">
+        <v>-46.3821788</v>
+      </c>
+      <c r="I444" t="n">
+        <v>803.849</v>
+      </c>
+      <c r="J444" t="n">
+        <v>801.227</v>
+      </c>
+      <c r="K444" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L444" t="inlineStr">
+        <is>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>ELIAS-PV-27</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>PV-27</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>7396952.046</v>
+      </c>
+      <c r="F445" t="n">
+        <v>358919.472</v>
+      </c>
+      <c r="G445" t="n">
+        <v>-23.5315893</v>
+      </c>
+      <c r="H445" t="n">
+        <v>-46.3820231</v>
+      </c>
+      <c r="I445" t="n">
+        <v>810.896</v>
+      </c>
+      <c r="J445" t="n">
+        <v>808.804</v>
+      </c>
+      <c r="K445" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L445" t="inlineStr">
+        <is>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>ELIAS-PV-28</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>PV-28</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>7396913.479</v>
+      </c>
+      <c r="F446" t="n">
+        <v>358940.543</v>
+      </c>
+      <c r="G446" t="n">
+        <v>-23.5319394</v>
+      </c>
+      <c r="H446" t="n">
+        <v>-46.3818203</v>
+      </c>
+      <c r="I446" t="n">
+        <v>813.813</v>
+      </c>
+      <c r="J446" t="n">
+        <v>811.614</v>
+      </c>
+      <c r="K446" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L446" t="inlineStr">
+        <is>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>ELIAS-PV-29</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>PV-29</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>7396888.957</v>
+      </c>
+      <c r="F447" t="n">
+        <v>358954.374</v>
+      </c>
+      <c r="G447" t="n">
+        <v>-23.5321621</v>
+      </c>
+      <c r="H447" t="n">
+        <v>-46.3816872</v>
+      </c>
+      <c r="I447" t="n">
+        <v>815.335</v>
+      </c>
+      <c r="J447" t="n">
+        <v>813.135</v>
+      </c>
+      <c r="K447" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L447" t="inlineStr">
+        <is>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
         </is>
       </c>
     </row>
@@ -21219,7 +21507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R454"/>
+  <dimension ref="A1:R460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -53290,6 +53578,450 @@
       </c>
       <c r="R454" t="n">
         <v>-46.3820136</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>ELIAS-003</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>PV-23 - PV-24</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>PV-23</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>PV-24</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G455" t="n">
+        <v>200</v>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I455" t="n">
+        <v>44.64</v>
+      </c>
+      <c r="J455" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K455" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="L455" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="M455" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N455" t="inlineStr">
+        <is>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+        </is>
+      </c>
+      <c r="O455" t="n">
+        <v>-23.5309793</v>
+      </c>
+      <c r="P455" t="n">
+        <v>-46.3832624</v>
+      </c>
+      <c r="Q455" t="n">
+        <v>-23.5307209</v>
+      </c>
+      <c r="R455" t="n">
+        <v>-46.3829268</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>ELIAS-004</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>PV-24 - PV-25</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>PV-24</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>PV-25</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G456" t="n">
+        <v>200</v>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I456" t="n">
+        <v>82.91</v>
+      </c>
+      <c r="J456" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K456" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="L456" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M456" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N456" t="inlineStr">
+        <is>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+        </is>
+      </c>
+      <c r="O456" t="n">
+        <v>-23.5307209</v>
+      </c>
+      <c r="P456" t="n">
+        <v>-46.3829268</v>
+      </c>
+      <c r="Q456" t="n">
+        <v>-23.5307563</v>
+      </c>
+      <c r="R456" t="n">
+        <v>-46.3821157</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>ELIAS-005</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>PV-25 - PV-26</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>PV-25</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>PV-26</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G457" t="n">
+        <v>200</v>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I457" t="n">
+        <v>44.29</v>
+      </c>
+      <c r="J457" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K457" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="L457" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M457" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N457" t="inlineStr">
+        <is>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+        </is>
+      </c>
+      <c r="O457" t="n">
+        <v>-23.5307563</v>
+      </c>
+      <c r="P457" t="n">
+        <v>-46.3821157</v>
+      </c>
+      <c r="Q457" t="n">
+        <v>-23.5311521</v>
+      </c>
+      <c r="R457" t="n">
+        <v>-46.3821788</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>ELIAS-006</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>PV-26 - PV-27</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>PV-26</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>PV-27</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G458" t="n">
+        <v>200</v>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I458" t="n">
+        <v>50.97</v>
+      </c>
+      <c r="J458" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K458" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L458" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="M458" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N458" t="inlineStr">
+        <is>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+        </is>
+      </c>
+      <c r="O458" t="n">
+        <v>-23.5311521</v>
+      </c>
+      <c r="P458" t="n">
+        <v>-46.3821788</v>
+      </c>
+      <c r="Q458" t="n">
+        <v>-23.5315893</v>
+      </c>
+      <c r="R458" t="n">
+        <v>-46.3820231</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>ELIAS-007</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>PV-27 - PV-28</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>PV-27</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>PV-28</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G459" t="n">
+        <v>200</v>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I459" t="n">
+        <v>43.95</v>
+      </c>
+      <c r="J459" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="K459" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L459" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M459" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N459" t="inlineStr">
+        <is>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+        </is>
+      </c>
+      <c r="O459" t="n">
+        <v>-23.5315893</v>
+      </c>
+      <c r="P459" t="n">
+        <v>-46.3820231</v>
+      </c>
+      <c r="Q459" t="n">
+        <v>-23.5319394</v>
+      </c>
+      <c r="R459" t="n">
+        <v>-46.3818203</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>ELIAS-008</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>PV-28 - PV-29</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>PV-28</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>PV-29</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G460" t="n">
+        <v>200</v>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I460" t="n">
+        <v>28.15</v>
+      </c>
+      <c r="J460" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K460" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L460" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M460" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N460" t="inlineStr">
+        <is>
+          <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+        </is>
+      </c>
+      <c r="O460" t="n">
+        <v>-23.5319394</v>
+      </c>
+      <c r="P460" t="n">
+        <v>-46.3818203</v>
+      </c>
+      <c r="Q460" t="n">
+        <v>-23.5321621</v>
+      </c>
+      <c r="R460" t="n">
+        <v>-46.3816872</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="31.109375" customWidth="1" min="1" max="1"/>
@@ -1181,6 +1181,33 @@
         </is>
       </c>
       <c r="E26" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>RCE Maria dos Santos Machado</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>RCE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1197,7 +1224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L447"/>
+  <dimension ref="A1:L452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -21493,6 +21520,201 @@
       <c r="L447" t="inlineStr">
         <is>
           <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>PVP</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>MSM-PVP-09</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>PVP-09</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>7391178.44</v>
+      </c>
+      <c r="F448" t="n">
+        <v>338156.44</v>
+      </c>
+      <c r="G448" t="n">
+        <v>-23.5817824</v>
+      </c>
+      <c r="H448" t="n">
+        <v>-46.5859865</v>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>MSM-PI-1</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>PI-1</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>7391179.4</v>
+      </c>
+      <c r="F449" t="n">
+        <v>338179.5</v>
+      </c>
+      <c r="G449" t="n">
+        <v>-23.581776</v>
+      </c>
+      <c r="H449" t="n">
+        <v>-46.5857605</v>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>MSM-PI-2</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>PI-2</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>7391227.64</v>
+      </c>
+      <c r="F450" t="n">
+        <v>338227.56</v>
+      </c>
+      <c r="G450" t="n">
+        <v>-23.5813453</v>
+      </c>
+      <c r="H450" t="n">
+        <v>-46.5852845</v>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>MSM-PI-3</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>PI-3</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>7391286.79</v>
+      </c>
+      <c r="F451" t="n">
+        <v>338260.79</v>
+      </c>
+      <c r="G451" t="n">
+        <v>-23.5808145</v>
+      </c>
+      <c r="H451" t="n">
+        <v>-46.5849525</v>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>MSM-PI-4</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>PI-4</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>7391325.91</v>
+      </c>
+      <c r="F452" t="n">
+        <v>338287.591</v>
+      </c>
+      <c r="G452" t="n">
+        <v>-23.580464</v>
+      </c>
+      <c r="H452" t="n">
+        <v>-46.5846857</v>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
         </is>
       </c>
     </row>
@@ -21507,7 +21729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R460"/>
+  <dimension ref="A1:R464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -54022,6 +54244,266 @@
       </c>
       <c r="R460" t="n">
         <v>-46.3816872</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>MSM-001</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>PVP-09 - PI-1</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>PVP-09</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>PI-1</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G461" t="n">
+        <v>200</v>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I461" t="n">
+        <v>20</v>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
+        </is>
+      </c>
+      <c r="O461" t="n">
+        <v>-23.5817824</v>
+      </c>
+      <c r="P461" t="n">
+        <v>-46.5859865</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>-23.581776</v>
+      </c>
+      <c r="R461" t="n">
+        <v>-46.5857605</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>MSM-002</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>PI-1 - PI-2</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>PI-1</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>PI-2</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G462" t="n">
+        <v>200</v>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I462" t="n">
+        <v>66</v>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
+        </is>
+      </c>
+      <c r="O462" t="n">
+        <v>-23.581776</v>
+      </c>
+      <c r="P462" t="n">
+        <v>-46.5857605</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>-23.5813453</v>
+      </c>
+      <c r="R462" t="n">
+        <v>-46.5852845</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>MSM-003</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>PI-2 - PI-3</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>PI-2</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>PI-3</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G463" t="n">
+        <v>200</v>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I463" t="n">
+        <v>62</v>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
+        </is>
+      </c>
+      <c r="O463" t="n">
+        <v>-23.5813453</v>
+      </c>
+      <c r="P463" t="n">
+        <v>-46.5852845</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>-23.5808145</v>
+      </c>
+      <c r="R463" t="n">
+        <v>-46.5849525</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>MSM-004</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>PI-3 - PI-4</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>PI-3</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>PI-4</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G464" t="n">
+        <v>200</v>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I464" t="n">
+        <v>41</v>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
+        </is>
+      </c>
+      <c r="O464" t="n">
+        <v>-23.5808145</v>
+      </c>
+      <c r="P464" t="n">
+        <v>-46.5849525</v>
+      </c>
+      <c r="Q464" t="n">
+        <v>-23.580464</v>
+      </c>
+      <c r="R464" t="n">
+        <v>-46.5846857</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="31.109375" customWidth="1" min="1" max="1"/>
@@ -1181,33 +1181,6 @@
         </is>
       </c>
       <c r="E26" t="inlineStr">
-        <is>
-          <t>SIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>rce_maria_dos_santos_machado</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>RCE Maria dos Santos Machado</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>RCE</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1224,7 +1197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L452"/>
+  <dimension ref="A1:L447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -21520,201 +21493,6 @@
       <c r="L447" t="inlineStr">
         <is>
           <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="448">
-      <c r="A448" t="inlineStr">
-        <is>
-          <t>rce_maria_dos_santos_machado</t>
-        </is>
-      </c>
-      <c r="B448" t="inlineStr">
-        <is>
-          <t>PVP</t>
-        </is>
-      </c>
-      <c r="C448" t="inlineStr">
-        <is>
-          <t>MSM-PVP-09</t>
-        </is>
-      </c>
-      <c r="D448" t="inlineStr">
-        <is>
-          <t>PVP-09</t>
-        </is>
-      </c>
-      <c r="E448" t="n">
-        <v>7391178.44</v>
-      </c>
-      <c r="F448" t="n">
-        <v>338156.44</v>
-      </c>
-      <c r="G448" t="n">
-        <v>-23.5817824</v>
-      </c>
-      <c r="H448" t="n">
-        <v>-46.5859865</v>
-      </c>
-      <c r="L448" t="inlineStr">
-        <is>
-          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="449">
-      <c r="A449" t="inlineStr">
-        <is>
-          <t>rce_maria_dos_santos_machado</t>
-        </is>
-      </c>
-      <c r="B449" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="C449" t="inlineStr">
-        <is>
-          <t>MSM-PI-1</t>
-        </is>
-      </c>
-      <c r="D449" t="inlineStr">
-        <is>
-          <t>PI-1</t>
-        </is>
-      </c>
-      <c r="E449" t="n">
-        <v>7391179.4</v>
-      </c>
-      <c r="F449" t="n">
-        <v>338179.5</v>
-      </c>
-      <c r="G449" t="n">
-        <v>-23.581776</v>
-      </c>
-      <c r="H449" t="n">
-        <v>-46.5857605</v>
-      </c>
-      <c r="L449" t="inlineStr">
-        <is>
-          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="450">
-      <c r="A450" t="inlineStr">
-        <is>
-          <t>rce_maria_dos_santos_machado</t>
-        </is>
-      </c>
-      <c r="B450" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="C450" t="inlineStr">
-        <is>
-          <t>MSM-PI-2</t>
-        </is>
-      </c>
-      <c r="D450" t="inlineStr">
-        <is>
-          <t>PI-2</t>
-        </is>
-      </c>
-      <c r="E450" t="n">
-        <v>7391227.64</v>
-      </c>
-      <c r="F450" t="n">
-        <v>338227.56</v>
-      </c>
-      <c r="G450" t="n">
-        <v>-23.5813453</v>
-      </c>
-      <c r="H450" t="n">
-        <v>-46.5852845</v>
-      </c>
-      <c r="L450" t="inlineStr">
-        <is>
-          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="451">
-      <c r="A451" t="inlineStr">
-        <is>
-          <t>rce_maria_dos_santos_machado</t>
-        </is>
-      </c>
-      <c r="B451" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="C451" t="inlineStr">
-        <is>
-          <t>MSM-PI-3</t>
-        </is>
-      </c>
-      <c r="D451" t="inlineStr">
-        <is>
-          <t>PI-3</t>
-        </is>
-      </c>
-      <c r="E451" t="n">
-        <v>7391286.79</v>
-      </c>
-      <c r="F451" t="n">
-        <v>338260.79</v>
-      </c>
-      <c r="G451" t="n">
-        <v>-23.5808145</v>
-      </c>
-      <c r="H451" t="n">
-        <v>-46.5849525</v>
-      </c>
-      <c r="L451" t="inlineStr">
-        <is>
-          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="452">
-      <c r="A452" t="inlineStr">
-        <is>
-          <t>rce_maria_dos_santos_machado</t>
-        </is>
-      </c>
-      <c r="B452" t="inlineStr">
-        <is>
-          <t>PI</t>
-        </is>
-      </c>
-      <c r="C452" t="inlineStr">
-        <is>
-          <t>MSM-PI-4</t>
-        </is>
-      </c>
-      <c r="D452" t="inlineStr">
-        <is>
-          <t>PI-4</t>
-        </is>
-      </c>
-      <c r="E452" t="n">
-        <v>7391325.91</v>
-      </c>
-      <c r="F452" t="n">
-        <v>338287.591</v>
-      </c>
-      <c r="G452" t="n">
-        <v>-23.580464</v>
-      </c>
-      <c r="H452" t="n">
-        <v>-46.5846857</v>
-      </c>
-      <c r="L452" t="inlineStr">
-        <is>
-          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
         </is>
       </c>
     </row>
@@ -21729,7 +21507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R464"/>
+  <dimension ref="A1:R460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -54244,266 +54022,6 @@
       </c>
       <c r="R460" t="n">
         <v>-46.3816872</v>
-      </c>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr">
-        <is>
-          <t>rce_maria_dos_santos_machado</t>
-        </is>
-      </c>
-      <c r="B461" t="inlineStr">
-        <is>
-          <t>MSM-001</t>
-        </is>
-      </c>
-      <c r="C461" t="inlineStr">
-        <is>
-          <t>PVP-09 - PI-1</t>
-        </is>
-      </c>
-      <c r="D461" t="inlineStr">
-        <is>
-          <t>PVP-09</t>
-        </is>
-      </c>
-      <c r="E461" t="inlineStr">
-        <is>
-          <t>PI-1</t>
-        </is>
-      </c>
-      <c r="F461" t="inlineStr">
-        <is>
-          <t>PVC</t>
-        </is>
-      </c>
-      <c r="G461" t="n">
-        <v>200</v>
-      </c>
-      <c r="H461" t="inlineStr">
-        <is>
-          <t>Vala a Ceu Aberto - VCA</t>
-        </is>
-      </c>
-      <c r="I461" t="n">
-        <v>20</v>
-      </c>
-      <c r="M461" t="inlineStr">
-        <is>
-          <t>em andamento</t>
-        </is>
-      </c>
-      <c r="N461" t="inlineStr">
-        <is>
-          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
-        </is>
-      </c>
-      <c r="O461" t="n">
-        <v>-23.5817824</v>
-      </c>
-      <c r="P461" t="n">
-        <v>-46.5859865</v>
-      </c>
-      <c r="Q461" t="n">
-        <v>-23.581776</v>
-      </c>
-      <c r="R461" t="n">
-        <v>-46.5857605</v>
-      </c>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr">
-        <is>
-          <t>rce_maria_dos_santos_machado</t>
-        </is>
-      </c>
-      <c r="B462" t="inlineStr">
-        <is>
-          <t>MSM-002</t>
-        </is>
-      </c>
-      <c r="C462" t="inlineStr">
-        <is>
-          <t>PI-1 - PI-2</t>
-        </is>
-      </c>
-      <c r="D462" t="inlineStr">
-        <is>
-          <t>PI-1</t>
-        </is>
-      </c>
-      <c r="E462" t="inlineStr">
-        <is>
-          <t>PI-2</t>
-        </is>
-      </c>
-      <c r="F462" t="inlineStr">
-        <is>
-          <t>PVC</t>
-        </is>
-      </c>
-      <c r="G462" t="n">
-        <v>200</v>
-      </c>
-      <c r="H462" t="inlineStr">
-        <is>
-          <t>Vala a Ceu Aberto - VCA</t>
-        </is>
-      </c>
-      <c r="I462" t="n">
-        <v>66</v>
-      </c>
-      <c r="M462" t="inlineStr">
-        <is>
-          <t>em andamento</t>
-        </is>
-      </c>
-      <c r="N462" t="inlineStr">
-        <is>
-          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
-        </is>
-      </c>
-      <c r="O462" t="n">
-        <v>-23.581776</v>
-      </c>
-      <c r="P462" t="n">
-        <v>-46.5857605</v>
-      </c>
-      <c r="Q462" t="n">
-        <v>-23.5813453</v>
-      </c>
-      <c r="R462" t="n">
-        <v>-46.5852845</v>
-      </c>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr">
-        <is>
-          <t>rce_maria_dos_santos_machado</t>
-        </is>
-      </c>
-      <c r="B463" t="inlineStr">
-        <is>
-          <t>MSM-003</t>
-        </is>
-      </c>
-      <c r="C463" t="inlineStr">
-        <is>
-          <t>PI-2 - PI-3</t>
-        </is>
-      </c>
-      <c r="D463" t="inlineStr">
-        <is>
-          <t>PI-2</t>
-        </is>
-      </c>
-      <c r="E463" t="inlineStr">
-        <is>
-          <t>PI-3</t>
-        </is>
-      </c>
-      <c r="F463" t="inlineStr">
-        <is>
-          <t>PVC</t>
-        </is>
-      </c>
-      <c r="G463" t="n">
-        <v>200</v>
-      </c>
-      <c r="H463" t="inlineStr">
-        <is>
-          <t>Vala a Ceu Aberto - VCA</t>
-        </is>
-      </c>
-      <c r="I463" t="n">
-        <v>62</v>
-      </c>
-      <c r="M463" t="inlineStr">
-        <is>
-          <t>em andamento</t>
-        </is>
-      </c>
-      <c r="N463" t="inlineStr">
-        <is>
-          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
-        </is>
-      </c>
-      <c r="O463" t="n">
-        <v>-23.5813453</v>
-      </c>
-      <c r="P463" t="n">
-        <v>-46.5852845</v>
-      </c>
-      <c r="Q463" t="n">
-        <v>-23.5808145</v>
-      </c>
-      <c r="R463" t="n">
-        <v>-46.5849525</v>
-      </c>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr">
-        <is>
-          <t>rce_maria_dos_santos_machado</t>
-        </is>
-      </c>
-      <c r="B464" t="inlineStr">
-        <is>
-          <t>MSM-004</t>
-        </is>
-      </c>
-      <c r="C464" t="inlineStr">
-        <is>
-          <t>PI-3 - PI-4</t>
-        </is>
-      </c>
-      <c r="D464" t="inlineStr">
-        <is>
-          <t>PI-3</t>
-        </is>
-      </c>
-      <c r="E464" t="inlineStr">
-        <is>
-          <t>PI-4</t>
-        </is>
-      </c>
-      <c r="F464" t="inlineStr">
-        <is>
-          <t>PVC</t>
-        </is>
-      </c>
-      <c r="G464" t="n">
-        <v>200</v>
-      </c>
-      <c r="H464" t="inlineStr">
-        <is>
-          <t>Vala a Ceu Aberto - VCA</t>
-        </is>
-      </c>
-      <c r="I464" t="n">
-        <v>41</v>
-      </c>
-      <c r="M464" t="inlineStr">
-        <is>
-          <t>em andamento</t>
-        </is>
-      </c>
-      <c r="N464" t="inlineStr">
-        <is>
-          <t>Adicionado via prints enviados em 17/07/2026; coordenadas SIRGAS 2000 / UTM zona 23S convertidas para latitude/longitude; trechos em VCA.</t>
-        </is>
-      </c>
-      <c r="O464" t="n">
-        <v>-23.5808145</v>
-      </c>
-      <c r="P464" t="n">
-        <v>-46.5849525</v>
-      </c>
-      <c r="Q464" t="n">
-        <v>-23.580464</v>
-      </c>
-      <c r="R464" t="n">
-        <v>-46.5846857</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="31.109375" customWidth="1" min="1" max="1"/>
@@ -1181,6 +1181,33 @@
         </is>
       </c>
       <c r="E26" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>RCE Maria dos Santos Machado</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>RCE</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Adicionado via coordenada PI-4 enviada em 17/07/2026; ligação no PV-16 do CTS João Canzi; PIs intermediários distribuídos por distância informada.</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1197,7 +1224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L447"/>
+  <dimension ref="A1:L452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -21493,6 +21520,186 @@
       <c r="L447" t="inlineStr">
         <is>
           <t>Adicionado via prints do projeto RCE Elias Sleiman recebidos em 22/06/2026; lancamento completo em VCA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>MSM-PV-16</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>PV-16</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>7397127.313</v>
+      </c>
+      <c r="F448" t="n">
+        <v>358662.509</v>
+      </c>
+      <c r="G448" t="n">
+        <v>-23.5299843</v>
+      </c>
+      <c r="H448" t="n">
+        <v>-46.3845231</v>
+      </c>
+      <c r="I448" t="n">
+        <v>777.73</v>
+      </c>
+      <c r="J448" t="n">
+        <v>774.633</v>
+      </c>
+      <c r="K448" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L448" t="inlineStr">
+        <is>
+          <t>Ponto de ligação no CTS João Canzi. Adicionado via coordenada PI-4 enviada em 17/07/2026; ligação no PV-16 do CTS João Canzi; PIs intermediários distribuídos por distância informada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>MSM-PI-1</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>PI-1</t>
+        </is>
+      </c>
+      <c r="G449" t="n">
+        <v>-23.5298809</v>
+      </c>
+      <c r="H449" t="n">
+        <v>-46.3845564</v>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>Adicionado via coordenada PI-4 enviada em 17/07/2026; ligação no PV-16 do CTS João Canzi; PIs intermediários distribuídos por distância informada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>MSM-PI-2</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>PI-2</t>
+        </is>
+      </c>
+      <c r="G450" t="n">
+        <v>-23.529364</v>
+      </c>
+      <c r="H450" t="n">
+        <v>-46.3847229</v>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>Adicionado via coordenada PI-4 enviada em 17/07/2026; ligação no PV-16 do CTS João Canzi; PIs intermediários distribuídos por distância informada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>MSM-PI-3</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>PI-3</t>
+        </is>
+      </c>
+      <c r="G451" t="n">
+        <v>-23.5287954</v>
+      </c>
+      <c r="H451" t="n">
+        <v>-46.384906</v>
+      </c>
+      <c r="L451" t="inlineStr">
+        <is>
+          <t>Adicionado via coordenada PI-4 enviada em 17/07/2026; ligação no PV-16 do CTS João Canzi; PIs intermediários distribuídos por distância informada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>MSM-PI-4</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>PI-4</t>
+        </is>
+      </c>
+      <c r="G452" t="n">
+        <v>-23.5281583</v>
+      </c>
+      <c r="H452" t="n">
+        <v>-46.3851111</v>
+      </c>
+      <c r="L452" t="inlineStr">
+        <is>
+          <t>Adicionado via coordenada PI-4 enviada em 17/07/2026; ligação no PV-16 do CTS João Canzi; PIs intermediários distribuídos por distância informada.</t>
         </is>
       </c>
     </row>
@@ -21507,7 +21714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R460"/>
+  <dimension ref="A1:R464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -54022,6 +54229,266 @@
       </c>
       <c r="R460" t="n">
         <v>-46.3816872</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>MSM-001</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>PV-16 - PI-1</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>PV-16</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>PI-1</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G461" t="n">
+        <v>200</v>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I461" t="n">
+        <v>12</v>
+      </c>
+      <c r="M461" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N461" t="inlineStr">
+        <is>
+          <t>Adicionado via coordenada PI-4 enviada em 17/07/2026; ligação no PV-16 do CTS João Canzi; PIs intermediários distribuídos por distância informada.</t>
+        </is>
+      </c>
+      <c r="O461" t="n">
+        <v>-23.5299843</v>
+      </c>
+      <c r="P461" t="n">
+        <v>-46.3845231</v>
+      </c>
+      <c r="Q461" t="n">
+        <v>-23.5298809</v>
+      </c>
+      <c r="R461" t="n">
+        <v>-46.3845564</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>MSM-002</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>PI-1 - PI-2</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>PI-1</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>PI-2</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G462" t="n">
+        <v>200</v>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I462" t="n">
+        <v>60</v>
+      </c>
+      <c r="M462" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N462" t="inlineStr">
+        <is>
+          <t>Adicionado via coordenada PI-4 enviada em 17/07/2026; ligação no PV-16 do CTS João Canzi; PIs intermediários distribuídos por distância informada.</t>
+        </is>
+      </c>
+      <c r="O462" t="n">
+        <v>-23.5298809</v>
+      </c>
+      <c r="P462" t="n">
+        <v>-46.3845564</v>
+      </c>
+      <c r="Q462" t="n">
+        <v>-23.529364</v>
+      </c>
+      <c r="R462" t="n">
+        <v>-46.3847229</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>MSM-003</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>PI-2 - PI-3</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>PI-2</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>PI-3</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G463" t="n">
+        <v>200</v>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I463" t="n">
+        <v>66</v>
+      </c>
+      <c r="M463" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N463" t="inlineStr">
+        <is>
+          <t>Adicionado via coordenada PI-4 enviada em 17/07/2026; ligação no PV-16 do CTS João Canzi; PIs intermediários distribuídos por distância informada.</t>
+        </is>
+      </c>
+      <c r="O463" t="n">
+        <v>-23.529364</v>
+      </c>
+      <c r="P463" t="n">
+        <v>-46.3847229</v>
+      </c>
+      <c r="Q463" t="n">
+        <v>-23.5287954</v>
+      </c>
+      <c r="R463" t="n">
+        <v>-46.384906</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>rce_maria_dos_santos_machado</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>MSM-004</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>PI-3 - PI-4</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>PI-3</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>PI-4</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G464" t="n">
+        <v>200</v>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I464" t="n">
+        <v>73.94</v>
+      </c>
+      <c r="M464" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N464" t="inlineStr">
+        <is>
+          <t>Adicionado via coordenada PI-4 enviada em 17/07/2026; ligação no PV-16 do CTS João Canzi; PIs intermediários distribuídos por distância informada.</t>
+        </is>
+      </c>
+      <c r="O464" t="n">
+        <v>-23.5287954</v>
+      </c>
+      <c r="P464" t="n">
+        <v>-46.384906</v>
+      </c>
+      <c r="Q464" t="n">
+        <v>-23.5281583</v>
+      </c>
+      <c r="R464" t="n">
+        <v>-46.3851111</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -1224,7 +1224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L452"/>
+  <dimension ref="A1:L453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -21700,6 +21700,54 @@
       <c r="L452" t="inlineStr">
         <is>
           <t>Adicionado via coordenada PI-4 enviada em 17/07/2026; ligação no PV-16 do CTS João Canzi; PIs intermediários distribuídos por distância informada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>ELIAS-PV-17-LIG-JC</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>PV-17</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>7397122.275</v>
+      </c>
+      <c r="F453" t="n">
+        <v>358726.884</v>
+      </c>
+      <c r="G453" t="n">
+        <v>-23.5300354</v>
+      </c>
+      <c r="H453" t="n">
+        <v>-46.3838931</v>
+      </c>
+      <c r="I453" t="n">
+        <v>782.299</v>
+      </c>
+      <c r="J453" t="n">
+        <v>779.199</v>
+      </c>
+      <c r="K453" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L453" t="inlineStr">
+        <is>
+          <t>Interligação adicionada em 17/07/2026 entre o PV-17 do CTS João Canzi e o PV-21 da RCE Elias Sleiman.</t>
         </is>
       </c>
     </row>
@@ -21714,7 +21762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R464"/>
+  <dimension ref="A1:R465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -54489,6 +54537,80 @@
       </c>
       <c r="R464" t="n">
         <v>-46.3851111</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>rce_elias_sleiman</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>ELIAS-000</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>PV-17 - PV-21</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>PV-17</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>PV-21</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G465" t="n">
+        <v>200</v>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I465" t="n">
+        <v>23.32</v>
+      </c>
+      <c r="J465" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K465" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="L465" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M465" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N465" t="inlineStr">
+        <is>
+          <t>Interligação adicionada em 17/07/2026 entre o PV-17 do CTS João Canzi e o PV-21 da RCE Elias Sleiman.</t>
+        </is>
+      </c>
+      <c r="O465" t="n">
+        <v>-23.5300354</v>
+      </c>
+      <c r="P465" t="n">
+        <v>-46.3838931</v>
+      </c>
+      <c r="Q465" t="n">
+        <v>-23.5301384</v>
+      </c>
+      <c r="R465" t="n">
+        <v>-46.3836941</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -1224,7 +1224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L453"/>
+  <dimension ref="A1:L456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -19442,29 +19442,29 @@
         </is>
       </c>
       <c r="E403" t="n">
-        <v>7396941.756</v>
+        <v>7396927.156</v>
       </c>
       <c r="F403" t="n">
-        <v>358324.032</v>
+        <v>358327.601</v>
       </c>
       <c r="G403" t="n">
-        <v>-23.5316304</v>
+        <v>-23.5317625</v>
       </c>
       <c r="H403" t="n">
-        <v>-46.3878556</v>
+        <v>-46.3878221</v>
       </c>
       <c r="I403" t="n">
-        <v>767.318</v>
+        <v>767.145</v>
       </c>
       <c r="J403" t="n">
-        <v>763.468</v>
+        <v>763.135</v>
       </c>
       <c r="K403" t="n">
-        <v>3.85</v>
+        <v>4.01</v>
       </c>
       <c r="L403" t="inlineStr">
         <is>
-          <t>Movido para RCE Elvira de Araujo conforme correcao de obra em 09.JUN.2026.</t>
+          <t>Atualizado via prints enviados em 17/07/2026: continuidade da RCE Elvira de Araújo do PV-02 ao PV-05.</t>
         </is>
       </c>
     </row>
@@ -21748,6 +21748,150 @@
       <c r="L453" t="inlineStr">
         <is>
           <t>Interligação adicionada em 17/07/2026 entre o PV-17 do CTS João Canzi e o PV-21 da RCE Elias Sleiman.</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>rce_elvira_de_araujo</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>ELVIRA-PV-03</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>PV-03</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>7396959.815</v>
+      </c>
+      <c r="F454" t="n">
+        <v>358322.872</v>
+      </c>
+      <c r="G454" t="n">
+        <v>-23.5314672</v>
+      </c>
+      <c r="H454" t="n">
+        <v>-46.3878653</v>
+      </c>
+      <c r="I454" t="n">
+        <v>769.252</v>
+      </c>
+      <c r="J454" t="n">
+        <v>766.7670000000001</v>
+      </c>
+      <c r="K454" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L454" t="inlineStr">
+        <is>
+          <t>Atualizado via prints enviados em 17/07/2026: continuidade da RCE Elvira de Araújo do PV-02 ao PV-05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>rce_elvira_de_araujo</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>ELVIRA-PV-04</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>PV-04</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>7397004.412</v>
+      </c>
+      <c r="F455" t="n">
+        <v>358316.86</v>
+      </c>
+      <c r="G455" t="n">
+        <v>-23.5310639</v>
+      </c>
+      <c r="H455" t="n">
+        <v>-46.3879199</v>
+      </c>
+      <c r="I455" t="n">
+        <v>776.184</v>
+      </c>
+      <c r="J455" t="n">
+        <v>774.138</v>
+      </c>
+      <c r="K455" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L455" t="inlineStr">
+        <is>
+          <t>Atualizado via prints enviados em 17/07/2026: continuidade da RCE Elvira de Araújo do PV-02 ao PV-05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>rce_elvira_de_araujo</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>ELVIRA-PV-05</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>PV-05</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>7397057.922</v>
+      </c>
+      <c r="F456" t="n">
+        <v>358309.601</v>
+      </c>
+      <c r="G456" t="n">
+        <v>-23.5305801</v>
+      </c>
+      <c r="H456" t="n">
+        <v>-46.387986</v>
+      </c>
+      <c r="I456" t="n">
+        <v>782.579</v>
+      </c>
+      <c r="J456" t="n">
+        <v>780.861</v>
+      </c>
+      <c r="K456" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L456" t="inlineStr">
+        <is>
+          <t>Atualizado via prints enviados em 17/07/2026: continuidade da RCE Elvira de Araújo do PV-02 ao PV-05.</t>
         </is>
       </c>
     </row>
@@ -21762,7 +21906,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R465"/>
+  <dimension ref="A1:R468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -50232,7 +50376,7 @@
         <v>4.15</v>
       </c>
       <c r="K405" t="n">
-        <v>3.85</v>
+        <v>4.01</v>
       </c>
       <c r="L405" t="n">
         <v>4.15</v>
@@ -50254,10 +50398,10 @@
         <v>-46.3877736</v>
       </c>
       <c r="Q405" t="n">
-        <v>-23.5316304</v>
+        <v>-23.5317625</v>
       </c>
       <c r="R405" t="n">
-        <v>-46.3878556</v>
+        <v>-46.3878221</v>
       </c>
     </row>
     <row r="406" hidden="1">
@@ -54611,6 +54755,228 @@
       </c>
       <c r="R465" t="n">
         <v>-46.3836941</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>rce_elvira_de_araujo</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>ELVIRA-005</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>PV-02 - PV-03</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>PV-02</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>PV-03</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G466" t="n">
+        <v>200</v>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I466" t="n">
+        <v>33</v>
+      </c>
+      <c r="J466" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="K466" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="L466" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="M466" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N466" t="inlineStr">
+        <is>
+          <t>Atualizado via prints enviados em 17/07/2026: continuidade da RCE Elvira de Araújo do PV-02 ao PV-05.</t>
+        </is>
+      </c>
+      <c r="O466" t="n">
+        <v>-23.5317625</v>
+      </c>
+      <c r="P466" t="n">
+        <v>-46.3878221</v>
+      </c>
+      <c r="Q466" t="n">
+        <v>-23.5314672</v>
+      </c>
+      <c r="R466" t="n">
+        <v>-46.3878653</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>rce_elvira_de_araujo</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>ELVIRA-006</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>PV-03 - PV-04</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>PV-03</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>PV-04</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G467" t="n">
+        <v>200</v>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I467" t="n">
+        <v>45</v>
+      </c>
+      <c r="J467" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="K467" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L467" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="M467" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N467" t="inlineStr">
+        <is>
+          <t>Atualizado via prints enviados em 17/07/2026: continuidade da RCE Elvira de Araújo do PV-02 ao PV-05.</t>
+        </is>
+      </c>
+      <c r="O467" t="n">
+        <v>-23.5314672</v>
+      </c>
+      <c r="P467" t="n">
+        <v>-46.3878653</v>
+      </c>
+      <c r="Q467" t="n">
+        <v>-23.5310639</v>
+      </c>
+      <c r="R467" t="n">
+        <v>-46.3879199</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>rce_elvira_de_araujo</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>ELVIRA-007</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>PV-04 - PV-05</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>PV-04</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>PV-05</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G468" t="n">
+        <v>200</v>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I468" t="n">
+        <v>54</v>
+      </c>
+      <c r="J468" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="K468" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="L468" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M468" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N468" t="inlineStr">
+        <is>
+          <t>Atualizado via prints enviados em 17/07/2026: continuidade da RCE Elvira de Araújo do PV-02 ao PV-05.</t>
+        </is>
+      </c>
+      <c r="O468" t="n">
+        <v>-23.5310639</v>
+      </c>
+      <c r="P468" t="n">
+        <v>-46.3879199</v>
+      </c>
+      <c r="Q468" t="n">
+        <v>-23.5305801</v>
+      </c>
+      <c r="R468" t="n">
+        <v>-46.387986</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -1224,7 +1224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L456"/>
+  <dimension ref="A1:L457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -21892,6 +21892,48 @@
       <c r="L456" t="inlineStr">
         <is>
           <t>Atualizado via prints enviados em 17/07/2026: continuidade da RCE Elvira de Araújo do PV-02 ao PV-05.</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>cts_lourdes_complementar</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>PV</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>LOUR-PT-001</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>PT-001</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>7397075.247974937</v>
+      </c>
+      <c r="F457" t="n">
+        <v>357881.2343928794</v>
+      </c>
+      <c r="G457" t="n">
+        <v>-23.5303862</v>
+      </c>
+      <c r="H457" t="n">
+        <v>-46.3921796</v>
+      </c>
+      <c r="K457" t="n">
+        <v>0</v>
+      </c>
+      <c r="L457" t="inlineStr">
+        <is>
+          <t>Interligação VCA adicionada em 17/07/2026 entre PV-05 do CTS Lourdes Complementar e PT-001 do CTS Jardim Lourdes.</t>
         </is>
       </c>
     </row>
@@ -21906,7 +21948,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R468"/>
+  <dimension ref="A1:R469"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -54977,6 +55019,80 @@
       </c>
       <c r="R468" t="n">
         <v>-46.387986</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>cts_lourdes_complementar</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>LOUR-005</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>PV-05 - PT-001</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>PV-05</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>PT-001</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G469" t="n">
+        <v>300</v>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>Vala a Ceu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I469" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="J469" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K469" t="n">
+        <v>0</v>
+      </c>
+      <c r="L469" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M469" t="inlineStr">
+        <is>
+          <t>em andamento</t>
+        </is>
+      </c>
+      <c r="N469" t="inlineStr">
+        <is>
+          <t>Interligação VCA adicionada em 17/07/2026 entre PV-05 do CTS Lourdes Complementar e PT-001 do CTS Jardim Lourdes.</t>
+        </is>
+      </c>
+      <c r="O469" t="n">
+        <v>-23.530465</v>
+      </c>
+      <c r="P469" t="n">
+        <v>-46.3923061</v>
+      </c>
+      <c r="Q469" t="n">
+        <v>-23.5303862</v>
+      </c>
+      <c r="R469" t="n">
+        <v>-46.3921796</v>
       </c>
     </row>
   </sheetData>

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="31.109375" customWidth="1" min="1" max="1"/>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Base real substituída pelo shape completo enviado em 17/07/2026: 19 PVs, 59 PIs e 75 trechos em VCA.</t>
+          <t>Base real substituída pelo shape completo enviado em 17/07/2026, com trecho PV-4.1 ao PV-06 separado para RCE São João em 20/07/2026: 16 PVs, 59 PIs e 73 trechos em VCA.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1235,6 +1235,33 @@
         </is>
       </c>
       <c r="E28" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>rce_sao_joao</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>RCE Rua São João</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>RCE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Trecho corrigido em 20/07/2026: PV-4.1 ao PV-06, 3 PVs, 2 trechos em VCA, 82,99 m de PVC DN200.</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -22180,7 +22207,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>rce_sao_joao</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -22190,7 +22217,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>SL-PV-05</t>
+          <t>SJ-PV-05</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -22221,14 +22248,14 @@
       </c>
       <c r="L460" t="inlineStr">
         <is>
-          <t>Base substituída pelo shape completo enviado em 17/07/2026: Cadastro PV, Cadastro PI e Cadastro Rede da RCE Comunidade São Lucas.</t>
+          <t>Trecho reclassificado para RCE São João em 20/07/2026, conforme conferência em mapa.</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>rce_sao_joao</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -22238,7 +22265,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>SL-PV-06</t>
+          <t>SJ-PV-06</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -22269,7 +22296,7 @@
       </c>
       <c r="L461" t="inlineStr">
         <is>
-          <t>Base substituída pelo shape completo enviado em 17/07/2026: Cadastro PV, Cadastro PI e Cadastro Rede da RCE Comunidade São Lucas.</t>
+          <t>Trecho reclassificado para RCE São João em 20/07/2026, conforme conferência em mapa.</t>
         </is>
       </c>
     </row>
@@ -22996,7 +23023,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>rce_sao_joao</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -23006,7 +23033,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>SL-PV-4.1</t>
+          <t>SJ-PV-4.1</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -23037,7 +23064,7 @@
       </c>
       <c r="L477" t="inlineStr">
         <is>
-          <t>Base substituída pelo shape completo enviado em 17/07/2026: Cadastro PV, Cadastro PI e Cadastro Rede da RCE Comunidade São Lucas.</t>
+          <t>Trecho reclassificado para RCE São João em 20/07/2026, conforme conferência em mapa.</t>
         </is>
       </c>
     </row>
@@ -55587,12 +55614,12 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>rce_sao_joao</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>SL-026</t>
+          <t>SJ-002</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -55642,7 +55669,7 @@
       </c>
       <c r="N443" t="inlineStr">
         <is>
-          <t>Base substituída pelo shape completo enviado em 17/07/2026: Cadastro PV, Cadastro PI e Cadastro Rede da RCE Comunidade São Lucas.</t>
+          <t>Trecho reclassificado para RCE São João em 20/07/2026, conforme conferência em mapa.</t>
         </is>
       </c>
       <c r="O443" t="n">
@@ -58769,12 +58796,12 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>rce_comunidade_sao_lucas</t>
+          <t>rce_sao_joao</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>SL-069</t>
+          <t>SJ-001</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -58824,7 +58851,7 @@
       </c>
       <c r="N486" t="inlineStr">
         <is>
-          <t>Base substituída pelo shape completo enviado em 17/07/2026: Cadastro PV, Cadastro PI e Cadastro Rede da RCE Comunidade São Lucas.</t>
+          <t>Trecho reclassificado para RCE São João em 20/07/2026, conforme conferência em mapa.</t>
         </is>
       </c>
       <c r="O486" t="n">

--- a/docs/planilha_base_mapa.xlsx
+++ b/docs/planilha_base_mapa.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="31.109375" customWidth="1" min="1" max="1"/>
@@ -1262,6 +1262,33 @@
         </is>
       </c>
       <c r="E29" t="inlineStr">
+        <is>
+          <t>SIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>interl_rua_ayrton_senna</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>INTERL. RUA AYRTON SENNA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>INTERL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>As built INT Ayrton Senna enviado em 20/07/2026: PIE-01 ao PI-02, 3 pontos, 2 trechos em VCA, PVC DN200. Extensao total no perfil: 62,05 m.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
         <is>
           <t>SIM</t>
         </is>
@@ -1278,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L504"/>
+  <dimension ref="A1:L507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -24361,6 +24388,150 @@
       <c r="L504" t="inlineStr">
         <is>
           <t>Base substituída/adicionada pelo shape enviado em 20/07/2026: RCE Elias Sleiman.</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>interl_rua_ayrton_senna</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>AS-PIE-01</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>PIE-01</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>7397669.226</v>
+      </c>
+      <c r="F505" t="n">
+        <v>358321.476</v>
+      </c>
+      <c r="G505" t="n">
+        <v>-23.525061</v>
+      </c>
+      <c r="H505" t="n">
+        <v>-46.3878118</v>
+      </c>
+      <c r="I505" t="n">
+        <v>798.5599999999999</v>
+      </c>
+      <c r="J505" t="n">
+        <v>796.98</v>
+      </c>
+      <c r="K505" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="L505" t="inlineStr">
+        <is>
+          <t>As built INT Ayrton Senna enviado em 20/07/2026: PIE-01 ao PI-02, 3 pontos, 2 trechos em VCA, PVC DN200.</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>interl_rua_ayrton_senna</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>AS-PI-01</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>PI-01</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>7397708.236</v>
+      </c>
+      <c r="F506" t="n">
+        <v>358282.877</v>
+      </c>
+      <c r="G506" t="n">
+        <v>-23.5247053</v>
+      </c>
+      <c r="H506" t="n">
+        <v>-46.3881861</v>
+      </c>
+      <c r="I506" t="n">
+        <v>800.347</v>
+      </c>
+      <c r="J506" t="n">
+        <v>798.687</v>
+      </c>
+      <c r="K506" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L506" t="inlineStr">
+        <is>
+          <t>As built INT Ayrton Senna enviado em 20/07/2026: PIE-01 ao PI-02, 3 pontos, 2 trechos em VCA, PVC DN200.</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>interl_rua_ayrton_senna</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>PI</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>AS-PI-02</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>PI-02</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>7397706.339</v>
+      </c>
+      <c r="F507" t="n">
+        <v>358275.959</v>
+      </c>
+      <c r="G507" t="n">
+        <v>-23.5247218</v>
+      </c>
+      <c r="H507" t="n">
+        <v>-46.388254</v>
+      </c>
+      <c r="I507" t="n">
+        <v>799.735</v>
+      </c>
+      <c r="J507" t="n">
+        <v>798.765</v>
+      </c>
+      <c r="K507" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L507" t="inlineStr">
+        <is>
+          <t>As built INT Ayrton Senna enviado em 20/07/2026: PIE-01 ao PI-02, 3 pontos, 2 trechos em VCA, PVC DN200.</t>
         </is>
       </c>
     </row>
@@ -24375,7 +24546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R514"/>
+  <dimension ref="A1:R516"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="30.21875" customWidth="1" min="1" max="1"/>
@@ -60937,6 +61108,154 @@
       </c>
       <c r="R514" t="n">
         <v>-46.3838928</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>interl_rua_ayrton_senna</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>AS-001</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>PIE-01 - PI-01</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>PIE-01</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>PI-01</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G515" t="n">
+        <v>200</v>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>Vala a Céu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I515" t="n">
+        <v>54.88</v>
+      </c>
+      <c r="J515" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="K515" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="L515" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M515" t="inlineStr">
+        <is>
+          <t>concluída</t>
+        </is>
+      </c>
+      <c r="N515" t="inlineStr">
+        <is>
+          <t>As built INT Ayrton Senna enviado em 20/07/2026: PIE-01 ao PI-02, 3 pontos, 2 trechos em VCA, PVC DN200.</t>
+        </is>
+      </c>
+      <c r="O515" t="n">
+        <v>-23.525061</v>
+      </c>
+      <c r="P515" t="n">
+        <v>-46.3878118</v>
+      </c>
+      <c r="Q515" t="n">
+        <v>-23.5247053</v>
+      </c>
+      <c r="R515" t="n">
+        <v>-46.3881861</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>interl_rua_ayrton_senna</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>AS-002</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>PI-01 - PI-02</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>PI-01</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>PI-02</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>PVC</t>
+        </is>
+      </c>
+      <c r="G516" t="n">
+        <v>200</v>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>Vala a Céu Aberto - VCA</t>
+        </is>
+      </c>
+      <c r="I516" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="J516" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="K516" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="L516" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="M516" t="inlineStr">
+        <is>
+          <t>concluída</t>
+        </is>
+      </c>
+      <c r="N516" t="inlineStr">
+        <is>
+          <t>As built INT Ayrton Senna enviado em 20/07/2026: PIE-01 ao PI-02, 3 pontos, 2 trechos em VCA, PVC DN200.</t>
+        </is>
+      </c>
+      <c r="O516" t="n">
+        <v>-23.5247053</v>
+      </c>
+      <c r="P516" t="n">
+        <v>-46.3881861</v>
+      </c>
+      <c r="Q516" t="n">
+        <v>-23.5247218</v>
+      </c>
+      <c r="R516" t="n">
+        <v>-46.388254</v>
       </c>
     </row>
   </sheetData>
